--- a/evaluaciones-frontend/public/assets/formato_banco_preguntas_asig_EF_1P.xlsx
+++ b/evaluaciones-frontend/public/assets/formato_banco_preguntas_asig_EF_1P.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -91,8 +91,13 @@
       <color rgb="FF4527A0"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="78">
+  <fills count="80">
     <fill>
       <patternFill/>
     </fill>
@@ -481,8 +486,20 @@
         <bgColor rgb="FFF3F0FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F4F6"/>
+        <bgColor rgb="FFF3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border/>
     <border>
       <left style="thin"/>
@@ -598,11 +615,44 @@
         <color rgb="FFB8A8F5"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFB8A8F5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8A8F5"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFB8A8F5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8A8F5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8A8F5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="371">
+  <cellXfs count="374">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1569,6 +1619,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="77" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="78" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="78" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="79" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2342,7 +2401,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
-    <col hidden="1" min="14" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="40"/>
     <col width="24" customWidth="1" min="41" max="41"/>
     <col width="14" customWidth="1" min="42" max="42"/>
     <col width="14" customWidth="1" min="43" max="43"/>
@@ -3276,7 +3335,7 @@
         </is>
       </c>
       <c r="AP6" s="364">
-        <f>IF(AND(AP2=15,AP3=30,AP4=15,AP5=60),"COMPLETA","REVISAR")</f>
+        <f>IF(AND(AP2&gt;=15,AP3&gt;=30,AP4&gt;=15,AP5&gt;=60),"COMPLETA","REVISAR")</f>
         <v/>
       </c>
       <c r="AQ6" s="365" t="str"/>
@@ -10789,399 +10848,5119 @@
         <v/>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="371" t="n"/>
+      <c r="B62" s="371" t="n"/>
+      <c r="C62" s="371" t="n"/>
+      <c r="D62" s="371">
+        <f>IF($A62="Verdadero o Falso Simple","Verdadero",IF($A62="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A62="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E62" s="371">
+        <f>IF($A62="Verdadero o Falso Simple","Falso",IF($A62="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A62="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F62" s="371">
+        <f>IF($A62="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A62="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G62" s="371">
+        <f>IF($A62="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A62="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H62" s="371">
+        <f>IF($A62="Verdadero o Falso Simple","",IF($A62="Respuesta A/B/Ambas/Ninguna","",IF($A62="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I62" s="371" t="n"/>
+      <c r="J62" s="372" t="n"/>
+      <c r="K62" s="372">
+        <f>IF(TRIM($A62)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L62" s="371">
+        <f>IF(TRIM($A62)="","",IF(OR($A62="Selección de la mejor respuesta",$A62="SELECCION_MEJOR_RESPUESTA",$A62="Subítem de caso o problema",$A62="SUBITEM_CASO"),IF(TRIM($C62)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D62:$H62&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I62)&lt;&gt;"",OR(LEFT(TRIM($I62),1)="A",LEFT(TRIM($I62),1)="B",LEFT(TRIM($I62),1)="C",LEFT(TRIM($I62),1)="D",LEFT(TRIM($I62),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A62)="","",IF(COUNTIF($Q62:$AJ62,"?*")=0,"OK","Falta revisar: "&amp;$Q62&amp;$R62&amp;$S62&amp;$T62&amp;$U62&amp;$V62&amp;$W62&amp;$X62&amp;$Y62&amp;$Z62&amp;$AA62&amp;$AB62&amp;$AC62&amp;$AD62&amp;$AE62&amp;$AF62&amp;$AG62&amp;$AH62&amp;$AI62&amp;$AJ62))))</f>
+        <v/>
+      </c>
+      <c r="M62" s="373" t="n"/>
+      <c r="Q62">
+        <f>IF(TRIM($C62)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R62">
+        <f>IF(TRIM($K62)="",IF(COUNTIF($Q62:$Q62,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S62">
         <f>IF(AND(TRIM($K62)&lt;&gt;"",TRIM($K62)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q62:$R62,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T62">
+        <f>IF(AND(OR($A62="Ítems agrupados por caso clínico o problema",$A62="Subítem de caso o problema",$A62="Emparejamiento Ampliado",$A62="Opción de Emparejamiento Ampliado"),TRIM($B62)=""),IF(COUNTIF($Q62:$S62,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U62">
+        <f>IF(AND(OR($A62="Verdadero o Falso Simple",$A62="Respuesta A/B/Ambas/Ninguna",$A62="Verdadero o Falso Complejas",$A62="Selección de la mejor respuesta",$A62="Subítem de caso o problema",$A62="Opción de Emparejamiento Ampliado"),TRIM($I62)=""),IF(COUNTIF($Q62:$T62,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V62">
+        <f>IF(AND(OR($A62="Verdadero o Falso Simple",$A62="Respuesta A/B/Ambas/Ninguna",$A62="Verdadero o Falso Complejas",$A62="Selección de la mejor respuesta",$A62="Subítem de caso o problema",$A62="Opción de Emparejamiento Ampliado"),TRIM($J62)=""),IF(COUNTIF($Q62:$U62,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W62">
+        <f>IF(AND(OR($A62="Ítems agrupados por caso clínico o problema",$A62="Emparejamiento Ampliado"),TRIM($I62)&lt;&gt;""),IF(COUNTIF($Q62:$V62,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X62">
+        <f>IF(AND(OR($A62="Ítems agrupados por caso clínico o problema",$A62="Emparejamiento Ampliado"),TRIM($J62)&lt;&gt;""),IF(COUNTIF($Q62:$W62,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y62">
+        <f>IF(AND($A62="Verdadero o Falso Simple",OR(COUNTIF($D62:$E62,"?*")&lt;2,COUNTIF($F62:$H62,"?*")&gt;0)),IF(COUNTIF($Q62:$X62,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z62">
+        <f>IF(AND($A62="Verdadero o Falso Simple",TRIM($I62)&lt;&gt;"",NOT(OR(LEFT(TRIM($I62),1)="A",LEFT(TRIM($I62),1)="B"))),IF(COUNTIF($Q62:$Y62,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA62">
+        <f>IF(AND($A62="Respuesta A/B/Ambas/Ninguna",COUNTIF($D62:$G62,"?*")&lt;4),IF(COUNTIF($Q62:$Z62,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB62">
+        <f>IF(AND($A62="Respuesta A/B/Ambas/Ninguna",COUNTIF($H62:$H62,"?*")&gt;0),IF(COUNTIF($Q62:$AA62,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC62">
+        <f>IF(AND($A62="Respuesta A/B/Ambas/Ninguna",TRIM($I62)&lt;&gt;"",NOT(OR(LEFT(TRIM($I62),1)="A",LEFT(TRIM($I62),1)="B",LEFT(TRIM($I62),1)="C",LEFT(TRIM($I62),1)="D"))),IF(COUNTIF($Q62:$AB62,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD62">
+        <f>IF(AND($A62="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D62,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E62,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F62,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G62,"4.","")))=0)),IF(COUNTIF($Q62:$AC62,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE62">
+        <f>IF(AND($A62="Verdadero o Falso Complejas",COUNTIF($H62:$H62,"?*")&gt;0),IF(COUNTIF($Q62:$AD62,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF62">
+        <f>IF(AND($A62="Verdadero o Falso Complejas",TRIM($I62)&lt;&gt;"",NOT(OR(LEFT(TRIM($I62),1)="A",LEFT(TRIM($I62),1)="B",LEFT(TRIM($I62),1)="C",LEFT(TRIM($I62),1)="D",LEFT(TRIM($I62),1)="E"))),IF(COUNTIF($Q62:$AE62,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG62">
+        <f>IF(AND(OR($A62="Selección de la mejor respuesta",$A62="Subítem de caso o problema"),COUNTA($D62:$H62)&lt;5),IF(COUNTIF($Q62:$AF62,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH62">
+        <f>IF(AND(OR($A62="Selección de la mejor respuesta",$A62="Subítem de caso o problema"),TRIM($I62)&lt;&gt;"",NOT(OR(LEFT(TRIM($I62),1)="A",LEFT(TRIM($I62),1)="B",LEFT(TRIM($I62),1)="C",LEFT(TRIM($I62),1)="D",LEFT(TRIM($I62),1)="E"))),IF(COUNTIF($Q62:$AG62,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI62">
+        <f>IF(AND(OR($A62="Ítems agrupados por caso clínico o problema",$A62="Opción de Emparejamiento Ampliado"),COUNTIF($D62:$H62,"?*")&gt;0),IF(COUNTIF($Q62:$AH62,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ62">
+        <f>IF(AND($A62="Emparejamiento Ampliado",COUNTIF($D62:$H62,"?*")&lt;2),IF(COUNTIF($Q62:$AI62,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK62">
+        <f>IF(AND($A62="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I62),1)="A",LEFT(TRIM($I62),1)="B",LEFT(TRIM($I62),1)="C",LEFT(TRIM($I62),1)="D",LEFT(TRIM($I62),1)="E"))),IF(COUNTIF($Q62:$AJ62,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL62">
+        <f>IF(TRIM($K62)="",IF(COUNTIF($M62:$M62,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM62">
         <f>IF(AND(TRIM($K62)&lt;&gt;"",TRIM($K62)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M62:$N62,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="24" customHeight="1">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="371" t="n"/>
+      <c r="B63" s="371" t="n"/>
+      <c r="C63" s="371" t="n"/>
+      <c r="D63" s="371">
+        <f>IF($A63="Verdadero o Falso Simple","Verdadero",IF($A63="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A63="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E63" s="371">
+        <f>IF($A63="Verdadero o Falso Simple","Falso",IF($A63="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A63="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F63" s="371">
+        <f>IF($A63="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A63="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G63" s="371">
+        <f>IF($A63="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A63="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H63" s="371">
+        <f>IF($A63="Verdadero o Falso Simple","",IF($A63="Respuesta A/B/Ambas/Ninguna","",IF($A63="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I63" s="371" t="n"/>
+      <c r="J63" s="372" t="n"/>
+      <c r="K63" s="372">
+        <f>IF(TRIM($A63)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L63" s="371">
+        <f>IF(TRIM($A63)="","",IF(OR($A63="Selección de la mejor respuesta",$A63="SELECCION_MEJOR_RESPUESTA",$A63="Subítem de caso o problema",$A63="SUBITEM_CASO"),IF(TRIM($C63)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D63:$H63&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I63)&lt;&gt;"",OR(LEFT(TRIM($I63),1)="A",LEFT(TRIM($I63),1)="B",LEFT(TRIM($I63),1)="C",LEFT(TRIM($I63),1)="D",LEFT(TRIM($I63),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A63)="","",IF(COUNTIF($Q63:$AJ63,"?*")=0,"OK","Falta revisar: "&amp;$Q63&amp;$R63&amp;$S63&amp;$T63&amp;$U63&amp;$V63&amp;$W63&amp;$X63&amp;$Y63&amp;$Z63&amp;$AA63&amp;$AB63&amp;$AC63&amp;$AD63&amp;$AE63&amp;$AF63&amp;$AG63&amp;$AH63&amp;$AI63&amp;$AJ63))))</f>
+        <v/>
+      </c>
+      <c r="M63" s="373" t="n"/>
+      <c r="Q63">
+        <f>IF(TRIM($C63)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R63">
+        <f>IF(TRIM($K63)="",IF(COUNTIF($Q63:$Q63,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S63">
         <f>IF(AND(TRIM($K63)&lt;&gt;"",TRIM($K63)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q63:$R63,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T63">
+        <f>IF(AND(OR($A63="Ítems agrupados por caso clínico o problema",$A63="Subítem de caso o problema",$A63="Emparejamiento Ampliado",$A63="Opción de Emparejamiento Ampliado"),TRIM($B63)=""),IF(COUNTIF($Q63:$S63,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U63">
+        <f>IF(AND(OR($A63="Verdadero o Falso Simple",$A63="Respuesta A/B/Ambas/Ninguna",$A63="Verdadero o Falso Complejas",$A63="Selección de la mejor respuesta",$A63="Subítem de caso o problema",$A63="Opción de Emparejamiento Ampliado"),TRIM($I63)=""),IF(COUNTIF($Q63:$T63,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V63">
+        <f>IF(AND(OR($A63="Verdadero o Falso Simple",$A63="Respuesta A/B/Ambas/Ninguna",$A63="Verdadero o Falso Complejas",$A63="Selección de la mejor respuesta",$A63="Subítem de caso o problema",$A63="Opción de Emparejamiento Ampliado"),TRIM($J63)=""),IF(COUNTIF($Q63:$U63,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W63">
+        <f>IF(AND(OR($A63="Ítems agrupados por caso clínico o problema",$A63="Emparejamiento Ampliado"),TRIM($I63)&lt;&gt;""),IF(COUNTIF($Q63:$V63,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X63">
+        <f>IF(AND(OR($A63="Ítems agrupados por caso clínico o problema",$A63="Emparejamiento Ampliado"),TRIM($J63)&lt;&gt;""),IF(COUNTIF($Q63:$W63,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y63">
+        <f>IF(AND($A63="Verdadero o Falso Simple",OR(COUNTIF($D63:$E63,"?*")&lt;2,COUNTIF($F63:$H63,"?*")&gt;0)),IF(COUNTIF($Q63:$X63,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z63">
+        <f>IF(AND($A63="Verdadero o Falso Simple",TRIM($I63)&lt;&gt;"",NOT(OR(LEFT(TRIM($I63),1)="A",LEFT(TRIM($I63),1)="B"))),IF(COUNTIF($Q63:$Y63,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA63">
+        <f>IF(AND($A63="Respuesta A/B/Ambas/Ninguna",COUNTIF($D63:$G63,"?*")&lt;4),IF(COUNTIF($Q63:$Z63,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB63">
+        <f>IF(AND($A63="Respuesta A/B/Ambas/Ninguna",COUNTIF($H63:$H63,"?*")&gt;0),IF(COUNTIF($Q63:$AA63,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC63">
+        <f>IF(AND($A63="Respuesta A/B/Ambas/Ninguna",TRIM($I63)&lt;&gt;"",NOT(OR(LEFT(TRIM($I63),1)="A",LEFT(TRIM($I63),1)="B",LEFT(TRIM($I63),1)="C",LEFT(TRIM($I63),1)="D"))),IF(COUNTIF($Q63:$AB63,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD63">
+        <f>IF(AND($A63="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D63,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E63,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F63,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G63,"4.","")))=0)),IF(COUNTIF($Q63:$AC63,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE63">
+        <f>IF(AND($A63="Verdadero o Falso Complejas",COUNTIF($H63:$H63,"?*")&gt;0),IF(COUNTIF($Q63:$AD63,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF63">
+        <f>IF(AND($A63="Verdadero o Falso Complejas",TRIM($I63)&lt;&gt;"",NOT(OR(LEFT(TRIM($I63),1)="A",LEFT(TRIM($I63),1)="B",LEFT(TRIM($I63),1)="C",LEFT(TRIM($I63),1)="D",LEFT(TRIM($I63),1)="E"))),IF(COUNTIF($Q63:$AE63,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG63">
+        <f>IF(AND(OR($A63="Selección de la mejor respuesta",$A63="Subítem de caso o problema"),COUNTA($D63:$H63)&lt;5),IF(COUNTIF($Q63:$AF63,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH63">
+        <f>IF(AND(OR($A63="Selección de la mejor respuesta",$A63="Subítem de caso o problema"),TRIM($I63)&lt;&gt;"",NOT(OR(LEFT(TRIM($I63),1)="A",LEFT(TRIM($I63),1)="B",LEFT(TRIM($I63),1)="C",LEFT(TRIM($I63),1)="D",LEFT(TRIM($I63),1)="E"))),IF(COUNTIF($Q63:$AG63,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI63">
+        <f>IF(AND(OR($A63="Ítems agrupados por caso clínico o problema",$A63="Opción de Emparejamiento Ampliado"),COUNTIF($D63:$H63,"?*")&gt;0),IF(COUNTIF($Q63:$AH63,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ63">
+        <f>IF(AND($A63="Emparejamiento Ampliado",COUNTIF($D63:$H63,"?*")&lt;2),IF(COUNTIF($Q63:$AI63,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK63">
+        <f>IF(AND($A63="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I63),1)="A",LEFT(TRIM($I63),1)="B",LEFT(TRIM($I63),1)="C",LEFT(TRIM($I63),1)="D",LEFT(TRIM($I63),1)="E"))),IF(COUNTIF($Q63:$AJ63,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL63">
+        <f>IF(TRIM($K63)="",IF(COUNTIF($M63:$M63,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM63">
         <f>IF(AND(TRIM($K63)&lt;&gt;"",TRIM($K63)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M63:$N63,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="24" customHeight="1">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="371" t="n"/>
+      <c r="B64" s="371" t="n"/>
+      <c r="C64" s="371" t="n"/>
+      <c r="D64" s="371">
+        <f>IF($A64="Verdadero o Falso Simple","Verdadero",IF($A64="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A64="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E64" s="371">
+        <f>IF($A64="Verdadero o Falso Simple","Falso",IF($A64="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A64="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F64" s="371">
+        <f>IF($A64="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A64="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G64" s="371">
+        <f>IF($A64="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A64="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H64" s="371">
+        <f>IF($A64="Verdadero o Falso Simple","",IF($A64="Respuesta A/B/Ambas/Ninguna","",IF($A64="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I64" s="371" t="n"/>
+      <c r="J64" s="372" t="n"/>
+      <c r="K64" s="372">
+        <f>IF(TRIM($A64)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L64" s="371">
+        <f>IF(TRIM($A64)="","",IF(OR($A64="Selección de la mejor respuesta",$A64="SELECCION_MEJOR_RESPUESTA",$A64="Subítem de caso o problema",$A64="SUBITEM_CASO"),IF(TRIM($C64)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D64:$H64&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I64)&lt;&gt;"",OR(LEFT(TRIM($I64),1)="A",LEFT(TRIM($I64),1)="B",LEFT(TRIM($I64),1)="C",LEFT(TRIM($I64),1)="D",LEFT(TRIM($I64),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A64)="","",IF(COUNTIF($Q64:$AJ64,"?*")=0,"OK","Falta revisar: "&amp;$Q64&amp;$R64&amp;$S64&amp;$T64&amp;$U64&amp;$V64&amp;$W64&amp;$X64&amp;$Y64&amp;$Z64&amp;$AA64&amp;$AB64&amp;$AC64&amp;$AD64&amp;$AE64&amp;$AF64&amp;$AG64&amp;$AH64&amp;$AI64&amp;$AJ64))))</f>
+        <v/>
+      </c>
+      <c r="M64" s="373" t="n"/>
+      <c r="Q64">
+        <f>IF(TRIM($C64)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R64">
+        <f>IF(TRIM($K64)="",IF(COUNTIF($Q64:$Q64,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S64">
         <f>IF(AND(TRIM($K64)&lt;&gt;"",TRIM($K64)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q64:$R64,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T64">
+        <f>IF(AND(OR($A64="Ítems agrupados por caso clínico o problema",$A64="Subítem de caso o problema",$A64="Emparejamiento Ampliado",$A64="Opción de Emparejamiento Ampliado"),TRIM($B64)=""),IF(COUNTIF($Q64:$S64,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U64">
+        <f>IF(AND(OR($A64="Verdadero o Falso Simple",$A64="Respuesta A/B/Ambas/Ninguna",$A64="Verdadero o Falso Complejas",$A64="Selección de la mejor respuesta",$A64="Subítem de caso o problema",$A64="Opción de Emparejamiento Ampliado"),TRIM($I64)=""),IF(COUNTIF($Q64:$T64,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V64">
+        <f>IF(AND(OR($A64="Verdadero o Falso Simple",$A64="Respuesta A/B/Ambas/Ninguna",$A64="Verdadero o Falso Complejas",$A64="Selección de la mejor respuesta",$A64="Subítem de caso o problema",$A64="Opción de Emparejamiento Ampliado"),TRIM($J64)=""),IF(COUNTIF($Q64:$U64,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W64">
+        <f>IF(AND(OR($A64="Ítems agrupados por caso clínico o problema",$A64="Emparejamiento Ampliado"),TRIM($I64)&lt;&gt;""),IF(COUNTIF($Q64:$V64,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X64">
+        <f>IF(AND(OR($A64="Ítems agrupados por caso clínico o problema",$A64="Emparejamiento Ampliado"),TRIM($J64)&lt;&gt;""),IF(COUNTIF($Q64:$W64,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y64">
+        <f>IF(AND($A64="Verdadero o Falso Simple",OR(COUNTIF($D64:$E64,"?*")&lt;2,COUNTIF($F64:$H64,"?*")&gt;0)),IF(COUNTIF($Q64:$X64,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z64">
+        <f>IF(AND($A64="Verdadero o Falso Simple",TRIM($I64)&lt;&gt;"",NOT(OR(LEFT(TRIM($I64),1)="A",LEFT(TRIM($I64),1)="B"))),IF(COUNTIF($Q64:$Y64,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA64">
+        <f>IF(AND($A64="Respuesta A/B/Ambas/Ninguna",COUNTIF($D64:$G64,"?*")&lt;4),IF(COUNTIF($Q64:$Z64,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB64">
+        <f>IF(AND($A64="Respuesta A/B/Ambas/Ninguna",COUNTIF($H64:$H64,"?*")&gt;0),IF(COUNTIF($Q64:$AA64,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC64">
+        <f>IF(AND($A64="Respuesta A/B/Ambas/Ninguna",TRIM($I64)&lt;&gt;"",NOT(OR(LEFT(TRIM($I64),1)="A",LEFT(TRIM($I64),1)="B",LEFT(TRIM($I64),1)="C",LEFT(TRIM($I64),1)="D"))),IF(COUNTIF($Q64:$AB64,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD64">
+        <f>IF(AND($A64="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D64,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E64,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F64,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G64,"4.","")))=0)),IF(COUNTIF($Q64:$AC64,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE64">
+        <f>IF(AND($A64="Verdadero o Falso Complejas",COUNTIF($H64:$H64,"?*")&gt;0),IF(COUNTIF($Q64:$AD64,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF64">
+        <f>IF(AND($A64="Verdadero o Falso Complejas",TRIM($I64)&lt;&gt;"",NOT(OR(LEFT(TRIM($I64),1)="A",LEFT(TRIM($I64),1)="B",LEFT(TRIM($I64),1)="C",LEFT(TRIM($I64),1)="D",LEFT(TRIM($I64),1)="E"))),IF(COUNTIF($Q64:$AE64,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG64">
+        <f>IF(AND(OR($A64="Selección de la mejor respuesta",$A64="Subítem de caso o problema"),COUNTA($D64:$H64)&lt;5),IF(COUNTIF($Q64:$AF64,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH64">
+        <f>IF(AND(OR($A64="Selección de la mejor respuesta",$A64="Subítem de caso o problema"),TRIM($I64)&lt;&gt;"",NOT(OR(LEFT(TRIM($I64),1)="A",LEFT(TRIM($I64),1)="B",LEFT(TRIM($I64),1)="C",LEFT(TRIM($I64),1)="D",LEFT(TRIM($I64),1)="E"))),IF(COUNTIF($Q64:$AG64,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI64">
+        <f>IF(AND(OR($A64="Ítems agrupados por caso clínico o problema",$A64="Opción de Emparejamiento Ampliado"),COUNTIF($D64:$H64,"?*")&gt;0),IF(COUNTIF($Q64:$AH64,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ64">
+        <f>IF(AND($A64="Emparejamiento Ampliado",COUNTIF($D64:$H64,"?*")&lt;2),IF(COUNTIF($Q64:$AI64,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK64">
+        <f>IF(AND($A64="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I64),1)="A",LEFT(TRIM($I64),1)="B",LEFT(TRIM($I64),1)="C",LEFT(TRIM($I64),1)="D",LEFT(TRIM($I64),1)="E"))),IF(COUNTIF($Q64:$AJ64,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL64">
+        <f>IF(TRIM($K64)="",IF(COUNTIF($M64:$M64,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM64">
         <f>IF(AND(TRIM($K64)&lt;&gt;"",TRIM($K64)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M64:$N64,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="65" ht="24" customHeight="1">
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="371" t="n"/>
+      <c r="B65" s="371" t="n"/>
+      <c r="C65" s="371" t="n"/>
+      <c r="D65" s="371">
+        <f>IF($A65="Verdadero o Falso Simple","Verdadero",IF($A65="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A65="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E65" s="371">
+        <f>IF($A65="Verdadero o Falso Simple","Falso",IF($A65="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A65="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F65" s="371">
+        <f>IF($A65="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A65="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G65" s="371">
+        <f>IF($A65="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A65="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H65" s="371">
+        <f>IF($A65="Verdadero o Falso Simple","",IF($A65="Respuesta A/B/Ambas/Ninguna","",IF($A65="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I65" s="371" t="n"/>
+      <c r="J65" s="372" t="n"/>
+      <c r="K65" s="372">
+        <f>IF(TRIM($A65)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L65" s="371">
+        <f>IF(TRIM($A65)="","",IF(OR($A65="Selección de la mejor respuesta",$A65="SELECCION_MEJOR_RESPUESTA",$A65="Subítem de caso o problema",$A65="SUBITEM_CASO"),IF(TRIM($C65)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D65:$H65&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I65)&lt;&gt;"",OR(LEFT(TRIM($I65),1)="A",LEFT(TRIM($I65),1)="B",LEFT(TRIM($I65),1)="C",LEFT(TRIM($I65),1)="D",LEFT(TRIM($I65),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A65)="","",IF(COUNTIF($Q65:$AJ65,"?*")=0,"OK","Falta revisar: "&amp;$Q65&amp;$R65&amp;$S65&amp;$T65&amp;$U65&amp;$V65&amp;$W65&amp;$X65&amp;$Y65&amp;$Z65&amp;$AA65&amp;$AB65&amp;$AC65&amp;$AD65&amp;$AE65&amp;$AF65&amp;$AG65&amp;$AH65&amp;$AI65&amp;$AJ65))))</f>
+        <v/>
+      </c>
+      <c r="M65" s="373" t="n"/>
+      <c r="Q65">
+        <f>IF(TRIM($C65)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R65">
+        <f>IF(TRIM($K65)="",IF(COUNTIF($Q65:$Q65,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S65">
         <f>IF(AND(TRIM($K65)&lt;&gt;"",TRIM($K65)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q65:$R65,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T65">
+        <f>IF(AND(OR($A65="Ítems agrupados por caso clínico o problema",$A65="Subítem de caso o problema",$A65="Emparejamiento Ampliado",$A65="Opción de Emparejamiento Ampliado"),TRIM($B65)=""),IF(COUNTIF($Q65:$S65,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U65">
+        <f>IF(AND(OR($A65="Verdadero o Falso Simple",$A65="Respuesta A/B/Ambas/Ninguna",$A65="Verdadero o Falso Complejas",$A65="Selección de la mejor respuesta",$A65="Subítem de caso o problema",$A65="Opción de Emparejamiento Ampliado"),TRIM($I65)=""),IF(COUNTIF($Q65:$T65,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V65">
+        <f>IF(AND(OR($A65="Verdadero o Falso Simple",$A65="Respuesta A/B/Ambas/Ninguna",$A65="Verdadero o Falso Complejas",$A65="Selección de la mejor respuesta",$A65="Subítem de caso o problema",$A65="Opción de Emparejamiento Ampliado"),TRIM($J65)=""),IF(COUNTIF($Q65:$U65,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W65">
+        <f>IF(AND(OR($A65="Ítems agrupados por caso clínico o problema",$A65="Emparejamiento Ampliado"),TRIM($I65)&lt;&gt;""),IF(COUNTIF($Q65:$V65,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X65">
+        <f>IF(AND(OR($A65="Ítems agrupados por caso clínico o problema",$A65="Emparejamiento Ampliado"),TRIM($J65)&lt;&gt;""),IF(COUNTIF($Q65:$W65,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y65">
+        <f>IF(AND($A65="Verdadero o Falso Simple",OR(COUNTIF($D65:$E65,"?*")&lt;2,COUNTIF($F65:$H65,"?*")&gt;0)),IF(COUNTIF($Q65:$X65,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z65">
+        <f>IF(AND($A65="Verdadero o Falso Simple",TRIM($I65)&lt;&gt;"",NOT(OR(LEFT(TRIM($I65),1)="A",LEFT(TRIM($I65),1)="B"))),IF(COUNTIF($Q65:$Y65,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA65">
+        <f>IF(AND($A65="Respuesta A/B/Ambas/Ninguna",COUNTIF($D65:$G65,"?*")&lt;4),IF(COUNTIF($Q65:$Z65,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB65">
+        <f>IF(AND($A65="Respuesta A/B/Ambas/Ninguna",COUNTIF($H65:$H65,"?*")&gt;0),IF(COUNTIF($Q65:$AA65,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC65">
+        <f>IF(AND($A65="Respuesta A/B/Ambas/Ninguna",TRIM($I65)&lt;&gt;"",NOT(OR(LEFT(TRIM($I65),1)="A",LEFT(TRIM($I65),1)="B",LEFT(TRIM($I65),1)="C",LEFT(TRIM($I65),1)="D"))),IF(COUNTIF($Q65:$AB65,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD65">
+        <f>IF(AND($A65="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D65,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E65,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F65,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G65,"4.","")))=0)),IF(COUNTIF($Q65:$AC65,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE65">
+        <f>IF(AND($A65="Verdadero o Falso Complejas",COUNTIF($H65:$H65,"?*")&gt;0),IF(COUNTIF($Q65:$AD65,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF65">
+        <f>IF(AND($A65="Verdadero o Falso Complejas",TRIM($I65)&lt;&gt;"",NOT(OR(LEFT(TRIM($I65),1)="A",LEFT(TRIM($I65),1)="B",LEFT(TRIM($I65),1)="C",LEFT(TRIM($I65),1)="D",LEFT(TRIM($I65),1)="E"))),IF(COUNTIF($Q65:$AE65,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG65">
+        <f>IF(AND(OR($A65="Selección de la mejor respuesta",$A65="Subítem de caso o problema"),COUNTA($D65:$H65)&lt;5),IF(COUNTIF($Q65:$AF65,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH65">
+        <f>IF(AND(OR($A65="Selección de la mejor respuesta",$A65="Subítem de caso o problema"),TRIM($I65)&lt;&gt;"",NOT(OR(LEFT(TRIM($I65),1)="A",LEFT(TRIM($I65),1)="B",LEFT(TRIM($I65),1)="C",LEFT(TRIM($I65),1)="D",LEFT(TRIM($I65),1)="E"))),IF(COUNTIF($Q65:$AG65,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI65">
+        <f>IF(AND(OR($A65="Ítems agrupados por caso clínico o problema",$A65="Opción de Emparejamiento Ampliado"),COUNTIF($D65:$H65,"?*")&gt;0),IF(COUNTIF($Q65:$AH65,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ65">
+        <f>IF(AND($A65="Emparejamiento Ampliado",COUNTIF($D65:$H65,"?*")&lt;2),IF(COUNTIF($Q65:$AI65,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK65">
+        <f>IF(AND($A65="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I65),1)="A",LEFT(TRIM($I65),1)="B",LEFT(TRIM($I65),1)="C",LEFT(TRIM($I65),1)="D",LEFT(TRIM($I65),1)="E"))),IF(COUNTIF($Q65:$AJ65,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL65">
+        <f>IF(TRIM($K65)="",IF(COUNTIF($M65:$M65,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM65">
         <f>IF(AND(TRIM($K65)&lt;&gt;"",TRIM($K65)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M65:$N65,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="371" t="n"/>
+      <c r="B66" s="371" t="n"/>
+      <c r="C66" s="371" t="n"/>
+      <c r="D66" s="371">
+        <f>IF($A66="Verdadero o Falso Simple","Verdadero",IF($A66="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A66="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E66" s="371">
+        <f>IF($A66="Verdadero o Falso Simple","Falso",IF($A66="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A66="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F66" s="371">
+        <f>IF($A66="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A66="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G66" s="371">
+        <f>IF($A66="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A66="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H66" s="371">
+        <f>IF($A66="Verdadero o Falso Simple","",IF($A66="Respuesta A/B/Ambas/Ninguna","",IF($A66="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I66" s="371" t="n"/>
+      <c r="J66" s="372" t="n"/>
+      <c r="K66" s="372">
+        <f>IF(TRIM($A66)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L66" s="371">
+        <f>IF(TRIM($A66)="","",IF(OR($A66="Selección de la mejor respuesta",$A66="SELECCION_MEJOR_RESPUESTA",$A66="Subítem de caso o problema",$A66="SUBITEM_CASO"),IF(TRIM($C66)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D66:$H66&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I66)&lt;&gt;"",OR(LEFT(TRIM($I66),1)="A",LEFT(TRIM($I66),1)="B",LEFT(TRIM($I66),1)="C",LEFT(TRIM($I66),1)="D",LEFT(TRIM($I66),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A66)="","",IF(COUNTIF($Q66:$AJ66,"?*")=0,"OK","Falta revisar: "&amp;$Q66&amp;$R66&amp;$S66&amp;$T66&amp;$U66&amp;$V66&amp;$W66&amp;$X66&amp;$Y66&amp;$Z66&amp;$AA66&amp;$AB66&amp;$AC66&amp;$AD66&amp;$AE66&amp;$AF66&amp;$AG66&amp;$AH66&amp;$AI66&amp;$AJ66))))</f>
+        <v/>
+      </c>
+      <c r="M66" s="373" t="n"/>
+      <c r="Q66">
+        <f>IF(TRIM($C66)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R66">
+        <f>IF(TRIM($K66)="",IF(COUNTIF($Q66:$Q66,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S66">
         <f>IF(AND(TRIM($K66)&lt;&gt;"",TRIM($K66)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q66:$R66,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T66">
+        <f>IF(AND(OR($A66="Ítems agrupados por caso clínico o problema",$A66="Subítem de caso o problema",$A66="Emparejamiento Ampliado",$A66="Opción de Emparejamiento Ampliado"),TRIM($B66)=""),IF(COUNTIF($Q66:$S66,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U66">
+        <f>IF(AND(OR($A66="Verdadero o Falso Simple",$A66="Respuesta A/B/Ambas/Ninguna",$A66="Verdadero o Falso Complejas",$A66="Selección de la mejor respuesta",$A66="Subítem de caso o problema",$A66="Opción de Emparejamiento Ampliado"),TRIM($I66)=""),IF(COUNTIF($Q66:$T66,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V66">
+        <f>IF(AND(OR($A66="Verdadero o Falso Simple",$A66="Respuesta A/B/Ambas/Ninguna",$A66="Verdadero o Falso Complejas",$A66="Selección de la mejor respuesta",$A66="Subítem de caso o problema",$A66="Opción de Emparejamiento Ampliado"),TRIM($J66)=""),IF(COUNTIF($Q66:$U66,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W66">
+        <f>IF(AND(OR($A66="Ítems agrupados por caso clínico o problema",$A66="Emparejamiento Ampliado"),TRIM($I66)&lt;&gt;""),IF(COUNTIF($Q66:$V66,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X66">
+        <f>IF(AND(OR($A66="Ítems agrupados por caso clínico o problema",$A66="Emparejamiento Ampliado"),TRIM($J66)&lt;&gt;""),IF(COUNTIF($Q66:$W66,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y66">
+        <f>IF(AND($A66="Verdadero o Falso Simple",OR(COUNTIF($D66:$E66,"?*")&lt;2,COUNTIF($F66:$H66,"?*")&gt;0)),IF(COUNTIF($Q66:$X66,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z66">
+        <f>IF(AND($A66="Verdadero o Falso Simple",TRIM($I66)&lt;&gt;"",NOT(OR(LEFT(TRIM($I66),1)="A",LEFT(TRIM($I66),1)="B"))),IF(COUNTIF($Q66:$Y66,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA66">
+        <f>IF(AND($A66="Respuesta A/B/Ambas/Ninguna",COUNTIF($D66:$G66,"?*")&lt;4),IF(COUNTIF($Q66:$Z66,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB66">
+        <f>IF(AND($A66="Respuesta A/B/Ambas/Ninguna",COUNTIF($H66:$H66,"?*")&gt;0),IF(COUNTIF($Q66:$AA66,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC66">
+        <f>IF(AND($A66="Respuesta A/B/Ambas/Ninguna",TRIM($I66)&lt;&gt;"",NOT(OR(LEFT(TRIM($I66),1)="A",LEFT(TRIM($I66),1)="B",LEFT(TRIM($I66),1)="C",LEFT(TRIM($I66),1)="D"))),IF(COUNTIF($Q66:$AB66,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD66">
+        <f>IF(AND($A66="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D66,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E66,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F66,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G66,"4.","")))=0)),IF(COUNTIF($Q66:$AC66,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE66">
+        <f>IF(AND($A66="Verdadero o Falso Complejas",COUNTIF($H66:$H66,"?*")&gt;0),IF(COUNTIF($Q66:$AD66,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF66">
+        <f>IF(AND($A66="Verdadero o Falso Complejas",TRIM($I66)&lt;&gt;"",NOT(OR(LEFT(TRIM($I66),1)="A",LEFT(TRIM($I66),1)="B",LEFT(TRIM($I66),1)="C",LEFT(TRIM($I66),1)="D",LEFT(TRIM($I66),1)="E"))),IF(COUNTIF($Q66:$AE66,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG66">
+        <f>IF(AND(OR($A66="Selección de la mejor respuesta",$A66="Subítem de caso o problema"),COUNTA($D66:$H66)&lt;5),IF(COUNTIF($Q66:$AF66,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH66">
+        <f>IF(AND(OR($A66="Selección de la mejor respuesta",$A66="Subítem de caso o problema"),TRIM($I66)&lt;&gt;"",NOT(OR(LEFT(TRIM($I66),1)="A",LEFT(TRIM($I66),1)="B",LEFT(TRIM($I66),1)="C",LEFT(TRIM($I66),1)="D",LEFT(TRIM($I66),1)="E"))),IF(COUNTIF($Q66:$AG66,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI66">
+        <f>IF(AND(OR($A66="Ítems agrupados por caso clínico o problema",$A66="Opción de Emparejamiento Ampliado"),COUNTIF($D66:$H66,"?*")&gt;0),IF(COUNTIF($Q66:$AH66,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ66">
+        <f>IF(AND($A66="Emparejamiento Ampliado",COUNTIF($D66:$H66,"?*")&lt;2),IF(COUNTIF($Q66:$AI66,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK66">
+        <f>IF(AND($A66="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I66),1)="A",LEFT(TRIM($I66),1)="B",LEFT(TRIM($I66),1)="C",LEFT(TRIM($I66),1)="D",LEFT(TRIM($I66),1)="E"))),IF(COUNTIF($Q66:$AJ66,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL66">
+        <f>IF(TRIM($K66)="",IF(COUNTIF($M66:$M66,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM66">
         <f>IF(AND(TRIM($K66)&lt;&gt;"",TRIM($K66)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M66:$N66,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="24" customHeight="1">
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="371" t="n"/>
+      <c r="B67" s="371" t="n"/>
+      <c r="C67" s="371" t="n"/>
+      <c r="D67" s="371">
+        <f>IF($A67="Verdadero o Falso Simple","Verdadero",IF($A67="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A67="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E67" s="371">
+        <f>IF($A67="Verdadero o Falso Simple","Falso",IF($A67="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A67="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F67" s="371">
+        <f>IF($A67="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A67="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G67" s="371">
+        <f>IF($A67="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A67="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H67" s="371">
+        <f>IF($A67="Verdadero o Falso Simple","",IF($A67="Respuesta A/B/Ambas/Ninguna","",IF($A67="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I67" s="371" t="n"/>
+      <c r="J67" s="372" t="n"/>
+      <c r="K67" s="372">
+        <f>IF(TRIM($A67)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L67" s="371">
+        <f>IF(TRIM($A67)="","",IF(OR($A67="Selección de la mejor respuesta",$A67="SELECCION_MEJOR_RESPUESTA",$A67="Subítem de caso o problema",$A67="SUBITEM_CASO"),IF(TRIM($C67)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D67:$H67&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I67)&lt;&gt;"",OR(LEFT(TRIM($I67),1)="A",LEFT(TRIM($I67),1)="B",LEFT(TRIM($I67),1)="C",LEFT(TRIM($I67),1)="D",LEFT(TRIM($I67),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A67)="","",IF(COUNTIF($Q67:$AJ67,"?*")=0,"OK","Falta revisar: "&amp;$Q67&amp;$R67&amp;$S67&amp;$T67&amp;$U67&amp;$V67&amp;$W67&amp;$X67&amp;$Y67&amp;$Z67&amp;$AA67&amp;$AB67&amp;$AC67&amp;$AD67&amp;$AE67&amp;$AF67&amp;$AG67&amp;$AH67&amp;$AI67&amp;$AJ67))))</f>
+        <v/>
+      </c>
+      <c r="M67" s="373" t="n"/>
+      <c r="Q67">
+        <f>IF(TRIM($C67)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R67">
+        <f>IF(TRIM($K67)="",IF(COUNTIF($Q67:$Q67,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S67">
         <f>IF(AND(TRIM($K67)&lt;&gt;"",TRIM($K67)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q67:$R67,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T67">
+        <f>IF(AND(OR($A67="Ítems agrupados por caso clínico o problema",$A67="Subítem de caso o problema",$A67="Emparejamiento Ampliado",$A67="Opción de Emparejamiento Ampliado"),TRIM($B67)=""),IF(COUNTIF($Q67:$S67,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U67">
+        <f>IF(AND(OR($A67="Verdadero o Falso Simple",$A67="Respuesta A/B/Ambas/Ninguna",$A67="Verdadero o Falso Complejas",$A67="Selección de la mejor respuesta",$A67="Subítem de caso o problema",$A67="Opción de Emparejamiento Ampliado"),TRIM($I67)=""),IF(COUNTIF($Q67:$T67,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V67">
+        <f>IF(AND(OR($A67="Verdadero o Falso Simple",$A67="Respuesta A/B/Ambas/Ninguna",$A67="Verdadero o Falso Complejas",$A67="Selección de la mejor respuesta",$A67="Subítem de caso o problema",$A67="Opción de Emparejamiento Ampliado"),TRIM($J67)=""),IF(COUNTIF($Q67:$U67,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W67">
+        <f>IF(AND(OR($A67="Ítems agrupados por caso clínico o problema",$A67="Emparejamiento Ampliado"),TRIM($I67)&lt;&gt;""),IF(COUNTIF($Q67:$V67,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X67">
+        <f>IF(AND(OR($A67="Ítems agrupados por caso clínico o problema",$A67="Emparejamiento Ampliado"),TRIM($J67)&lt;&gt;""),IF(COUNTIF($Q67:$W67,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y67">
+        <f>IF(AND($A67="Verdadero o Falso Simple",OR(COUNTIF($D67:$E67,"?*")&lt;2,COUNTIF($F67:$H67,"?*")&gt;0)),IF(COUNTIF($Q67:$X67,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z67">
+        <f>IF(AND($A67="Verdadero o Falso Simple",TRIM($I67)&lt;&gt;"",NOT(OR(LEFT(TRIM($I67),1)="A",LEFT(TRIM($I67),1)="B"))),IF(COUNTIF($Q67:$Y67,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA67">
+        <f>IF(AND($A67="Respuesta A/B/Ambas/Ninguna",COUNTIF($D67:$G67,"?*")&lt;4),IF(COUNTIF($Q67:$Z67,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB67">
+        <f>IF(AND($A67="Respuesta A/B/Ambas/Ninguna",COUNTIF($H67:$H67,"?*")&gt;0),IF(COUNTIF($Q67:$AA67,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC67">
+        <f>IF(AND($A67="Respuesta A/B/Ambas/Ninguna",TRIM($I67)&lt;&gt;"",NOT(OR(LEFT(TRIM($I67),1)="A",LEFT(TRIM($I67),1)="B",LEFT(TRIM($I67),1)="C",LEFT(TRIM($I67),1)="D"))),IF(COUNTIF($Q67:$AB67,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD67">
+        <f>IF(AND($A67="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D67,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E67,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F67,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G67,"4.","")))=0)),IF(COUNTIF($Q67:$AC67,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE67">
+        <f>IF(AND($A67="Verdadero o Falso Complejas",COUNTIF($H67:$H67,"?*")&gt;0),IF(COUNTIF($Q67:$AD67,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF67">
+        <f>IF(AND($A67="Verdadero o Falso Complejas",TRIM($I67)&lt;&gt;"",NOT(OR(LEFT(TRIM($I67),1)="A",LEFT(TRIM($I67),1)="B",LEFT(TRIM($I67),1)="C",LEFT(TRIM($I67),1)="D",LEFT(TRIM($I67),1)="E"))),IF(COUNTIF($Q67:$AE67,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG67">
+        <f>IF(AND(OR($A67="Selección de la mejor respuesta",$A67="Subítem de caso o problema"),COUNTA($D67:$H67)&lt;5),IF(COUNTIF($Q67:$AF67,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH67">
+        <f>IF(AND(OR($A67="Selección de la mejor respuesta",$A67="Subítem de caso o problema"),TRIM($I67)&lt;&gt;"",NOT(OR(LEFT(TRIM($I67),1)="A",LEFT(TRIM($I67),1)="B",LEFT(TRIM($I67),1)="C",LEFT(TRIM($I67),1)="D",LEFT(TRIM($I67),1)="E"))),IF(COUNTIF($Q67:$AG67,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI67">
+        <f>IF(AND(OR($A67="Ítems agrupados por caso clínico o problema",$A67="Opción de Emparejamiento Ampliado"),COUNTIF($D67:$H67,"?*")&gt;0),IF(COUNTIF($Q67:$AH67,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ67">
+        <f>IF(AND($A67="Emparejamiento Ampliado",COUNTIF($D67:$H67,"?*")&lt;2),IF(COUNTIF($Q67:$AI67,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK67">
+        <f>IF(AND($A67="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I67),1)="A",LEFT(TRIM($I67),1)="B",LEFT(TRIM($I67),1)="C",LEFT(TRIM($I67),1)="D",LEFT(TRIM($I67),1)="E"))),IF(COUNTIF($Q67:$AJ67,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL67">
+        <f>IF(TRIM($K67)="",IF(COUNTIF($M67:$M67,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM67">
         <f>IF(AND(TRIM($K67)&lt;&gt;"",TRIM($K67)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M67:$N67,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="24" customHeight="1">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="371" t="n"/>
+      <c r="B68" s="371" t="n"/>
+      <c r="C68" s="371" t="n"/>
+      <c r="D68" s="371">
+        <f>IF($A68="Verdadero o Falso Simple","Verdadero",IF($A68="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A68="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E68" s="371">
+        <f>IF($A68="Verdadero o Falso Simple","Falso",IF($A68="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A68="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F68" s="371">
+        <f>IF($A68="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A68="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G68" s="371">
+        <f>IF($A68="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A68="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H68" s="371">
+        <f>IF($A68="Verdadero o Falso Simple","",IF($A68="Respuesta A/B/Ambas/Ninguna","",IF($A68="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I68" s="371" t="n"/>
+      <c r="J68" s="372" t="n"/>
+      <c r="K68" s="372">
+        <f>IF(TRIM($A68)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L68" s="371">
+        <f>IF(TRIM($A68)="","",IF(OR($A68="Selección de la mejor respuesta",$A68="SELECCION_MEJOR_RESPUESTA",$A68="Subítem de caso o problema",$A68="SUBITEM_CASO"),IF(TRIM($C68)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D68:$H68&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I68)&lt;&gt;"",OR(LEFT(TRIM($I68),1)="A",LEFT(TRIM($I68),1)="B",LEFT(TRIM($I68),1)="C",LEFT(TRIM($I68),1)="D",LEFT(TRIM($I68),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A68)="","",IF(COUNTIF($Q68:$AJ68,"?*")=0,"OK","Falta revisar: "&amp;$Q68&amp;$R68&amp;$S68&amp;$T68&amp;$U68&amp;$V68&amp;$W68&amp;$X68&amp;$Y68&amp;$Z68&amp;$AA68&amp;$AB68&amp;$AC68&amp;$AD68&amp;$AE68&amp;$AF68&amp;$AG68&amp;$AH68&amp;$AI68&amp;$AJ68))))</f>
+        <v/>
+      </c>
+      <c r="M68" s="373" t="n"/>
+      <c r="Q68">
+        <f>IF(TRIM($C68)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R68">
+        <f>IF(TRIM($K68)="",IF(COUNTIF($Q68:$Q68,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S68">
         <f>IF(AND(TRIM($K68)&lt;&gt;"",TRIM($K68)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q68:$R68,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T68">
+        <f>IF(AND(OR($A68="Ítems agrupados por caso clínico o problema",$A68="Subítem de caso o problema",$A68="Emparejamiento Ampliado",$A68="Opción de Emparejamiento Ampliado"),TRIM($B68)=""),IF(COUNTIF($Q68:$S68,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U68">
+        <f>IF(AND(OR($A68="Verdadero o Falso Simple",$A68="Respuesta A/B/Ambas/Ninguna",$A68="Verdadero o Falso Complejas",$A68="Selección de la mejor respuesta",$A68="Subítem de caso o problema",$A68="Opción de Emparejamiento Ampliado"),TRIM($I68)=""),IF(COUNTIF($Q68:$T68,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V68">
+        <f>IF(AND(OR($A68="Verdadero o Falso Simple",$A68="Respuesta A/B/Ambas/Ninguna",$A68="Verdadero o Falso Complejas",$A68="Selección de la mejor respuesta",$A68="Subítem de caso o problema",$A68="Opción de Emparejamiento Ampliado"),TRIM($J68)=""),IF(COUNTIF($Q68:$U68,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W68">
+        <f>IF(AND(OR($A68="Ítems agrupados por caso clínico o problema",$A68="Emparejamiento Ampliado"),TRIM($I68)&lt;&gt;""),IF(COUNTIF($Q68:$V68,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X68">
+        <f>IF(AND(OR($A68="Ítems agrupados por caso clínico o problema",$A68="Emparejamiento Ampliado"),TRIM($J68)&lt;&gt;""),IF(COUNTIF($Q68:$W68,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y68">
+        <f>IF(AND($A68="Verdadero o Falso Simple",OR(COUNTIF($D68:$E68,"?*")&lt;2,COUNTIF($F68:$H68,"?*")&gt;0)),IF(COUNTIF($Q68:$X68,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z68">
+        <f>IF(AND($A68="Verdadero o Falso Simple",TRIM($I68)&lt;&gt;"",NOT(OR(LEFT(TRIM($I68),1)="A",LEFT(TRIM($I68),1)="B"))),IF(COUNTIF($Q68:$Y68,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA68">
+        <f>IF(AND($A68="Respuesta A/B/Ambas/Ninguna",COUNTIF($D68:$G68,"?*")&lt;4),IF(COUNTIF($Q68:$Z68,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB68">
+        <f>IF(AND($A68="Respuesta A/B/Ambas/Ninguna",COUNTIF($H68:$H68,"?*")&gt;0),IF(COUNTIF($Q68:$AA68,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC68">
+        <f>IF(AND($A68="Respuesta A/B/Ambas/Ninguna",TRIM($I68)&lt;&gt;"",NOT(OR(LEFT(TRIM($I68),1)="A",LEFT(TRIM($I68),1)="B",LEFT(TRIM($I68),1)="C",LEFT(TRIM($I68),1)="D"))),IF(COUNTIF($Q68:$AB68,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD68">
+        <f>IF(AND($A68="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D68,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E68,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F68,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G68,"4.","")))=0)),IF(COUNTIF($Q68:$AC68,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE68">
+        <f>IF(AND($A68="Verdadero o Falso Complejas",COUNTIF($H68:$H68,"?*")&gt;0),IF(COUNTIF($Q68:$AD68,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF68">
+        <f>IF(AND($A68="Verdadero o Falso Complejas",TRIM($I68)&lt;&gt;"",NOT(OR(LEFT(TRIM($I68),1)="A",LEFT(TRIM($I68),1)="B",LEFT(TRIM($I68),1)="C",LEFT(TRIM($I68),1)="D",LEFT(TRIM($I68),1)="E"))),IF(COUNTIF($Q68:$AE68,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG68">
+        <f>IF(AND(OR($A68="Selección de la mejor respuesta",$A68="Subítem de caso o problema"),COUNTA($D68:$H68)&lt;5),IF(COUNTIF($Q68:$AF68,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH68">
+        <f>IF(AND(OR($A68="Selección de la mejor respuesta",$A68="Subítem de caso o problema"),TRIM($I68)&lt;&gt;"",NOT(OR(LEFT(TRIM($I68),1)="A",LEFT(TRIM($I68),1)="B",LEFT(TRIM($I68),1)="C",LEFT(TRIM($I68),1)="D",LEFT(TRIM($I68),1)="E"))),IF(COUNTIF($Q68:$AG68,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI68">
+        <f>IF(AND(OR($A68="Ítems agrupados por caso clínico o problema",$A68="Opción de Emparejamiento Ampliado"),COUNTIF($D68:$H68,"?*")&gt;0),IF(COUNTIF($Q68:$AH68,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ68">
+        <f>IF(AND($A68="Emparejamiento Ampliado",COUNTIF($D68:$H68,"?*")&lt;2),IF(COUNTIF($Q68:$AI68,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK68">
+        <f>IF(AND($A68="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I68),1)="A",LEFT(TRIM($I68),1)="B",LEFT(TRIM($I68),1)="C",LEFT(TRIM($I68),1)="D",LEFT(TRIM($I68),1)="E"))),IF(COUNTIF($Q68:$AJ68,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL68">
+        <f>IF(TRIM($K68)="",IF(COUNTIF($M68:$M68,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM68">
         <f>IF(AND(TRIM($K68)&lt;&gt;"",TRIM($K68)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M68:$N68,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="24" customHeight="1">
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="371" t="n"/>
+      <c r="B69" s="371" t="n"/>
+      <c r="C69" s="371" t="n"/>
+      <c r="D69" s="371">
+        <f>IF($A69="Verdadero o Falso Simple","Verdadero",IF($A69="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A69="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E69" s="371">
+        <f>IF($A69="Verdadero o Falso Simple","Falso",IF($A69="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A69="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F69" s="371">
+        <f>IF($A69="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A69="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G69" s="371">
+        <f>IF($A69="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A69="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H69" s="371">
+        <f>IF($A69="Verdadero o Falso Simple","",IF($A69="Respuesta A/B/Ambas/Ninguna","",IF($A69="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I69" s="371" t="n"/>
+      <c r="J69" s="372" t="n"/>
+      <c r="K69" s="372">
+        <f>IF(TRIM($A69)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L69" s="371">
+        <f>IF(TRIM($A69)="","",IF(OR($A69="Selección de la mejor respuesta",$A69="SELECCION_MEJOR_RESPUESTA",$A69="Subítem de caso o problema",$A69="SUBITEM_CASO"),IF(TRIM($C69)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D69:$H69&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I69)&lt;&gt;"",OR(LEFT(TRIM($I69),1)="A",LEFT(TRIM($I69),1)="B",LEFT(TRIM($I69),1)="C",LEFT(TRIM($I69),1)="D",LEFT(TRIM($I69),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A69)="","",IF(COUNTIF($Q69:$AJ69,"?*")=0,"OK","Falta revisar: "&amp;$Q69&amp;$R69&amp;$S69&amp;$T69&amp;$U69&amp;$V69&amp;$W69&amp;$X69&amp;$Y69&amp;$Z69&amp;$AA69&amp;$AB69&amp;$AC69&amp;$AD69&amp;$AE69&amp;$AF69&amp;$AG69&amp;$AH69&amp;$AI69&amp;$AJ69))))</f>
+        <v/>
+      </c>
+      <c r="M69" s="373" t="n"/>
+      <c r="Q69">
+        <f>IF(TRIM($C69)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R69">
+        <f>IF(TRIM($K69)="",IF(COUNTIF($Q69:$Q69,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S69">
         <f>IF(AND(TRIM($K69)&lt;&gt;"",TRIM($K69)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q69:$R69,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T69">
+        <f>IF(AND(OR($A69="Ítems agrupados por caso clínico o problema",$A69="Subítem de caso o problema",$A69="Emparejamiento Ampliado",$A69="Opción de Emparejamiento Ampliado"),TRIM($B69)=""),IF(COUNTIF($Q69:$S69,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U69">
+        <f>IF(AND(OR($A69="Verdadero o Falso Simple",$A69="Respuesta A/B/Ambas/Ninguna",$A69="Verdadero o Falso Complejas",$A69="Selección de la mejor respuesta",$A69="Subítem de caso o problema",$A69="Opción de Emparejamiento Ampliado"),TRIM($I69)=""),IF(COUNTIF($Q69:$T69,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V69">
+        <f>IF(AND(OR($A69="Verdadero o Falso Simple",$A69="Respuesta A/B/Ambas/Ninguna",$A69="Verdadero o Falso Complejas",$A69="Selección de la mejor respuesta",$A69="Subítem de caso o problema",$A69="Opción de Emparejamiento Ampliado"),TRIM($J69)=""),IF(COUNTIF($Q69:$U69,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W69">
+        <f>IF(AND(OR($A69="Ítems agrupados por caso clínico o problema",$A69="Emparejamiento Ampliado"),TRIM($I69)&lt;&gt;""),IF(COUNTIF($Q69:$V69,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X69">
+        <f>IF(AND(OR($A69="Ítems agrupados por caso clínico o problema",$A69="Emparejamiento Ampliado"),TRIM($J69)&lt;&gt;""),IF(COUNTIF($Q69:$W69,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y69">
+        <f>IF(AND($A69="Verdadero o Falso Simple",OR(COUNTIF($D69:$E69,"?*")&lt;2,COUNTIF($F69:$H69,"?*")&gt;0)),IF(COUNTIF($Q69:$X69,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z69">
+        <f>IF(AND($A69="Verdadero o Falso Simple",TRIM($I69)&lt;&gt;"",NOT(OR(LEFT(TRIM($I69),1)="A",LEFT(TRIM($I69),1)="B"))),IF(COUNTIF($Q69:$Y69,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA69">
+        <f>IF(AND($A69="Respuesta A/B/Ambas/Ninguna",COUNTIF($D69:$G69,"?*")&lt;4),IF(COUNTIF($Q69:$Z69,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB69">
+        <f>IF(AND($A69="Respuesta A/B/Ambas/Ninguna",COUNTIF($H69:$H69,"?*")&gt;0),IF(COUNTIF($Q69:$AA69,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC69">
+        <f>IF(AND($A69="Respuesta A/B/Ambas/Ninguna",TRIM($I69)&lt;&gt;"",NOT(OR(LEFT(TRIM($I69),1)="A",LEFT(TRIM($I69),1)="B",LEFT(TRIM($I69),1)="C",LEFT(TRIM($I69),1)="D"))),IF(COUNTIF($Q69:$AB69,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD69">
+        <f>IF(AND($A69="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D69,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E69,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F69,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G69,"4.","")))=0)),IF(COUNTIF($Q69:$AC69,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE69">
+        <f>IF(AND($A69="Verdadero o Falso Complejas",COUNTIF($H69:$H69,"?*")&gt;0),IF(COUNTIF($Q69:$AD69,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF69">
+        <f>IF(AND($A69="Verdadero o Falso Complejas",TRIM($I69)&lt;&gt;"",NOT(OR(LEFT(TRIM($I69),1)="A",LEFT(TRIM($I69),1)="B",LEFT(TRIM($I69),1)="C",LEFT(TRIM($I69),1)="D",LEFT(TRIM($I69),1)="E"))),IF(COUNTIF($Q69:$AE69,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG69">
+        <f>IF(AND(OR($A69="Selección de la mejor respuesta",$A69="Subítem de caso o problema"),COUNTA($D69:$H69)&lt;5),IF(COUNTIF($Q69:$AF69,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH69">
+        <f>IF(AND(OR($A69="Selección de la mejor respuesta",$A69="Subítem de caso o problema"),TRIM($I69)&lt;&gt;"",NOT(OR(LEFT(TRIM($I69),1)="A",LEFT(TRIM($I69),1)="B",LEFT(TRIM($I69),1)="C",LEFT(TRIM($I69),1)="D",LEFT(TRIM($I69),1)="E"))),IF(COUNTIF($Q69:$AG69,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI69">
+        <f>IF(AND(OR($A69="Ítems agrupados por caso clínico o problema",$A69="Opción de Emparejamiento Ampliado"),COUNTIF($D69:$H69,"?*")&gt;0),IF(COUNTIF($Q69:$AH69,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ69">
+        <f>IF(AND($A69="Emparejamiento Ampliado",COUNTIF($D69:$H69,"?*")&lt;2),IF(COUNTIF($Q69:$AI69,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK69">
+        <f>IF(AND($A69="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I69),1)="A",LEFT(TRIM($I69),1)="B",LEFT(TRIM($I69),1)="C",LEFT(TRIM($I69),1)="D",LEFT(TRIM($I69),1)="E"))),IF(COUNTIF($Q69:$AJ69,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL69">
+        <f>IF(TRIM($K69)="",IF(COUNTIF($M69:$M69,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM69">
         <f>IF(AND(TRIM($K69)&lt;&gt;"",TRIM($K69)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M69:$N69,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="70" ht="24" customHeight="1">
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="371" t="n"/>
+      <c r="B70" s="371" t="n"/>
+      <c r="C70" s="371" t="n"/>
+      <c r="D70" s="371">
+        <f>IF($A70="Verdadero o Falso Simple","Verdadero",IF($A70="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A70="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E70" s="371">
+        <f>IF($A70="Verdadero o Falso Simple","Falso",IF($A70="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A70="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F70" s="371">
+        <f>IF($A70="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A70="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G70" s="371">
+        <f>IF($A70="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A70="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H70" s="371">
+        <f>IF($A70="Verdadero o Falso Simple","",IF($A70="Respuesta A/B/Ambas/Ninguna","",IF($A70="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I70" s="371" t="n"/>
+      <c r="J70" s="372" t="n"/>
+      <c r="K70" s="372">
+        <f>IF(TRIM($A70)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L70" s="371">
+        <f>IF(TRIM($A70)="","",IF(OR($A70="Selección de la mejor respuesta",$A70="SELECCION_MEJOR_RESPUESTA",$A70="Subítem de caso o problema",$A70="SUBITEM_CASO"),IF(TRIM($C70)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D70:$H70&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I70)&lt;&gt;"",OR(LEFT(TRIM($I70),1)="A",LEFT(TRIM($I70),1)="B",LEFT(TRIM($I70),1)="C",LEFT(TRIM($I70),1)="D",LEFT(TRIM($I70),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A70)="","",IF(COUNTIF($Q70:$AJ70,"?*")=0,"OK","Falta revisar: "&amp;$Q70&amp;$R70&amp;$S70&amp;$T70&amp;$U70&amp;$V70&amp;$W70&amp;$X70&amp;$Y70&amp;$Z70&amp;$AA70&amp;$AB70&amp;$AC70&amp;$AD70&amp;$AE70&amp;$AF70&amp;$AG70&amp;$AH70&amp;$AI70&amp;$AJ70))))</f>
+        <v/>
+      </c>
+      <c r="M70" s="373" t="n"/>
+      <c r="Q70">
+        <f>IF(TRIM($C70)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R70">
+        <f>IF(TRIM($K70)="",IF(COUNTIF($Q70:$Q70,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S70">
         <f>IF(AND(TRIM($K70)&lt;&gt;"",TRIM($K70)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q70:$R70,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T70">
+        <f>IF(AND(OR($A70="Ítems agrupados por caso clínico o problema",$A70="Subítem de caso o problema",$A70="Emparejamiento Ampliado",$A70="Opción de Emparejamiento Ampliado"),TRIM($B70)=""),IF(COUNTIF($Q70:$S70,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U70">
+        <f>IF(AND(OR($A70="Verdadero o Falso Simple",$A70="Respuesta A/B/Ambas/Ninguna",$A70="Verdadero o Falso Complejas",$A70="Selección de la mejor respuesta",$A70="Subítem de caso o problema",$A70="Opción de Emparejamiento Ampliado"),TRIM($I70)=""),IF(COUNTIF($Q70:$T70,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V70">
+        <f>IF(AND(OR($A70="Verdadero o Falso Simple",$A70="Respuesta A/B/Ambas/Ninguna",$A70="Verdadero o Falso Complejas",$A70="Selección de la mejor respuesta",$A70="Subítem de caso o problema",$A70="Opción de Emparejamiento Ampliado"),TRIM($J70)=""),IF(COUNTIF($Q70:$U70,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W70">
+        <f>IF(AND(OR($A70="Ítems agrupados por caso clínico o problema",$A70="Emparejamiento Ampliado"),TRIM($I70)&lt;&gt;""),IF(COUNTIF($Q70:$V70,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X70">
+        <f>IF(AND(OR($A70="Ítems agrupados por caso clínico o problema",$A70="Emparejamiento Ampliado"),TRIM($J70)&lt;&gt;""),IF(COUNTIF($Q70:$W70,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y70">
+        <f>IF(AND($A70="Verdadero o Falso Simple",OR(COUNTIF($D70:$E70,"?*")&lt;2,COUNTIF($F70:$H70,"?*")&gt;0)),IF(COUNTIF($Q70:$X70,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z70">
+        <f>IF(AND($A70="Verdadero o Falso Simple",TRIM($I70)&lt;&gt;"",NOT(OR(LEFT(TRIM($I70),1)="A",LEFT(TRIM($I70),1)="B"))),IF(COUNTIF($Q70:$Y70,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA70">
+        <f>IF(AND($A70="Respuesta A/B/Ambas/Ninguna",COUNTIF($D70:$G70,"?*")&lt;4),IF(COUNTIF($Q70:$Z70,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB70">
+        <f>IF(AND($A70="Respuesta A/B/Ambas/Ninguna",COUNTIF($H70:$H70,"?*")&gt;0),IF(COUNTIF($Q70:$AA70,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC70">
+        <f>IF(AND($A70="Respuesta A/B/Ambas/Ninguna",TRIM($I70)&lt;&gt;"",NOT(OR(LEFT(TRIM($I70),1)="A",LEFT(TRIM($I70),1)="B",LEFT(TRIM($I70),1)="C",LEFT(TRIM($I70),1)="D"))),IF(COUNTIF($Q70:$AB70,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD70">
+        <f>IF(AND($A70="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D70,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E70,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F70,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G70,"4.","")))=0)),IF(COUNTIF($Q70:$AC70,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE70">
+        <f>IF(AND($A70="Verdadero o Falso Complejas",COUNTIF($H70:$H70,"?*")&gt;0),IF(COUNTIF($Q70:$AD70,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF70">
+        <f>IF(AND($A70="Verdadero o Falso Complejas",TRIM($I70)&lt;&gt;"",NOT(OR(LEFT(TRIM($I70),1)="A",LEFT(TRIM($I70),1)="B",LEFT(TRIM($I70),1)="C",LEFT(TRIM($I70),1)="D",LEFT(TRIM($I70),1)="E"))),IF(COUNTIF($Q70:$AE70,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG70">
+        <f>IF(AND(OR($A70="Selección de la mejor respuesta",$A70="Subítem de caso o problema"),COUNTA($D70:$H70)&lt;5),IF(COUNTIF($Q70:$AF70,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH70">
+        <f>IF(AND(OR($A70="Selección de la mejor respuesta",$A70="Subítem de caso o problema"),TRIM($I70)&lt;&gt;"",NOT(OR(LEFT(TRIM($I70),1)="A",LEFT(TRIM($I70),1)="B",LEFT(TRIM($I70),1)="C",LEFT(TRIM($I70),1)="D",LEFT(TRIM($I70),1)="E"))),IF(COUNTIF($Q70:$AG70,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI70">
+        <f>IF(AND(OR($A70="Ítems agrupados por caso clínico o problema",$A70="Opción de Emparejamiento Ampliado"),COUNTIF($D70:$H70,"?*")&gt;0),IF(COUNTIF($Q70:$AH70,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ70">
+        <f>IF(AND($A70="Emparejamiento Ampliado",COUNTIF($D70:$H70,"?*")&lt;2),IF(COUNTIF($Q70:$AI70,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK70">
+        <f>IF(AND($A70="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I70),1)="A",LEFT(TRIM($I70),1)="B",LEFT(TRIM($I70),1)="C",LEFT(TRIM($I70),1)="D",LEFT(TRIM($I70),1)="E"))),IF(COUNTIF($Q70:$AJ70,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL70">
+        <f>IF(TRIM($K70)="",IF(COUNTIF($M70:$M70,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM70">
         <f>IF(AND(TRIM($K70)&lt;&gt;"",TRIM($K70)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M70:$N70,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="71" ht="24" customHeight="1">
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="371" t="n"/>
+      <c r="B71" s="371" t="n"/>
+      <c r="C71" s="371" t="n"/>
+      <c r="D71" s="371">
+        <f>IF($A71="Verdadero o Falso Simple","Verdadero",IF($A71="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A71="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E71" s="371">
+        <f>IF($A71="Verdadero o Falso Simple","Falso",IF($A71="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A71="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F71" s="371">
+        <f>IF($A71="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A71="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G71" s="371">
+        <f>IF($A71="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A71="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H71" s="371">
+        <f>IF($A71="Verdadero o Falso Simple","",IF($A71="Respuesta A/B/Ambas/Ninguna","",IF($A71="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I71" s="371" t="n"/>
+      <c r="J71" s="372" t="n"/>
+      <c r="K71" s="372">
+        <f>IF(TRIM($A71)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L71" s="371">
+        <f>IF(TRIM($A71)="","",IF(OR($A71="Selección de la mejor respuesta",$A71="SELECCION_MEJOR_RESPUESTA",$A71="Subítem de caso o problema",$A71="SUBITEM_CASO"),IF(TRIM($C71)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D71:$H71&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I71)&lt;&gt;"",OR(LEFT(TRIM($I71),1)="A",LEFT(TRIM($I71),1)="B",LEFT(TRIM($I71),1)="C",LEFT(TRIM($I71),1)="D",LEFT(TRIM($I71),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A71)="","",IF(COUNTIF($Q71:$AJ71,"?*")=0,"OK","Falta revisar: "&amp;$Q71&amp;$R71&amp;$S71&amp;$T71&amp;$U71&amp;$V71&amp;$W71&amp;$X71&amp;$Y71&amp;$Z71&amp;$AA71&amp;$AB71&amp;$AC71&amp;$AD71&amp;$AE71&amp;$AF71&amp;$AG71&amp;$AH71&amp;$AI71&amp;$AJ71))))</f>
+        <v/>
+      </c>
+      <c r="M71" s="373" t="n"/>
+      <c r="Q71">
+        <f>IF(TRIM($C71)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R71">
+        <f>IF(TRIM($K71)="",IF(COUNTIF($Q71:$Q71,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S71">
         <f>IF(AND(TRIM($K71)&lt;&gt;"",TRIM($K71)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q71:$R71,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T71">
+        <f>IF(AND(OR($A71="Ítems agrupados por caso clínico o problema",$A71="Subítem de caso o problema",$A71="Emparejamiento Ampliado",$A71="Opción de Emparejamiento Ampliado"),TRIM($B71)=""),IF(COUNTIF($Q71:$S71,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U71">
+        <f>IF(AND(OR($A71="Verdadero o Falso Simple",$A71="Respuesta A/B/Ambas/Ninguna",$A71="Verdadero o Falso Complejas",$A71="Selección de la mejor respuesta",$A71="Subítem de caso o problema",$A71="Opción de Emparejamiento Ampliado"),TRIM($I71)=""),IF(COUNTIF($Q71:$T71,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V71">
+        <f>IF(AND(OR($A71="Verdadero o Falso Simple",$A71="Respuesta A/B/Ambas/Ninguna",$A71="Verdadero o Falso Complejas",$A71="Selección de la mejor respuesta",$A71="Subítem de caso o problema",$A71="Opción de Emparejamiento Ampliado"),TRIM($J71)=""),IF(COUNTIF($Q71:$U71,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W71">
+        <f>IF(AND(OR($A71="Ítems agrupados por caso clínico o problema",$A71="Emparejamiento Ampliado"),TRIM($I71)&lt;&gt;""),IF(COUNTIF($Q71:$V71,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X71">
+        <f>IF(AND(OR($A71="Ítems agrupados por caso clínico o problema",$A71="Emparejamiento Ampliado"),TRIM($J71)&lt;&gt;""),IF(COUNTIF($Q71:$W71,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y71">
+        <f>IF(AND($A71="Verdadero o Falso Simple",OR(COUNTIF($D71:$E71,"?*")&lt;2,COUNTIF($F71:$H71,"?*")&gt;0)),IF(COUNTIF($Q71:$X71,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z71">
+        <f>IF(AND($A71="Verdadero o Falso Simple",TRIM($I71)&lt;&gt;"",NOT(OR(LEFT(TRIM($I71),1)="A",LEFT(TRIM($I71),1)="B"))),IF(COUNTIF($Q71:$Y71,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA71">
+        <f>IF(AND($A71="Respuesta A/B/Ambas/Ninguna",COUNTIF($D71:$G71,"?*")&lt;4),IF(COUNTIF($Q71:$Z71,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB71">
+        <f>IF(AND($A71="Respuesta A/B/Ambas/Ninguna",COUNTIF($H71:$H71,"?*")&gt;0),IF(COUNTIF($Q71:$AA71,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC71">
+        <f>IF(AND($A71="Respuesta A/B/Ambas/Ninguna",TRIM($I71)&lt;&gt;"",NOT(OR(LEFT(TRIM($I71),1)="A",LEFT(TRIM($I71),1)="B",LEFT(TRIM($I71),1)="C",LEFT(TRIM($I71),1)="D"))),IF(COUNTIF($Q71:$AB71,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD71">
+        <f>IF(AND($A71="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D71,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E71,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F71,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G71,"4.","")))=0)),IF(COUNTIF($Q71:$AC71,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE71">
+        <f>IF(AND($A71="Verdadero o Falso Complejas",COUNTIF($H71:$H71,"?*")&gt;0),IF(COUNTIF($Q71:$AD71,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF71">
+        <f>IF(AND($A71="Verdadero o Falso Complejas",TRIM($I71)&lt;&gt;"",NOT(OR(LEFT(TRIM($I71),1)="A",LEFT(TRIM($I71),1)="B",LEFT(TRIM($I71),1)="C",LEFT(TRIM($I71),1)="D",LEFT(TRIM($I71),1)="E"))),IF(COUNTIF($Q71:$AE71,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG71">
+        <f>IF(AND(OR($A71="Selección de la mejor respuesta",$A71="Subítem de caso o problema"),COUNTA($D71:$H71)&lt;5),IF(COUNTIF($Q71:$AF71,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH71">
+        <f>IF(AND(OR($A71="Selección de la mejor respuesta",$A71="Subítem de caso o problema"),TRIM($I71)&lt;&gt;"",NOT(OR(LEFT(TRIM($I71),1)="A",LEFT(TRIM($I71),1)="B",LEFT(TRIM($I71),1)="C",LEFT(TRIM($I71),1)="D",LEFT(TRIM($I71),1)="E"))),IF(COUNTIF($Q71:$AG71,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI71">
+        <f>IF(AND(OR($A71="Ítems agrupados por caso clínico o problema",$A71="Opción de Emparejamiento Ampliado"),COUNTIF($D71:$H71,"?*")&gt;0),IF(COUNTIF($Q71:$AH71,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ71">
+        <f>IF(AND($A71="Emparejamiento Ampliado",COUNTIF($D71:$H71,"?*")&lt;2),IF(COUNTIF($Q71:$AI71,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK71">
+        <f>IF(AND($A71="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I71),1)="A",LEFT(TRIM($I71),1)="B",LEFT(TRIM($I71),1)="C",LEFT(TRIM($I71),1)="D",LEFT(TRIM($I71),1)="E"))),IF(COUNTIF($Q71:$AJ71,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL71">
+        <f>IF(TRIM($K71)="",IF(COUNTIF($M71:$M71,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM71">
         <f>IF(AND(TRIM($K71)&lt;&gt;"",TRIM($K71)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M71:$N71,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="72" ht="24" customHeight="1">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="371" t="n"/>
+      <c r="B72" s="371" t="n"/>
+      <c r="C72" s="371" t="n"/>
+      <c r="D72" s="371">
+        <f>IF($A72="Verdadero o Falso Simple","Verdadero",IF($A72="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A72="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E72" s="371">
+        <f>IF($A72="Verdadero o Falso Simple","Falso",IF($A72="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A72="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F72" s="371">
+        <f>IF($A72="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A72="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G72" s="371">
+        <f>IF($A72="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A72="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H72" s="371">
+        <f>IF($A72="Verdadero o Falso Simple","",IF($A72="Respuesta A/B/Ambas/Ninguna","",IF($A72="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I72" s="371" t="n"/>
+      <c r="J72" s="372" t="n"/>
+      <c r="K72" s="372">
+        <f>IF(TRIM($A72)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L72" s="371">
+        <f>IF(TRIM($A72)="","",IF(OR($A72="Selección de la mejor respuesta",$A72="SELECCION_MEJOR_RESPUESTA",$A72="Subítem de caso o problema",$A72="SUBITEM_CASO"),IF(TRIM($C72)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D72:$H72&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I72)&lt;&gt;"",OR(LEFT(TRIM($I72),1)="A",LEFT(TRIM($I72),1)="B",LEFT(TRIM($I72),1)="C",LEFT(TRIM($I72),1)="D",LEFT(TRIM($I72),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A72)="","",IF(COUNTIF($Q72:$AJ72,"?*")=0,"OK","Falta revisar: "&amp;$Q72&amp;$R72&amp;$S72&amp;$T72&amp;$U72&amp;$V72&amp;$W72&amp;$X72&amp;$Y72&amp;$Z72&amp;$AA72&amp;$AB72&amp;$AC72&amp;$AD72&amp;$AE72&amp;$AF72&amp;$AG72&amp;$AH72&amp;$AI72&amp;$AJ72))))</f>
+        <v/>
+      </c>
+      <c r="M72" s="373" t="n"/>
+      <c r="Q72">
+        <f>IF(TRIM($C72)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R72">
+        <f>IF(TRIM($K72)="",IF(COUNTIF($Q72:$Q72,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S72">
         <f>IF(AND(TRIM($K72)&lt;&gt;"",TRIM($K72)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q72:$R72,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T72">
+        <f>IF(AND(OR($A72="Ítems agrupados por caso clínico o problema",$A72="Subítem de caso o problema",$A72="Emparejamiento Ampliado",$A72="Opción de Emparejamiento Ampliado"),TRIM($B72)=""),IF(COUNTIF($Q72:$S72,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U72">
+        <f>IF(AND(OR($A72="Verdadero o Falso Simple",$A72="Respuesta A/B/Ambas/Ninguna",$A72="Verdadero o Falso Complejas",$A72="Selección de la mejor respuesta",$A72="Subítem de caso o problema",$A72="Opción de Emparejamiento Ampliado"),TRIM($I72)=""),IF(COUNTIF($Q72:$T72,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V72">
+        <f>IF(AND(OR($A72="Verdadero o Falso Simple",$A72="Respuesta A/B/Ambas/Ninguna",$A72="Verdadero o Falso Complejas",$A72="Selección de la mejor respuesta",$A72="Subítem de caso o problema",$A72="Opción de Emparejamiento Ampliado"),TRIM($J72)=""),IF(COUNTIF($Q72:$U72,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W72">
+        <f>IF(AND(OR($A72="Ítems agrupados por caso clínico o problema",$A72="Emparejamiento Ampliado"),TRIM($I72)&lt;&gt;""),IF(COUNTIF($Q72:$V72,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X72">
+        <f>IF(AND(OR($A72="Ítems agrupados por caso clínico o problema",$A72="Emparejamiento Ampliado"),TRIM($J72)&lt;&gt;""),IF(COUNTIF($Q72:$W72,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y72">
+        <f>IF(AND($A72="Verdadero o Falso Simple",OR(COUNTIF($D72:$E72,"?*")&lt;2,COUNTIF($F72:$H72,"?*")&gt;0)),IF(COUNTIF($Q72:$X72,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z72">
+        <f>IF(AND($A72="Verdadero o Falso Simple",TRIM($I72)&lt;&gt;"",NOT(OR(LEFT(TRIM($I72),1)="A",LEFT(TRIM($I72),1)="B"))),IF(COUNTIF($Q72:$Y72,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA72">
+        <f>IF(AND($A72="Respuesta A/B/Ambas/Ninguna",COUNTIF($D72:$G72,"?*")&lt;4),IF(COUNTIF($Q72:$Z72,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB72">
+        <f>IF(AND($A72="Respuesta A/B/Ambas/Ninguna",COUNTIF($H72:$H72,"?*")&gt;0),IF(COUNTIF($Q72:$AA72,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC72">
+        <f>IF(AND($A72="Respuesta A/B/Ambas/Ninguna",TRIM($I72)&lt;&gt;"",NOT(OR(LEFT(TRIM($I72),1)="A",LEFT(TRIM($I72),1)="B",LEFT(TRIM($I72),1)="C",LEFT(TRIM($I72),1)="D"))),IF(COUNTIF($Q72:$AB72,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD72">
+        <f>IF(AND($A72="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D72,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E72,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F72,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G72,"4.","")))=0)),IF(COUNTIF($Q72:$AC72,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE72">
+        <f>IF(AND($A72="Verdadero o Falso Complejas",COUNTIF($H72:$H72,"?*")&gt;0),IF(COUNTIF($Q72:$AD72,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF72">
+        <f>IF(AND($A72="Verdadero o Falso Complejas",TRIM($I72)&lt;&gt;"",NOT(OR(LEFT(TRIM($I72),1)="A",LEFT(TRIM($I72),1)="B",LEFT(TRIM($I72),1)="C",LEFT(TRIM($I72),1)="D",LEFT(TRIM($I72),1)="E"))),IF(COUNTIF($Q72:$AE72,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG72">
+        <f>IF(AND(OR($A72="Selección de la mejor respuesta",$A72="Subítem de caso o problema"),COUNTA($D72:$H72)&lt;5),IF(COUNTIF($Q72:$AF72,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH72">
+        <f>IF(AND(OR($A72="Selección de la mejor respuesta",$A72="Subítem de caso o problema"),TRIM($I72)&lt;&gt;"",NOT(OR(LEFT(TRIM($I72),1)="A",LEFT(TRIM($I72),1)="B",LEFT(TRIM($I72),1)="C",LEFT(TRIM($I72),1)="D",LEFT(TRIM($I72),1)="E"))),IF(COUNTIF($Q72:$AG72,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI72">
+        <f>IF(AND(OR($A72="Ítems agrupados por caso clínico o problema",$A72="Opción de Emparejamiento Ampliado"),COUNTIF($D72:$H72,"?*")&gt;0),IF(COUNTIF($Q72:$AH72,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ72">
+        <f>IF(AND($A72="Emparejamiento Ampliado",COUNTIF($D72:$H72,"?*")&lt;2),IF(COUNTIF($Q72:$AI72,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK72">
+        <f>IF(AND($A72="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I72),1)="A",LEFT(TRIM($I72),1)="B",LEFT(TRIM($I72),1)="C",LEFT(TRIM($I72),1)="D",LEFT(TRIM($I72),1)="E"))),IF(COUNTIF($Q72:$AJ72,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL72">
+        <f>IF(TRIM($K72)="",IF(COUNTIF($M72:$M72,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM72">
         <f>IF(AND(TRIM($K72)&lt;&gt;"",TRIM($K72)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M72:$N72,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="24" customHeight="1">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="371" t="n"/>
+      <c r="B73" s="371" t="n"/>
+      <c r="C73" s="371" t="n"/>
+      <c r="D73" s="371">
+        <f>IF($A73="Verdadero o Falso Simple","Verdadero",IF($A73="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A73="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E73" s="371">
+        <f>IF($A73="Verdadero o Falso Simple","Falso",IF($A73="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A73="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F73" s="371">
+        <f>IF($A73="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A73="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G73" s="371">
+        <f>IF($A73="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A73="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H73" s="371">
+        <f>IF($A73="Verdadero o Falso Simple","",IF($A73="Respuesta A/B/Ambas/Ninguna","",IF($A73="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I73" s="371" t="n"/>
+      <c r="J73" s="372" t="n"/>
+      <c r="K73" s="372">
+        <f>IF(TRIM($A73)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L73" s="371">
+        <f>IF(TRIM($A73)="","",IF(OR($A73="Selección de la mejor respuesta",$A73="SELECCION_MEJOR_RESPUESTA",$A73="Subítem de caso o problema",$A73="SUBITEM_CASO"),IF(TRIM($C73)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D73:$H73&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I73)&lt;&gt;"",OR(LEFT(TRIM($I73),1)="A",LEFT(TRIM($I73),1)="B",LEFT(TRIM($I73),1)="C",LEFT(TRIM($I73),1)="D",LEFT(TRIM($I73),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A73)="","",IF(COUNTIF($Q73:$AJ73,"?*")=0,"OK","Falta revisar: "&amp;$Q73&amp;$R73&amp;$S73&amp;$T73&amp;$U73&amp;$V73&amp;$W73&amp;$X73&amp;$Y73&amp;$Z73&amp;$AA73&amp;$AB73&amp;$AC73&amp;$AD73&amp;$AE73&amp;$AF73&amp;$AG73&amp;$AH73&amp;$AI73&amp;$AJ73))))</f>
+        <v/>
+      </c>
+      <c r="M73" s="373" t="n"/>
+      <c r="Q73">
+        <f>IF(TRIM($C73)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R73">
+        <f>IF(TRIM($K73)="",IF(COUNTIF($Q73:$Q73,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S73">
         <f>IF(AND(TRIM($K73)&lt;&gt;"",TRIM($K73)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q73:$R73,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T73">
+        <f>IF(AND(OR($A73="Ítems agrupados por caso clínico o problema",$A73="Subítem de caso o problema",$A73="Emparejamiento Ampliado",$A73="Opción de Emparejamiento Ampliado"),TRIM($B73)=""),IF(COUNTIF($Q73:$S73,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U73">
+        <f>IF(AND(OR($A73="Verdadero o Falso Simple",$A73="Respuesta A/B/Ambas/Ninguna",$A73="Verdadero o Falso Complejas",$A73="Selección de la mejor respuesta",$A73="Subítem de caso o problema",$A73="Opción de Emparejamiento Ampliado"),TRIM($I73)=""),IF(COUNTIF($Q73:$T73,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V73">
+        <f>IF(AND(OR($A73="Verdadero o Falso Simple",$A73="Respuesta A/B/Ambas/Ninguna",$A73="Verdadero o Falso Complejas",$A73="Selección de la mejor respuesta",$A73="Subítem de caso o problema",$A73="Opción de Emparejamiento Ampliado"),TRIM($J73)=""),IF(COUNTIF($Q73:$U73,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W73">
+        <f>IF(AND(OR($A73="Ítems agrupados por caso clínico o problema",$A73="Emparejamiento Ampliado"),TRIM($I73)&lt;&gt;""),IF(COUNTIF($Q73:$V73,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X73">
+        <f>IF(AND(OR($A73="Ítems agrupados por caso clínico o problema",$A73="Emparejamiento Ampliado"),TRIM($J73)&lt;&gt;""),IF(COUNTIF($Q73:$W73,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y73">
+        <f>IF(AND($A73="Verdadero o Falso Simple",OR(COUNTIF($D73:$E73,"?*")&lt;2,COUNTIF($F73:$H73,"?*")&gt;0)),IF(COUNTIF($Q73:$X73,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z73">
+        <f>IF(AND($A73="Verdadero o Falso Simple",TRIM($I73)&lt;&gt;"",NOT(OR(LEFT(TRIM($I73),1)="A",LEFT(TRIM($I73),1)="B"))),IF(COUNTIF($Q73:$Y73,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA73">
+        <f>IF(AND($A73="Respuesta A/B/Ambas/Ninguna",COUNTIF($D73:$G73,"?*")&lt;4),IF(COUNTIF($Q73:$Z73,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB73">
+        <f>IF(AND($A73="Respuesta A/B/Ambas/Ninguna",COUNTIF($H73:$H73,"?*")&gt;0),IF(COUNTIF($Q73:$AA73,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC73">
+        <f>IF(AND($A73="Respuesta A/B/Ambas/Ninguna",TRIM($I73)&lt;&gt;"",NOT(OR(LEFT(TRIM($I73),1)="A",LEFT(TRIM($I73),1)="B",LEFT(TRIM($I73),1)="C",LEFT(TRIM($I73),1)="D"))),IF(COUNTIF($Q73:$AB73,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD73">
+        <f>IF(AND($A73="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D73,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E73,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F73,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G73,"4.","")))=0)),IF(COUNTIF($Q73:$AC73,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE73">
+        <f>IF(AND($A73="Verdadero o Falso Complejas",COUNTIF($H73:$H73,"?*")&gt;0),IF(COUNTIF($Q73:$AD73,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF73">
+        <f>IF(AND($A73="Verdadero o Falso Complejas",TRIM($I73)&lt;&gt;"",NOT(OR(LEFT(TRIM($I73),1)="A",LEFT(TRIM($I73),1)="B",LEFT(TRIM($I73),1)="C",LEFT(TRIM($I73),1)="D",LEFT(TRIM($I73),1)="E"))),IF(COUNTIF($Q73:$AE73,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG73">
+        <f>IF(AND(OR($A73="Selección de la mejor respuesta",$A73="Subítem de caso o problema"),COUNTA($D73:$H73)&lt;5),IF(COUNTIF($Q73:$AF73,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH73">
+        <f>IF(AND(OR($A73="Selección de la mejor respuesta",$A73="Subítem de caso o problema"),TRIM($I73)&lt;&gt;"",NOT(OR(LEFT(TRIM($I73),1)="A",LEFT(TRIM($I73),1)="B",LEFT(TRIM($I73),1)="C",LEFT(TRIM($I73),1)="D",LEFT(TRIM($I73),1)="E"))),IF(COUNTIF($Q73:$AG73,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI73">
+        <f>IF(AND(OR($A73="Ítems agrupados por caso clínico o problema",$A73="Opción de Emparejamiento Ampliado"),COUNTIF($D73:$H73,"?*")&gt;0),IF(COUNTIF($Q73:$AH73,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ73">
+        <f>IF(AND($A73="Emparejamiento Ampliado",COUNTIF($D73:$H73,"?*")&lt;2),IF(COUNTIF($Q73:$AI73,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK73">
+        <f>IF(AND($A73="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I73),1)="A",LEFT(TRIM($I73),1)="B",LEFT(TRIM($I73),1)="C",LEFT(TRIM($I73),1)="D",LEFT(TRIM($I73),1)="E"))),IF(COUNTIF($Q73:$AJ73,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL73">
+        <f>IF(TRIM($K73)="",IF(COUNTIF($M73:$M73,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM73">
         <f>IF(AND(TRIM($K73)&lt;&gt;"",TRIM($K73)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M73:$N73,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="24" customHeight="1">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="371" t="n"/>
+      <c r="B74" s="371" t="n"/>
+      <c r="C74" s="371" t="n"/>
+      <c r="D74" s="371">
+        <f>IF($A74="Verdadero o Falso Simple","Verdadero",IF($A74="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A74="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E74" s="371">
+        <f>IF($A74="Verdadero o Falso Simple","Falso",IF($A74="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A74="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F74" s="371">
+        <f>IF($A74="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A74="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G74" s="371">
+        <f>IF($A74="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A74="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H74" s="371">
+        <f>IF($A74="Verdadero o Falso Simple","",IF($A74="Respuesta A/B/Ambas/Ninguna","",IF($A74="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I74" s="371" t="n"/>
+      <c r="J74" s="372" t="n"/>
+      <c r="K74" s="372">
+        <f>IF(TRIM($A74)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L74" s="371">
+        <f>IF(TRIM($A74)="","",IF(OR($A74="Selección de la mejor respuesta",$A74="SELECCION_MEJOR_RESPUESTA",$A74="Subítem de caso o problema",$A74="SUBITEM_CASO"),IF(TRIM($C74)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D74:$H74&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I74)&lt;&gt;"",OR(LEFT(TRIM($I74),1)="A",LEFT(TRIM($I74),1)="B",LEFT(TRIM($I74),1)="C",LEFT(TRIM($I74),1)="D",LEFT(TRIM($I74),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A74)="","",IF(COUNTIF($Q74:$AJ74,"?*")=0,"OK","Falta revisar: "&amp;$Q74&amp;$R74&amp;$S74&amp;$T74&amp;$U74&amp;$V74&amp;$W74&amp;$X74&amp;$Y74&amp;$Z74&amp;$AA74&amp;$AB74&amp;$AC74&amp;$AD74&amp;$AE74&amp;$AF74&amp;$AG74&amp;$AH74&amp;$AI74&amp;$AJ74))))</f>
+        <v/>
+      </c>
+      <c r="M74" s="373" t="n"/>
+      <c r="Q74">
+        <f>IF(TRIM($C74)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R74">
+        <f>IF(TRIM($K74)="",IF(COUNTIF($Q74:$Q74,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S74">
         <f>IF(AND(TRIM($K74)&lt;&gt;"",TRIM($K74)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q74:$R74,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T74">
+        <f>IF(AND(OR($A74="Ítems agrupados por caso clínico o problema",$A74="Subítem de caso o problema",$A74="Emparejamiento Ampliado",$A74="Opción de Emparejamiento Ampliado"),TRIM($B74)=""),IF(COUNTIF($Q74:$S74,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U74">
+        <f>IF(AND(OR($A74="Verdadero o Falso Simple",$A74="Respuesta A/B/Ambas/Ninguna",$A74="Verdadero o Falso Complejas",$A74="Selección de la mejor respuesta",$A74="Subítem de caso o problema",$A74="Opción de Emparejamiento Ampliado"),TRIM($I74)=""),IF(COUNTIF($Q74:$T74,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V74">
+        <f>IF(AND(OR($A74="Verdadero o Falso Simple",$A74="Respuesta A/B/Ambas/Ninguna",$A74="Verdadero o Falso Complejas",$A74="Selección de la mejor respuesta",$A74="Subítem de caso o problema",$A74="Opción de Emparejamiento Ampliado"),TRIM($J74)=""),IF(COUNTIF($Q74:$U74,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W74">
+        <f>IF(AND(OR($A74="Ítems agrupados por caso clínico o problema",$A74="Emparejamiento Ampliado"),TRIM($I74)&lt;&gt;""),IF(COUNTIF($Q74:$V74,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X74">
+        <f>IF(AND(OR($A74="Ítems agrupados por caso clínico o problema",$A74="Emparejamiento Ampliado"),TRIM($J74)&lt;&gt;""),IF(COUNTIF($Q74:$W74,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y74">
+        <f>IF(AND($A74="Verdadero o Falso Simple",OR(COUNTIF($D74:$E74,"?*")&lt;2,COUNTIF($F74:$H74,"?*")&gt;0)),IF(COUNTIF($Q74:$X74,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z74">
+        <f>IF(AND($A74="Verdadero o Falso Simple",TRIM($I74)&lt;&gt;"",NOT(OR(LEFT(TRIM($I74),1)="A",LEFT(TRIM($I74),1)="B"))),IF(COUNTIF($Q74:$Y74,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA74">
+        <f>IF(AND($A74="Respuesta A/B/Ambas/Ninguna",COUNTIF($D74:$G74,"?*")&lt;4),IF(COUNTIF($Q74:$Z74,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB74">
+        <f>IF(AND($A74="Respuesta A/B/Ambas/Ninguna",COUNTIF($H74:$H74,"?*")&gt;0),IF(COUNTIF($Q74:$AA74,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC74">
+        <f>IF(AND($A74="Respuesta A/B/Ambas/Ninguna",TRIM($I74)&lt;&gt;"",NOT(OR(LEFT(TRIM($I74),1)="A",LEFT(TRIM($I74),1)="B",LEFT(TRIM($I74),1)="C",LEFT(TRIM($I74),1)="D"))),IF(COUNTIF($Q74:$AB74,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD74">
+        <f>IF(AND($A74="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D74,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E74,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F74,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G74,"4.","")))=0)),IF(COUNTIF($Q74:$AC74,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE74">
+        <f>IF(AND($A74="Verdadero o Falso Complejas",COUNTIF($H74:$H74,"?*")&gt;0),IF(COUNTIF($Q74:$AD74,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF74">
+        <f>IF(AND($A74="Verdadero o Falso Complejas",TRIM($I74)&lt;&gt;"",NOT(OR(LEFT(TRIM($I74),1)="A",LEFT(TRIM($I74),1)="B",LEFT(TRIM($I74),1)="C",LEFT(TRIM($I74),1)="D",LEFT(TRIM($I74),1)="E"))),IF(COUNTIF($Q74:$AE74,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG74">
+        <f>IF(AND(OR($A74="Selección de la mejor respuesta",$A74="Subítem de caso o problema"),COUNTA($D74:$H74)&lt;5),IF(COUNTIF($Q74:$AF74,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH74">
+        <f>IF(AND(OR($A74="Selección de la mejor respuesta",$A74="Subítem de caso o problema"),TRIM($I74)&lt;&gt;"",NOT(OR(LEFT(TRIM($I74),1)="A",LEFT(TRIM($I74),1)="B",LEFT(TRIM($I74),1)="C",LEFT(TRIM($I74),1)="D",LEFT(TRIM($I74),1)="E"))),IF(COUNTIF($Q74:$AG74,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI74">
+        <f>IF(AND(OR($A74="Ítems agrupados por caso clínico o problema",$A74="Opción de Emparejamiento Ampliado"),COUNTIF($D74:$H74,"?*")&gt;0),IF(COUNTIF($Q74:$AH74,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ74">
+        <f>IF(AND($A74="Emparejamiento Ampliado",COUNTIF($D74:$H74,"?*")&lt;2),IF(COUNTIF($Q74:$AI74,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK74">
+        <f>IF(AND($A74="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I74),1)="A",LEFT(TRIM($I74),1)="B",LEFT(TRIM($I74),1)="C",LEFT(TRIM($I74),1)="D",LEFT(TRIM($I74),1)="E"))),IF(COUNTIF($Q74:$AJ74,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL74">
+        <f>IF(TRIM($K74)="",IF(COUNTIF($M74:$M74,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM74">
         <f>IF(AND(TRIM($K74)&lt;&gt;"",TRIM($K74)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M74:$N74,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="24" customHeight="1">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="371" t="n"/>
+      <c r="B75" s="371" t="n"/>
+      <c r="C75" s="371" t="n"/>
+      <c r="D75" s="371">
+        <f>IF($A75="Verdadero o Falso Simple","Verdadero",IF($A75="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A75="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E75" s="371">
+        <f>IF($A75="Verdadero o Falso Simple","Falso",IF($A75="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A75="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F75" s="371">
+        <f>IF($A75="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A75="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G75" s="371">
+        <f>IF($A75="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A75="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H75" s="371">
+        <f>IF($A75="Verdadero o Falso Simple","",IF($A75="Respuesta A/B/Ambas/Ninguna","",IF($A75="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I75" s="371" t="n"/>
+      <c r="J75" s="372" t="n"/>
+      <c r="K75" s="372">
+        <f>IF(TRIM($A75)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L75" s="371">
+        <f>IF(TRIM($A75)="","",IF(OR($A75="Selección de la mejor respuesta",$A75="SELECCION_MEJOR_RESPUESTA",$A75="Subítem de caso o problema",$A75="SUBITEM_CASO"),IF(TRIM($C75)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D75:$H75&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I75)&lt;&gt;"",OR(LEFT(TRIM($I75),1)="A",LEFT(TRIM($I75),1)="B",LEFT(TRIM($I75),1)="C",LEFT(TRIM($I75),1)="D",LEFT(TRIM($I75),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A75)="","",IF(COUNTIF($Q75:$AJ75,"?*")=0,"OK","Falta revisar: "&amp;$Q75&amp;$R75&amp;$S75&amp;$T75&amp;$U75&amp;$V75&amp;$W75&amp;$X75&amp;$Y75&amp;$Z75&amp;$AA75&amp;$AB75&amp;$AC75&amp;$AD75&amp;$AE75&amp;$AF75&amp;$AG75&amp;$AH75&amp;$AI75&amp;$AJ75))))</f>
+        <v/>
+      </c>
+      <c r="M75" s="373" t="n"/>
+      <c r="Q75">
+        <f>IF(TRIM($C75)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R75">
+        <f>IF(TRIM($K75)="",IF(COUNTIF($Q75:$Q75,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S75">
         <f>IF(AND(TRIM($K75)&lt;&gt;"",TRIM($K75)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q75:$R75,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T75">
+        <f>IF(AND(OR($A75="Ítems agrupados por caso clínico o problema",$A75="Subítem de caso o problema",$A75="Emparejamiento Ampliado",$A75="Opción de Emparejamiento Ampliado"),TRIM($B75)=""),IF(COUNTIF($Q75:$S75,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U75">
+        <f>IF(AND(OR($A75="Verdadero o Falso Simple",$A75="Respuesta A/B/Ambas/Ninguna",$A75="Verdadero o Falso Complejas",$A75="Selección de la mejor respuesta",$A75="Subítem de caso o problema",$A75="Opción de Emparejamiento Ampliado"),TRIM($I75)=""),IF(COUNTIF($Q75:$T75,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V75">
+        <f>IF(AND(OR($A75="Verdadero o Falso Simple",$A75="Respuesta A/B/Ambas/Ninguna",$A75="Verdadero o Falso Complejas",$A75="Selección de la mejor respuesta",$A75="Subítem de caso o problema",$A75="Opción de Emparejamiento Ampliado"),TRIM($J75)=""),IF(COUNTIF($Q75:$U75,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W75">
+        <f>IF(AND(OR($A75="Ítems agrupados por caso clínico o problema",$A75="Emparejamiento Ampliado"),TRIM($I75)&lt;&gt;""),IF(COUNTIF($Q75:$V75,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X75">
+        <f>IF(AND(OR($A75="Ítems agrupados por caso clínico o problema",$A75="Emparejamiento Ampliado"),TRIM($J75)&lt;&gt;""),IF(COUNTIF($Q75:$W75,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y75">
+        <f>IF(AND($A75="Verdadero o Falso Simple",OR(COUNTIF($D75:$E75,"?*")&lt;2,COUNTIF($F75:$H75,"?*")&gt;0)),IF(COUNTIF($Q75:$X75,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z75">
+        <f>IF(AND($A75="Verdadero o Falso Simple",TRIM($I75)&lt;&gt;"",NOT(OR(LEFT(TRIM($I75),1)="A",LEFT(TRIM($I75),1)="B"))),IF(COUNTIF($Q75:$Y75,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA75">
+        <f>IF(AND($A75="Respuesta A/B/Ambas/Ninguna",COUNTIF($D75:$G75,"?*")&lt;4),IF(COUNTIF($Q75:$Z75,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB75">
+        <f>IF(AND($A75="Respuesta A/B/Ambas/Ninguna",COUNTIF($H75:$H75,"?*")&gt;0),IF(COUNTIF($Q75:$AA75,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC75">
+        <f>IF(AND($A75="Respuesta A/B/Ambas/Ninguna",TRIM($I75)&lt;&gt;"",NOT(OR(LEFT(TRIM($I75),1)="A",LEFT(TRIM($I75),1)="B",LEFT(TRIM($I75),1)="C",LEFT(TRIM($I75),1)="D"))),IF(COUNTIF($Q75:$AB75,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD75">
+        <f>IF(AND($A75="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D75,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E75,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F75,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G75,"4.","")))=0)),IF(COUNTIF($Q75:$AC75,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE75">
+        <f>IF(AND($A75="Verdadero o Falso Complejas",COUNTIF($H75:$H75,"?*")&gt;0),IF(COUNTIF($Q75:$AD75,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF75">
+        <f>IF(AND($A75="Verdadero o Falso Complejas",TRIM($I75)&lt;&gt;"",NOT(OR(LEFT(TRIM($I75),1)="A",LEFT(TRIM($I75),1)="B",LEFT(TRIM($I75),1)="C",LEFT(TRIM($I75),1)="D",LEFT(TRIM($I75),1)="E"))),IF(COUNTIF($Q75:$AE75,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG75">
+        <f>IF(AND(OR($A75="Selección de la mejor respuesta",$A75="Subítem de caso o problema"),COUNTA($D75:$H75)&lt;5),IF(COUNTIF($Q75:$AF75,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH75">
+        <f>IF(AND(OR($A75="Selección de la mejor respuesta",$A75="Subítem de caso o problema"),TRIM($I75)&lt;&gt;"",NOT(OR(LEFT(TRIM($I75),1)="A",LEFT(TRIM($I75),1)="B",LEFT(TRIM($I75),1)="C",LEFT(TRIM($I75),1)="D",LEFT(TRIM($I75),1)="E"))),IF(COUNTIF($Q75:$AG75,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI75">
+        <f>IF(AND(OR($A75="Ítems agrupados por caso clínico o problema",$A75="Opción de Emparejamiento Ampliado"),COUNTIF($D75:$H75,"?*")&gt;0),IF(COUNTIF($Q75:$AH75,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ75">
+        <f>IF(AND($A75="Emparejamiento Ampliado",COUNTIF($D75:$H75,"?*")&lt;2),IF(COUNTIF($Q75:$AI75,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK75">
+        <f>IF(AND($A75="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I75),1)="A",LEFT(TRIM($I75),1)="B",LEFT(TRIM($I75),1)="C",LEFT(TRIM($I75),1)="D",LEFT(TRIM($I75),1)="E"))),IF(COUNTIF($Q75:$AJ75,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL75">
+        <f>IF(TRIM($K75)="",IF(COUNTIF($M75:$M75,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM75">
         <f>IF(AND(TRIM($K75)&lt;&gt;"",TRIM($K75)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M75:$N75,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="24" customHeight="1">
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="371" t="n"/>
+      <c r="B76" s="371" t="n"/>
+      <c r="C76" s="371" t="n"/>
+      <c r="D76" s="371">
+        <f>IF($A76="Verdadero o Falso Simple","Verdadero",IF($A76="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A76="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E76" s="371">
+        <f>IF($A76="Verdadero o Falso Simple","Falso",IF($A76="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A76="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F76" s="371">
+        <f>IF($A76="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A76="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G76" s="371">
+        <f>IF($A76="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A76="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H76" s="371">
+        <f>IF($A76="Verdadero o Falso Simple","",IF($A76="Respuesta A/B/Ambas/Ninguna","",IF($A76="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I76" s="371" t="n"/>
+      <c r="J76" s="372" t="n"/>
+      <c r="K76" s="372">
+        <f>IF(TRIM($A76)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L76" s="371">
+        <f>IF(TRIM($A76)="","",IF(OR($A76="Selección de la mejor respuesta",$A76="SELECCION_MEJOR_RESPUESTA",$A76="Subítem de caso o problema",$A76="SUBITEM_CASO"),IF(TRIM($C76)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D76:$H76&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I76)&lt;&gt;"",OR(LEFT(TRIM($I76),1)="A",LEFT(TRIM($I76),1)="B",LEFT(TRIM($I76),1)="C",LEFT(TRIM($I76),1)="D",LEFT(TRIM($I76),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A76)="","",IF(COUNTIF($Q76:$AJ76,"?*")=0,"OK","Falta revisar: "&amp;$Q76&amp;$R76&amp;$S76&amp;$T76&amp;$U76&amp;$V76&amp;$W76&amp;$X76&amp;$Y76&amp;$Z76&amp;$AA76&amp;$AB76&amp;$AC76&amp;$AD76&amp;$AE76&amp;$AF76&amp;$AG76&amp;$AH76&amp;$AI76&amp;$AJ76))))</f>
+        <v/>
+      </c>
+      <c r="M76" s="373" t="n"/>
+      <c r="Q76">
+        <f>IF(TRIM($C76)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R76">
+        <f>IF(TRIM($K76)="",IF(COUNTIF($Q76:$Q76,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S76">
         <f>IF(AND(TRIM($K76)&lt;&gt;"",TRIM($K76)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q76:$R76,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T76">
+        <f>IF(AND(OR($A76="Ítems agrupados por caso clínico o problema",$A76="Subítem de caso o problema",$A76="Emparejamiento Ampliado",$A76="Opción de Emparejamiento Ampliado"),TRIM($B76)=""),IF(COUNTIF($Q76:$S76,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U76">
+        <f>IF(AND(OR($A76="Verdadero o Falso Simple",$A76="Respuesta A/B/Ambas/Ninguna",$A76="Verdadero o Falso Complejas",$A76="Selección de la mejor respuesta",$A76="Subítem de caso o problema",$A76="Opción de Emparejamiento Ampliado"),TRIM($I76)=""),IF(COUNTIF($Q76:$T76,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V76">
+        <f>IF(AND(OR($A76="Verdadero o Falso Simple",$A76="Respuesta A/B/Ambas/Ninguna",$A76="Verdadero o Falso Complejas",$A76="Selección de la mejor respuesta",$A76="Subítem de caso o problema",$A76="Opción de Emparejamiento Ampliado"),TRIM($J76)=""),IF(COUNTIF($Q76:$U76,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W76">
+        <f>IF(AND(OR($A76="Ítems agrupados por caso clínico o problema",$A76="Emparejamiento Ampliado"),TRIM($I76)&lt;&gt;""),IF(COUNTIF($Q76:$V76,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X76">
+        <f>IF(AND(OR($A76="Ítems agrupados por caso clínico o problema",$A76="Emparejamiento Ampliado"),TRIM($J76)&lt;&gt;""),IF(COUNTIF($Q76:$W76,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y76">
+        <f>IF(AND($A76="Verdadero o Falso Simple",OR(COUNTIF($D76:$E76,"?*")&lt;2,COUNTIF($F76:$H76,"?*")&gt;0)),IF(COUNTIF($Q76:$X76,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z76">
+        <f>IF(AND($A76="Verdadero o Falso Simple",TRIM($I76)&lt;&gt;"",NOT(OR(LEFT(TRIM($I76),1)="A",LEFT(TRIM($I76),1)="B"))),IF(COUNTIF($Q76:$Y76,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA76">
+        <f>IF(AND($A76="Respuesta A/B/Ambas/Ninguna",COUNTIF($D76:$G76,"?*")&lt;4),IF(COUNTIF($Q76:$Z76,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB76">
+        <f>IF(AND($A76="Respuesta A/B/Ambas/Ninguna",COUNTIF($H76:$H76,"?*")&gt;0),IF(COUNTIF($Q76:$AA76,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC76">
+        <f>IF(AND($A76="Respuesta A/B/Ambas/Ninguna",TRIM($I76)&lt;&gt;"",NOT(OR(LEFT(TRIM($I76),1)="A",LEFT(TRIM($I76),1)="B",LEFT(TRIM($I76),1)="C",LEFT(TRIM($I76),1)="D"))),IF(COUNTIF($Q76:$AB76,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD76">
+        <f>IF(AND($A76="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D76,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E76,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F76,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G76,"4.","")))=0)),IF(COUNTIF($Q76:$AC76,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE76">
+        <f>IF(AND($A76="Verdadero o Falso Complejas",COUNTIF($H76:$H76,"?*")&gt;0),IF(COUNTIF($Q76:$AD76,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF76">
+        <f>IF(AND($A76="Verdadero o Falso Complejas",TRIM($I76)&lt;&gt;"",NOT(OR(LEFT(TRIM($I76),1)="A",LEFT(TRIM($I76),1)="B",LEFT(TRIM($I76),1)="C",LEFT(TRIM($I76),1)="D",LEFT(TRIM($I76),1)="E"))),IF(COUNTIF($Q76:$AE76,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG76">
+        <f>IF(AND(OR($A76="Selección de la mejor respuesta",$A76="Subítem de caso o problema"),COUNTA($D76:$H76)&lt;5),IF(COUNTIF($Q76:$AF76,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH76">
+        <f>IF(AND(OR($A76="Selección de la mejor respuesta",$A76="Subítem de caso o problema"),TRIM($I76)&lt;&gt;"",NOT(OR(LEFT(TRIM($I76),1)="A",LEFT(TRIM($I76),1)="B",LEFT(TRIM($I76),1)="C",LEFT(TRIM($I76),1)="D",LEFT(TRIM($I76),1)="E"))),IF(COUNTIF($Q76:$AG76,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI76">
+        <f>IF(AND(OR($A76="Ítems agrupados por caso clínico o problema",$A76="Opción de Emparejamiento Ampliado"),COUNTIF($D76:$H76,"?*")&gt;0),IF(COUNTIF($Q76:$AH76,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ76">
+        <f>IF(AND($A76="Emparejamiento Ampliado",COUNTIF($D76:$H76,"?*")&lt;2),IF(COUNTIF($Q76:$AI76,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK76">
+        <f>IF(AND($A76="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I76),1)="A",LEFT(TRIM($I76),1)="B",LEFT(TRIM($I76),1)="C",LEFT(TRIM($I76),1)="D",LEFT(TRIM($I76),1)="E"))),IF(COUNTIF($Q76:$AJ76,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL76">
+        <f>IF(TRIM($K76)="",IF(COUNTIF($M76:$M76,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM76">
         <f>IF(AND(TRIM($K76)&lt;&gt;"",TRIM($K76)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M76:$N76,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="77" ht="24" customHeight="1">
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="371" t="n"/>
+      <c r="B77" s="371" t="n"/>
+      <c r="C77" s="371" t="n"/>
+      <c r="D77" s="371">
+        <f>IF($A77="Verdadero o Falso Simple","Verdadero",IF($A77="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A77="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E77" s="371">
+        <f>IF($A77="Verdadero o Falso Simple","Falso",IF($A77="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A77="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F77" s="371">
+        <f>IF($A77="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A77="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G77" s="371">
+        <f>IF($A77="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A77="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H77" s="371">
+        <f>IF($A77="Verdadero o Falso Simple","",IF($A77="Respuesta A/B/Ambas/Ninguna","",IF($A77="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I77" s="371" t="n"/>
+      <c r="J77" s="372" t="n"/>
+      <c r="K77" s="372">
+        <f>IF(TRIM($A77)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L77" s="371">
+        <f>IF(TRIM($A77)="","",IF(OR($A77="Selección de la mejor respuesta",$A77="SELECCION_MEJOR_RESPUESTA",$A77="Subítem de caso o problema",$A77="SUBITEM_CASO"),IF(TRIM($C77)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D77:$H77&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I77)&lt;&gt;"",OR(LEFT(TRIM($I77),1)="A",LEFT(TRIM($I77),1)="B",LEFT(TRIM($I77),1)="C",LEFT(TRIM($I77),1)="D",LEFT(TRIM($I77),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A77)="","",IF(COUNTIF($Q77:$AJ77,"?*")=0,"OK","Falta revisar: "&amp;$Q77&amp;$R77&amp;$S77&amp;$T77&amp;$U77&amp;$V77&amp;$W77&amp;$X77&amp;$Y77&amp;$Z77&amp;$AA77&amp;$AB77&amp;$AC77&amp;$AD77&amp;$AE77&amp;$AF77&amp;$AG77&amp;$AH77&amp;$AI77&amp;$AJ77))))</f>
+        <v/>
+      </c>
+      <c r="M77" s="373" t="n"/>
+      <c r="Q77">
+        <f>IF(TRIM($C77)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R77">
+        <f>IF(TRIM($K77)="",IF(COUNTIF($Q77:$Q77,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S77">
         <f>IF(AND(TRIM($K77)&lt;&gt;"",TRIM($K77)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q77:$R77,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T77">
+        <f>IF(AND(OR($A77="Ítems agrupados por caso clínico o problema",$A77="Subítem de caso o problema",$A77="Emparejamiento Ampliado",$A77="Opción de Emparejamiento Ampliado"),TRIM($B77)=""),IF(COUNTIF($Q77:$S77,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U77">
+        <f>IF(AND(OR($A77="Verdadero o Falso Simple",$A77="Respuesta A/B/Ambas/Ninguna",$A77="Verdadero o Falso Complejas",$A77="Selección de la mejor respuesta",$A77="Subítem de caso o problema",$A77="Opción de Emparejamiento Ampliado"),TRIM($I77)=""),IF(COUNTIF($Q77:$T77,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V77">
+        <f>IF(AND(OR($A77="Verdadero o Falso Simple",$A77="Respuesta A/B/Ambas/Ninguna",$A77="Verdadero o Falso Complejas",$A77="Selección de la mejor respuesta",$A77="Subítem de caso o problema",$A77="Opción de Emparejamiento Ampliado"),TRIM($J77)=""),IF(COUNTIF($Q77:$U77,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W77">
+        <f>IF(AND(OR($A77="Ítems agrupados por caso clínico o problema",$A77="Emparejamiento Ampliado"),TRIM($I77)&lt;&gt;""),IF(COUNTIF($Q77:$V77,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X77">
+        <f>IF(AND(OR($A77="Ítems agrupados por caso clínico o problema",$A77="Emparejamiento Ampliado"),TRIM($J77)&lt;&gt;""),IF(COUNTIF($Q77:$W77,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y77">
+        <f>IF(AND($A77="Verdadero o Falso Simple",OR(COUNTIF($D77:$E77,"?*")&lt;2,COUNTIF($F77:$H77,"?*")&gt;0)),IF(COUNTIF($Q77:$X77,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z77">
+        <f>IF(AND($A77="Verdadero o Falso Simple",TRIM($I77)&lt;&gt;"",NOT(OR(LEFT(TRIM($I77),1)="A",LEFT(TRIM($I77),1)="B"))),IF(COUNTIF($Q77:$Y77,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA77">
+        <f>IF(AND($A77="Respuesta A/B/Ambas/Ninguna",COUNTIF($D77:$G77,"?*")&lt;4),IF(COUNTIF($Q77:$Z77,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB77">
+        <f>IF(AND($A77="Respuesta A/B/Ambas/Ninguna",COUNTIF($H77:$H77,"?*")&gt;0),IF(COUNTIF($Q77:$AA77,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC77">
+        <f>IF(AND($A77="Respuesta A/B/Ambas/Ninguna",TRIM($I77)&lt;&gt;"",NOT(OR(LEFT(TRIM($I77),1)="A",LEFT(TRIM($I77),1)="B",LEFT(TRIM($I77),1)="C",LEFT(TRIM($I77),1)="D"))),IF(COUNTIF($Q77:$AB77,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD77">
+        <f>IF(AND($A77="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D77,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E77,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F77,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G77,"4.","")))=0)),IF(COUNTIF($Q77:$AC77,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE77">
+        <f>IF(AND($A77="Verdadero o Falso Complejas",COUNTIF($H77:$H77,"?*")&gt;0),IF(COUNTIF($Q77:$AD77,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF77">
+        <f>IF(AND($A77="Verdadero o Falso Complejas",TRIM($I77)&lt;&gt;"",NOT(OR(LEFT(TRIM($I77),1)="A",LEFT(TRIM($I77),1)="B",LEFT(TRIM($I77),1)="C",LEFT(TRIM($I77),1)="D",LEFT(TRIM($I77),1)="E"))),IF(COUNTIF($Q77:$AE77,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG77">
+        <f>IF(AND(OR($A77="Selección de la mejor respuesta",$A77="Subítem de caso o problema"),COUNTA($D77:$H77)&lt;5),IF(COUNTIF($Q77:$AF77,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH77">
+        <f>IF(AND(OR($A77="Selección de la mejor respuesta",$A77="Subítem de caso o problema"),TRIM($I77)&lt;&gt;"",NOT(OR(LEFT(TRIM($I77),1)="A",LEFT(TRIM($I77),1)="B",LEFT(TRIM($I77),1)="C",LEFT(TRIM($I77),1)="D",LEFT(TRIM($I77),1)="E"))),IF(COUNTIF($Q77:$AG77,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI77">
+        <f>IF(AND(OR($A77="Ítems agrupados por caso clínico o problema",$A77="Opción de Emparejamiento Ampliado"),COUNTIF($D77:$H77,"?*")&gt;0),IF(COUNTIF($Q77:$AH77,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ77">
+        <f>IF(AND($A77="Emparejamiento Ampliado",COUNTIF($D77:$H77,"?*")&lt;2),IF(COUNTIF($Q77:$AI77,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK77">
+        <f>IF(AND($A77="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I77),1)="A",LEFT(TRIM($I77),1)="B",LEFT(TRIM($I77),1)="C",LEFT(TRIM($I77),1)="D",LEFT(TRIM($I77),1)="E"))),IF(COUNTIF($Q77:$AJ77,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL77">
+        <f>IF(TRIM($K77)="",IF(COUNTIF($M77:$M77,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM77">
         <f>IF(AND(TRIM($K77)&lt;&gt;"",TRIM($K77)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M77:$N77,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="78" ht="24" customHeight="1">
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="371" t="n"/>
+      <c r="B78" s="371" t="n"/>
+      <c r="C78" s="371" t="n"/>
+      <c r="D78" s="371">
+        <f>IF($A78="Verdadero o Falso Simple","Verdadero",IF($A78="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A78="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E78" s="371">
+        <f>IF($A78="Verdadero o Falso Simple","Falso",IF($A78="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A78="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F78" s="371">
+        <f>IF($A78="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A78="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G78" s="371">
+        <f>IF($A78="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A78="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H78" s="371">
+        <f>IF($A78="Verdadero o Falso Simple","",IF($A78="Respuesta A/B/Ambas/Ninguna","",IF($A78="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I78" s="371" t="n"/>
+      <c r="J78" s="372" t="n"/>
+      <c r="K78" s="372">
+        <f>IF(TRIM($A78)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L78" s="371">
+        <f>IF(TRIM($A78)="","",IF(OR($A78="Selección de la mejor respuesta",$A78="SELECCION_MEJOR_RESPUESTA",$A78="Subítem de caso o problema",$A78="SUBITEM_CASO"),IF(TRIM($C78)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D78:$H78&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I78)&lt;&gt;"",OR(LEFT(TRIM($I78),1)="A",LEFT(TRIM($I78),1)="B",LEFT(TRIM($I78),1)="C",LEFT(TRIM($I78),1)="D",LEFT(TRIM($I78),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A78)="","",IF(COUNTIF($Q78:$AJ78,"?*")=0,"OK","Falta revisar: "&amp;$Q78&amp;$R78&amp;$S78&amp;$T78&amp;$U78&amp;$V78&amp;$W78&amp;$X78&amp;$Y78&amp;$Z78&amp;$AA78&amp;$AB78&amp;$AC78&amp;$AD78&amp;$AE78&amp;$AF78&amp;$AG78&amp;$AH78&amp;$AI78&amp;$AJ78))))</f>
+        <v/>
+      </c>
+      <c r="M78" s="373" t="n"/>
+      <c r="Q78">
+        <f>IF(TRIM($C78)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R78">
+        <f>IF(TRIM($K78)="",IF(COUNTIF($Q78:$Q78,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S78">
         <f>IF(AND(TRIM($K78)&lt;&gt;"",TRIM($K78)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q78:$R78,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T78">
+        <f>IF(AND(OR($A78="Ítems agrupados por caso clínico o problema",$A78="Subítem de caso o problema",$A78="Emparejamiento Ampliado",$A78="Opción de Emparejamiento Ampliado"),TRIM($B78)=""),IF(COUNTIF($Q78:$S78,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U78">
+        <f>IF(AND(OR($A78="Verdadero o Falso Simple",$A78="Respuesta A/B/Ambas/Ninguna",$A78="Verdadero o Falso Complejas",$A78="Selección de la mejor respuesta",$A78="Subítem de caso o problema",$A78="Opción de Emparejamiento Ampliado"),TRIM($I78)=""),IF(COUNTIF($Q78:$T78,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V78">
+        <f>IF(AND(OR($A78="Verdadero o Falso Simple",$A78="Respuesta A/B/Ambas/Ninguna",$A78="Verdadero o Falso Complejas",$A78="Selección de la mejor respuesta",$A78="Subítem de caso o problema",$A78="Opción de Emparejamiento Ampliado"),TRIM($J78)=""),IF(COUNTIF($Q78:$U78,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W78">
+        <f>IF(AND(OR($A78="Ítems agrupados por caso clínico o problema",$A78="Emparejamiento Ampliado"),TRIM($I78)&lt;&gt;""),IF(COUNTIF($Q78:$V78,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X78">
+        <f>IF(AND(OR($A78="Ítems agrupados por caso clínico o problema",$A78="Emparejamiento Ampliado"),TRIM($J78)&lt;&gt;""),IF(COUNTIF($Q78:$W78,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y78">
+        <f>IF(AND($A78="Verdadero o Falso Simple",OR(COUNTIF($D78:$E78,"?*")&lt;2,COUNTIF($F78:$H78,"?*")&gt;0)),IF(COUNTIF($Q78:$X78,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z78">
+        <f>IF(AND($A78="Verdadero o Falso Simple",TRIM($I78)&lt;&gt;"",NOT(OR(LEFT(TRIM($I78),1)="A",LEFT(TRIM($I78),1)="B"))),IF(COUNTIF($Q78:$Y78,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA78">
+        <f>IF(AND($A78="Respuesta A/B/Ambas/Ninguna",COUNTIF($D78:$G78,"?*")&lt;4),IF(COUNTIF($Q78:$Z78,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB78">
+        <f>IF(AND($A78="Respuesta A/B/Ambas/Ninguna",COUNTIF($H78:$H78,"?*")&gt;0),IF(COUNTIF($Q78:$AA78,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC78">
+        <f>IF(AND($A78="Respuesta A/B/Ambas/Ninguna",TRIM($I78)&lt;&gt;"",NOT(OR(LEFT(TRIM($I78),1)="A",LEFT(TRIM($I78),1)="B",LEFT(TRIM($I78),1)="C",LEFT(TRIM($I78),1)="D"))),IF(COUNTIF($Q78:$AB78,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD78">
+        <f>IF(AND($A78="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D78,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E78,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F78,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G78,"4.","")))=0)),IF(COUNTIF($Q78:$AC78,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE78">
+        <f>IF(AND($A78="Verdadero o Falso Complejas",COUNTIF($H78:$H78,"?*")&gt;0),IF(COUNTIF($Q78:$AD78,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF78">
+        <f>IF(AND($A78="Verdadero o Falso Complejas",TRIM($I78)&lt;&gt;"",NOT(OR(LEFT(TRIM($I78),1)="A",LEFT(TRIM($I78),1)="B",LEFT(TRIM($I78),1)="C",LEFT(TRIM($I78),1)="D",LEFT(TRIM($I78),1)="E"))),IF(COUNTIF($Q78:$AE78,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG78">
+        <f>IF(AND(OR($A78="Selección de la mejor respuesta",$A78="Subítem de caso o problema"),COUNTA($D78:$H78)&lt;5),IF(COUNTIF($Q78:$AF78,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH78">
+        <f>IF(AND(OR($A78="Selección de la mejor respuesta",$A78="Subítem de caso o problema"),TRIM($I78)&lt;&gt;"",NOT(OR(LEFT(TRIM($I78),1)="A",LEFT(TRIM($I78),1)="B",LEFT(TRIM($I78),1)="C",LEFT(TRIM($I78),1)="D",LEFT(TRIM($I78),1)="E"))),IF(COUNTIF($Q78:$AG78,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI78">
+        <f>IF(AND(OR($A78="Ítems agrupados por caso clínico o problema",$A78="Opción de Emparejamiento Ampliado"),COUNTIF($D78:$H78,"?*")&gt;0),IF(COUNTIF($Q78:$AH78,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ78">
+        <f>IF(AND($A78="Emparejamiento Ampliado",COUNTIF($D78:$H78,"?*")&lt;2),IF(COUNTIF($Q78:$AI78,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK78">
+        <f>IF(AND($A78="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I78),1)="A",LEFT(TRIM($I78),1)="B",LEFT(TRIM($I78),1)="C",LEFT(TRIM($I78),1)="D",LEFT(TRIM($I78),1)="E"))),IF(COUNTIF($Q78:$AJ78,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL78">
+        <f>IF(TRIM($K78)="",IF(COUNTIF($M78:$M78,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM78">
         <f>IF(AND(TRIM($K78)&lt;&gt;"",TRIM($K78)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M78:$N78,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="79" ht="24" customHeight="1">
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="371" t="n"/>
+      <c r="B79" s="371" t="n"/>
+      <c r="C79" s="371" t="n"/>
+      <c r="D79" s="371">
+        <f>IF($A79="Verdadero o Falso Simple","Verdadero",IF($A79="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A79="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E79" s="371">
+        <f>IF($A79="Verdadero o Falso Simple","Falso",IF($A79="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A79="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F79" s="371">
+        <f>IF($A79="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A79="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G79" s="371">
+        <f>IF($A79="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A79="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H79" s="371">
+        <f>IF($A79="Verdadero o Falso Simple","",IF($A79="Respuesta A/B/Ambas/Ninguna","",IF($A79="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="371" t="n"/>
+      <c r="J79" s="372" t="n"/>
+      <c r="K79" s="372">
+        <f>IF(TRIM($A79)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L79" s="371">
+        <f>IF(TRIM($A79)="","",IF(OR($A79="Selección de la mejor respuesta",$A79="SELECCION_MEJOR_RESPUESTA",$A79="Subítem de caso o problema",$A79="SUBITEM_CASO"),IF(TRIM($C79)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D79:$H79&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I79)&lt;&gt;"",OR(LEFT(TRIM($I79),1)="A",LEFT(TRIM($I79),1)="B",LEFT(TRIM($I79),1)="C",LEFT(TRIM($I79),1)="D",LEFT(TRIM($I79),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A79)="","",IF(COUNTIF($Q79:$AJ79,"?*")=0,"OK","Falta revisar: "&amp;$Q79&amp;$R79&amp;$S79&amp;$T79&amp;$U79&amp;$V79&amp;$W79&amp;$X79&amp;$Y79&amp;$Z79&amp;$AA79&amp;$AB79&amp;$AC79&amp;$AD79&amp;$AE79&amp;$AF79&amp;$AG79&amp;$AH79&amp;$AI79&amp;$AJ79))))</f>
+        <v/>
+      </c>
+      <c r="M79" s="373" t="n"/>
+      <c r="Q79">
+        <f>IF(TRIM($C79)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R79">
+        <f>IF(TRIM($K79)="",IF(COUNTIF($Q79:$Q79,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S79">
         <f>IF(AND(TRIM($K79)&lt;&gt;"",TRIM($K79)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q79:$R79,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T79">
+        <f>IF(AND(OR($A79="Ítems agrupados por caso clínico o problema",$A79="Subítem de caso o problema",$A79="Emparejamiento Ampliado",$A79="Opción de Emparejamiento Ampliado"),TRIM($B79)=""),IF(COUNTIF($Q79:$S79,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U79">
+        <f>IF(AND(OR($A79="Verdadero o Falso Simple",$A79="Respuesta A/B/Ambas/Ninguna",$A79="Verdadero o Falso Complejas",$A79="Selección de la mejor respuesta",$A79="Subítem de caso o problema",$A79="Opción de Emparejamiento Ampliado"),TRIM($I79)=""),IF(COUNTIF($Q79:$T79,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V79">
+        <f>IF(AND(OR($A79="Verdadero o Falso Simple",$A79="Respuesta A/B/Ambas/Ninguna",$A79="Verdadero o Falso Complejas",$A79="Selección de la mejor respuesta",$A79="Subítem de caso o problema",$A79="Opción de Emparejamiento Ampliado"),TRIM($J79)=""),IF(COUNTIF($Q79:$U79,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W79">
+        <f>IF(AND(OR($A79="Ítems agrupados por caso clínico o problema",$A79="Emparejamiento Ampliado"),TRIM($I79)&lt;&gt;""),IF(COUNTIF($Q79:$V79,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X79">
+        <f>IF(AND(OR($A79="Ítems agrupados por caso clínico o problema",$A79="Emparejamiento Ampliado"),TRIM($J79)&lt;&gt;""),IF(COUNTIF($Q79:$W79,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y79">
+        <f>IF(AND($A79="Verdadero o Falso Simple",OR(COUNTIF($D79:$E79,"?*")&lt;2,COUNTIF($F79:$H79,"?*")&gt;0)),IF(COUNTIF($Q79:$X79,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z79">
+        <f>IF(AND($A79="Verdadero o Falso Simple",TRIM($I79)&lt;&gt;"",NOT(OR(LEFT(TRIM($I79),1)="A",LEFT(TRIM($I79),1)="B"))),IF(COUNTIF($Q79:$Y79,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA79">
+        <f>IF(AND($A79="Respuesta A/B/Ambas/Ninguna",COUNTIF($D79:$G79,"?*")&lt;4),IF(COUNTIF($Q79:$Z79,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB79">
+        <f>IF(AND($A79="Respuesta A/B/Ambas/Ninguna",COUNTIF($H79:$H79,"?*")&gt;0),IF(COUNTIF($Q79:$AA79,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC79">
+        <f>IF(AND($A79="Respuesta A/B/Ambas/Ninguna",TRIM($I79)&lt;&gt;"",NOT(OR(LEFT(TRIM($I79),1)="A",LEFT(TRIM($I79),1)="B",LEFT(TRIM($I79),1)="C",LEFT(TRIM($I79),1)="D"))),IF(COUNTIF($Q79:$AB79,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD79">
+        <f>IF(AND($A79="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D79,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E79,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F79,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G79,"4.","")))=0)),IF(COUNTIF($Q79:$AC79,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE79">
+        <f>IF(AND($A79="Verdadero o Falso Complejas",COUNTIF($H79:$H79,"?*")&gt;0),IF(COUNTIF($Q79:$AD79,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF79">
+        <f>IF(AND($A79="Verdadero o Falso Complejas",TRIM($I79)&lt;&gt;"",NOT(OR(LEFT(TRIM($I79),1)="A",LEFT(TRIM($I79),1)="B",LEFT(TRIM($I79),1)="C",LEFT(TRIM($I79),1)="D",LEFT(TRIM($I79),1)="E"))),IF(COUNTIF($Q79:$AE79,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG79">
+        <f>IF(AND(OR($A79="Selección de la mejor respuesta",$A79="Subítem de caso o problema"),COUNTA($D79:$H79)&lt;5),IF(COUNTIF($Q79:$AF79,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH79">
+        <f>IF(AND(OR($A79="Selección de la mejor respuesta",$A79="Subítem de caso o problema"),TRIM($I79)&lt;&gt;"",NOT(OR(LEFT(TRIM($I79),1)="A",LEFT(TRIM($I79),1)="B",LEFT(TRIM($I79),1)="C",LEFT(TRIM($I79),1)="D",LEFT(TRIM($I79),1)="E"))),IF(COUNTIF($Q79:$AG79,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI79">
+        <f>IF(AND(OR($A79="Ítems agrupados por caso clínico o problema",$A79="Opción de Emparejamiento Ampliado"),COUNTIF($D79:$H79,"?*")&gt;0),IF(COUNTIF($Q79:$AH79,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ79">
+        <f>IF(AND($A79="Emparejamiento Ampliado",COUNTIF($D79:$H79,"?*")&lt;2),IF(COUNTIF($Q79:$AI79,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK79">
+        <f>IF(AND($A79="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I79),1)="A",LEFT(TRIM($I79),1)="B",LEFT(TRIM($I79),1)="C",LEFT(TRIM($I79),1)="D",LEFT(TRIM($I79),1)="E"))),IF(COUNTIF($Q79:$AJ79,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL79">
+        <f>IF(TRIM($K79)="",IF(COUNTIF($M79:$M79,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM79">
         <f>IF(AND(TRIM($K79)&lt;&gt;"",TRIM($K79)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M79:$N79,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="24" customHeight="1">
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="371" t="n"/>
+      <c r="B80" s="371" t="n"/>
+      <c r="C80" s="371" t="n"/>
+      <c r="D80" s="371">
+        <f>IF($A80="Verdadero o Falso Simple","Verdadero",IF($A80="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A80="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E80" s="371">
+        <f>IF($A80="Verdadero o Falso Simple","Falso",IF($A80="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A80="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F80" s="371">
+        <f>IF($A80="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A80="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G80" s="371">
+        <f>IF($A80="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A80="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H80" s="371">
+        <f>IF($A80="Verdadero o Falso Simple","",IF($A80="Respuesta A/B/Ambas/Ninguna","",IF($A80="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I80" s="371" t="n"/>
+      <c r="J80" s="372" t="n"/>
+      <c r="K80" s="372">
+        <f>IF(TRIM($A80)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L80" s="371">
+        <f>IF(TRIM($A80)="","",IF(OR($A80="Selección de la mejor respuesta",$A80="SELECCION_MEJOR_RESPUESTA",$A80="Subítem de caso o problema",$A80="SUBITEM_CASO"),IF(TRIM($C80)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D80:$H80&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I80)&lt;&gt;"",OR(LEFT(TRIM($I80),1)="A",LEFT(TRIM($I80),1)="B",LEFT(TRIM($I80),1)="C",LEFT(TRIM($I80),1)="D",LEFT(TRIM($I80),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A80)="","",IF(COUNTIF($Q80:$AJ80,"?*")=0,"OK","Falta revisar: "&amp;$Q80&amp;$R80&amp;$S80&amp;$T80&amp;$U80&amp;$V80&amp;$W80&amp;$X80&amp;$Y80&amp;$Z80&amp;$AA80&amp;$AB80&amp;$AC80&amp;$AD80&amp;$AE80&amp;$AF80&amp;$AG80&amp;$AH80&amp;$AI80&amp;$AJ80))))</f>
+        <v/>
+      </c>
+      <c r="M80" s="373" t="n"/>
+      <c r="Q80">
+        <f>IF(TRIM($C80)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R80">
+        <f>IF(TRIM($K80)="",IF(COUNTIF($Q80:$Q80,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S80">
         <f>IF(AND(TRIM($K80)&lt;&gt;"",TRIM($K80)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q80:$R80,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T80">
+        <f>IF(AND(OR($A80="Ítems agrupados por caso clínico o problema",$A80="Subítem de caso o problema",$A80="Emparejamiento Ampliado",$A80="Opción de Emparejamiento Ampliado"),TRIM($B80)=""),IF(COUNTIF($Q80:$S80,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U80">
+        <f>IF(AND(OR($A80="Verdadero o Falso Simple",$A80="Respuesta A/B/Ambas/Ninguna",$A80="Verdadero o Falso Complejas",$A80="Selección de la mejor respuesta",$A80="Subítem de caso o problema",$A80="Opción de Emparejamiento Ampliado"),TRIM($I80)=""),IF(COUNTIF($Q80:$T80,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V80">
+        <f>IF(AND(OR($A80="Verdadero o Falso Simple",$A80="Respuesta A/B/Ambas/Ninguna",$A80="Verdadero o Falso Complejas",$A80="Selección de la mejor respuesta",$A80="Subítem de caso o problema",$A80="Opción de Emparejamiento Ampliado"),TRIM($J80)=""),IF(COUNTIF($Q80:$U80,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W80">
+        <f>IF(AND(OR($A80="Ítems agrupados por caso clínico o problema",$A80="Emparejamiento Ampliado"),TRIM($I80)&lt;&gt;""),IF(COUNTIF($Q80:$V80,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X80">
+        <f>IF(AND(OR($A80="Ítems agrupados por caso clínico o problema",$A80="Emparejamiento Ampliado"),TRIM($J80)&lt;&gt;""),IF(COUNTIF($Q80:$W80,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y80">
+        <f>IF(AND($A80="Verdadero o Falso Simple",OR(COUNTIF($D80:$E80,"?*")&lt;2,COUNTIF($F80:$H80,"?*")&gt;0)),IF(COUNTIF($Q80:$X80,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z80">
+        <f>IF(AND($A80="Verdadero o Falso Simple",TRIM($I80)&lt;&gt;"",NOT(OR(LEFT(TRIM($I80),1)="A",LEFT(TRIM($I80),1)="B"))),IF(COUNTIF($Q80:$Y80,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA80">
+        <f>IF(AND($A80="Respuesta A/B/Ambas/Ninguna",COUNTIF($D80:$G80,"?*")&lt;4),IF(COUNTIF($Q80:$Z80,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB80">
+        <f>IF(AND($A80="Respuesta A/B/Ambas/Ninguna",COUNTIF($H80:$H80,"?*")&gt;0),IF(COUNTIF($Q80:$AA80,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC80">
+        <f>IF(AND($A80="Respuesta A/B/Ambas/Ninguna",TRIM($I80)&lt;&gt;"",NOT(OR(LEFT(TRIM($I80),1)="A",LEFT(TRIM($I80),1)="B",LEFT(TRIM($I80),1)="C",LEFT(TRIM($I80),1)="D"))),IF(COUNTIF($Q80:$AB80,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD80">
+        <f>IF(AND($A80="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D80,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E80,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F80,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G80,"4.","")))=0)),IF(COUNTIF($Q80:$AC80,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE80">
+        <f>IF(AND($A80="Verdadero o Falso Complejas",COUNTIF($H80:$H80,"?*")&gt;0),IF(COUNTIF($Q80:$AD80,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF80">
+        <f>IF(AND($A80="Verdadero o Falso Complejas",TRIM($I80)&lt;&gt;"",NOT(OR(LEFT(TRIM($I80),1)="A",LEFT(TRIM($I80),1)="B",LEFT(TRIM($I80),1)="C",LEFT(TRIM($I80),1)="D",LEFT(TRIM($I80),1)="E"))),IF(COUNTIF($Q80:$AE80,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG80">
+        <f>IF(AND(OR($A80="Selección de la mejor respuesta",$A80="Subítem de caso o problema"),COUNTA($D80:$H80)&lt;5),IF(COUNTIF($Q80:$AF80,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH80">
+        <f>IF(AND(OR($A80="Selección de la mejor respuesta",$A80="Subítem de caso o problema"),TRIM($I80)&lt;&gt;"",NOT(OR(LEFT(TRIM($I80),1)="A",LEFT(TRIM($I80),1)="B",LEFT(TRIM($I80),1)="C",LEFT(TRIM($I80),1)="D",LEFT(TRIM($I80),1)="E"))),IF(COUNTIF($Q80:$AG80,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI80">
+        <f>IF(AND(OR($A80="Ítems agrupados por caso clínico o problema",$A80="Opción de Emparejamiento Ampliado"),COUNTIF($D80:$H80,"?*")&gt;0),IF(COUNTIF($Q80:$AH80,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ80">
+        <f>IF(AND($A80="Emparejamiento Ampliado",COUNTIF($D80:$H80,"?*")&lt;2),IF(COUNTIF($Q80:$AI80,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK80">
+        <f>IF(AND($A80="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I80),1)="A",LEFT(TRIM($I80),1)="B",LEFT(TRIM($I80),1)="C",LEFT(TRIM($I80),1)="D",LEFT(TRIM($I80),1)="E"))),IF(COUNTIF($Q80:$AJ80,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL80">
+        <f>IF(TRIM($K80)="",IF(COUNTIF($M80:$M80,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM80">
         <f>IF(AND(TRIM($K80)&lt;&gt;"",TRIM($K80)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M80:$N80,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="24" customHeight="1">
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="371" t="n"/>
+      <c r="B81" s="371" t="n"/>
+      <c r="C81" s="371" t="n"/>
+      <c r="D81" s="371">
+        <f>IF($A81="Verdadero o Falso Simple","Verdadero",IF($A81="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A81="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E81" s="371">
+        <f>IF($A81="Verdadero o Falso Simple","Falso",IF($A81="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A81="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F81" s="371">
+        <f>IF($A81="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A81="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G81" s="371">
+        <f>IF($A81="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A81="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H81" s="371">
+        <f>IF($A81="Verdadero o Falso Simple","",IF($A81="Respuesta A/B/Ambas/Ninguna","",IF($A81="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I81" s="371" t="n"/>
+      <c r="J81" s="372" t="n"/>
+      <c r="K81" s="372">
+        <f>IF(TRIM($A81)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L81" s="371">
+        <f>IF(TRIM($A81)="","",IF(OR($A81="Selección de la mejor respuesta",$A81="SELECCION_MEJOR_RESPUESTA",$A81="Subítem de caso o problema",$A81="SUBITEM_CASO"),IF(TRIM($C81)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D81:$H81&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I81)&lt;&gt;"",OR(LEFT(TRIM($I81),1)="A",LEFT(TRIM($I81),1)="B",LEFT(TRIM($I81),1)="C",LEFT(TRIM($I81),1)="D",LEFT(TRIM($I81),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A81)="","",IF(COUNTIF($Q81:$AJ81,"?*")=0,"OK","Falta revisar: "&amp;$Q81&amp;$R81&amp;$S81&amp;$T81&amp;$U81&amp;$V81&amp;$W81&amp;$X81&amp;$Y81&amp;$Z81&amp;$AA81&amp;$AB81&amp;$AC81&amp;$AD81&amp;$AE81&amp;$AF81&amp;$AG81&amp;$AH81&amp;$AI81&amp;$AJ81))))</f>
+        <v/>
+      </c>
+      <c r="M81" s="373" t="n"/>
+      <c r="Q81">
+        <f>IF(TRIM($C81)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R81">
+        <f>IF(TRIM($K81)="",IF(COUNTIF($Q81:$Q81,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S81">
         <f>IF(AND(TRIM($K81)&lt;&gt;"",TRIM($K81)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q81:$R81,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T81">
+        <f>IF(AND(OR($A81="Ítems agrupados por caso clínico o problema",$A81="Subítem de caso o problema",$A81="Emparejamiento Ampliado",$A81="Opción de Emparejamiento Ampliado"),TRIM($B81)=""),IF(COUNTIF($Q81:$S81,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U81">
+        <f>IF(AND(OR($A81="Verdadero o Falso Simple",$A81="Respuesta A/B/Ambas/Ninguna",$A81="Verdadero o Falso Complejas",$A81="Selección de la mejor respuesta",$A81="Subítem de caso o problema",$A81="Opción de Emparejamiento Ampliado"),TRIM($I81)=""),IF(COUNTIF($Q81:$T81,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V81">
+        <f>IF(AND(OR($A81="Verdadero o Falso Simple",$A81="Respuesta A/B/Ambas/Ninguna",$A81="Verdadero o Falso Complejas",$A81="Selección de la mejor respuesta",$A81="Subítem de caso o problema",$A81="Opción de Emparejamiento Ampliado"),TRIM($J81)=""),IF(COUNTIF($Q81:$U81,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W81">
+        <f>IF(AND(OR($A81="Ítems agrupados por caso clínico o problema",$A81="Emparejamiento Ampliado"),TRIM($I81)&lt;&gt;""),IF(COUNTIF($Q81:$V81,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X81">
+        <f>IF(AND(OR($A81="Ítems agrupados por caso clínico o problema",$A81="Emparejamiento Ampliado"),TRIM($J81)&lt;&gt;""),IF(COUNTIF($Q81:$W81,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y81">
+        <f>IF(AND($A81="Verdadero o Falso Simple",OR(COUNTIF($D81:$E81,"?*")&lt;2,COUNTIF($F81:$H81,"?*")&gt;0)),IF(COUNTIF($Q81:$X81,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z81">
+        <f>IF(AND($A81="Verdadero o Falso Simple",TRIM($I81)&lt;&gt;"",NOT(OR(LEFT(TRIM($I81),1)="A",LEFT(TRIM($I81),1)="B"))),IF(COUNTIF($Q81:$Y81,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA81">
+        <f>IF(AND($A81="Respuesta A/B/Ambas/Ninguna",COUNTIF($D81:$G81,"?*")&lt;4),IF(COUNTIF($Q81:$Z81,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB81">
+        <f>IF(AND($A81="Respuesta A/B/Ambas/Ninguna",COUNTIF($H81:$H81,"?*")&gt;0),IF(COUNTIF($Q81:$AA81,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC81">
+        <f>IF(AND($A81="Respuesta A/B/Ambas/Ninguna",TRIM($I81)&lt;&gt;"",NOT(OR(LEFT(TRIM($I81),1)="A",LEFT(TRIM($I81),1)="B",LEFT(TRIM($I81),1)="C",LEFT(TRIM($I81),1)="D"))),IF(COUNTIF($Q81:$AB81,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD81">
+        <f>IF(AND($A81="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D81,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E81,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F81,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G81,"4.","")))=0)),IF(COUNTIF($Q81:$AC81,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE81">
+        <f>IF(AND($A81="Verdadero o Falso Complejas",COUNTIF($H81:$H81,"?*")&gt;0),IF(COUNTIF($Q81:$AD81,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF81">
+        <f>IF(AND($A81="Verdadero o Falso Complejas",TRIM($I81)&lt;&gt;"",NOT(OR(LEFT(TRIM($I81),1)="A",LEFT(TRIM($I81),1)="B",LEFT(TRIM($I81),1)="C",LEFT(TRIM($I81),1)="D",LEFT(TRIM($I81),1)="E"))),IF(COUNTIF($Q81:$AE81,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG81">
+        <f>IF(AND(OR($A81="Selección de la mejor respuesta",$A81="Subítem de caso o problema"),COUNTA($D81:$H81)&lt;5),IF(COUNTIF($Q81:$AF81,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH81">
+        <f>IF(AND(OR($A81="Selección de la mejor respuesta",$A81="Subítem de caso o problema"),TRIM($I81)&lt;&gt;"",NOT(OR(LEFT(TRIM($I81),1)="A",LEFT(TRIM($I81),1)="B",LEFT(TRIM($I81),1)="C",LEFT(TRIM($I81),1)="D",LEFT(TRIM($I81),1)="E"))),IF(COUNTIF($Q81:$AG81,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI81">
+        <f>IF(AND(OR($A81="Ítems agrupados por caso clínico o problema",$A81="Opción de Emparejamiento Ampliado"),COUNTIF($D81:$H81,"?*")&gt;0),IF(COUNTIF($Q81:$AH81,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ81">
+        <f>IF(AND($A81="Emparejamiento Ampliado",COUNTIF($D81:$H81,"?*")&lt;2),IF(COUNTIF($Q81:$AI81,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK81">
+        <f>IF(AND($A81="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I81),1)="A",LEFT(TRIM($I81),1)="B",LEFT(TRIM($I81),1)="C",LEFT(TRIM($I81),1)="D",LEFT(TRIM($I81),1)="E"))),IF(COUNTIF($Q81:$AJ81,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL81">
+        <f>IF(TRIM($K81)="",IF(COUNTIF($M81:$M81,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM81">
         <f>IF(AND(TRIM($K81)&lt;&gt;"",TRIM($K81)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M81:$N81,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1">
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="371" t="n"/>
+      <c r="B82" s="371" t="n"/>
+      <c r="C82" s="371" t="n"/>
+      <c r="D82" s="371">
+        <f>IF($A82="Verdadero o Falso Simple","Verdadero",IF($A82="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A82="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E82" s="371">
+        <f>IF($A82="Verdadero o Falso Simple","Falso",IF($A82="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A82="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F82" s="371">
+        <f>IF($A82="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A82="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G82" s="371">
+        <f>IF($A82="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A82="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H82" s="371">
+        <f>IF($A82="Verdadero o Falso Simple","",IF($A82="Respuesta A/B/Ambas/Ninguna","",IF($A82="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="371" t="n"/>
+      <c r="J82" s="372" t="n"/>
+      <c r="K82" s="372">
+        <f>IF(TRIM($A82)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L82" s="371">
+        <f>IF(TRIM($A82)="","",IF(OR($A82="Selección de la mejor respuesta",$A82="SELECCION_MEJOR_RESPUESTA",$A82="Subítem de caso o problema",$A82="SUBITEM_CASO"),IF(TRIM($C82)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D82:$H82&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I82)&lt;&gt;"",OR(LEFT(TRIM($I82),1)="A",LEFT(TRIM($I82),1)="B",LEFT(TRIM($I82),1)="C",LEFT(TRIM($I82),1)="D",LEFT(TRIM($I82),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A82)="","",IF(COUNTIF($Q82:$AJ82,"?*")=0,"OK","Falta revisar: "&amp;$Q82&amp;$R82&amp;$S82&amp;$T82&amp;$U82&amp;$V82&amp;$W82&amp;$X82&amp;$Y82&amp;$Z82&amp;$AA82&amp;$AB82&amp;$AC82&amp;$AD82&amp;$AE82&amp;$AF82&amp;$AG82&amp;$AH82&amp;$AI82&amp;$AJ82))))</f>
+        <v/>
+      </c>
+      <c r="M82" s="373" t="n"/>
+      <c r="Q82">
+        <f>IF(TRIM($C82)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R82">
+        <f>IF(TRIM($K82)="",IF(COUNTIF($Q82:$Q82,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S82">
         <f>IF(AND(TRIM($K82)&lt;&gt;"",TRIM($K82)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q82:$R82,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T82">
+        <f>IF(AND(OR($A82="Ítems agrupados por caso clínico o problema",$A82="Subítem de caso o problema",$A82="Emparejamiento Ampliado",$A82="Opción de Emparejamiento Ampliado"),TRIM($B82)=""),IF(COUNTIF($Q82:$S82,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U82">
+        <f>IF(AND(OR($A82="Verdadero o Falso Simple",$A82="Respuesta A/B/Ambas/Ninguna",$A82="Verdadero o Falso Complejas",$A82="Selección de la mejor respuesta",$A82="Subítem de caso o problema",$A82="Opción de Emparejamiento Ampliado"),TRIM($I82)=""),IF(COUNTIF($Q82:$T82,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V82">
+        <f>IF(AND(OR($A82="Verdadero o Falso Simple",$A82="Respuesta A/B/Ambas/Ninguna",$A82="Verdadero o Falso Complejas",$A82="Selección de la mejor respuesta",$A82="Subítem de caso o problema",$A82="Opción de Emparejamiento Ampliado"),TRIM($J82)=""),IF(COUNTIF($Q82:$U82,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W82">
+        <f>IF(AND(OR($A82="Ítems agrupados por caso clínico o problema",$A82="Emparejamiento Ampliado"),TRIM($I82)&lt;&gt;""),IF(COUNTIF($Q82:$V82,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X82">
+        <f>IF(AND(OR($A82="Ítems agrupados por caso clínico o problema",$A82="Emparejamiento Ampliado"),TRIM($J82)&lt;&gt;""),IF(COUNTIF($Q82:$W82,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y82">
+        <f>IF(AND($A82="Verdadero o Falso Simple",OR(COUNTIF($D82:$E82,"?*")&lt;2,COUNTIF($F82:$H82,"?*")&gt;0)),IF(COUNTIF($Q82:$X82,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z82">
+        <f>IF(AND($A82="Verdadero o Falso Simple",TRIM($I82)&lt;&gt;"",NOT(OR(LEFT(TRIM($I82),1)="A",LEFT(TRIM($I82),1)="B"))),IF(COUNTIF($Q82:$Y82,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA82">
+        <f>IF(AND($A82="Respuesta A/B/Ambas/Ninguna",COUNTIF($D82:$G82,"?*")&lt;4),IF(COUNTIF($Q82:$Z82,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB82">
+        <f>IF(AND($A82="Respuesta A/B/Ambas/Ninguna",COUNTIF($H82:$H82,"?*")&gt;0),IF(COUNTIF($Q82:$AA82,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC82">
+        <f>IF(AND($A82="Respuesta A/B/Ambas/Ninguna",TRIM($I82)&lt;&gt;"",NOT(OR(LEFT(TRIM($I82),1)="A",LEFT(TRIM($I82),1)="B",LEFT(TRIM($I82),1)="C",LEFT(TRIM($I82),1)="D"))),IF(COUNTIF($Q82:$AB82,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD82">
+        <f>IF(AND($A82="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D82,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E82,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F82,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G82,"4.","")))=0)),IF(COUNTIF($Q82:$AC82,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE82">
+        <f>IF(AND($A82="Verdadero o Falso Complejas",COUNTIF($H82:$H82,"?*")&gt;0),IF(COUNTIF($Q82:$AD82,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF82">
+        <f>IF(AND($A82="Verdadero o Falso Complejas",TRIM($I82)&lt;&gt;"",NOT(OR(LEFT(TRIM($I82),1)="A",LEFT(TRIM($I82),1)="B",LEFT(TRIM($I82),1)="C",LEFT(TRIM($I82),1)="D",LEFT(TRIM($I82),1)="E"))),IF(COUNTIF($Q82:$AE82,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG82">
+        <f>IF(AND(OR($A82="Selección de la mejor respuesta",$A82="Subítem de caso o problema"),COUNTA($D82:$H82)&lt;5),IF(COUNTIF($Q82:$AF82,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH82">
+        <f>IF(AND(OR($A82="Selección de la mejor respuesta",$A82="Subítem de caso o problema"),TRIM($I82)&lt;&gt;"",NOT(OR(LEFT(TRIM($I82),1)="A",LEFT(TRIM($I82),1)="B",LEFT(TRIM($I82),1)="C",LEFT(TRIM($I82),1)="D",LEFT(TRIM($I82),1)="E"))),IF(COUNTIF($Q82:$AG82,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI82">
+        <f>IF(AND(OR($A82="Ítems agrupados por caso clínico o problema",$A82="Opción de Emparejamiento Ampliado"),COUNTIF($D82:$H82,"?*")&gt;0),IF(COUNTIF($Q82:$AH82,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ82">
+        <f>IF(AND($A82="Emparejamiento Ampliado",COUNTIF($D82:$H82,"?*")&lt;2),IF(COUNTIF($Q82:$AI82,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK82">
+        <f>IF(AND($A82="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I82),1)="A",LEFT(TRIM($I82),1)="B",LEFT(TRIM($I82),1)="C",LEFT(TRIM($I82),1)="D",LEFT(TRIM($I82),1)="E"))),IF(COUNTIF($Q82:$AJ82,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL82">
+        <f>IF(TRIM($K82)="",IF(COUNTIF($M82:$M82,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM82">
         <f>IF(AND(TRIM($K82)&lt;&gt;"",TRIM($K82)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M82:$N82,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="24" customHeight="1">
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="371" t="n"/>
+      <c r="B83" s="371" t="n"/>
+      <c r="C83" s="371" t="n"/>
+      <c r="D83" s="371">
+        <f>IF($A83="Verdadero o Falso Simple","Verdadero",IF($A83="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A83="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E83" s="371">
+        <f>IF($A83="Verdadero o Falso Simple","Falso",IF($A83="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A83="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F83" s="371">
+        <f>IF($A83="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A83="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G83" s="371">
+        <f>IF($A83="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A83="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H83" s="371">
+        <f>IF($A83="Verdadero o Falso Simple","",IF($A83="Respuesta A/B/Ambas/Ninguna","",IF($A83="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I83" s="371" t="n"/>
+      <c r="J83" s="372" t="n"/>
+      <c r="K83" s="372">
+        <f>IF(TRIM($A83)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L83" s="371">
+        <f>IF(TRIM($A83)="","",IF(OR($A83="Selección de la mejor respuesta",$A83="SELECCION_MEJOR_RESPUESTA",$A83="Subítem de caso o problema",$A83="SUBITEM_CASO"),IF(TRIM($C83)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D83:$H83&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I83)&lt;&gt;"",OR(LEFT(TRIM($I83),1)="A",LEFT(TRIM($I83),1)="B",LEFT(TRIM($I83),1)="C",LEFT(TRIM($I83),1)="D",LEFT(TRIM($I83),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A83)="","",IF(COUNTIF($Q83:$AJ83,"?*")=0,"OK","Falta revisar: "&amp;$Q83&amp;$R83&amp;$S83&amp;$T83&amp;$U83&amp;$V83&amp;$W83&amp;$X83&amp;$Y83&amp;$Z83&amp;$AA83&amp;$AB83&amp;$AC83&amp;$AD83&amp;$AE83&amp;$AF83&amp;$AG83&amp;$AH83&amp;$AI83&amp;$AJ83))))</f>
+        <v/>
+      </c>
+      <c r="M83" s="373" t="n"/>
+      <c r="Q83">
+        <f>IF(TRIM($C83)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R83">
+        <f>IF(TRIM($K83)="",IF(COUNTIF($Q83:$Q83,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S83">
         <f>IF(AND(TRIM($K83)&lt;&gt;"",TRIM($K83)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q83:$R83,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T83">
+        <f>IF(AND(OR($A83="Ítems agrupados por caso clínico o problema",$A83="Subítem de caso o problema",$A83="Emparejamiento Ampliado",$A83="Opción de Emparejamiento Ampliado"),TRIM($B83)=""),IF(COUNTIF($Q83:$S83,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U83">
+        <f>IF(AND(OR($A83="Verdadero o Falso Simple",$A83="Respuesta A/B/Ambas/Ninguna",$A83="Verdadero o Falso Complejas",$A83="Selección de la mejor respuesta",$A83="Subítem de caso o problema",$A83="Opción de Emparejamiento Ampliado"),TRIM($I83)=""),IF(COUNTIF($Q83:$T83,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V83">
+        <f>IF(AND(OR($A83="Verdadero o Falso Simple",$A83="Respuesta A/B/Ambas/Ninguna",$A83="Verdadero o Falso Complejas",$A83="Selección de la mejor respuesta",$A83="Subítem de caso o problema",$A83="Opción de Emparejamiento Ampliado"),TRIM($J83)=""),IF(COUNTIF($Q83:$U83,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W83">
+        <f>IF(AND(OR($A83="Ítems agrupados por caso clínico o problema",$A83="Emparejamiento Ampliado"),TRIM($I83)&lt;&gt;""),IF(COUNTIF($Q83:$V83,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X83">
+        <f>IF(AND(OR($A83="Ítems agrupados por caso clínico o problema",$A83="Emparejamiento Ampliado"),TRIM($J83)&lt;&gt;""),IF(COUNTIF($Q83:$W83,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y83">
+        <f>IF(AND($A83="Verdadero o Falso Simple",OR(COUNTIF($D83:$E83,"?*")&lt;2,COUNTIF($F83:$H83,"?*")&gt;0)),IF(COUNTIF($Q83:$X83,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z83">
+        <f>IF(AND($A83="Verdadero o Falso Simple",TRIM($I83)&lt;&gt;"",NOT(OR(LEFT(TRIM($I83),1)="A",LEFT(TRIM($I83),1)="B"))),IF(COUNTIF($Q83:$Y83,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA83">
+        <f>IF(AND($A83="Respuesta A/B/Ambas/Ninguna",COUNTIF($D83:$G83,"?*")&lt;4),IF(COUNTIF($Q83:$Z83,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB83">
+        <f>IF(AND($A83="Respuesta A/B/Ambas/Ninguna",COUNTIF($H83:$H83,"?*")&gt;0),IF(COUNTIF($Q83:$AA83,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC83">
+        <f>IF(AND($A83="Respuesta A/B/Ambas/Ninguna",TRIM($I83)&lt;&gt;"",NOT(OR(LEFT(TRIM($I83),1)="A",LEFT(TRIM($I83),1)="B",LEFT(TRIM($I83),1)="C",LEFT(TRIM($I83),1)="D"))),IF(COUNTIF($Q83:$AB83,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD83">
+        <f>IF(AND($A83="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D83,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E83,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F83,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G83,"4.","")))=0)),IF(COUNTIF($Q83:$AC83,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE83">
+        <f>IF(AND($A83="Verdadero o Falso Complejas",COUNTIF($H83:$H83,"?*")&gt;0),IF(COUNTIF($Q83:$AD83,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF83">
+        <f>IF(AND($A83="Verdadero o Falso Complejas",TRIM($I83)&lt;&gt;"",NOT(OR(LEFT(TRIM($I83),1)="A",LEFT(TRIM($I83),1)="B",LEFT(TRIM($I83),1)="C",LEFT(TRIM($I83),1)="D",LEFT(TRIM($I83),1)="E"))),IF(COUNTIF($Q83:$AE83,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG83">
+        <f>IF(AND(OR($A83="Selección de la mejor respuesta",$A83="Subítem de caso o problema"),COUNTA($D83:$H83)&lt;5),IF(COUNTIF($Q83:$AF83,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH83">
+        <f>IF(AND(OR($A83="Selección de la mejor respuesta",$A83="Subítem de caso o problema"),TRIM($I83)&lt;&gt;"",NOT(OR(LEFT(TRIM($I83),1)="A",LEFT(TRIM($I83),1)="B",LEFT(TRIM($I83),1)="C",LEFT(TRIM($I83),1)="D",LEFT(TRIM($I83),1)="E"))),IF(COUNTIF($Q83:$AG83,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI83">
+        <f>IF(AND(OR($A83="Ítems agrupados por caso clínico o problema",$A83="Opción de Emparejamiento Ampliado"),COUNTIF($D83:$H83,"?*")&gt;0),IF(COUNTIF($Q83:$AH83,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ83">
+        <f>IF(AND($A83="Emparejamiento Ampliado",COUNTIF($D83:$H83,"?*")&lt;2),IF(COUNTIF($Q83:$AI83,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK83">
+        <f>IF(AND($A83="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I83),1)="A",LEFT(TRIM($I83),1)="B",LEFT(TRIM($I83),1)="C",LEFT(TRIM($I83),1)="D",LEFT(TRIM($I83),1)="E"))),IF(COUNTIF($Q83:$AJ83,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL83">
+        <f>IF(TRIM($K83)="",IF(COUNTIF($M83:$M83,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM83">
         <f>IF(AND(TRIM($K83)&lt;&gt;"",TRIM($K83)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M83:$N83,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="24" customHeight="1">
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="371" t="n"/>
+      <c r="B84" s="371" t="n"/>
+      <c r="C84" s="371" t="n"/>
+      <c r="D84" s="371">
+        <f>IF($A84="Verdadero o Falso Simple","Verdadero",IF($A84="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A84="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E84" s="371">
+        <f>IF($A84="Verdadero o Falso Simple","Falso",IF($A84="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A84="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F84" s="371">
+        <f>IF($A84="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A84="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G84" s="371">
+        <f>IF($A84="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A84="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H84" s="371">
+        <f>IF($A84="Verdadero o Falso Simple","",IF($A84="Respuesta A/B/Ambas/Ninguna","",IF($A84="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I84" s="371" t="n"/>
+      <c r="J84" s="372" t="n"/>
+      <c r="K84" s="372">
+        <f>IF(TRIM($A84)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L84" s="371">
+        <f>IF(TRIM($A84)="","",IF(OR($A84="Selección de la mejor respuesta",$A84="SELECCION_MEJOR_RESPUESTA",$A84="Subítem de caso o problema",$A84="SUBITEM_CASO"),IF(TRIM($C84)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D84:$H84&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I84)&lt;&gt;"",OR(LEFT(TRIM($I84),1)="A",LEFT(TRIM($I84),1)="B",LEFT(TRIM($I84),1)="C",LEFT(TRIM($I84),1)="D",LEFT(TRIM($I84),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A84)="","",IF(COUNTIF($Q84:$AJ84,"?*")=0,"OK","Falta revisar: "&amp;$Q84&amp;$R84&amp;$S84&amp;$T84&amp;$U84&amp;$V84&amp;$W84&amp;$X84&amp;$Y84&amp;$Z84&amp;$AA84&amp;$AB84&amp;$AC84&amp;$AD84&amp;$AE84&amp;$AF84&amp;$AG84&amp;$AH84&amp;$AI84&amp;$AJ84))))</f>
+        <v/>
+      </c>
+      <c r="M84" s="373" t="n"/>
+      <c r="Q84">
+        <f>IF(TRIM($C84)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R84">
+        <f>IF(TRIM($K84)="",IF(COUNTIF($Q84:$Q84,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S84">
         <f>IF(AND(TRIM($K84)&lt;&gt;"",TRIM($K84)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q84:$R84,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T84">
+        <f>IF(AND(OR($A84="Ítems agrupados por caso clínico o problema",$A84="Subítem de caso o problema",$A84="Emparejamiento Ampliado",$A84="Opción de Emparejamiento Ampliado"),TRIM($B84)=""),IF(COUNTIF($Q84:$S84,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U84">
+        <f>IF(AND(OR($A84="Verdadero o Falso Simple",$A84="Respuesta A/B/Ambas/Ninguna",$A84="Verdadero o Falso Complejas",$A84="Selección de la mejor respuesta",$A84="Subítem de caso o problema",$A84="Opción de Emparejamiento Ampliado"),TRIM($I84)=""),IF(COUNTIF($Q84:$T84,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V84">
+        <f>IF(AND(OR($A84="Verdadero o Falso Simple",$A84="Respuesta A/B/Ambas/Ninguna",$A84="Verdadero o Falso Complejas",$A84="Selección de la mejor respuesta",$A84="Subítem de caso o problema",$A84="Opción de Emparejamiento Ampliado"),TRIM($J84)=""),IF(COUNTIF($Q84:$U84,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W84">
+        <f>IF(AND(OR($A84="Ítems agrupados por caso clínico o problema",$A84="Emparejamiento Ampliado"),TRIM($I84)&lt;&gt;""),IF(COUNTIF($Q84:$V84,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X84">
+        <f>IF(AND(OR($A84="Ítems agrupados por caso clínico o problema",$A84="Emparejamiento Ampliado"),TRIM($J84)&lt;&gt;""),IF(COUNTIF($Q84:$W84,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y84">
+        <f>IF(AND($A84="Verdadero o Falso Simple",OR(COUNTIF($D84:$E84,"?*")&lt;2,COUNTIF($F84:$H84,"?*")&gt;0)),IF(COUNTIF($Q84:$X84,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z84">
+        <f>IF(AND($A84="Verdadero o Falso Simple",TRIM($I84)&lt;&gt;"",NOT(OR(LEFT(TRIM($I84),1)="A",LEFT(TRIM($I84),1)="B"))),IF(COUNTIF($Q84:$Y84,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA84">
+        <f>IF(AND($A84="Respuesta A/B/Ambas/Ninguna",COUNTIF($D84:$G84,"?*")&lt;4),IF(COUNTIF($Q84:$Z84,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB84">
+        <f>IF(AND($A84="Respuesta A/B/Ambas/Ninguna",COUNTIF($H84:$H84,"?*")&gt;0),IF(COUNTIF($Q84:$AA84,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC84">
+        <f>IF(AND($A84="Respuesta A/B/Ambas/Ninguna",TRIM($I84)&lt;&gt;"",NOT(OR(LEFT(TRIM($I84),1)="A",LEFT(TRIM($I84),1)="B",LEFT(TRIM($I84),1)="C",LEFT(TRIM($I84),1)="D"))),IF(COUNTIF($Q84:$AB84,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD84">
+        <f>IF(AND($A84="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D84,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E84,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F84,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G84,"4.","")))=0)),IF(COUNTIF($Q84:$AC84,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE84">
+        <f>IF(AND($A84="Verdadero o Falso Complejas",COUNTIF($H84:$H84,"?*")&gt;0),IF(COUNTIF($Q84:$AD84,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF84">
+        <f>IF(AND($A84="Verdadero o Falso Complejas",TRIM($I84)&lt;&gt;"",NOT(OR(LEFT(TRIM($I84),1)="A",LEFT(TRIM($I84),1)="B",LEFT(TRIM($I84),1)="C",LEFT(TRIM($I84),1)="D",LEFT(TRIM($I84),1)="E"))),IF(COUNTIF($Q84:$AE84,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG84">
+        <f>IF(AND(OR($A84="Selección de la mejor respuesta",$A84="Subítem de caso o problema"),COUNTA($D84:$H84)&lt;5),IF(COUNTIF($Q84:$AF84,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH84">
+        <f>IF(AND(OR($A84="Selección de la mejor respuesta",$A84="Subítem de caso o problema"),TRIM($I84)&lt;&gt;"",NOT(OR(LEFT(TRIM($I84),1)="A",LEFT(TRIM($I84),1)="B",LEFT(TRIM($I84),1)="C",LEFT(TRIM($I84),1)="D",LEFT(TRIM($I84),1)="E"))),IF(COUNTIF($Q84:$AG84,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI84">
+        <f>IF(AND(OR($A84="Ítems agrupados por caso clínico o problema",$A84="Opción de Emparejamiento Ampliado"),COUNTIF($D84:$H84,"?*")&gt;0),IF(COUNTIF($Q84:$AH84,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ84">
+        <f>IF(AND($A84="Emparejamiento Ampliado",COUNTIF($D84:$H84,"?*")&lt;2),IF(COUNTIF($Q84:$AI84,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK84">
+        <f>IF(AND($A84="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I84),1)="A",LEFT(TRIM($I84),1)="B",LEFT(TRIM($I84),1)="C",LEFT(TRIM($I84),1)="D",LEFT(TRIM($I84),1)="E"))),IF(COUNTIF($Q84:$AJ84,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL84">
+        <f>IF(TRIM($K84)="",IF(COUNTIF($M84:$M84,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM84">
         <f>IF(AND(TRIM($K84)&lt;&gt;"",TRIM($K84)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M84:$N84,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="24" customHeight="1">
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="371" t="n"/>
+      <c r="B85" s="371" t="n"/>
+      <c r="C85" s="371" t="n"/>
+      <c r="D85" s="371">
+        <f>IF($A85="Verdadero o Falso Simple","Verdadero",IF($A85="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A85="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="371">
+        <f>IF($A85="Verdadero o Falso Simple","Falso",IF($A85="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A85="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="371">
+        <f>IF($A85="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A85="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G85" s="371">
+        <f>IF($A85="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A85="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H85" s="371">
+        <f>IF($A85="Verdadero o Falso Simple","",IF($A85="Respuesta A/B/Ambas/Ninguna","",IF($A85="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="371" t="n"/>
+      <c r="J85" s="372" t="n"/>
+      <c r="K85" s="372">
+        <f>IF(TRIM($A85)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L85" s="371">
+        <f>IF(TRIM($A85)="","",IF(OR($A85="Selección de la mejor respuesta",$A85="SELECCION_MEJOR_RESPUESTA",$A85="Subítem de caso o problema",$A85="SUBITEM_CASO"),IF(TRIM($C85)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D85:$H85&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I85)&lt;&gt;"",OR(LEFT(TRIM($I85),1)="A",LEFT(TRIM($I85),1)="B",LEFT(TRIM($I85),1)="C",LEFT(TRIM($I85),1)="D",LEFT(TRIM($I85),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A85)="","",IF(COUNTIF($Q85:$AJ85,"?*")=0,"OK","Falta revisar: "&amp;$Q85&amp;$R85&amp;$S85&amp;$T85&amp;$U85&amp;$V85&amp;$W85&amp;$X85&amp;$Y85&amp;$Z85&amp;$AA85&amp;$AB85&amp;$AC85&amp;$AD85&amp;$AE85&amp;$AF85&amp;$AG85&amp;$AH85&amp;$AI85&amp;$AJ85))))</f>
+        <v/>
+      </c>
+      <c r="M85" s="373" t="n"/>
+      <c r="Q85">
+        <f>IF(TRIM($C85)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R85">
+        <f>IF(TRIM($K85)="",IF(COUNTIF($Q85:$Q85,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S85">
         <f>IF(AND(TRIM($K85)&lt;&gt;"",TRIM($K85)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q85:$R85,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T85">
+        <f>IF(AND(OR($A85="Ítems agrupados por caso clínico o problema",$A85="Subítem de caso o problema",$A85="Emparejamiento Ampliado",$A85="Opción de Emparejamiento Ampliado"),TRIM($B85)=""),IF(COUNTIF($Q85:$S85,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U85">
+        <f>IF(AND(OR($A85="Verdadero o Falso Simple",$A85="Respuesta A/B/Ambas/Ninguna",$A85="Verdadero o Falso Complejas",$A85="Selección de la mejor respuesta",$A85="Subítem de caso o problema",$A85="Opción de Emparejamiento Ampliado"),TRIM($I85)=""),IF(COUNTIF($Q85:$T85,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V85">
+        <f>IF(AND(OR($A85="Verdadero o Falso Simple",$A85="Respuesta A/B/Ambas/Ninguna",$A85="Verdadero o Falso Complejas",$A85="Selección de la mejor respuesta",$A85="Subítem de caso o problema",$A85="Opción de Emparejamiento Ampliado"),TRIM($J85)=""),IF(COUNTIF($Q85:$U85,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W85">
+        <f>IF(AND(OR($A85="Ítems agrupados por caso clínico o problema",$A85="Emparejamiento Ampliado"),TRIM($I85)&lt;&gt;""),IF(COUNTIF($Q85:$V85,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X85">
+        <f>IF(AND(OR($A85="Ítems agrupados por caso clínico o problema",$A85="Emparejamiento Ampliado"),TRIM($J85)&lt;&gt;""),IF(COUNTIF($Q85:$W85,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y85">
+        <f>IF(AND($A85="Verdadero o Falso Simple",OR(COUNTIF($D85:$E85,"?*")&lt;2,COUNTIF($F85:$H85,"?*")&gt;0)),IF(COUNTIF($Q85:$X85,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z85">
+        <f>IF(AND($A85="Verdadero o Falso Simple",TRIM($I85)&lt;&gt;"",NOT(OR(LEFT(TRIM($I85),1)="A",LEFT(TRIM($I85),1)="B"))),IF(COUNTIF($Q85:$Y85,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA85">
+        <f>IF(AND($A85="Respuesta A/B/Ambas/Ninguna",COUNTIF($D85:$G85,"?*")&lt;4),IF(COUNTIF($Q85:$Z85,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB85">
+        <f>IF(AND($A85="Respuesta A/B/Ambas/Ninguna",COUNTIF($H85:$H85,"?*")&gt;0),IF(COUNTIF($Q85:$AA85,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC85">
+        <f>IF(AND($A85="Respuesta A/B/Ambas/Ninguna",TRIM($I85)&lt;&gt;"",NOT(OR(LEFT(TRIM($I85),1)="A",LEFT(TRIM($I85),1)="B",LEFT(TRIM($I85),1)="C",LEFT(TRIM($I85),1)="D"))),IF(COUNTIF($Q85:$AB85,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD85">
+        <f>IF(AND($A85="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D85,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E85,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F85,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G85,"4.","")))=0)),IF(COUNTIF($Q85:$AC85,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE85">
+        <f>IF(AND($A85="Verdadero o Falso Complejas",COUNTIF($H85:$H85,"?*")&gt;0),IF(COUNTIF($Q85:$AD85,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF85">
+        <f>IF(AND($A85="Verdadero o Falso Complejas",TRIM($I85)&lt;&gt;"",NOT(OR(LEFT(TRIM($I85),1)="A",LEFT(TRIM($I85),1)="B",LEFT(TRIM($I85),1)="C",LEFT(TRIM($I85),1)="D",LEFT(TRIM($I85),1)="E"))),IF(COUNTIF($Q85:$AE85,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG85">
+        <f>IF(AND(OR($A85="Selección de la mejor respuesta",$A85="Subítem de caso o problema"),COUNTA($D85:$H85)&lt;5),IF(COUNTIF($Q85:$AF85,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH85">
+        <f>IF(AND(OR($A85="Selección de la mejor respuesta",$A85="Subítem de caso o problema"),TRIM($I85)&lt;&gt;"",NOT(OR(LEFT(TRIM($I85),1)="A",LEFT(TRIM($I85),1)="B",LEFT(TRIM($I85),1)="C",LEFT(TRIM($I85),1)="D",LEFT(TRIM($I85),1)="E"))),IF(COUNTIF($Q85:$AG85,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI85">
+        <f>IF(AND(OR($A85="Ítems agrupados por caso clínico o problema",$A85="Opción de Emparejamiento Ampliado"),COUNTIF($D85:$H85,"?*")&gt;0),IF(COUNTIF($Q85:$AH85,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ85">
+        <f>IF(AND($A85="Emparejamiento Ampliado",COUNTIF($D85:$H85,"?*")&lt;2),IF(COUNTIF($Q85:$AI85,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK85">
+        <f>IF(AND($A85="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I85),1)="A",LEFT(TRIM($I85),1)="B",LEFT(TRIM($I85),1)="C",LEFT(TRIM($I85),1)="D",LEFT(TRIM($I85),1)="E"))),IF(COUNTIF($Q85:$AJ85,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL85">
+        <f>IF(TRIM($K85)="",IF(COUNTIF($M85:$M85,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM85">
         <f>IF(AND(TRIM($K85)&lt;&gt;"",TRIM($K85)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M85:$N85,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="24" customHeight="1">
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="371" t="n"/>
+      <c r="B86" s="371" t="n"/>
+      <c r="C86" s="371" t="n"/>
+      <c r="D86" s="371">
+        <f>IF($A86="Verdadero o Falso Simple","Verdadero",IF($A86="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A86="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E86" s="371">
+        <f>IF($A86="Verdadero o Falso Simple","Falso",IF($A86="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A86="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F86" s="371">
+        <f>IF($A86="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A86="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G86" s="371">
+        <f>IF($A86="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A86="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H86" s="371">
+        <f>IF($A86="Verdadero o Falso Simple","",IF($A86="Respuesta A/B/Ambas/Ninguna","",IF($A86="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="371" t="n"/>
+      <c r="J86" s="372" t="n"/>
+      <c r="K86" s="372">
+        <f>IF(TRIM($A86)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L86" s="371">
+        <f>IF(TRIM($A86)="","",IF(OR($A86="Selección de la mejor respuesta",$A86="SELECCION_MEJOR_RESPUESTA",$A86="Subítem de caso o problema",$A86="SUBITEM_CASO"),IF(TRIM($C86)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D86:$H86&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I86)&lt;&gt;"",OR(LEFT(TRIM($I86),1)="A",LEFT(TRIM($I86),1)="B",LEFT(TRIM($I86),1)="C",LEFT(TRIM($I86),1)="D",LEFT(TRIM($I86),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A86)="","",IF(COUNTIF($Q86:$AJ86,"?*")=0,"OK","Falta revisar: "&amp;$Q86&amp;$R86&amp;$S86&amp;$T86&amp;$U86&amp;$V86&amp;$W86&amp;$X86&amp;$Y86&amp;$Z86&amp;$AA86&amp;$AB86&amp;$AC86&amp;$AD86&amp;$AE86&amp;$AF86&amp;$AG86&amp;$AH86&amp;$AI86&amp;$AJ86))))</f>
+        <v/>
+      </c>
+      <c r="M86" s="373" t="n"/>
+      <c r="Q86">
+        <f>IF(TRIM($C86)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R86">
+        <f>IF(TRIM($K86)="",IF(COUNTIF($Q86:$Q86,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S86">
         <f>IF(AND(TRIM($K86)&lt;&gt;"",TRIM($K86)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q86:$R86,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T86">
+        <f>IF(AND(OR($A86="Ítems agrupados por caso clínico o problema",$A86="Subítem de caso o problema",$A86="Emparejamiento Ampliado",$A86="Opción de Emparejamiento Ampliado"),TRIM($B86)=""),IF(COUNTIF($Q86:$S86,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U86">
+        <f>IF(AND(OR($A86="Verdadero o Falso Simple",$A86="Respuesta A/B/Ambas/Ninguna",$A86="Verdadero o Falso Complejas",$A86="Selección de la mejor respuesta",$A86="Subítem de caso o problema",$A86="Opción de Emparejamiento Ampliado"),TRIM($I86)=""),IF(COUNTIF($Q86:$T86,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V86">
+        <f>IF(AND(OR($A86="Verdadero o Falso Simple",$A86="Respuesta A/B/Ambas/Ninguna",$A86="Verdadero o Falso Complejas",$A86="Selección de la mejor respuesta",$A86="Subítem de caso o problema",$A86="Opción de Emparejamiento Ampliado"),TRIM($J86)=""),IF(COUNTIF($Q86:$U86,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W86">
+        <f>IF(AND(OR($A86="Ítems agrupados por caso clínico o problema",$A86="Emparejamiento Ampliado"),TRIM($I86)&lt;&gt;""),IF(COUNTIF($Q86:$V86,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X86">
+        <f>IF(AND(OR($A86="Ítems agrupados por caso clínico o problema",$A86="Emparejamiento Ampliado"),TRIM($J86)&lt;&gt;""),IF(COUNTIF($Q86:$W86,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y86">
+        <f>IF(AND($A86="Verdadero o Falso Simple",OR(COUNTIF($D86:$E86,"?*")&lt;2,COUNTIF($F86:$H86,"?*")&gt;0)),IF(COUNTIF($Q86:$X86,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z86">
+        <f>IF(AND($A86="Verdadero o Falso Simple",TRIM($I86)&lt;&gt;"",NOT(OR(LEFT(TRIM($I86),1)="A",LEFT(TRIM($I86),1)="B"))),IF(COUNTIF($Q86:$Y86,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA86">
+        <f>IF(AND($A86="Respuesta A/B/Ambas/Ninguna",COUNTIF($D86:$G86,"?*")&lt;4),IF(COUNTIF($Q86:$Z86,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB86">
+        <f>IF(AND($A86="Respuesta A/B/Ambas/Ninguna",COUNTIF($H86:$H86,"?*")&gt;0),IF(COUNTIF($Q86:$AA86,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC86">
+        <f>IF(AND($A86="Respuesta A/B/Ambas/Ninguna",TRIM($I86)&lt;&gt;"",NOT(OR(LEFT(TRIM($I86),1)="A",LEFT(TRIM($I86),1)="B",LEFT(TRIM($I86),1)="C",LEFT(TRIM($I86),1)="D"))),IF(COUNTIF($Q86:$AB86,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD86">
+        <f>IF(AND($A86="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D86,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E86,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F86,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G86,"4.","")))=0)),IF(COUNTIF($Q86:$AC86,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE86">
+        <f>IF(AND($A86="Verdadero o Falso Complejas",COUNTIF($H86:$H86,"?*")&gt;0),IF(COUNTIF($Q86:$AD86,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF86">
+        <f>IF(AND($A86="Verdadero o Falso Complejas",TRIM($I86)&lt;&gt;"",NOT(OR(LEFT(TRIM($I86),1)="A",LEFT(TRIM($I86),1)="B",LEFT(TRIM($I86),1)="C",LEFT(TRIM($I86),1)="D",LEFT(TRIM($I86),1)="E"))),IF(COUNTIF($Q86:$AE86,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG86">
+        <f>IF(AND(OR($A86="Selección de la mejor respuesta",$A86="Subítem de caso o problema"),COUNTA($D86:$H86)&lt;5),IF(COUNTIF($Q86:$AF86,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH86">
+        <f>IF(AND(OR($A86="Selección de la mejor respuesta",$A86="Subítem de caso o problema"),TRIM($I86)&lt;&gt;"",NOT(OR(LEFT(TRIM($I86),1)="A",LEFT(TRIM($I86),1)="B",LEFT(TRIM($I86),1)="C",LEFT(TRIM($I86),1)="D",LEFT(TRIM($I86),1)="E"))),IF(COUNTIF($Q86:$AG86,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI86">
+        <f>IF(AND(OR($A86="Ítems agrupados por caso clínico o problema",$A86="Opción de Emparejamiento Ampliado"),COUNTIF($D86:$H86,"?*")&gt;0),IF(COUNTIF($Q86:$AH86,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ86">
+        <f>IF(AND($A86="Emparejamiento Ampliado",COUNTIF($D86:$H86,"?*")&lt;2),IF(COUNTIF($Q86:$AI86,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK86">
+        <f>IF(AND($A86="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I86),1)="A",LEFT(TRIM($I86),1)="B",LEFT(TRIM($I86),1)="C",LEFT(TRIM($I86),1)="D",LEFT(TRIM($I86),1)="E"))),IF(COUNTIF($Q86:$AJ86,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL86">
+        <f>IF(TRIM($K86)="",IF(COUNTIF($M86:$M86,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM86">
         <f>IF(AND(TRIM($K86)&lt;&gt;"",TRIM($K86)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M86:$N86,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="24" customHeight="1">
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="371" t="n"/>
+      <c r="B87" s="371" t="n"/>
+      <c r="C87" s="371" t="n"/>
+      <c r="D87" s="371">
+        <f>IF($A87="Verdadero o Falso Simple","Verdadero",IF($A87="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A87="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E87" s="371">
+        <f>IF($A87="Verdadero o Falso Simple","Falso",IF($A87="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A87="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F87" s="371">
+        <f>IF($A87="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A87="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G87" s="371">
+        <f>IF($A87="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A87="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H87" s="371">
+        <f>IF($A87="Verdadero o Falso Simple","",IF($A87="Respuesta A/B/Ambas/Ninguna","",IF($A87="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I87" s="371" t="n"/>
+      <c r="J87" s="372" t="n"/>
+      <c r="K87" s="372">
+        <f>IF(TRIM($A87)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L87" s="371">
+        <f>IF(TRIM($A87)="","",IF(OR($A87="Selección de la mejor respuesta",$A87="SELECCION_MEJOR_RESPUESTA",$A87="Subítem de caso o problema",$A87="SUBITEM_CASO"),IF(TRIM($C87)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D87:$H87&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I87)&lt;&gt;"",OR(LEFT(TRIM($I87),1)="A",LEFT(TRIM($I87),1)="B",LEFT(TRIM($I87),1)="C",LEFT(TRIM($I87),1)="D",LEFT(TRIM($I87),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A87)="","",IF(COUNTIF($Q87:$AJ87,"?*")=0,"OK","Falta revisar: "&amp;$Q87&amp;$R87&amp;$S87&amp;$T87&amp;$U87&amp;$V87&amp;$W87&amp;$X87&amp;$Y87&amp;$Z87&amp;$AA87&amp;$AB87&amp;$AC87&amp;$AD87&amp;$AE87&amp;$AF87&amp;$AG87&amp;$AH87&amp;$AI87&amp;$AJ87))))</f>
+        <v/>
+      </c>
+      <c r="M87" s="373" t="n"/>
+      <c r="Q87">
+        <f>IF(TRIM($C87)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R87">
+        <f>IF(TRIM($K87)="",IF(COUNTIF($Q87:$Q87,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S87">
         <f>IF(AND(TRIM($K87)&lt;&gt;"",TRIM($K87)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q87:$R87,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T87">
+        <f>IF(AND(OR($A87="Ítems agrupados por caso clínico o problema",$A87="Subítem de caso o problema",$A87="Emparejamiento Ampliado",$A87="Opción de Emparejamiento Ampliado"),TRIM($B87)=""),IF(COUNTIF($Q87:$S87,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U87">
+        <f>IF(AND(OR($A87="Verdadero o Falso Simple",$A87="Respuesta A/B/Ambas/Ninguna",$A87="Verdadero o Falso Complejas",$A87="Selección de la mejor respuesta",$A87="Subítem de caso o problema",$A87="Opción de Emparejamiento Ampliado"),TRIM($I87)=""),IF(COUNTIF($Q87:$T87,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V87">
+        <f>IF(AND(OR($A87="Verdadero o Falso Simple",$A87="Respuesta A/B/Ambas/Ninguna",$A87="Verdadero o Falso Complejas",$A87="Selección de la mejor respuesta",$A87="Subítem de caso o problema",$A87="Opción de Emparejamiento Ampliado"),TRIM($J87)=""),IF(COUNTIF($Q87:$U87,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W87">
+        <f>IF(AND(OR($A87="Ítems agrupados por caso clínico o problema",$A87="Emparejamiento Ampliado"),TRIM($I87)&lt;&gt;""),IF(COUNTIF($Q87:$V87,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X87">
+        <f>IF(AND(OR($A87="Ítems agrupados por caso clínico o problema",$A87="Emparejamiento Ampliado"),TRIM($J87)&lt;&gt;""),IF(COUNTIF($Q87:$W87,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y87">
+        <f>IF(AND($A87="Verdadero o Falso Simple",OR(COUNTIF($D87:$E87,"?*")&lt;2,COUNTIF($F87:$H87,"?*")&gt;0)),IF(COUNTIF($Q87:$X87,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z87">
+        <f>IF(AND($A87="Verdadero o Falso Simple",TRIM($I87)&lt;&gt;"",NOT(OR(LEFT(TRIM($I87),1)="A",LEFT(TRIM($I87),1)="B"))),IF(COUNTIF($Q87:$Y87,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA87">
+        <f>IF(AND($A87="Respuesta A/B/Ambas/Ninguna",COUNTIF($D87:$G87,"?*")&lt;4),IF(COUNTIF($Q87:$Z87,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB87">
+        <f>IF(AND($A87="Respuesta A/B/Ambas/Ninguna",COUNTIF($H87:$H87,"?*")&gt;0),IF(COUNTIF($Q87:$AA87,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC87">
+        <f>IF(AND($A87="Respuesta A/B/Ambas/Ninguna",TRIM($I87)&lt;&gt;"",NOT(OR(LEFT(TRIM($I87),1)="A",LEFT(TRIM($I87),1)="B",LEFT(TRIM($I87),1)="C",LEFT(TRIM($I87),1)="D"))),IF(COUNTIF($Q87:$AB87,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD87">
+        <f>IF(AND($A87="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D87,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E87,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F87,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G87,"4.","")))=0)),IF(COUNTIF($Q87:$AC87,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE87">
+        <f>IF(AND($A87="Verdadero o Falso Complejas",COUNTIF($H87:$H87,"?*")&gt;0),IF(COUNTIF($Q87:$AD87,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF87">
+        <f>IF(AND($A87="Verdadero o Falso Complejas",TRIM($I87)&lt;&gt;"",NOT(OR(LEFT(TRIM($I87),1)="A",LEFT(TRIM($I87),1)="B",LEFT(TRIM($I87),1)="C",LEFT(TRIM($I87),1)="D",LEFT(TRIM($I87),1)="E"))),IF(COUNTIF($Q87:$AE87,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG87">
+        <f>IF(AND(OR($A87="Selección de la mejor respuesta",$A87="Subítem de caso o problema"),COUNTA($D87:$H87)&lt;5),IF(COUNTIF($Q87:$AF87,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH87">
+        <f>IF(AND(OR($A87="Selección de la mejor respuesta",$A87="Subítem de caso o problema"),TRIM($I87)&lt;&gt;"",NOT(OR(LEFT(TRIM($I87),1)="A",LEFT(TRIM($I87),1)="B",LEFT(TRIM($I87),1)="C",LEFT(TRIM($I87),1)="D",LEFT(TRIM($I87),1)="E"))),IF(COUNTIF($Q87:$AG87,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI87">
+        <f>IF(AND(OR($A87="Ítems agrupados por caso clínico o problema",$A87="Opción de Emparejamiento Ampliado"),COUNTIF($D87:$H87,"?*")&gt;0),IF(COUNTIF($Q87:$AH87,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ87">
+        <f>IF(AND($A87="Emparejamiento Ampliado",COUNTIF($D87:$H87,"?*")&lt;2),IF(COUNTIF($Q87:$AI87,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK87">
+        <f>IF(AND($A87="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I87),1)="A",LEFT(TRIM($I87),1)="B",LEFT(TRIM($I87),1)="C",LEFT(TRIM($I87),1)="D",LEFT(TRIM($I87),1)="E"))),IF(COUNTIF($Q87:$AJ87,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL87">
+        <f>IF(TRIM($K87)="",IF(COUNTIF($M87:$M87,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM87">
         <f>IF(AND(TRIM($K87)&lt;&gt;"",TRIM($K87)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M87:$N87,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="24" customHeight="1">
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="371" t="n"/>
+      <c r="B88" s="371" t="n"/>
+      <c r="C88" s="371" t="n"/>
+      <c r="D88" s="371">
+        <f>IF($A88="Verdadero o Falso Simple","Verdadero",IF($A88="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A88="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E88" s="371">
+        <f>IF($A88="Verdadero o Falso Simple","Falso",IF($A88="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A88="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F88" s="371">
+        <f>IF($A88="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A88="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G88" s="371">
+        <f>IF($A88="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A88="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H88" s="371">
+        <f>IF($A88="Verdadero o Falso Simple","",IF($A88="Respuesta A/B/Ambas/Ninguna","",IF($A88="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I88" s="371" t="n"/>
+      <c r="J88" s="372" t="n"/>
+      <c r="K88" s="372">
+        <f>IF(TRIM($A88)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L88" s="371">
+        <f>IF(TRIM($A88)="","",IF(OR($A88="Selección de la mejor respuesta",$A88="SELECCION_MEJOR_RESPUESTA",$A88="Subítem de caso o problema",$A88="SUBITEM_CASO"),IF(TRIM($C88)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D88:$H88&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I88)&lt;&gt;"",OR(LEFT(TRIM($I88),1)="A",LEFT(TRIM($I88),1)="B",LEFT(TRIM($I88),1)="C",LEFT(TRIM($I88),1)="D",LEFT(TRIM($I88),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A88)="","",IF(COUNTIF($Q88:$AJ88,"?*")=0,"OK","Falta revisar: "&amp;$Q88&amp;$R88&amp;$S88&amp;$T88&amp;$U88&amp;$V88&amp;$W88&amp;$X88&amp;$Y88&amp;$Z88&amp;$AA88&amp;$AB88&amp;$AC88&amp;$AD88&amp;$AE88&amp;$AF88&amp;$AG88&amp;$AH88&amp;$AI88&amp;$AJ88))))</f>
+        <v/>
+      </c>
+      <c r="M88" s="373" t="n"/>
+      <c r="Q88">
+        <f>IF(TRIM($C88)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R88">
+        <f>IF(TRIM($K88)="",IF(COUNTIF($Q88:$Q88,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S88">
         <f>IF(AND(TRIM($K88)&lt;&gt;"",TRIM($K88)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q88:$R88,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T88">
+        <f>IF(AND(OR($A88="Ítems agrupados por caso clínico o problema",$A88="Subítem de caso o problema",$A88="Emparejamiento Ampliado",$A88="Opción de Emparejamiento Ampliado"),TRIM($B88)=""),IF(COUNTIF($Q88:$S88,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U88">
+        <f>IF(AND(OR($A88="Verdadero o Falso Simple",$A88="Respuesta A/B/Ambas/Ninguna",$A88="Verdadero o Falso Complejas",$A88="Selección de la mejor respuesta",$A88="Subítem de caso o problema",$A88="Opción de Emparejamiento Ampliado"),TRIM($I88)=""),IF(COUNTIF($Q88:$T88,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V88">
+        <f>IF(AND(OR($A88="Verdadero o Falso Simple",$A88="Respuesta A/B/Ambas/Ninguna",$A88="Verdadero o Falso Complejas",$A88="Selección de la mejor respuesta",$A88="Subítem de caso o problema",$A88="Opción de Emparejamiento Ampliado"),TRIM($J88)=""),IF(COUNTIF($Q88:$U88,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W88">
+        <f>IF(AND(OR($A88="Ítems agrupados por caso clínico o problema",$A88="Emparejamiento Ampliado"),TRIM($I88)&lt;&gt;""),IF(COUNTIF($Q88:$V88,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X88">
+        <f>IF(AND(OR($A88="Ítems agrupados por caso clínico o problema",$A88="Emparejamiento Ampliado"),TRIM($J88)&lt;&gt;""),IF(COUNTIF($Q88:$W88,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y88">
+        <f>IF(AND($A88="Verdadero o Falso Simple",OR(COUNTIF($D88:$E88,"?*")&lt;2,COUNTIF($F88:$H88,"?*")&gt;0)),IF(COUNTIF($Q88:$X88,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z88">
+        <f>IF(AND($A88="Verdadero o Falso Simple",TRIM($I88)&lt;&gt;"",NOT(OR(LEFT(TRIM($I88),1)="A",LEFT(TRIM($I88),1)="B"))),IF(COUNTIF($Q88:$Y88,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA88">
+        <f>IF(AND($A88="Respuesta A/B/Ambas/Ninguna",COUNTIF($D88:$G88,"?*")&lt;4),IF(COUNTIF($Q88:$Z88,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB88">
+        <f>IF(AND($A88="Respuesta A/B/Ambas/Ninguna",COUNTIF($H88:$H88,"?*")&gt;0),IF(COUNTIF($Q88:$AA88,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC88">
+        <f>IF(AND($A88="Respuesta A/B/Ambas/Ninguna",TRIM($I88)&lt;&gt;"",NOT(OR(LEFT(TRIM($I88),1)="A",LEFT(TRIM($I88),1)="B",LEFT(TRIM($I88),1)="C",LEFT(TRIM($I88),1)="D"))),IF(COUNTIF($Q88:$AB88,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD88">
+        <f>IF(AND($A88="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D88,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E88,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F88,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G88,"4.","")))=0)),IF(COUNTIF($Q88:$AC88,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE88">
+        <f>IF(AND($A88="Verdadero o Falso Complejas",COUNTIF($H88:$H88,"?*")&gt;0),IF(COUNTIF($Q88:$AD88,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF88">
+        <f>IF(AND($A88="Verdadero o Falso Complejas",TRIM($I88)&lt;&gt;"",NOT(OR(LEFT(TRIM($I88),1)="A",LEFT(TRIM($I88),1)="B",LEFT(TRIM($I88),1)="C",LEFT(TRIM($I88),1)="D",LEFT(TRIM($I88),1)="E"))),IF(COUNTIF($Q88:$AE88,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG88">
+        <f>IF(AND(OR($A88="Selección de la mejor respuesta",$A88="Subítem de caso o problema"),COUNTA($D88:$H88)&lt;5),IF(COUNTIF($Q88:$AF88,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH88">
+        <f>IF(AND(OR($A88="Selección de la mejor respuesta",$A88="Subítem de caso o problema"),TRIM($I88)&lt;&gt;"",NOT(OR(LEFT(TRIM($I88),1)="A",LEFT(TRIM($I88),1)="B",LEFT(TRIM($I88),1)="C",LEFT(TRIM($I88),1)="D",LEFT(TRIM($I88),1)="E"))),IF(COUNTIF($Q88:$AG88,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI88">
+        <f>IF(AND(OR($A88="Ítems agrupados por caso clínico o problema",$A88="Opción de Emparejamiento Ampliado"),COUNTIF($D88:$H88,"?*")&gt;0),IF(COUNTIF($Q88:$AH88,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ88">
+        <f>IF(AND($A88="Emparejamiento Ampliado",COUNTIF($D88:$H88,"?*")&lt;2),IF(COUNTIF($Q88:$AI88,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK88">
+        <f>IF(AND($A88="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I88),1)="A",LEFT(TRIM($I88),1)="B",LEFT(TRIM($I88),1)="C",LEFT(TRIM($I88),1)="D",LEFT(TRIM($I88),1)="E"))),IF(COUNTIF($Q88:$AJ88,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL88">
+        <f>IF(TRIM($K88)="",IF(COUNTIF($M88:$M88,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM88">
         <f>IF(AND(TRIM($K88)&lt;&gt;"",TRIM($K88)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M88:$N88,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="24" customHeight="1">
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="371" t="n"/>
+      <c r="B89" s="371" t="n"/>
+      <c r="C89" s="371" t="n"/>
+      <c r="D89" s="371">
+        <f>IF($A89="Verdadero o Falso Simple","Verdadero",IF($A89="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A89="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E89" s="371">
+        <f>IF($A89="Verdadero o Falso Simple","Falso",IF($A89="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A89="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F89" s="371">
+        <f>IF($A89="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A89="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G89" s="371">
+        <f>IF($A89="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A89="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H89" s="371">
+        <f>IF($A89="Verdadero o Falso Simple","",IF($A89="Respuesta A/B/Ambas/Ninguna","",IF($A89="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I89" s="371" t="n"/>
+      <c r="J89" s="372" t="n"/>
+      <c r="K89" s="372">
+        <f>IF(TRIM($A89)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L89" s="371">
+        <f>IF(TRIM($A89)="","",IF(OR($A89="Selección de la mejor respuesta",$A89="SELECCION_MEJOR_RESPUESTA",$A89="Subítem de caso o problema",$A89="SUBITEM_CASO"),IF(TRIM($C89)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D89:$H89&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I89)&lt;&gt;"",OR(LEFT(TRIM($I89),1)="A",LEFT(TRIM($I89),1)="B",LEFT(TRIM($I89),1)="C",LEFT(TRIM($I89),1)="D",LEFT(TRIM($I89),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A89)="","",IF(COUNTIF($Q89:$AJ89,"?*")=0,"OK","Falta revisar: "&amp;$Q89&amp;$R89&amp;$S89&amp;$T89&amp;$U89&amp;$V89&amp;$W89&amp;$X89&amp;$Y89&amp;$Z89&amp;$AA89&amp;$AB89&amp;$AC89&amp;$AD89&amp;$AE89&amp;$AF89&amp;$AG89&amp;$AH89&amp;$AI89&amp;$AJ89))))</f>
+        <v/>
+      </c>
+      <c r="M89" s="373" t="n"/>
+      <c r="Q89">
+        <f>IF(TRIM($C89)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R89">
+        <f>IF(TRIM($K89)="",IF(COUNTIF($Q89:$Q89,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S89">
         <f>IF(AND(TRIM($K89)&lt;&gt;"",TRIM($K89)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q89:$R89,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T89">
+        <f>IF(AND(OR($A89="Ítems agrupados por caso clínico o problema",$A89="Subítem de caso o problema",$A89="Emparejamiento Ampliado",$A89="Opción de Emparejamiento Ampliado"),TRIM($B89)=""),IF(COUNTIF($Q89:$S89,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U89">
+        <f>IF(AND(OR($A89="Verdadero o Falso Simple",$A89="Respuesta A/B/Ambas/Ninguna",$A89="Verdadero o Falso Complejas",$A89="Selección de la mejor respuesta",$A89="Subítem de caso o problema",$A89="Opción de Emparejamiento Ampliado"),TRIM($I89)=""),IF(COUNTIF($Q89:$T89,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V89">
+        <f>IF(AND(OR($A89="Verdadero o Falso Simple",$A89="Respuesta A/B/Ambas/Ninguna",$A89="Verdadero o Falso Complejas",$A89="Selección de la mejor respuesta",$A89="Subítem de caso o problema",$A89="Opción de Emparejamiento Ampliado"),TRIM($J89)=""),IF(COUNTIF($Q89:$U89,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W89">
+        <f>IF(AND(OR($A89="Ítems agrupados por caso clínico o problema",$A89="Emparejamiento Ampliado"),TRIM($I89)&lt;&gt;""),IF(COUNTIF($Q89:$V89,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X89">
+        <f>IF(AND(OR($A89="Ítems agrupados por caso clínico o problema",$A89="Emparejamiento Ampliado"),TRIM($J89)&lt;&gt;""),IF(COUNTIF($Q89:$W89,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y89">
+        <f>IF(AND($A89="Verdadero o Falso Simple",OR(COUNTIF($D89:$E89,"?*")&lt;2,COUNTIF($F89:$H89,"?*")&gt;0)),IF(COUNTIF($Q89:$X89,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z89">
+        <f>IF(AND($A89="Verdadero o Falso Simple",TRIM($I89)&lt;&gt;"",NOT(OR(LEFT(TRIM($I89),1)="A",LEFT(TRIM($I89),1)="B"))),IF(COUNTIF($Q89:$Y89,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA89">
+        <f>IF(AND($A89="Respuesta A/B/Ambas/Ninguna",COUNTIF($D89:$G89,"?*")&lt;4),IF(COUNTIF($Q89:$Z89,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB89">
+        <f>IF(AND($A89="Respuesta A/B/Ambas/Ninguna",COUNTIF($H89:$H89,"?*")&gt;0),IF(COUNTIF($Q89:$AA89,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC89">
+        <f>IF(AND($A89="Respuesta A/B/Ambas/Ninguna",TRIM($I89)&lt;&gt;"",NOT(OR(LEFT(TRIM($I89),1)="A",LEFT(TRIM($I89),1)="B",LEFT(TRIM($I89),1)="C",LEFT(TRIM($I89),1)="D"))),IF(COUNTIF($Q89:$AB89,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD89">
+        <f>IF(AND($A89="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D89,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E89,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F89,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G89,"4.","")))=0)),IF(COUNTIF($Q89:$AC89,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE89">
+        <f>IF(AND($A89="Verdadero o Falso Complejas",COUNTIF($H89:$H89,"?*")&gt;0),IF(COUNTIF($Q89:$AD89,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF89">
+        <f>IF(AND($A89="Verdadero o Falso Complejas",TRIM($I89)&lt;&gt;"",NOT(OR(LEFT(TRIM($I89),1)="A",LEFT(TRIM($I89),1)="B",LEFT(TRIM($I89),1)="C",LEFT(TRIM($I89),1)="D",LEFT(TRIM($I89),1)="E"))),IF(COUNTIF($Q89:$AE89,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG89">
+        <f>IF(AND(OR($A89="Selección de la mejor respuesta",$A89="Subítem de caso o problema"),COUNTA($D89:$H89)&lt;5),IF(COUNTIF($Q89:$AF89,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH89">
+        <f>IF(AND(OR($A89="Selección de la mejor respuesta",$A89="Subítem de caso o problema"),TRIM($I89)&lt;&gt;"",NOT(OR(LEFT(TRIM($I89),1)="A",LEFT(TRIM($I89),1)="B",LEFT(TRIM($I89),1)="C",LEFT(TRIM($I89),1)="D",LEFT(TRIM($I89),1)="E"))),IF(COUNTIF($Q89:$AG89,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI89">
+        <f>IF(AND(OR($A89="Ítems agrupados por caso clínico o problema",$A89="Opción de Emparejamiento Ampliado"),COUNTIF($D89:$H89,"?*")&gt;0),IF(COUNTIF($Q89:$AH89,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ89">
+        <f>IF(AND($A89="Emparejamiento Ampliado",COUNTIF($D89:$H89,"?*")&lt;2),IF(COUNTIF($Q89:$AI89,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK89">
+        <f>IF(AND($A89="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I89),1)="A",LEFT(TRIM($I89),1)="B",LEFT(TRIM($I89),1)="C",LEFT(TRIM($I89),1)="D",LEFT(TRIM($I89),1)="E"))),IF(COUNTIF($Q89:$AJ89,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL89">
+        <f>IF(TRIM($K89)="",IF(COUNTIF($M89:$M89,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM89">
         <f>IF(AND(TRIM($K89)&lt;&gt;"",TRIM($K89)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M89:$N89,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="90" ht="24" customHeight="1">
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="371" t="n"/>
+      <c r="B90" s="371" t="n"/>
+      <c r="C90" s="371" t="n"/>
+      <c r="D90" s="371">
+        <f>IF($A90="Verdadero o Falso Simple","Verdadero",IF($A90="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A90="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E90" s="371">
+        <f>IF($A90="Verdadero o Falso Simple","Falso",IF($A90="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A90="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F90" s="371">
+        <f>IF($A90="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A90="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G90" s="371">
+        <f>IF($A90="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A90="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H90" s="371">
+        <f>IF($A90="Verdadero o Falso Simple","",IF($A90="Respuesta A/B/Ambas/Ninguna","",IF($A90="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I90" s="371" t="n"/>
+      <c r="J90" s="372" t="n"/>
+      <c r="K90" s="372">
+        <f>IF(TRIM($A90)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L90" s="371">
+        <f>IF(TRIM($A90)="","",IF(OR($A90="Selección de la mejor respuesta",$A90="SELECCION_MEJOR_RESPUESTA",$A90="Subítem de caso o problema",$A90="SUBITEM_CASO"),IF(TRIM($C90)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D90:$H90&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I90)&lt;&gt;"",OR(LEFT(TRIM($I90),1)="A",LEFT(TRIM($I90),1)="B",LEFT(TRIM($I90),1)="C",LEFT(TRIM($I90),1)="D",LEFT(TRIM($I90),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A90)="","",IF(COUNTIF($Q90:$AJ90,"?*")=0,"OK","Falta revisar: "&amp;$Q90&amp;$R90&amp;$S90&amp;$T90&amp;$U90&amp;$V90&amp;$W90&amp;$X90&amp;$Y90&amp;$Z90&amp;$AA90&amp;$AB90&amp;$AC90&amp;$AD90&amp;$AE90&amp;$AF90&amp;$AG90&amp;$AH90&amp;$AI90&amp;$AJ90))))</f>
+        <v/>
+      </c>
+      <c r="M90" s="373" t="n"/>
+      <c r="Q90">
+        <f>IF(TRIM($C90)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R90">
+        <f>IF(TRIM($K90)="",IF(COUNTIF($Q90:$Q90,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S90">
         <f>IF(AND(TRIM($K90)&lt;&gt;"",TRIM($K90)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q90:$R90,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T90">
+        <f>IF(AND(OR($A90="Ítems agrupados por caso clínico o problema",$A90="Subítem de caso o problema",$A90="Emparejamiento Ampliado",$A90="Opción de Emparejamiento Ampliado"),TRIM($B90)=""),IF(COUNTIF($Q90:$S90,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U90">
+        <f>IF(AND(OR($A90="Verdadero o Falso Simple",$A90="Respuesta A/B/Ambas/Ninguna",$A90="Verdadero o Falso Complejas",$A90="Selección de la mejor respuesta",$A90="Subítem de caso o problema",$A90="Opción de Emparejamiento Ampliado"),TRIM($I90)=""),IF(COUNTIF($Q90:$T90,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V90">
+        <f>IF(AND(OR($A90="Verdadero o Falso Simple",$A90="Respuesta A/B/Ambas/Ninguna",$A90="Verdadero o Falso Complejas",$A90="Selección de la mejor respuesta",$A90="Subítem de caso o problema",$A90="Opción de Emparejamiento Ampliado"),TRIM($J90)=""),IF(COUNTIF($Q90:$U90,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W90">
+        <f>IF(AND(OR($A90="Ítems agrupados por caso clínico o problema",$A90="Emparejamiento Ampliado"),TRIM($I90)&lt;&gt;""),IF(COUNTIF($Q90:$V90,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X90">
+        <f>IF(AND(OR($A90="Ítems agrupados por caso clínico o problema",$A90="Emparejamiento Ampliado"),TRIM($J90)&lt;&gt;""),IF(COUNTIF($Q90:$W90,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y90">
+        <f>IF(AND($A90="Verdadero o Falso Simple",OR(COUNTIF($D90:$E90,"?*")&lt;2,COUNTIF($F90:$H90,"?*")&gt;0)),IF(COUNTIF($Q90:$X90,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z90">
+        <f>IF(AND($A90="Verdadero o Falso Simple",TRIM($I90)&lt;&gt;"",NOT(OR(LEFT(TRIM($I90),1)="A",LEFT(TRIM($I90),1)="B"))),IF(COUNTIF($Q90:$Y90,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA90">
+        <f>IF(AND($A90="Respuesta A/B/Ambas/Ninguna",COUNTIF($D90:$G90,"?*")&lt;4),IF(COUNTIF($Q90:$Z90,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB90">
+        <f>IF(AND($A90="Respuesta A/B/Ambas/Ninguna",COUNTIF($H90:$H90,"?*")&gt;0),IF(COUNTIF($Q90:$AA90,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC90">
+        <f>IF(AND($A90="Respuesta A/B/Ambas/Ninguna",TRIM($I90)&lt;&gt;"",NOT(OR(LEFT(TRIM($I90),1)="A",LEFT(TRIM($I90),1)="B",LEFT(TRIM($I90),1)="C",LEFT(TRIM($I90),1)="D"))),IF(COUNTIF($Q90:$AB90,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD90">
+        <f>IF(AND($A90="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D90,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E90,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F90,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G90,"4.","")))=0)),IF(COUNTIF($Q90:$AC90,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE90">
+        <f>IF(AND($A90="Verdadero o Falso Complejas",COUNTIF($H90:$H90,"?*")&gt;0),IF(COUNTIF($Q90:$AD90,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF90">
+        <f>IF(AND($A90="Verdadero o Falso Complejas",TRIM($I90)&lt;&gt;"",NOT(OR(LEFT(TRIM($I90),1)="A",LEFT(TRIM($I90),1)="B",LEFT(TRIM($I90),1)="C",LEFT(TRIM($I90),1)="D",LEFT(TRIM($I90),1)="E"))),IF(COUNTIF($Q90:$AE90,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG90">
+        <f>IF(AND(OR($A90="Selección de la mejor respuesta",$A90="Subítem de caso o problema"),COUNTA($D90:$H90)&lt;5),IF(COUNTIF($Q90:$AF90,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH90">
+        <f>IF(AND(OR($A90="Selección de la mejor respuesta",$A90="Subítem de caso o problema"),TRIM($I90)&lt;&gt;"",NOT(OR(LEFT(TRIM($I90),1)="A",LEFT(TRIM($I90),1)="B",LEFT(TRIM($I90),1)="C",LEFT(TRIM($I90),1)="D",LEFT(TRIM($I90),1)="E"))),IF(COUNTIF($Q90:$AG90,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI90">
+        <f>IF(AND(OR($A90="Ítems agrupados por caso clínico o problema",$A90="Opción de Emparejamiento Ampliado"),COUNTIF($D90:$H90,"?*")&gt;0),IF(COUNTIF($Q90:$AH90,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ90">
+        <f>IF(AND($A90="Emparejamiento Ampliado",COUNTIF($D90:$H90,"?*")&lt;2),IF(COUNTIF($Q90:$AI90,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK90">
+        <f>IF(AND($A90="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I90),1)="A",LEFT(TRIM($I90),1)="B",LEFT(TRIM($I90),1)="C",LEFT(TRIM($I90),1)="D",LEFT(TRIM($I90),1)="E"))),IF(COUNTIF($Q90:$AJ90,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL90">
+        <f>IF(TRIM($K90)="",IF(COUNTIF($M90:$M90,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM90">
         <f>IF(AND(TRIM($K90)&lt;&gt;"",TRIM($K90)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M90:$N90,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="91" ht="24" customHeight="1">
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="371" t="n"/>
+      <c r="B91" s="371" t="n"/>
+      <c r="C91" s="371" t="n"/>
+      <c r="D91" s="371">
+        <f>IF($A91="Verdadero o Falso Simple","Verdadero",IF($A91="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A91="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E91" s="371">
+        <f>IF($A91="Verdadero o Falso Simple","Falso",IF($A91="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A91="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F91" s="371">
+        <f>IF($A91="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A91="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G91" s="371">
+        <f>IF($A91="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A91="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H91" s="371">
+        <f>IF($A91="Verdadero o Falso Simple","",IF($A91="Respuesta A/B/Ambas/Ninguna","",IF($A91="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I91" s="371" t="n"/>
+      <c r="J91" s="372" t="n"/>
+      <c r="K91" s="372">
+        <f>IF(TRIM($A91)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L91" s="371">
+        <f>IF(TRIM($A91)="","",IF(OR($A91="Selección de la mejor respuesta",$A91="SELECCION_MEJOR_RESPUESTA",$A91="Subítem de caso o problema",$A91="SUBITEM_CASO"),IF(TRIM($C91)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D91:$H91&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I91)&lt;&gt;"",OR(LEFT(TRIM($I91),1)="A",LEFT(TRIM($I91),1)="B",LEFT(TRIM($I91),1)="C",LEFT(TRIM($I91),1)="D",LEFT(TRIM($I91),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A91)="","",IF(COUNTIF($Q91:$AJ91,"?*")=0,"OK","Falta revisar: "&amp;$Q91&amp;$R91&amp;$S91&amp;$T91&amp;$U91&amp;$V91&amp;$W91&amp;$X91&amp;$Y91&amp;$Z91&amp;$AA91&amp;$AB91&amp;$AC91&amp;$AD91&amp;$AE91&amp;$AF91&amp;$AG91&amp;$AH91&amp;$AI91&amp;$AJ91))))</f>
+        <v/>
+      </c>
+      <c r="M91" s="373" t="n"/>
+      <c r="Q91">
+        <f>IF(TRIM($C91)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R91">
+        <f>IF(TRIM($K91)="",IF(COUNTIF($Q91:$Q91,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S91">
         <f>IF(AND(TRIM($K91)&lt;&gt;"",TRIM($K91)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q91:$R91,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T91">
+        <f>IF(AND(OR($A91="Ítems agrupados por caso clínico o problema",$A91="Subítem de caso o problema",$A91="Emparejamiento Ampliado",$A91="Opción de Emparejamiento Ampliado"),TRIM($B91)=""),IF(COUNTIF($Q91:$S91,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U91">
+        <f>IF(AND(OR($A91="Verdadero o Falso Simple",$A91="Respuesta A/B/Ambas/Ninguna",$A91="Verdadero o Falso Complejas",$A91="Selección de la mejor respuesta",$A91="Subítem de caso o problema",$A91="Opción de Emparejamiento Ampliado"),TRIM($I91)=""),IF(COUNTIF($Q91:$T91,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V91">
+        <f>IF(AND(OR($A91="Verdadero o Falso Simple",$A91="Respuesta A/B/Ambas/Ninguna",$A91="Verdadero o Falso Complejas",$A91="Selección de la mejor respuesta",$A91="Subítem de caso o problema",$A91="Opción de Emparejamiento Ampliado"),TRIM($J91)=""),IF(COUNTIF($Q91:$U91,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W91">
+        <f>IF(AND(OR($A91="Ítems agrupados por caso clínico o problema",$A91="Emparejamiento Ampliado"),TRIM($I91)&lt;&gt;""),IF(COUNTIF($Q91:$V91,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X91">
+        <f>IF(AND(OR($A91="Ítems agrupados por caso clínico o problema",$A91="Emparejamiento Ampliado"),TRIM($J91)&lt;&gt;""),IF(COUNTIF($Q91:$W91,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y91">
+        <f>IF(AND($A91="Verdadero o Falso Simple",OR(COUNTIF($D91:$E91,"?*")&lt;2,COUNTIF($F91:$H91,"?*")&gt;0)),IF(COUNTIF($Q91:$X91,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z91">
+        <f>IF(AND($A91="Verdadero o Falso Simple",TRIM($I91)&lt;&gt;"",NOT(OR(LEFT(TRIM($I91),1)="A",LEFT(TRIM($I91),1)="B"))),IF(COUNTIF($Q91:$Y91,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA91">
+        <f>IF(AND($A91="Respuesta A/B/Ambas/Ninguna",COUNTIF($D91:$G91,"?*")&lt;4),IF(COUNTIF($Q91:$Z91,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB91">
+        <f>IF(AND($A91="Respuesta A/B/Ambas/Ninguna",COUNTIF($H91:$H91,"?*")&gt;0),IF(COUNTIF($Q91:$AA91,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC91">
+        <f>IF(AND($A91="Respuesta A/B/Ambas/Ninguna",TRIM($I91)&lt;&gt;"",NOT(OR(LEFT(TRIM($I91),1)="A",LEFT(TRIM($I91),1)="B",LEFT(TRIM($I91),1)="C",LEFT(TRIM($I91),1)="D"))),IF(COUNTIF($Q91:$AB91,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD91">
+        <f>IF(AND($A91="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D91,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E91,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F91,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G91,"4.","")))=0)),IF(COUNTIF($Q91:$AC91,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE91">
+        <f>IF(AND($A91="Verdadero o Falso Complejas",COUNTIF($H91:$H91,"?*")&gt;0),IF(COUNTIF($Q91:$AD91,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF91">
+        <f>IF(AND($A91="Verdadero o Falso Complejas",TRIM($I91)&lt;&gt;"",NOT(OR(LEFT(TRIM($I91),1)="A",LEFT(TRIM($I91),1)="B",LEFT(TRIM($I91),1)="C",LEFT(TRIM($I91),1)="D",LEFT(TRIM($I91),1)="E"))),IF(COUNTIF($Q91:$AE91,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG91">
+        <f>IF(AND(OR($A91="Selección de la mejor respuesta",$A91="Subítem de caso o problema"),COUNTA($D91:$H91)&lt;5),IF(COUNTIF($Q91:$AF91,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH91">
+        <f>IF(AND(OR($A91="Selección de la mejor respuesta",$A91="Subítem de caso o problema"),TRIM($I91)&lt;&gt;"",NOT(OR(LEFT(TRIM($I91),1)="A",LEFT(TRIM($I91),1)="B",LEFT(TRIM($I91),1)="C",LEFT(TRIM($I91),1)="D",LEFT(TRIM($I91),1)="E"))),IF(COUNTIF($Q91:$AG91,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI91">
+        <f>IF(AND(OR($A91="Ítems agrupados por caso clínico o problema",$A91="Opción de Emparejamiento Ampliado"),COUNTIF($D91:$H91,"?*")&gt;0),IF(COUNTIF($Q91:$AH91,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ91">
+        <f>IF(AND($A91="Emparejamiento Ampliado",COUNTIF($D91:$H91,"?*")&lt;2),IF(COUNTIF($Q91:$AI91,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK91">
+        <f>IF(AND($A91="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I91),1)="A",LEFT(TRIM($I91),1)="B",LEFT(TRIM($I91),1)="C",LEFT(TRIM($I91),1)="D",LEFT(TRIM($I91),1)="E"))),IF(COUNTIF($Q91:$AJ91,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL91">
+        <f>IF(TRIM($K91)="",IF(COUNTIF($M91:$M91,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM91">
         <f>IF(AND(TRIM($K91)&lt;&gt;"",TRIM($K91)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M91:$N91,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="92" ht="24" customHeight="1">
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="371" t="n"/>
+      <c r="B92" s="371" t="n"/>
+      <c r="C92" s="371" t="n"/>
+      <c r="D92" s="371">
+        <f>IF($A92="Verdadero o Falso Simple","Verdadero",IF($A92="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A92="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E92" s="371">
+        <f>IF($A92="Verdadero o Falso Simple","Falso",IF($A92="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A92="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F92" s="371">
+        <f>IF($A92="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A92="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G92" s="371">
+        <f>IF($A92="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A92="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H92" s="371">
+        <f>IF($A92="Verdadero o Falso Simple","",IF($A92="Respuesta A/B/Ambas/Ninguna","",IF($A92="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I92" s="371" t="n"/>
+      <c r="J92" s="372" t="n"/>
+      <c r="K92" s="372">
+        <f>IF(TRIM($A92)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L92" s="371">
+        <f>IF(TRIM($A92)="","",IF(OR($A92="Selección de la mejor respuesta",$A92="SELECCION_MEJOR_RESPUESTA",$A92="Subítem de caso o problema",$A92="SUBITEM_CASO"),IF(TRIM($C92)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D92:$H92&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I92)&lt;&gt;"",OR(LEFT(TRIM($I92),1)="A",LEFT(TRIM($I92),1)="B",LEFT(TRIM($I92),1)="C",LEFT(TRIM($I92),1)="D",LEFT(TRIM($I92),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A92)="","",IF(COUNTIF($Q92:$AJ92,"?*")=0,"OK","Falta revisar: "&amp;$Q92&amp;$R92&amp;$S92&amp;$T92&amp;$U92&amp;$V92&amp;$W92&amp;$X92&amp;$Y92&amp;$Z92&amp;$AA92&amp;$AB92&amp;$AC92&amp;$AD92&amp;$AE92&amp;$AF92&amp;$AG92&amp;$AH92&amp;$AI92&amp;$AJ92))))</f>
+        <v/>
+      </c>
+      <c r="M92" s="373" t="n"/>
+      <c r="Q92">
+        <f>IF(TRIM($C92)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R92">
+        <f>IF(TRIM($K92)="",IF(COUNTIF($Q92:$Q92,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S92">
         <f>IF(AND(TRIM($K92)&lt;&gt;"",TRIM($K92)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q92:$R92,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T92">
+        <f>IF(AND(OR($A92="Ítems agrupados por caso clínico o problema",$A92="Subítem de caso o problema",$A92="Emparejamiento Ampliado",$A92="Opción de Emparejamiento Ampliado"),TRIM($B92)=""),IF(COUNTIF($Q92:$S92,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U92">
+        <f>IF(AND(OR($A92="Verdadero o Falso Simple",$A92="Respuesta A/B/Ambas/Ninguna",$A92="Verdadero o Falso Complejas",$A92="Selección de la mejor respuesta",$A92="Subítem de caso o problema",$A92="Opción de Emparejamiento Ampliado"),TRIM($I92)=""),IF(COUNTIF($Q92:$T92,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V92">
+        <f>IF(AND(OR($A92="Verdadero o Falso Simple",$A92="Respuesta A/B/Ambas/Ninguna",$A92="Verdadero o Falso Complejas",$A92="Selección de la mejor respuesta",$A92="Subítem de caso o problema",$A92="Opción de Emparejamiento Ampliado"),TRIM($J92)=""),IF(COUNTIF($Q92:$U92,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W92">
+        <f>IF(AND(OR($A92="Ítems agrupados por caso clínico o problema",$A92="Emparejamiento Ampliado"),TRIM($I92)&lt;&gt;""),IF(COUNTIF($Q92:$V92,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X92">
+        <f>IF(AND(OR($A92="Ítems agrupados por caso clínico o problema",$A92="Emparejamiento Ampliado"),TRIM($J92)&lt;&gt;""),IF(COUNTIF($Q92:$W92,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y92">
+        <f>IF(AND($A92="Verdadero o Falso Simple",OR(COUNTIF($D92:$E92,"?*")&lt;2,COUNTIF($F92:$H92,"?*")&gt;0)),IF(COUNTIF($Q92:$X92,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z92">
+        <f>IF(AND($A92="Verdadero o Falso Simple",TRIM($I92)&lt;&gt;"",NOT(OR(LEFT(TRIM($I92),1)="A",LEFT(TRIM($I92),1)="B"))),IF(COUNTIF($Q92:$Y92,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA92">
+        <f>IF(AND($A92="Respuesta A/B/Ambas/Ninguna",COUNTIF($D92:$G92,"?*")&lt;4),IF(COUNTIF($Q92:$Z92,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB92">
+        <f>IF(AND($A92="Respuesta A/B/Ambas/Ninguna",COUNTIF($H92:$H92,"?*")&gt;0),IF(COUNTIF($Q92:$AA92,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC92">
+        <f>IF(AND($A92="Respuesta A/B/Ambas/Ninguna",TRIM($I92)&lt;&gt;"",NOT(OR(LEFT(TRIM($I92),1)="A",LEFT(TRIM($I92),1)="B",LEFT(TRIM($I92),1)="C",LEFT(TRIM($I92),1)="D"))),IF(COUNTIF($Q92:$AB92,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD92">
+        <f>IF(AND($A92="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D92,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E92,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F92,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G92,"4.","")))=0)),IF(COUNTIF($Q92:$AC92,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE92">
+        <f>IF(AND($A92="Verdadero o Falso Complejas",COUNTIF($H92:$H92,"?*")&gt;0),IF(COUNTIF($Q92:$AD92,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF92">
+        <f>IF(AND($A92="Verdadero o Falso Complejas",TRIM($I92)&lt;&gt;"",NOT(OR(LEFT(TRIM($I92),1)="A",LEFT(TRIM($I92),1)="B",LEFT(TRIM($I92),1)="C",LEFT(TRIM($I92),1)="D",LEFT(TRIM($I92),1)="E"))),IF(COUNTIF($Q92:$AE92,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG92">
+        <f>IF(AND(OR($A92="Selección de la mejor respuesta",$A92="Subítem de caso o problema"),COUNTA($D92:$H92)&lt;5),IF(COUNTIF($Q92:$AF92,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH92">
+        <f>IF(AND(OR($A92="Selección de la mejor respuesta",$A92="Subítem de caso o problema"),TRIM($I92)&lt;&gt;"",NOT(OR(LEFT(TRIM($I92),1)="A",LEFT(TRIM($I92),1)="B",LEFT(TRIM($I92),1)="C",LEFT(TRIM($I92),1)="D",LEFT(TRIM($I92),1)="E"))),IF(COUNTIF($Q92:$AG92,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI92">
+        <f>IF(AND(OR($A92="Ítems agrupados por caso clínico o problema",$A92="Opción de Emparejamiento Ampliado"),COUNTIF($D92:$H92,"?*")&gt;0),IF(COUNTIF($Q92:$AH92,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ92">
+        <f>IF(AND($A92="Emparejamiento Ampliado",COUNTIF($D92:$H92,"?*")&lt;2),IF(COUNTIF($Q92:$AI92,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK92">
+        <f>IF(AND($A92="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I92),1)="A",LEFT(TRIM($I92),1)="B",LEFT(TRIM($I92),1)="C",LEFT(TRIM($I92),1)="D",LEFT(TRIM($I92),1)="E"))),IF(COUNTIF($Q92:$AJ92,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL92">
+        <f>IF(TRIM($K92)="",IF(COUNTIF($M92:$M92,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM92">
         <f>IF(AND(TRIM($K92)&lt;&gt;"",TRIM($K92)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M92:$N92,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="93" ht="24" customHeight="1">
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="371" t="n"/>
+      <c r="B93" s="371" t="n"/>
+      <c r="C93" s="371" t="n"/>
+      <c r="D93" s="371">
+        <f>IF($A93="Verdadero o Falso Simple","Verdadero",IF($A93="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A93="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E93" s="371">
+        <f>IF($A93="Verdadero o Falso Simple","Falso",IF($A93="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A93="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F93" s="371">
+        <f>IF($A93="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A93="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G93" s="371">
+        <f>IF($A93="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A93="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H93" s="371">
+        <f>IF($A93="Verdadero o Falso Simple","",IF($A93="Respuesta A/B/Ambas/Ninguna","",IF($A93="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I93" s="371" t="n"/>
+      <c r="J93" s="372" t="n"/>
+      <c r="K93" s="372">
+        <f>IF(TRIM($A93)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L93" s="371">
+        <f>IF(TRIM($A93)="","",IF(OR($A93="Selección de la mejor respuesta",$A93="SELECCION_MEJOR_RESPUESTA",$A93="Subítem de caso o problema",$A93="SUBITEM_CASO"),IF(TRIM($C93)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D93:$H93&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I93)&lt;&gt;"",OR(LEFT(TRIM($I93),1)="A",LEFT(TRIM($I93),1)="B",LEFT(TRIM($I93),1)="C",LEFT(TRIM($I93),1)="D",LEFT(TRIM($I93),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A93)="","",IF(COUNTIF($Q93:$AJ93,"?*")=0,"OK","Falta revisar: "&amp;$Q93&amp;$R93&amp;$S93&amp;$T93&amp;$U93&amp;$V93&amp;$W93&amp;$X93&amp;$Y93&amp;$Z93&amp;$AA93&amp;$AB93&amp;$AC93&amp;$AD93&amp;$AE93&amp;$AF93&amp;$AG93&amp;$AH93&amp;$AI93&amp;$AJ93))))</f>
+        <v/>
+      </c>
+      <c r="M93" s="373" t="n"/>
+      <c r="Q93">
+        <f>IF(TRIM($C93)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R93">
+        <f>IF(TRIM($K93)="",IF(COUNTIF($Q93:$Q93,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S93">
         <f>IF(AND(TRIM($K93)&lt;&gt;"",TRIM($K93)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q93:$R93,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T93">
+        <f>IF(AND(OR($A93="Ítems agrupados por caso clínico o problema",$A93="Subítem de caso o problema",$A93="Emparejamiento Ampliado",$A93="Opción de Emparejamiento Ampliado"),TRIM($B93)=""),IF(COUNTIF($Q93:$S93,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U93">
+        <f>IF(AND(OR($A93="Verdadero o Falso Simple",$A93="Respuesta A/B/Ambas/Ninguna",$A93="Verdadero o Falso Complejas",$A93="Selección de la mejor respuesta",$A93="Subítem de caso o problema",$A93="Opción de Emparejamiento Ampliado"),TRIM($I93)=""),IF(COUNTIF($Q93:$T93,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V93">
+        <f>IF(AND(OR($A93="Verdadero o Falso Simple",$A93="Respuesta A/B/Ambas/Ninguna",$A93="Verdadero o Falso Complejas",$A93="Selección de la mejor respuesta",$A93="Subítem de caso o problema",$A93="Opción de Emparejamiento Ampliado"),TRIM($J93)=""),IF(COUNTIF($Q93:$U93,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W93">
+        <f>IF(AND(OR($A93="Ítems agrupados por caso clínico o problema",$A93="Emparejamiento Ampliado"),TRIM($I93)&lt;&gt;""),IF(COUNTIF($Q93:$V93,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X93">
+        <f>IF(AND(OR($A93="Ítems agrupados por caso clínico o problema",$A93="Emparejamiento Ampliado"),TRIM($J93)&lt;&gt;""),IF(COUNTIF($Q93:$W93,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y93">
+        <f>IF(AND($A93="Verdadero o Falso Simple",OR(COUNTIF($D93:$E93,"?*")&lt;2,COUNTIF($F93:$H93,"?*")&gt;0)),IF(COUNTIF($Q93:$X93,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z93">
+        <f>IF(AND($A93="Verdadero o Falso Simple",TRIM($I93)&lt;&gt;"",NOT(OR(LEFT(TRIM($I93),1)="A",LEFT(TRIM($I93),1)="B"))),IF(COUNTIF($Q93:$Y93,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA93">
+        <f>IF(AND($A93="Respuesta A/B/Ambas/Ninguna",COUNTIF($D93:$G93,"?*")&lt;4),IF(COUNTIF($Q93:$Z93,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB93">
+        <f>IF(AND($A93="Respuesta A/B/Ambas/Ninguna",COUNTIF($H93:$H93,"?*")&gt;0),IF(COUNTIF($Q93:$AA93,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC93">
+        <f>IF(AND($A93="Respuesta A/B/Ambas/Ninguna",TRIM($I93)&lt;&gt;"",NOT(OR(LEFT(TRIM($I93),1)="A",LEFT(TRIM($I93),1)="B",LEFT(TRIM($I93),1)="C",LEFT(TRIM($I93),1)="D"))),IF(COUNTIF($Q93:$AB93,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD93">
+        <f>IF(AND($A93="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D93,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E93,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F93,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G93,"4.","")))=0)),IF(COUNTIF($Q93:$AC93,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE93">
+        <f>IF(AND($A93="Verdadero o Falso Complejas",COUNTIF($H93:$H93,"?*")&gt;0),IF(COUNTIF($Q93:$AD93,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF93">
+        <f>IF(AND($A93="Verdadero o Falso Complejas",TRIM($I93)&lt;&gt;"",NOT(OR(LEFT(TRIM($I93),1)="A",LEFT(TRIM($I93),1)="B",LEFT(TRIM($I93),1)="C",LEFT(TRIM($I93),1)="D",LEFT(TRIM($I93),1)="E"))),IF(COUNTIF($Q93:$AE93,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG93">
+        <f>IF(AND(OR($A93="Selección de la mejor respuesta",$A93="Subítem de caso o problema"),COUNTA($D93:$H93)&lt;5),IF(COUNTIF($Q93:$AF93,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH93">
+        <f>IF(AND(OR($A93="Selección de la mejor respuesta",$A93="Subítem de caso o problema"),TRIM($I93)&lt;&gt;"",NOT(OR(LEFT(TRIM($I93),1)="A",LEFT(TRIM($I93),1)="B",LEFT(TRIM($I93),1)="C",LEFT(TRIM($I93),1)="D",LEFT(TRIM($I93),1)="E"))),IF(COUNTIF($Q93:$AG93,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI93">
+        <f>IF(AND(OR($A93="Ítems agrupados por caso clínico o problema",$A93="Opción de Emparejamiento Ampliado"),COUNTIF($D93:$H93,"?*")&gt;0),IF(COUNTIF($Q93:$AH93,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ93">
+        <f>IF(AND($A93="Emparejamiento Ampliado",COUNTIF($D93:$H93,"?*")&lt;2),IF(COUNTIF($Q93:$AI93,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK93">
+        <f>IF(AND($A93="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I93),1)="A",LEFT(TRIM($I93),1)="B",LEFT(TRIM($I93),1)="C",LEFT(TRIM($I93),1)="D",LEFT(TRIM($I93),1)="E"))),IF(COUNTIF($Q93:$AJ93,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL93">
+        <f>IF(TRIM($K93)="",IF(COUNTIF($M93:$M93,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM93">
         <f>IF(AND(TRIM($K93)&lt;&gt;"",TRIM($K93)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M93:$N93,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="94" ht="24" customHeight="1">
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="371" t="n"/>
+      <c r="B94" s="371" t="n"/>
+      <c r="C94" s="371" t="n"/>
+      <c r="D94" s="371">
+        <f>IF($A94="Verdadero o Falso Simple","Verdadero",IF($A94="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A94="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E94" s="371">
+        <f>IF($A94="Verdadero o Falso Simple","Falso",IF($A94="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A94="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F94" s="371">
+        <f>IF($A94="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A94="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G94" s="371">
+        <f>IF($A94="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A94="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H94" s="371">
+        <f>IF($A94="Verdadero o Falso Simple","",IF($A94="Respuesta A/B/Ambas/Ninguna","",IF($A94="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I94" s="371" t="n"/>
+      <c r="J94" s="372" t="n"/>
+      <c r="K94" s="372">
+        <f>IF(TRIM($A94)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L94" s="371">
+        <f>IF(TRIM($A94)="","",IF(OR($A94="Selección de la mejor respuesta",$A94="SELECCION_MEJOR_RESPUESTA",$A94="Subítem de caso o problema",$A94="SUBITEM_CASO"),IF(TRIM($C94)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D94:$H94&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I94)&lt;&gt;"",OR(LEFT(TRIM($I94),1)="A",LEFT(TRIM($I94),1)="B",LEFT(TRIM($I94),1)="C",LEFT(TRIM($I94),1)="D",LEFT(TRIM($I94),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A94)="","",IF(COUNTIF($Q94:$AJ94,"?*")=0,"OK","Falta revisar: "&amp;$Q94&amp;$R94&amp;$S94&amp;$T94&amp;$U94&amp;$V94&amp;$W94&amp;$X94&amp;$Y94&amp;$Z94&amp;$AA94&amp;$AB94&amp;$AC94&amp;$AD94&amp;$AE94&amp;$AF94&amp;$AG94&amp;$AH94&amp;$AI94&amp;$AJ94))))</f>
+        <v/>
+      </c>
+      <c r="M94" s="373" t="n"/>
+      <c r="Q94">
+        <f>IF(TRIM($C94)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R94">
+        <f>IF(TRIM($K94)="",IF(COUNTIF($Q94:$Q94,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S94">
         <f>IF(AND(TRIM($K94)&lt;&gt;"",TRIM($K94)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q94:$R94,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T94">
+        <f>IF(AND(OR($A94="Ítems agrupados por caso clínico o problema",$A94="Subítem de caso o problema",$A94="Emparejamiento Ampliado",$A94="Opción de Emparejamiento Ampliado"),TRIM($B94)=""),IF(COUNTIF($Q94:$S94,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U94">
+        <f>IF(AND(OR($A94="Verdadero o Falso Simple",$A94="Respuesta A/B/Ambas/Ninguna",$A94="Verdadero o Falso Complejas",$A94="Selección de la mejor respuesta",$A94="Subítem de caso o problema",$A94="Opción de Emparejamiento Ampliado"),TRIM($I94)=""),IF(COUNTIF($Q94:$T94,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V94">
+        <f>IF(AND(OR($A94="Verdadero o Falso Simple",$A94="Respuesta A/B/Ambas/Ninguna",$A94="Verdadero o Falso Complejas",$A94="Selección de la mejor respuesta",$A94="Subítem de caso o problema",$A94="Opción de Emparejamiento Ampliado"),TRIM($J94)=""),IF(COUNTIF($Q94:$U94,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W94">
+        <f>IF(AND(OR($A94="Ítems agrupados por caso clínico o problema",$A94="Emparejamiento Ampliado"),TRIM($I94)&lt;&gt;""),IF(COUNTIF($Q94:$V94,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X94">
+        <f>IF(AND(OR($A94="Ítems agrupados por caso clínico o problema",$A94="Emparejamiento Ampliado"),TRIM($J94)&lt;&gt;""),IF(COUNTIF($Q94:$W94,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y94">
+        <f>IF(AND($A94="Verdadero o Falso Simple",OR(COUNTIF($D94:$E94,"?*")&lt;2,COUNTIF($F94:$H94,"?*")&gt;0)),IF(COUNTIF($Q94:$X94,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z94">
+        <f>IF(AND($A94="Verdadero o Falso Simple",TRIM($I94)&lt;&gt;"",NOT(OR(LEFT(TRIM($I94),1)="A",LEFT(TRIM($I94),1)="B"))),IF(COUNTIF($Q94:$Y94,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA94">
+        <f>IF(AND($A94="Respuesta A/B/Ambas/Ninguna",COUNTIF($D94:$G94,"?*")&lt;4),IF(COUNTIF($Q94:$Z94,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB94">
+        <f>IF(AND($A94="Respuesta A/B/Ambas/Ninguna",COUNTIF($H94:$H94,"?*")&gt;0),IF(COUNTIF($Q94:$AA94,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC94">
+        <f>IF(AND($A94="Respuesta A/B/Ambas/Ninguna",TRIM($I94)&lt;&gt;"",NOT(OR(LEFT(TRIM($I94),1)="A",LEFT(TRIM($I94),1)="B",LEFT(TRIM($I94),1)="C",LEFT(TRIM($I94),1)="D"))),IF(COUNTIF($Q94:$AB94,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD94">
+        <f>IF(AND($A94="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D94,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E94,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F94,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G94,"4.","")))=0)),IF(COUNTIF($Q94:$AC94,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE94">
+        <f>IF(AND($A94="Verdadero o Falso Complejas",COUNTIF($H94:$H94,"?*")&gt;0),IF(COUNTIF($Q94:$AD94,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF94">
+        <f>IF(AND($A94="Verdadero o Falso Complejas",TRIM($I94)&lt;&gt;"",NOT(OR(LEFT(TRIM($I94),1)="A",LEFT(TRIM($I94),1)="B",LEFT(TRIM($I94),1)="C",LEFT(TRIM($I94),1)="D",LEFT(TRIM($I94),1)="E"))),IF(COUNTIF($Q94:$AE94,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG94">
+        <f>IF(AND(OR($A94="Selección de la mejor respuesta",$A94="Subítem de caso o problema"),COUNTA($D94:$H94)&lt;5),IF(COUNTIF($Q94:$AF94,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH94">
+        <f>IF(AND(OR($A94="Selección de la mejor respuesta",$A94="Subítem de caso o problema"),TRIM($I94)&lt;&gt;"",NOT(OR(LEFT(TRIM($I94),1)="A",LEFT(TRIM($I94),1)="B",LEFT(TRIM($I94),1)="C",LEFT(TRIM($I94),1)="D",LEFT(TRIM($I94),1)="E"))),IF(COUNTIF($Q94:$AG94,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI94">
+        <f>IF(AND(OR($A94="Ítems agrupados por caso clínico o problema",$A94="Opción de Emparejamiento Ampliado"),COUNTIF($D94:$H94,"?*")&gt;0),IF(COUNTIF($Q94:$AH94,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ94">
+        <f>IF(AND($A94="Emparejamiento Ampliado",COUNTIF($D94:$H94,"?*")&lt;2),IF(COUNTIF($Q94:$AI94,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK94">
+        <f>IF(AND($A94="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I94),1)="A",LEFT(TRIM($I94),1)="B",LEFT(TRIM($I94),1)="C",LEFT(TRIM($I94),1)="D",LEFT(TRIM($I94),1)="E"))),IF(COUNTIF($Q94:$AJ94,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL94">
+        <f>IF(TRIM($K94)="",IF(COUNTIF($M94:$M94,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM94">
         <f>IF(AND(TRIM($K94)&lt;&gt;"",TRIM($K94)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M94:$N94,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="95" ht="24" customHeight="1">
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="371" t="n"/>
+      <c r="B95" s="371" t="n"/>
+      <c r="C95" s="371" t="n"/>
+      <c r="D95" s="371">
+        <f>IF($A95="Verdadero o Falso Simple","Verdadero",IF($A95="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A95="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E95" s="371">
+        <f>IF($A95="Verdadero o Falso Simple","Falso",IF($A95="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A95="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F95" s="371">
+        <f>IF($A95="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A95="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G95" s="371">
+        <f>IF($A95="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A95="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H95" s="371">
+        <f>IF($A95="Verdadero o Falso Simple","",IF($A95="Respuesta A/B/Ambas/Ninguna","",IF($A95="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I95" s="371" t="n"/>
+      <c r="J95" s="372" t="n"/>
+      <c r="K95" s="372">
+        <f>IF(TRIM($A95)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L95" s="371">
+        <f>IF(TRIM($A95)="","",IF(OR($A95="Selección de la mejor respuesta",$A95="SELECCION_MEJOR_RESPUESTA",$A95="Subítem de caso o problema",$A95="SUBITEM_CASO"),IF(TRIM($C95)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D95:$H95&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I95)&lt;&gt;"",OR(LEFT(TRIM($I95),1)="A",LEFT(TRIM($I95),1)="B",LEFT(TRIM($I95),1)="C",LEFT(TRIM($I95),1)="D",LEFT(TRIM($I95),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A95)="","",IF(COUNTIF($Q95:$AJ95,"?*")=0,"OK","Falta revisar: "&amp;$Q95&amp;$R95&amp;$S95&amp;$T95&amp;$U95&amp;$V95&amp;$W95&amp;$X95&amp;$Y95&amp;$Z95&amp;$AA95&amp;$AB95&amp;$AC95&amp;$AD95&amp;$AE95&amp;$AF95&amp;$AG95&amp;$AH95&amp;$AI95&amp;$AJ95))))</f>
+        <v/>
+      </c>
+      <c r="M95" s="373" t="n"/>
+      <c r="Q95">
+        <f>IF(TRIM($C95)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R95">
+        <f>IF(TRIM($K95)="",IF(COUNTIF($Q95:$Q95,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S95">
         <f>IF(AND(TRIM($K95)&lt;&gt;"",TRIM($K95)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q95:$R95,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T95">
+        <f>IF(AND(OR($A95="Ítems agrupados por caso clínico o problema",$A95="Subítem de caso o problema",$A95="Emparejamiento Ampliado",$A95="Opción de Emparejamiento Ampliado"),TRIM($B95)=""),IF(COUNTIF($Q95:$S95,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U95">
+        <f>IF(AND(OR($A95="Verdadero o Falso Simple",$A95="Respuesta A/B/Ambas/Ninguna",$A95="Verdadero o Falso Complejas",$A95="Selección de la mejor respuesta",$A95="Subítem de caso o problema",$A95="Opción de Emparejamiento Ampliado"),TRIM($I95)=""),IF(COUNTIF($Q95:$T95,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V95">
+        <f>IF(AND(OR($A95="Verdadero o Falso Simple",$A95="Respuesta A/B/Ambas/Ninguna",$A95="Verdadero o Falso Complejas",$A95="Selección de la mejor respuesta",$A95="Subítem de caso o problema",$A95="Opción de Emparejamiento Ampliado"),TRIM($J95)=""),IF(COUNTIF($Q95:$U95,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W95">
+        <f>IF(AND(OR($A95="Ítems agrupados por caso clínico o problema",$A95="Emparejamiento Ampliado"),TRIM($I95)&lt;&gt;""),IF(COUNTIF($Q95:$V95,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X95">
+        <f>IF(AND(OR($A95="Ítems agrupados por caso clínico o problema",$A95="Emparejamiento Ampliado"),TRIM($J95)&lt;&gt;""),IF(COUNTIF($Q95:$W95,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y95">
+        <f>IF(AND($A95="Verdadero o Falso Simple",OR(COUNTIF($D95:$E95,"?*")&lt;2,COUNTIF($F95:$H95,"?*")&gt;0)),IF(COUNTIF($Q95:$X95,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z95">
+        <f>IF(AND($A95="Verdadero o Falso Simple",TRIM($I95)&lt;&gt;"",NOT(OR(LEFT(TRIM($I95),1)="A",LEFT(TRIM($I95),1)="B"))),IF(COUNTIF($Q95:$Y95,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA95">
+        <f>IF(AND($A95="Respuesta A/B/Ambas/Ninguna",COUNTIF($D95:$G95,"?*")&lt;4),IF(COUNTIF($Q95:$Z95,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB95">
+        <f>IF(AND($A95="Respuesta A/B/Ambas/Ninguna",COUNTIF($H95:$H95,"?*")&gt;0),IF(COUNTIF($Q95:$AA95,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC95">
+        <f>IF(AND($A95="Respuesta A/B/Ambas/Ninguna",TRIM($I95)&lt;&gt;"",NOT(OR(LEFT(TRIM($I95),1)="A",LEFT(TRIM($I95),1)="B",LEFT(TRIM($I95),1)="C",LEFT(TRIM($I95),1)="D"))),IF(COUNTIF($Q95:$AB95,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD95">
+        <f>IF(AND($A95="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D95,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E95,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F95,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G95,"4.","")))=0)),IF(COUNTIF($Q95:$AC95,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE95">
+        <f>IF(AND($A95="Verdadero o Falso Complejas",COUNTIF($H95:$H95,"?*")&gt;0),IF(COUNTIF($Q95:$AD95,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF95">
+        <f>IF(AND($A95="Verdadero o Falso Complejas",TRIM($I95)&lt;&gt;"",NOT(OR(LEFT(TRIM($I95),1)="A",LEFT(TRIM($I95),1)="B",LEFT(TRIM($I95),1)="C",LEFT(TRIM($I95),1)="D",LEFT(TRIM($I95),1)="E"))),IF(COUNTIF($Q95:$AE95,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG95">
+        <f>IF(AND(OR($A95="Selección de la mejor respuesta",$A95="Subítem de caso o problema"),COUNTA($D95:$H95)&lt;5),IF(COUNTIF($Q95:$AF95,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH95">
+        <f>IF(AND(OR($A95="Selección de la mejor respuesta",$A95="Subítem de caso o problema"),TRIM($I95)&lt;&gt;"",NOT(OR(LEFT(TRIM($I95),1)="A",LEFT(TRIM($I95),1)="B",LEFT(TRIM($I95),1)="C",LEFT(TRIM($I95),1)="D",LEFT(TRIM($I95),1)="E"))),IF(COUNTIF($Q95:$AG95,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI95">
+        <f>IF(AND(OR($A95="Ítems agrupados por caso clínico o problema",$A95="Opción de Emparejamiento Ampliado"),COUNTIF($D95:$H95,"?*")&gt;0),IF(COUNTIF($Q95:$AH95,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ95">
+        <f>IF(AND($A95="Emparejamiento Ampliado",COUNTIF($D95:$H95,"?*")&lt;2),IF(COUNTIF($Q95:$AI95,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK95">
+        <f>IF(AND($A95="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I95),1)="A",LEFT(TRIM($I95),1)="B",LEFT(TRIM($I95),1)="C",LEFT(TRIM($I95),1)="D",LEFT(TRIM($I95),1)="E"))),IF(COUNTIF($Q95:$AJ95,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL95">
+        <f>IF(TRIM($K95)="",IF(COUNTIF($M95:$M95,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM95">
         <f>IF(AND(TRIM($K95)&lt;&gt;"",TRIM($K95)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M95:$N95,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="96" ht="24" customHeight="1">
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="371" t="n"/>
+      <c r="B96" s="371" t="n"/>
+      <c r="C96" s="371" t="n"/>
+      <c r="D96" s="371">
+        <f>IF($A96="Verdadero o Falso Simple","Verdadero",IF($A96="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A96="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E96" s="371">
+        <f>IF($A96="Verdadero o Falso Simple","Falso",IF($A96="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A96="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F96" s="371">
+        <f>IF($A96="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A96="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G96" s="371">
+        <f>IF($A96="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A96="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H96" s="371">
+        <f>IF($A96="Verdadero o Falso Simple","",IF($A96="Respuesta A/B/Ambas/Ninguna","",IF($A96="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I96" s="371" t="n"/>
+      <c r="J96" s="372" t="n"/>
+      <c r="K96" s="372">
+        <f>IF(TRIM($A96)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L96" s="371">
+        <f>IF(TRIM($A96)="","",IF(OR($A96="Selección de la mejor respuesta",$A96="SELECCION_MEJOR_RESPUESTA",$A96="Subítem de caso o problema",$A96="SUBITEM_CASO"),IF(TRIM($C96)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D96:$H96&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I96)&lt;&gt;"",OR(LEFT(TRIM($I96),1)="A",LEFT(TRIM($I96),1)="B",LEFT(TRIM($I96),1)="C",LEFT(TRIM($I96),1)="D",LEFT(TRIM($I96),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A96)="","",IF(COUNTIF($Q96:$AJ96,"?*")=0,"OK","Falta revisar: "&amp;$Q96&amp;$R96&amp;$S96&amp;$T96&amp;$U96&amp;$V96&amp;$W96&amp;$X96&amp;$Y96&amp;$Z96&amp;$AA96&amp;$AB96&amp;$AC96&amp;$AD96&amp;$AE96&amp;$AF96&amp;$AG96&amp;$AH96&amp;$AI96&amp;$AJ96))))</f>
+        <v/>
+      </c>
+      <c r="M96" s="373" t="n"/>
+      <c r="Q96">
+        <f>IF(TRIM($C96)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R96">
+        <f>IF(TRIM($K96)="",IF(COUNTIF($Q96:$Q96,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S96">
         <f>IF(AND(TRIM($K96)&lt;&gt;"",TRIM($K96)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q96:$R96,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T96">
+        <f>IF(AND(OR($A96="Ítems agrupados por caso clínico o problema",$A96="Subítem de caso o problema",$A96="Emparejamiento Ampliado",$A96="Opción de Emparejamiento Ampliado"),TRIM($B96)=""),IF(COUNTIF($Q96:$S96,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U96">
+        <f>IF(AND(OR($A96="Verdadero o Falso Simple",$A96="Respuesta A/B/Ambas/Ninguna",$A96="Verdadero o Falso Complejas",$A96="Selección de la mejor respuesta",$A96="Subítem de caso o problema",$A96="Opción de Emparejamiento Ampliado"),TRIM($I96)=""),IF(COUNTIF($Q96:$T96,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V96">
+        <f>IF(AND(OR($A96="Verdadero o Falso Simple",$A96="Respuesta A/B/Ambas/Ninguna",$A96="Verdadero o Falso Complejas",$A96="Selección de la mejor respuesta",$A96="Subítem de caso o problema",$A96="Opción de Emparejamiento Ampliado"),TRIM($J96)=""),IF(COUNTIF($Q96:$U96,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W96">
+        <f>IF(AND(OR($A96="Ítems agrupados por caso clínico o problema",$A96="Emparejamiento Ampliado"),TRIM($I96)&lt;&gt;""),IF(COUNTIF($Q96:$V96,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X96">
+        <f>IF(AND(OR($A96="Ítems agrupados por caso clínico o problema",$A96="Emparejamiento Ampliado"),TRIM($J96)&lt;&gt;""),IF(COUNTIF($Q96:$W96,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y96">
+        <f>IF(AND($A96="Verdadero o Falso Simple",OR(COUNTIF($D96:$E96,"?*")&lt;2,COUNTIF($F96:$H96,"?*")&gt;0)),IF(COUNTIF($Q96:$X96,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z96">
+        <f>IF(AND($A96="Verdadero o Falso Simple",TRIM($I96)&lt;&gt;"",NOT(OR(LEFT(TRIM($I96),1)="A",LEFT(TRIM($I96),1)="B"))),IF(COUNTIF($Q96:$Y96,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA96">
+        <f>IF(AND($A96="Respuesta A/B/Ambas/Ninguna",COUNTIF($D96:$G96,"?*")&lt;4),IF(COUNTIF($Q96:$Z96,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB96">
+        <f>IF(AND($A96="Respuesta A/B/Ambas/Ninguna",COUNTIF($H96:$H96,"?*")&gt;0),IF(COUNTIF($Q96:$AA96,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC96">
+        <f>IF(AND($A96="Respuesta A/B/Ambas/Ninguna",TRIM($I96)&lt;&gt;"",NOT(OR(LEFT(TRIM($I96),1)="A",LEFT(TRIM($I96),1)="B",LEFT(TRIM($I96),1)="C",LEFT(TRIM($I96),1)="D"))),IF(COUNTIF($Q96:$AB96,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD96">
+        <f>IF(AND($A96="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D96,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E96,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F96,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G96,"4.","")))=0)),IF(COUNTIF($Q96:$AC96,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE96">
+        <f>IF(AND($A96="Verdadero o Falso Complejas",COUNTIF($H96:$H96,"?*")&gt;0),IF(COUNTIF($Q96:$AD96,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF96">
+        <f>IF(AND($A96="Verdadero o Falso Complejas",TRIM($I96)&lt;&gt;"",NOT(OR(LEFT(TRIM($I96),1)="A",LEFT(TRIM($I96),1)="B",LEFT(TRIM($I96),1)="C",LEFT(TRIM($I96),1)="D",LEFT(TRIM($I96),1)="E"))),IF(COUNTIF($Q96:$AE96,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG96">
+        <f>IF(AND(OR($A96="Selección de la mejor respuesta",$A96="Subítem de caso o problema"),COUNTA($D96:$H96)&lt;5),IF(COUNTIF($Q96:$AF96,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH96">
+        <f>IF(AND(OR($A96="Selección de la mejor respuesta",$A96="Subítem de caso o problema"),TRIM($I96)&lt;&gt;"",NOT(OR(LEFT(TRIM($I96),1)="A",LEFT(TRIM($I96),1)="B",LEFT(TRIM($I96),1)="C",LEFT(TRIM($I96),1)="D",LEFT(TRIM($I96),1)="E"))),IF(COUNTIF($Q96:$AG96,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI96">
+        <f>IF(AND(OR($A96="Ítems agrupados por caso clínico o problema",$A96="Opción de Emparejamiento Ampliado"),COUNTIF($D96:$H96,"?*")&gt;0),IF(COUNTIF($Q96:$AH96,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ96">
+        <f>IF(AND($A96="Emparejamiento Ampliado",COUNTIF($D96:$H96,"?*")&lt;2),IF(COUNTIF($Q96:$AI96,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK96">
+        <f>IF(AND($A96="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I96),1)="A",LEFT(TRIM($I96),1)="B",LEFT(TRIM($I96),1)="C",LEFT(TRIM($I96),1)="D",LEFT(TRIM($I96),1)="E"))),IF(COUNTIF($Q96:$AJ96,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL96">
+        <f>IF(TRIM($K96)="",IF(COUNTIF($M96:$M96,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM96">
         <f>IF(AND(TRIM($K96)&lt;&gt;"",TRIM($K96)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M96:$N96,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="97" ht="24" customHeight="1">
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="371" t="n"/>
+      <c r="B97" s="371" t="n"/>
+      <c r="C97" s="371" t="n"/>
+      <c r="D97" s="371">
+        <f>IF($A97="Verdadero o Falso Simple","Verdadero",IF($A97="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A97="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E97" s="371">
+        <f>IF($A97="Verdadero o Falso Simple","Falso",IF($A97="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A97="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F97" s="371">
+        <f>IF($A97="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A97="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G97" s="371">
+        <f>IF($A97="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A97="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H97" s="371">
+        <f>IF($A97="Verdadero o Falso Simple","",IF($A97="Respuesta A/B/Ambas/Ninguna","",IF($A97="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I97" s="371" t="n"/>
+      <c r="J97" s="372" t="n"/>
+      <c r="K97" s="372">
+        <f>IF(TRIM($A97)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L97" s="371">
+        <f>IF(TRIM($A97)="","",IF(OR($A97="Selección de la mejor respuesta",$A97="SELECCION_MEJOR_RESPUESTA",$A97="Subítem de caso o problema",$A97="SUBITEM_CASO"),IF(TRIM($C97)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D97:$H97&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I97)&lt;&gt;"",OR(LEFT(TRIM($I97),1)="A",LEFT(TRIM($I97),1)="B",LEFT(TRIM($I97),1)="C",LEFT(TRIM($I97),1)="D",LEFT(TRIM($I97),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A97)="","",IF(COUNTIF($Q97:$AJ97,"?*")=0,"OK","Falta revisar: "&amp;$Q97&amp;$R97&amp;$S97&amp;$T97&amp;$U97&amp;$V97&amp;$W97&amp;$X97&amp;$Y97&amp;$Z97&amp;$AA97&amp;$AB97&amp;$AC97&amp;$AD97&amp;$AE97&amp;$AF97&amp;$AG97&amp;$AH97&amp;$AI97&amp;$AJ97))))</f>
+        <v/>
+      </c>
+      <c r="M97" s="373" t="n"/>
+      <c r="Q97">
+        <f>IF(TRIM($C97)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R97">
+        <f>IF(TRIM($K97)="",IF(COUNTIF($Q97:$Q97,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S97">
         <f>IF(AND(TRIM($K97)&lt;&gt;"",TRIM($K97)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q97:$R97,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T97">
+        <f>IF(AND(OR($A97="Ítems agrupados por caso clínico o problema",$A97="Subítem de caso o problema",$A97="Emparejamiento Ampliado",$A97="Opción de Emparejamiento Ampliado"),TRIM($B97)=""),IF(COUNTIF($Q97:$S97,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U97">
+        <f>IF(AND(OR($A97="Verdadero o Falso Simple",$A97="Respuesta A/B/Ambas/Ninguna",$A97="Verdadero o Falso Complejas",$A97="Selección de la mejor respuesta",$A97="Subítem de caso o problema",$A97="Opción de Emparejamiento Ampliado"),TRIM($I97)=""),IF(COUNTIF($Q97:$T97,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V97">
+        <f>IF(AND(OR($A97="Verdadero o Falso Simple",$A97="Respuesta A/B/Ambas/Ninguna",$A97="Verdadero o Falso Complejas",$A97="Selección de la mejor respuesta",$A97="Subítem de caso o problema",$A97="Opción de Emparejamiento Ampliado"),TRIM($J97)=""),IF(COUNTIF($Q97:$U97,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W97">
+        <f>IF(AND(OR($A97="Ítems agrupados por caso clínico o problema",$A97="Emparejamiento Ampliado"),TRIM($I97)&lt;&gt;""),IF(COUNTIF($Q97:$V97,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X97">
+        <f>IF(AND(OR($A97="Ítems agrupados por caso clínico o problema",$A97="Emparejamiento Ampliado"),TRIM($J97)&lt;&gt;""),IF(COUNTIF($Q97:$W97,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y97">
+        <f>IF(AND($A97="Verdadero o Falso Simple",OR(COUNTIF($D97:$E97,"?*")&lt;2,COUNTIF($F97:$H97,"?*")&gt;0)),IF(COUNTIF($Q97:$X97,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z97">
+        <f>IF(AND($A97="Verdadero o Falso Simple",TRIM($I97)&lt;&gt;"",NOT(OR(LEFT(TRIM($I97),1)="A",LEFT(TRIM($I97),1)="B"))),IF(COUNTIF($Q97:$Y97,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA97">
+        <f>IF(AND($A97="Respuesta A/B/Ambas/Ninguna",COUNTIF($D97:$G97,"?*")&lt;4),IF(COUNTIF($Q97:$Z97,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB97">
+        <f>IF(AND($A97="Respuesta A/B/Ambas/Ninguna",COUNTIF($H97:$H97,"?*")&gt;0),IF(COUNTIF($Q97:$AA97,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC97">
+        <f>IF(AND($A97="Respuesta A/B/Ambas/Ninguna",TRIM($I97)&lt;&gt;"",NOT(OR(LEFT(TRIM($I97),1)="A",LEFT(TRIM($I97),1)="B",LEFT(TRIM($I97),1)="C",LEFT(TRIM($I97),1)="D"))),IF(COUNTIF($Q97:$AB97,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD97">
+        <f>IF(AND($A97="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D97,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E97,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F97,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G97,"4.","")))=0)),IF(COUNTIF($Q97:$AC97,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE97">
+        <f>IF(AND($A97="Verdadero o Falso Complejas",COUNTIF($H97:$H97,"?*")&gt;0),IF(COUNTIF($Q97:$AD97,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF97">
+        <f>IF(AND($A97="Verdadero o Falso Complejas",TRIM($I97)&lt;&gt;"",NOT(OR(LEFT(TRIM($I97),1)="A",LEFT(TRIM($I97),1)="B",LEFT(TRIM($I97),1)="C",LEFT(TRIM($I97),1)="D",LEFT(TRIM($I97),1)="E"))),IF(COUNTIF($Q97:$AE97,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG97">
+        <f>IF(AND(OR($A97="Selección de la mejor respuesta",$A97="Subítem de caso o problema"),COUNTA($D97:$H97)&lt;5),IF(COUNTIF($Q97:$AF97,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH97">
+        <f>IF(AND(OR($A97="Selección de la mejor respuesta",$A97="Subítem de caso o problema"),TRIM($I97)&lt;&gt;"",NOT(OR(LEFT(TRIM($I97),1)="A",LEFT(TRIM($I97),1)="B",LEFT(TRIM($I97),1)="C",LEFT(TRIM($I97),1)="D",LEFT(TRIM($I97),1)="E"))),IF(COUNTIF($Q97:$AG97,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI97">
+        <f>IF(AND(OR($A97="Ítems agrupados por caso clínico o problema",$A97="Opción de Emparejamiento Ampliado"),COUNTIF($D97:$H97,"?*")&gt;0),IF(COUNTIF($Q97:$AH97,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ97">
+        <f>IF(AND($A97="Emparejamiento Ampliado",COUNTIF($D97:$H97,"?*")&lt;2),IF(COUNTIF($Q97:$AI97,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK97">
+        <f>IF(AND($A97="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I97),1)="A",LEFT(TRIM($I97),1)="B",LEFT(TRIM($I97),1)="C",LEFT(TRIM($I97),1)="D",LEFT(TRIM($I97),1)="E"))),IF(COUNTIF($Q97:$AJ97,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL97">
+        <f>IF(TRIM($K97)="",IF(COUNTIF($M97:$M97,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM97">
         <f>IF(AND(TRIM($K97)&lt;&gt;"",TRIM($K97)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M97:$N97,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="98" ht="24" customHeight="1">
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="371" t="n"/>
+      <c r="B98" s="371" t="n"/>
+      <c r="C98" s="371" t="n"/>
+      <c r="D98" s="371">
+        <f>IF($A98="Verdadero o Falso Simple","Verdadero",IF($A98="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A98="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E98" s="371">
+        <f>IF($A98="Verdadero o Falso Simple","Falso",IF($A98="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A98="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F98" s="371">
+        <f>IF($A98="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A98="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G98" s="371">
+        <f>IF($A98="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A98="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H98" s="371">
+        <f>IF($A98="Verdadero o Falso Simple","",IF($A98="Respuesta A/B/Ambas/Ninguna","",IF($A98="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I98" s="371" t="n"/>
+      <c r="J98" s="372" t="n"/>
+      <c r="K98" s="372">
+        <f>IF(TRIM($A98)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L98" s="371">
+        <f>IF(TRIM($A98)="","",IF(OR($A98="Selección de la mejor respuesta",$A98="SELECCION_MEJOR_RESPUESTA",$A98="Subítem de caso o problema",$A98="SUBITEM_CASO"),IF(TRIM($C98)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D98:$H98&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I98)&lt;&gt;"",OR(LEFT(TRIM($I98),1)="A",LEFT(TRIM($I98),1)="B",LEFT(TRIM($I98),1)="C",LEFT(TRIM($I98),1)="D",LEFT(TRIM($I98),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A98)="","",IF(COUNTIF($Q98:$AJ98,"?*")=0,"OK","Falta revisar: "&amp;$Q98&amp;$R98&amp;$S98&amp;$T98&amp;$U98&amp;$V98&amp;$W98&amp;$X98&amp;$Y98&amp;$Z98&amp;$AA98&amp;$AB98&amp;$AC98&amp;$AD98&amp;$AE98&amp;$AF98&amp;$AG98&amp;$AH98&amp;$AI98&amp;$AJ98))))</f>
+        <v/>
+      </c>
+      <c r="M98" s="373" t="n"/>
+      <c r="Q98">
+        <f>IF(TRIM($C98)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R98">
+        <f>IF(TRIM($K98)="",IF(COUNTIF($Q98:$Q98,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S98">
         <f>IF(AND(TRIM($K98)&lt;&gt;"",TRIM($K98)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q98:$R98,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T98">
+        <f>IF(AND(OR($A98="Ítems agrupados por caso clínico o problema",$A98="Subítem de caso o problema",$A98="Emparejamiento Ampliado",$A98="Opción de Emparejamiento Ampliado"),TRIM($B98)=""),IF(COUNTIF($Q98:$S98,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U98">
+        <f>IF(AND(OR($A98="Verdadero o Falso Simple",$A98="Respuesta A/B/Ambas/Ninguna",$A98="Verdadero o Falso Complejas",$A98="Selección de la mejor respuesta",$A98="Subítem de caso o problema",$A98="Opción de Emparejamiento Ampliado"),TRIM($I98)=""),IF(COUNTIF($Q98:$T98,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V98">
+        <f>IF(AND(OR($A98="Verdadero o Falso Simple",$A98="Respuesta A/B/Ambas/Ninguna",$A98="Verdadero o Falso Complejas",$A98="Selección de la mejor respuesta",$A98="Subítem de caso o problema",$A98="Opción de Emparejamiento Ampliado"),TRIM($J98)=""),IF(COUNTIF($Q98:$U98,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W98">
+        <f>IF(AND(OR($A98="Ítems agrupados por caso clínico o problema",$A98="Emparejamiento Ampliado"),TRIM($I98)&lt;&gt;""),IF(COUNTIF($Q98:$V98,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X98">
+        <f>IF(AND(OR($A98="Ítems agrupados por caso clínico o problema",$A98="Emparejamiento Ampliado"),TRIM($J98)&lt;&gt;""),IF(COUNTIF($Q98:$W98,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y98">
+        <f>IF(AND($A98="Verdadero o Falso Simple",OR(COUNTIF($D98:$E98,"?*")&lt;2,COUNTIF($F98:$H98,"?*")&gt;0)),IF(COUNTIF($Q98:$X98,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z98">
+        <f>IF(AND($A98="Verdadero o Falso Simple",TRIM($I98)&lt;&gt;"",NOT(OR(LEFT(TRIM($I98),1)="A",LEFT(TRIM($I98),1)="B"))),IF(COUNTIF($Q98:$Y98,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA98">
+        <f>IF(AND($A98="Respuesta A/B/Ambas/Ninguna",COUNTIF($D98:$G98,"?*")&lt;4),IF(COUNTIF($Q98:$Z98,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB98">
+        <f>IF(AND($A98="Respuesta A/B/Ambas/Ninguna",COUNTIF($H98:$H98,"?*")&gt;0),IF(COUNTIF($Q98:$AA98,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC98">
+        <f>IF(AND($A98="Respuesta A/B/Ambas/Ninguna",TRIM($I98)&lt;&gt;"",NOT(OR(LEFT(TRIM($I98),1)="A",LEFT(TRIM($I98),1)="B",LEFT(TRIM($I98),1)="C",LEFT(TRIM($I98),1)="D"))),IF(COUNTIF($Q98:$AB98,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD98">
+        <f>IF(AND($A98="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D98,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E98,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F98,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G98,"4.","")))=0)),IF(COUNTIF($Q98:$AC98,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE98">
+        <f>IF(AND($A98="Verdadero o Falso Complejas",COUNTIF($H98:$H98,"?*")&gt;0),IF(COUNTIF($Q98:$AD98,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF98">
+        <f>IF(AND($A98="Verdadero o Falso Complejas",TRIM($I98)&lt;&gt;"",NOT(OR(LEFT(TRIM($I98),1)="A",LEFT(TRIM($I98),1)="B",LEFT(TRIM($I98),1)="C",LEFT(TRIM($I98),1)="D",LEFT(TRIM($I98),1)="E"))),IF(COUNTIF($Q98:$AE98,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG98">
+        <f>IF(AND(OR($A98="Selección de la mejor respuesta",$A98="Subítem de caso o problema"),COUNTA($D98:$H98)&lt;5),IF(COUNTIF($Q98:$AF98,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH98">
+        <f>IF(AND(OR($A98="Selección de la mejor respuesta",$A98="Subítem de caso o problema"),TRIM($I98)&lt;&gt;"",NOT(OR(LEFT(TRIM($I98),1)="A",LEFT(TRIM($I98),1)="B",LEFT(TRIM($I98),1)="C",LEFT(TRIM($I98),1)="D",LEFT(TRIM($I98),1)="E"))),IF(COUNTIF($Q98:$AG98,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI98">
+        <f>IF(AND(OR($A98="Ítems agrupados por caso clínico o problema",$A98="Opción de Emparejamiento Ampliado"),COUNTIF($D98:$H98,"?*")&gt;0),IF(COUNTIF($Q98:$AH98,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ98">
+        <f>IF(AND($A98="Emparejamiento Ampliado",COUNTIF($D98:$H98,"?*")&lt;2),IF(COUNTIF($Q98:$AI98,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK98">
+        <f>IF(AND($A98="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I98),1)="A",LEFT(TRIM($I98),1)="B",LEFT(TRIM($I98),1)="C",LEFT(TRIM($I98),1)="D",LEFT(TRIM($I98),1)="E"))),IF(COUNTIF($Q98:$AJ98,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL98">
+        <f>IF(TRIM($K98)="",IF(COUNTIF($M98:$M98,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM98">
         <f>IF(AND(TRIM($K98)&lt;&gt;"",TRIM($K98)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M98:$N98,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="99" ht="24" customHeight="1">
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="371" t="n"/>
+      <c r="B99" s="371" t="n"/>
+      <c r="C99" s="371" t="n"/>
+      <c r="D99" s="371">
+        <f>IF($A99="Verdadero o Falso Simple","Verdadero",IF($A99="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A99="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E99" s="371">
+        <f>IF($A99="Verdadero o Falso Simple","Falso",IF($A99="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A99="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F99" s="371">
+        <f>IF($A99="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A99="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G99" s="371">
+        <f>IF($A99="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A99="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H99" s="371">
+        <f>IF($A99="Verdadero o Falso Simple","",IF($A99="Respuesta A/B/Ambas/Ninguna","",IF($A99="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I99" s="371" t="n"/>
+      <c r="J99" s="372" t="n"/>
+      <c r="K99" s="372">
+        <f>IF(TRIM($A99)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L99" s="371">
+        <f>IF(TRIM($A99)="","",IF(OR($A99="Selección de la mejor respuesta",$A99="SELECCION_MEJOR_RESPUESTA",$A99="Subítem de caso o problema",$A99="SUBITEM_CASO"),IF(TRIM($C99)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D99:$H99&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I99)&lt;&gt;"",OR(LEFT(TRIM($I99),1)="A",LEFT(TRIM($I99),1)="B",LEFT(TRIM($I99),1)="C",LEFT(TRIM($I99),1)="D",LEFT(TRIM($I99),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A99)="","",IF(COUNTIF($Q99:$AJ99,"?*")=0,"OK","Falta revisar: "&amp;$Q99&amp;$R99&amp;$S99&amp;$T99&amp;$U99&amp;$V99&amp;$W99&amp;$X99&amp;$Y99&amp;$Z99&amp;$AA99&amp;$AB99&amp;$AC99&amp;$AD99&amp;$AE99&amp;$AF99&amp;$AG99&amp;$AH99&amp;$AI99&amp;$AJ99))))</f>
+        <v/>
+      </c>
+      <c r="M99" s="373" t="n"/>
+      <c r="Q99">
+        <f>IF(TRIM($C99)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R99">
+        <f>IF(TRIM($K99)="",IF(COUNTIF($Q99:$Q99,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S99">
         <f>IF(AND(TRIM($K99)&lt;&gt;"",TRIM($K99)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q99:$R99,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T99">
+        <f>IF(AND(OR($A99="Ítems agrupados por caso clínico o problema",$A99="Subítem de caso o problema",$A99="Emparejamiento Ampliado",$A99="Opción de Emparejamiento Ampliado"),TRIM($B99)=""),IF(COUNTIF($Q99:$S99,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U99">
+        <f>IF(AND(OR($A99="Verdadero o Falso Simple",$A99="Respuesta A/B/Ambas/Ninguna",$A99="Verdadero o Falso Complejas",$A99="Selección de la mejor respuesta",$A99="Subítem de caso o problema",$A99="Opción de Emparejamiento Ampliado"),TRIM($I99)=""),IF(COUNTIF($Q99:$T99,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V99">
+        <f>IF(AND(OR($A99="Verdadero o Falso Simple",$A99="Respuesta A/B/Ambas/Ninguna",$A99="Verdadero o Falso Complejas",$A99="Selección de la mejor respuesta",$A99="Subítem de caso o problema",$A99="Opción de Emparejamiento Ampliado"),TRIM($J99)=""),IF(COUNTIF($Q99:$U99,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W99">
+        <f>IF(AND(OR($A99="Ítems agrupados por caso clínico o problema",$A99="Emparejamiento Ampliado"),TRIM($I99)&lt;&gt;""),IF(COUNTIF($Q99:$V99,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X99">
+        <f>IF(AND(OR($A99="Ítems agrupados por caso clínico o problema",$A99="Emparejamiento Ampliado"),TRIM($J99)&lt;&gt;""),IF(COUNTIF($Q99:$W99,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y99">
+        <f>IF(AND($A99="Verdadero o Falso Simple",OR(COUNTIF($D99:$E99,"?*")&lt;2,COUNTIF($F99:$H99,"?*")&gt;0)),IF(COUNTIF($Q99:$X99,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z99">
+        <f>IF(AND($A99="Verdadero o Falso Simple",TRIM($I99)&lt;&gt;"",NOT(OR(LEFT(TRIM($I99),1)="A",LEFT(TRIM($I99),1)="B"))),IF(COUNTIF($Q99:$Y99,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA99">
+        <f>IF(AND($A99="Respuesta A/B/Ambas/Ninguna",COUNTIF($D99:$G99,"?*")&lt;4),IF(COUNTIF($Q99:$Z99,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB99">
+        <f>IF(AND($A99="Respuesta A/B/Ambas/Ninguna",COUNTIF($H99:$H99,"?*")&gt;0),IF(COUNTIF($Q99:$AA99,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC99">
+        <f>IF(AND($A99="Respuesta A/B/Ambas/Ninguna",TRIM($I99)&lt;&gt;"",NOT(OR(LEFT(TRIM($I99),1)="A",LEFT(TRIM($I99),1)="B",LEFT(TRIM($I99),1)="C",LEFT(TRIM($I99),1)="D"))),IF(COUNTIF($Q99:$AB99,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD99">
+        <f>IF(AND($A99="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D99,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E99,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F99,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G99,"4.","")))=0)),IF(COUNTIF($Q99:$AC99,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE99">
+        <f>IF(AND($A99="Verdadero o Falso Complejas",COUNTIF($H99:$H99,"?*")&gt;0),IF(COUNTIF($Q99:$AD99,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF99">
+        <f>IF(AND($A99="Verdadero o Falso Complejas",TRIM($I99)&lt;&gt;"",NOT(OR(LEFT(TRIM($I99),1)="A",LEFT(TRIM($I99),1)="B",LEFT(TRIM($I99),1)="C",LEFT(TRIM($I99),1)="D",LEFT(TRIM($I99),1)="E"))),IF(COUNTIF($Q99:$AE99,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG99">
+        <f>IF(AND(OR($A99="Selección de la mejor respuesta",$A99="Subítem de caso o problema"),COUNTA($D99:$H99)&lt;5),IF(COUNTIF($Q99:$AF99,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH99">
+        <f>IF(AND(OR($A99="Selección de la mejor respuesta",$A99="Subítem de caso o problema"),TRIM($I99)&lt;&gt;"",NOT(OR(LEFT(TRIM($I99),1)="A",LEFT(TRIM($I99),1)="B",LEFT(TRIM($I99),1)="C",LEFT(TRIM($I99),1)="D",LEFT(TRIM($I99),1)="E"))),IF(COUNTIF($Q99:$AG99,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI99">
+        <f>IF(AND(OR($A99="Ítems agrupados por caso clínico o problema",$A99="Opción de Emparejamiento Ampliado"),COUNTIF($D99:$H99,"?*")&gt;0),IF(COUNTIF($Q99:$AH99,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ99">
+        <f>IF(AND($A99="Emparejamiento Ampliado",COUNTIF($D99:$H99,"?*")&lt;2),IF(COUNTIF($Q99:$AI99,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK99">
+        <f>IF(AND($A99="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I99),1)="A",LEFT(TRIM($I99),1)="B",LEFT(TRIM($I99),1)="C",LEFT(TRIM($I99),1)="D",LEFT(TRIM($I99),1)="E"))),IF(COUNTIF($Q99:$AJ99,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL99">
+        <f>IF(TRIM($K99)="",IF(COUNTIF($M99:$M99,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM99">
         <f>IF(AND(TRIM($K99)&lt;&gt;"",TRIM($K99)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M99:$N99,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="100" ht="24" customHeight="1">
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="371" t="n"/>
+      <c r="B100" s="371" t="n"/>
+      <c r="C100" s="371" t="n"/>
+      <c r="D100" s="371">
+        <f>IF($A100="Verdadero o Falso Simple","Verdadero",IF($A100="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A100="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E100" s="371">
+        <f>IF($A100="Verdadero o Falso Simple","Falso",IF($A100="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A100="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F100" s="371">
+        <f>IF($A100="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A100="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G100" s="371">
+        <f>IF($A100="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A100="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H100" s="371">
+        <f>IF($A100="Verdadero o Falso Simple","",IF($A100="Respuesta A/B/Ambas/Ninguna","",IF($A100="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I100" s="371" t="n"/>
+      <c r="J100" s="372" t="n"/>
+      <c r="K100" s="372">
+        <f>IF(TRIM($A100)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L100" s="371">
+        <f>IF(TRIM($A100)="","",IF(OR($A100="Selección de la mejor respuesta",$A100="SELECCION_MEJOR_RESPUESTA",$A100="Subítem de caso o problema",$A100="SUBITEM_CASO"),IF(TRIM($C100)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D100:$H100&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I100)&lt;&gt;"",OR(LEFT(TRIM($I100),1)="A",LEFT(TRIM($I100),1)="B",LEFT(TRIM($I100),1)="C",LEFT(TRIM($I100),1)="D",LEFT(TRIM($I100),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A100)="","",IF(COUNTIF($Q100:$AJ100,"?*")=0,"OK","Falta revisar: "&amp;$Q100&amp;$R100&amp;$S100&amp;$T100&amp;$U100&amp;$V100&amp;$W100&amp;$X100&amp;$Y100&amp;$Z100&amp;$AA100&amp;$AB100&amp;$AC100&amp;$AD100&amp;$AE100&amp;$AF100&amp;$AG100&amp;$AH100&amp;$AI100&amp;$AJ100))))</f>
+        <v/>
+      </c>
+      <c r="M100" s="373" t="n"/>
+      <c r="Q100">
+        <f>IF(TRIM($C100)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R100">
+        <f>IF(TRIM($K100)="",IF(COUNTIF($Q100:$Q100,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S100">
         <f>IF(AND(TRIM($K100)&lt;&gt;"",TRIM($K100)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q100:$R100,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
+      <c r="T100">
+        <f>IF(AND(OR($A100="Ítems agrupados por caso clínico o problema",$A100="Subítem de caso o problema",$A100="Emparejamiento Ampliado",$A100="Opción de Emparejamiento Ampliado"),TRIM($B100)=""),IF(COUNTIF($Q100:$S100,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U100">
+        <f>IF(AND(OR($A100="Verdadero o Falso Simple",$A100="Respuesta A/B/Ambas/Ninguna",$A100="Verdadero o Falso Complejas",$A100="Selección de la mejor respuesta",$A100="Subítem de caso o problema",$A100="Opción de Emparejamiento Ampliado"),TRIM($I100)=""),IF(COUNTIF($Q100:$T100,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V100">
+        <f>IF(AND(OR($A100="Verdadero o Falso Simple",$A100="Respuesta A/B/Ambas/Ninguna",$A100="Verdadero o Falso Complejas",$A100="Selección de la mejor respuesta",$A100="Subítem de caso o problema",$A100="Opción de Emparejamiento Ampliado"),TRIM($J100)=""),IF(COUNTIF($Q100:$U100,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W100">
+        <f>IF(AND(OR($A100="Ítems agrupados por caso clínico o problema",$A100="Emparejamiento Ampliado"),TRIM($I100)&lt;&gt;""),IF(COUNTIF($Q100:$V100,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X100">
+        <f>IF(AND(OR($A100="Ítems agrupados por caso clínico o problema",$A100="Emparejamiento Ampliado"),TRIM($J100)&lt;&gt;""),IF(COUNTIF($Q100:$W100,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y100">
+        <f>IF(AND($A100="Verdadero o Falso Simple",OR(COUNTIF($D100:$E100,"?*")&lt;2,COUNTIF($F100:$H100,"?*")&gt;0)),IF(COUNTIF($Q100:$X100,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z100">
+        <f>IF(AND($A100="Verdadero o Falso Simple",TRIM($I100)&lt;&gt;"",NOT(OR(LEFT(TRIM($I100),1)="A",LEFT(TRIM($I100),1)="B"))),IF(COUNTIF($Q100:$Y100,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA100">
+        <f>IF(AND($A100="Respuesta A/B/Ambas/Ninguna",COUNTIF($D100:$G100,"?*")&lt;4),IF(COUNTIF($Q100:$Z100,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB100">
+        <f>IF(AND($A100="Respuesta A/B/Ambas/Ninguna",COUNTIF($H100:$H100,"?*")&gt;0),IF(COUNTIF($Q100:$AA100,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC100">
+        <f>IF(AND($A100="Respuesta A/B/Ambas/Ninguna",TRIM($I100)&lt;&gt;"",NOT(OR(LEFT(TRIM($I100),1)="A",LEFT(TRIM($I100),1)="B",LEFT(TRIM($I100),1)="C",LEFT(TRIM($I100),1)="D"))),IF(COUNTIF($Q100:$AB100,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD100">
+        <f>IF(AND($A100="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D100,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E100,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F100,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G100,"4.","")))=0)),IF(COUNTIF($Q100:$AC100,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE100">
+        <f>IF(AND($A100="Verdadero o Falso Complejas",COUNTIF($H100:$H100,"?*")&gt;0),IF(COUNTIF($Q100:$AD100,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF100">
+        <f>IF(AND($A100="Verdadero o Falso Complejas",TRIM($I100)&lt;&gt;"",NOT(OR(LEFT(TRIM($I100),1)="A",LEFT(TRIM($I100),1)="B",LEFT(TRIM($I100),1)="C",LEFT(TRIM($I100),1)="D",LEFT(TRIM($I100),1)="E"))),IF(COUNTIF($Q100:$AE100,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG100">
+        <f>IF(AND(OR($A100="Selección de la mejor respuesta",$A100="Subítem de caso o problema"),COUNTA($D100:$H100)&lt;5),IF(COUNTIF($Q100:$AF100,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH100">
+        <f>IF(AND(OR($A100="Selección de la mejor respuesta",$A100="Subítem de caso o problema"),TRIM($I100)&lt;&gt;"",NOT(OR(LEFT(TRIM($I100),1)="A",LEFT(TRIM($I100),1)="B",LEFT(TRIM($I100),1)="C",LEFT(TRIM($I100),1)="D",LEFT(TRIM($I100),1)="E"))),IF(COUNTIF($Q100:$AG100,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI100">
+        <f>IF(AND(OR($A100="Ítems agrupados por caso clínico o problema",$A100="Opción de Emparejamiento Ampliado"),COUNTIF($D100:$H100,"?*")&gt;0),IF(COUNTIF($Q100:$AH100,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ100">
+        <f>IF(AND($A100="Emparejamiento Ampliado",COUNTIF($D100:$H100,"?*")&lt;2),IF(COUNTIF($Q100:$AI100,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK100">
+        <f>IF(AND($A100="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I100),1)="A",LEFT(TRIM($I100),1)="B",LEFT(TRIM($I100),1)="C",LEFT(TRIM($I100),1)="D",LEFT(TRIM($I100),1)="E"))),IF(COUNTIF($Q100:$AJ100,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL100">
+        <f>IF(TRIM($K100)="",IF(COUNTIF($M100:$M100,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="AM100">
         <f>IF(AND(TRIM($K100)&lt;&gt;"",TRIM($K100)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($M100:$N100,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
         <v/>
       </c>
     </row>
-    <row r="101" ht="24" customHeight="1">
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="371" t="n"/>
+      <c r="B101" s="371" t="n"/>
+      <c r="C101" s="371" t="n"/>
+      <c r="D101" s="371">
+        <f>IF($A101="Verdadero o Falso Simple","Verdadero",IF($A101="Respuesta A/B/Ambas/Ninguna","A. Si la primera es verdadera",IF($A101="Verdadero o Falso Complejas","1. ","")))</f>
+        <v/>
+      </c>
+      <c r="E101" s="371">
+        <f>IF($A101="Verdadero o Falso Simple","Falso",IF($A101="Respuesta A/B/Ambas/Ninguna","B. Si la segunda es verdadera",IF($A101="Verdadero o Falso Complejas","2. ","")))</f>
+        <v/>
+      </c>
+      <c r="F101" s="371">
+        <f>IF($A101="Respuesta A/B/Ambas/Ninguna","C. Si ambas son verdaderas",IF($A101="Verdadero o Falso Complejas","3. ",""))</f>
+        <v/>
+      </c>
+      <c r="G101" s="371">
+        <f>IF($A101="Respuesta A/B/Ambas/Ninguna","D. Si ninguna es verdadera",IF($A101="Verdadero o Falso Complejas","4. ",""))</f>
+        <v/>
+      </c>
+      <c r="H101" s="371">
+        <f>IF($A101="Verdadero o Falso Simple","",IF($A101="Respuesta A/B/Ambas/Ninguna","",IF($A101="Verdadero o Falso Complejas","","")))</f>
+        <v/>
+      </c>
+      <c r="I101" s="371" t="n"/>
+      <c r="J101" s="372" t="n"/>
+      <c r="K101" s="372">
+        <f>IF(TRIM($A101)="","",VALIDACIONES!$G$1)</f>
+        <v/>
+      </c>
+      <c r="L101" s="371">
+        <f>IF(TRIM($A101)="","",IF(OR($A101="Selección de la mejor respuesta",$A101="SELECCION_MEJOR_RESPUESTA",$A101="Subítem de caso o problema",$A101="SUBITEM_CASO"),IF(TRIM($C101)="","Completar enunciado",IF(SUMPRODUCT(--(LEN(TRIM($D101:$H101&amp;""))&gt;0))&lt;5,"Completar opciones A-E",IF(AND(TRIM($I101)&lt;&gt;"",OR(LEFT(TRIM($I101),1)="A",LEFT(TRIM($I101),1)="B",LEFT(TRIM($I101),1)="C",LEFT(TRIM($I101),1)="D",LEFT(TRIM($I101),1)="E")),"OK","Completar respuesta correcta A-E"))),IF(TRIM($A101)="","",IF(COUNTIF($Q101:$AJ101,"?*")=0,"OK","Falta revisar: "&amp;$Q101&amp;$R101&amp;$S101&amp;$T101&amp;$U101&amp;$V101&amp;$W101&amp;$X101&amp;$Y101&amp;$Z101&amp;$AA101&amp;$AB101&amp;$AC101&amp;$AD101&amp;$AE101&amp;$AF101&amp;$AG101&amp;$AH101&amp;$AI101&amp;$AJ101))))</f>
+        <v/>
+      </c>
+      <c r="M101" s="373" t="n"/>
+      <c r="Q101">
+        <f>IF(TRIM($C101)="","enunciado","")</f>
+        <v/>
+      </c>
+      <c r="R101">
+        <f>IF(TRIM($K101)="",IF(COUNTIF($Q101:$Q101,"?*")&gt;0,", ","")&amp;"parcial","")</f>
+        <v/>
+      </c>
       <c r="S101">
         <f>IF(AND(TRIM($K101)&lt;&gt;"",TRIM($K101)&lt;&gt;VALIDACIONES!$G$1),IF(COUNTIF($Q101:$R101,"?*")&gt;0,", ","")&amp;"parcial distinto a "&amp;VALIDACIONES!$G$1,"")</f>
+        <v/>
+      </c>
+      <c r="T101">
+        <f>IF(AND(OR($A101="Ítems agrupados por caso clínico o problema",$A101="Subítem de caso o problema",$A101="Emparejamiento Ampliado",$A101="Opción de Emparejamiento Ampliado"),TRIM($B101)=""),IF(COUNTIF($Q101:$S101,"?*")&gt;0,", ","")&amp;"grupo","")</f>
+        <v/>
+      </c>
+      <c r="U101">
+        <f>IF(AND(OR($A101="Verdadero o Falso Simple",$A101="Respuesta A/B/Ambas/Ninguna",$A101="Verdadero o Falso Complejas",$A101="Selección de la mejor respuesta",$A101="Subítem de caso o problema",$A101="Opción de Emparejamiento Ampliado"),TRIM($I101)=""),IF(COUNTIF($Q101:$T101,"?*")&gt;0,", ","")&amp;"respuesta_correcta","")</f>
+        <v/>
+      </c>
+      <c r="V101">
+        <f>IF(AND(OR($A101="Verdadero o Falso Simple",$A101="Respuesta A/B/Ambas/Ninguna",$A101="Verdadero o Falso Complejas",$A101="Selección de la mejor respuesta",$A101="Subítem de caso o problema",$A101="Opción de Emparejamiento Ampliado"),TRIM($J101)=""),IF(COUNTIF($Q101:$U101,"?*")&gt;0,", ","")&amp;"dificultad","")</f>
+        <v/>
+      </c>
+      <c r="W101">
+        <f>IF(AND(OR($A101="Ítems agrupados por caso clínico o problema",$A101="Emparejamiento Ampliado"),TRIM($I101)&lt;&gt;""),IF(COUNTIF($Q101:$V101,"?*")&gt;0,", ","")&amp;"respuesta debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="X101">
+        <f>IF(AND(OR($A101="Ítems agrupados por caso clínico o problema",$A101="Emparejamiento Ampliado"),TRIM($J101)&lt;&gt;""),IF(COUNTIF($Q101:$W101,"?*")&gt;0,", ","")&amp;"dificultad debe ir vacia","")</f>
+        <v/>
+      </c>
+      <c r="Y101">
+        <f>IF(AND($A101="Verdadero o Falso Simple",OR(COUNTIF($D101:$E101,"?*")&lt;2,COUNTIF($F101:$H101,"?*")&gt;0)),IF(COUNTIF($Q101:$X101,"?*")&gt;0,", ","")&amp;"incisos A-B","")</f>
+        <v/>
+      </c>
+      <c r="Z101">
+        <f>IF(AND($A101="Verdadero o Falso Simple",TRIM($I101)&lt;&gt;"",NOT(OR(LEFT(TRIM($I101),1)="A",LEFT(TRIM($I101),1)="B"))),IF(COUNTIF($Q101:$Y101,"?*")&gt;0,", ","")&amp;"respuesta A-B","")</f>
+        <v/>
+      </c>
+      <c r="AA101">
+        <f>IF(AND($A101="Respuesta A/B/Ambas/Ninguna",COUNTIF($D101:$G101,"?*")&lt;4),IF(COUNTIF($Q101:$Z101,"?*")&gt;0,", ","")&amp;"opciones A-D","")</f>
+        <v/>
+      </c>
+      <c r="AB101">
+        <f>IF(AND($A101="Respuesta A/B/Ambas/Ninguna",COUNTIF($H101:$H101,"?*")&gt;0),IF(COUNTIF($Q101:$AA101,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AC101">
+        <f>IF(AND($A101="Respuesta A/B/Ambas/Ninguna",TRIM($I101)&lt;&gt;"",NOT(OR(LEFT(TRIM($I101),1)="A",LEFT(TRIM($I101),1)="B",LEFT(TRIM($I101),1)="C",LEFT(TRIM($I101),1)="D"))),IF(COUNTIF($Q101:$AB101,"?*")&gt;0,", ","")&amp;"respuesta A-D","")</f>
+        <v/>
+      </c>
+      <c r="AD101">
+        <f>IF(AND($A101="Verdadero o Falso Complejas",OR(LEN(TRIM(SUBSTITUTE($D101,"1.","")))=0,LEN(TRIM(SUBSTITUTE($E101,"2.","")))=0,LEN(TRIM(SUBSTITUTE($F101,"3.","")))=0,LEN(TRIM(SUBSTITUTE($G101,"4.","")))=0)),IF(COUNTIF($Q101:$AC101,"?*")&gt;0,", ","")&amp;"incisos 1-4","")</f>
+        <v/>
+      </c>
+      <c r="AE101">
+        <f>IF(AND($A101="Verdadero o Falso Complejas",COUNTIF($H101:$H101,"?*")&gt;0),IF(COUNTIF($Q101:$AD101,"?*")&gt;0,", ","")&amp;"opcion E deshabilitada","")</f>
+        <v/>
+      </c>
+      <c r="AF101">
+        <f>IF(AND($A101="Verdadero o Falso Complejas",TRIM($I101)&lt;&gt;"",NOT(OR(LEFT(TRIM($I101),1)="A",LEFT(TRIM($I101),1)="B",LEFT(TRIM($I101),1)="C",LEFT(TRIM($I101),1)="D",LEFT(TRIM($I101),1)="E"))),IF(COUNTIF($Q101:$AE101,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AG101">
+        <f>IF(AND(OR($A101="Selección de la mejor respuesta",$A101="Subítem de caso o problema"),COUNTA($D101:$H101)&lt;5),IF(COUNTIF($Q101:$AF101,"?*")&gt;0,", ","")&amp;"incisos A-E","")</f>
+        <v/>
+      </c>
+      <c r="AH101">
+        <f>IF(AND(OR($A101="Selección de la mejor respuesta",$A101="Subítem de caso o problema"),TRIM($I101)&lt;&gt;"",NOT(OR(LEFT(TRIM($I101),1)="A",LEFT(TRIM($I101),1)="B",LEFT(TRIM($I101),1)="C",LEFT(TRIM($I101),1)="D",LEFT(TRIM($I101),1)="E"))),IF(COUNTIF($Q101:$AG101,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AI101">
+        <f>IF(AND(OR($A101="Ítems agrupados por caso clínico o problema",$A101="Opción de Emparejamiento Ampliado"),COUNTIF($D101:$H101,"?*")&gt;0),IF(COUNTIF($Q101:$AH101,"?*")&gt;0,", ","")&amp;"sin incisos","")</f>
+        <v/>
+      </c>
+      <c r="AJ101">
+        <f>IF(AND($A101="Emparejamiento Ampliado",COUNTIF($D101:$H101,"?*")&lt;2),IF(COUNTIF($Q101:$AI101,"?*")&gt;0,", ","")&amp;"minimo 2 claves","")</f>
+        <v/>
+      </c>
+      <c r="AK101">
+        <f>IF(AND($A101="Opción de Emparejamiento Ampliado",NOT(OR(LEFT(TRIM($I101),1)="A",LEFT(TRIM($I101),1)="B",LEFT(TRIM($I101),1)="C",LEFT(TRIM($I101),1)="D",LEFT(TRIM($I101),1)="E"))),IF(COUNTIF($Q101:$AJ101,"?*")&gt;0,", ","")&amp;"respuesta A-E","")</f>
+        <v/>
+      </c>
+      <c r="AL101">
+        <f>IF(TRIM($K101)="",IF(COUNTIF($M101:$M101,"?*")&gt;0,", ","")&amp;"parcial","")</f>
         <v/>
       </c>
       <c r="AM101">
@@ -11585,27 +16364,27 @@
     <mergeCell ref="AO1:AQ1"/>
     <mergeCell ref="AO8:AQ8"/>
   </mergeCells>
-  <conditionalFormatting sqref="D2:H61">
+  <conditionalFormatting sqref="D2:H101">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>OR($A2="Ítems agrupados por caso clínico o problema",$A2="Opción de Emparejamiento Ampliado")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:H61">
+  <conditionalFormatting sqref="F2:H101">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>$A2="Verdadero o Falso Simple"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H61">
+  <conditionalFormatting sqref="H2:H101">
     <cfRule type="expression" priority="3" dxfId="0">
       <formula>OR($A2="Respuesta A/B/Ambas/Ninguna",$A2="Verdadero o Falso Complejas")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:J61">
+  <conditionalFormatting sqref="I2:J101">
     <cfRule type="expression" priority="4" dxfId="0">
       <formula>OR($A2="Ítems agrupados por caso clínico o problema",$A2="Emparejamiento Ampliado")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L61">
+  <conditionalFormatting sqref="L2:L101">
     <cfRule type="expression" priority="5" dxfId="4">
       <formula>LEFT($L2,2)="OK"</formula>
     </cfRule>
@@ -11613,7 +16392,7 @@
       <formula>AND($L2&lt;&gt;"",LEFT($L2,2)&lt;&gt;"OK")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="481">
+  <dataValidations count="801">
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
       <formula1>IF(OR(ISNUMBER(MATCH($A10,TIPOS_REQUIEREN_GRUPO,0)),OR($A10="CASO_CLINICO_TRONCO",$A10="CASO_CLINICO",$A10="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A10="PROBLEMA",$A10="SUBPROBLEMA",$A10="SUBITEM_CASO",$A10="SUBITEM_DE_CASO_O_PROBLEMA",$A10="EMPAREJAMIENTO_TRONCO",$A10="EMPAREJAMIENTO_AMPLIADO",$A10="EMPAREJAMIENTO_DE_CONCEPTOS",$A10="OPCION_EMPAREJAMIENTO",$A10="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B10))&gt;0,LEN(TRIM($B10))=0)</formula1>
     </dataValidation>
@@ -13054,8 +17833,968 @@
     <dataValidation sqref="J9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
       <formula1>INDIRECT(IF(ISNUMBER(MATCH($A9,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
     </dataValidation>
-    <dataValidation sqref="A2:A61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Tipo no válido" error="Seleccione un tipo desde la lista del formato oficial." promptTitle="Tipo de pregunta" prompt="Seleccione un tipo. Las columnas de incisos se completan automáticamente según la tipología." type="list">
+    <dataValidation sqref="A2:A101" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Tipo no válido" error="Seleccione un tipo desde la lista del formato oficial." promptTitle="Tipo de pregunta" prompt="Seleccione un tipo. Las columnas de incisos se completan automáticamente según la tipología." type="list">
       <formula1>LISTA_TIPOS_2P</formula1>
+    </dataValidation>
+    <dataValidation sqref="B62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A62,TIPOS_REQUIEREN_GRUPO,0)),OR($A62="CASO_CLINICO_TRONCO",$A62="CASO_CLINICO",$A62="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A62="PROBLEMA",$A62="SUBPROBLEMA",$A62="SUBITEM_CASO",$A62="SUBITEM_DE_CASO_O_PROBLEMA",$A62="EMPAREJAMIENTO_TRONCO",$A62="EMPAREJAMIENTO_AMPLIADO",$A62="EMPAREJAMIENTO_DE_CONCEPTOS",$A62="OPCION_EMPAREJAMIENTO",$A62="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B62))&gt;0,LEN(TRIM($B62))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A62,TIPOS_OPCION_D,0)),OR($A62="SELECCION_MEJOR_RESPUESTA",$A62="SELECCION_SIMPLE",$A62="SELECCION_UNICA",$A62="SELECCION_DE_LA_MEJOR_RESPUESTA",$A62="SUBITEM_CASO",$A62="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D62))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A62,TIPOS_OPCION_E,0)),OR($A62="SELECCION_MEJOR_RESPUESTA",$A62="SELECCION_SIMPLE",$A62="SELECCION_UNICA",$A62="SELECCION_DE_LA_MEJOR_RESPUESTA",$A62="SUBITEM_CASO",$A62="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E62))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A62,TIPOS_OPCION_F,0)),OR($A62="SELECCION_MEJOR_RESPUESTA",$A62="SELECCION_SIMPLE",$A62="SELECCION_UNICA",$A62="SELECCION_DE_LA_MEJOR_RESPUESTA",$A62="SUBITEM_CASO",$A62="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F62))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A62,TIPOS_OPCION_G,0)),OR($A62="SELECCION_MEJOR_RESPUESTA",$A62="SELECCION_SIMPLE",$A62="SELECCION_UNICA",$A62="SELECCION_DE_LA_MEJOR_RESPUESTA",$A62="SUBITEM_CASO",$A62="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G62))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A62,TIPOS_OPCION_H,0)),OR($A62="SELECCION_MEJOR_RESPUESTA",$A62="SELECCION_SIMPLE",$A62="SELECCION_UNICA",$A62="SELECCION_DE_LA_MEJOR_RESPUESTA",$A62="SUBITEM_CASO",$A62="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H62))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I62" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A62="SELECCION_MEJOR_RESPUESTA",$A62="SELECCION_SIMPLE",$A62="SELECCION_UNICA",$A62="SELECCION_DE_LA_MEJOR_RESPUESTA",$A62="SUBITEM_CASO",$A62="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A62,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A62,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B63" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A63,TIPOS_REQUIEREN_GRUPO,0)),OR($A63="CASO_CLINICO_TRONCO",$A63="CASO_CLINICO",$A63="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A63="PROBLEMA",$A63="SUBPROBLEMA",$A63="SUBITEM_CASO",$A63="SUBITEM_DE_CASO_O_PROBLEMA",$A63="EMPAREJAMIENTO_TRONCO",$A63="EMPAREJAMIENTO_AMPLIADO",$A63="EMPAREJAMIENTO_DE_CONCEPTOS",$A63="OPCION_EMPAREJAMIENTO",$A63="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B63))&gt;0,LEN(TRIM($B63))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A63,TIPOS_OPCION_D,0)),OR($A63="SELECCION_MEJOR_RESPUESTA",$A63="SELECCION_SIMPLE",$A63="SELECCION_UNICA",$A63="SELECCION_DE_LA_MEJOR_RESPUESTA",$A63="SUBITEM_CASO",$A63="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D63))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A63,TIPOS_OPCION_E,0)),OR($A63="SELECCION_MEJOR_RESPUESTA",$A63="SELECCION_SIMPLE",$A63="SELECCION_UNICA",$A63="SELECCION_DE_LA_MEJOR_RESPUESTA",$A63="SUBITEM_CASO",$A63="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E63))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A63,TIPOS_OPCION_F,0)),OR($A63="SELECCION_MEJOR_RESPUESTA",$A63="SELECCION_SIMPLE",$A63="SELECCION_UNICA",$A63="SELECCION_DE_LA_MEJOR_RESPUESTA",$A63="SUBITEM_CASO",$A63="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F63))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A63,TIPOS_OPCION_G,0)),OR($A63="SELECCION_MEJOR_RESPUESTA",$A63="SELECCION_SIMPLE",$A63="SELECCION_UNICA",$A63="SELECCION_DE_LA_MEJOR_RESPUESTA",$A63="SUBITEM_CASO",$A63="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G63))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A63,TIPOS_OPCION_H,0)),OR($A63="SELECCION_MEJOR_RESPUESTA",$A63="SELECCION_SIMPLE",$A63="SELECCION_UNICA",$A63="SELECCION_DE_LA_MEJOR_RESPUESTA",$A63="SUBITEM_CASO",$A63="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H63))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I63" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A63="SELECCION_MEJOR_RESPUESTA",$A63="SELECCION_SIMPLE",$A63="SELECCION_UNICA",$A63="SELECCION_DE_LA_MEJOR_RESPUESTA",$A63="SUBITEM_CASO",$A63="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A63,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J63" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A63,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A64,TIPOS_REQUIEREN_GRUPO,0)),OR($A64="CASO_CLINICO_TRONCO",$A64="CASO_CLINICO",$A64="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A64="PROBLEMA",$A64="SUBPROBLEMA",$A64="SUBITEM_CASO",$A64="SUBITEM_DE_CASO_O_PROBLEMA",$A64="EMPAREJAMIENTO_TRONCO",$A64="EMPAREJAMIENTO_AMPLIADO",$A64="EMPAREJAMIENTO_DE_CONCEPTOS",$A64="OPCION_EMPAREJAMIENTO",$A64="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B64))&gt;0,LEN(TRIM($B64))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A64,TIPOS_OPCION_D,0)),OR($A64="SELECCION_MEJOR_RESPUESTA",$A64="SELECCION_SIMPLE",$A64="SELECCION_UNICA",$A64="SELECCION_DE_LA_MEJOR_RESPUESTA",$A64="SUBITEM_CASO",$A64="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D64))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A64,TIPOS_OPCION_E,0)),OR($A64="SELECCION_MEJOR_RESPUESTA",$A64="SELECCION_SIMPLE",$A64="SELECCION_UNICA",$A64="SELECCION_DE_LA_MEJOR_RESPUESTA",$A64="SUBITEM_CASO",$A64="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E64))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A64,TIPOS_OPCION_F,0)),OR($A64="SELECCION_MEJOR_RESPUESTA",$A64="SELECCION_SIMPLE",$A64="SELECCION_UNICA",$A64="SELECCION_DE_LA_MEJOR_RESPUESTA",$A64="SUBITEM_CASO",$A64="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F64))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A64,TIPOS_OPCION_G,0)),OR($A64="SELECCION_MEJOR_RESPUESTA",$A64="SELECCION_SIMPLE",$A64="SELECCION_UNICA",$A64="SELECCION_DE_LA_MEJOR_RESPUESTA",$A64="SUBITEM_CASO",$A64="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G64))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A64,TIPOS_OPCION_H,0)),OR($A64="SELECCION_MEJOR_RESPUESTA",$A64="SELECCION_SIMPLE",$A64="SELECCION_UNICA",$A64="SELECCION_DE_LA_MEJOR_RESPUESTA",$A64="SUBITEM_CASO",$A64="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H64))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A64="SELECCION_MEJOR_RESPUESTA",$A64="SELECCION_SIMPLE",$A64="SELECCION_UNICA",$A64="SELECCION_DE_LA_MEJOR_RESPUESTA",$A64="SUBITEM_CASO",$A64="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A64,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A64,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B65" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A65,TIPOS_REQUIEREN_GRUPO,0)),OR($A65="CASO_CLINICO_TRONCO",$A65="CASO_CLINICO",$A65="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A65="PROBLEMA",$A65="SUBPROBLEMA",$A65="SUBITEM_CASO",$A65="SUBITEM_DE_CASO_O_PROBLEMA",$A65="EMPAREJAMIENTO_TRONCO",$A65="EMPAREJAMIENTO_AMPLIADO",$A65="EMPAREJAMIENTO_DE_CONCEPTOS",$A65="OPCION_EMPAREJAMIENTO",$A65="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B65))&gt;0,LEN(TRIM($B65))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D65" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A65,TIPOS_OPCION_D,0)),OR($A65="SELECCION_MEJOR_RESPUESTA",$A65="SELECCION_SIMPLE",$A65="SELECCION_UNICA",$A65="SELECCION_DE_LA_MEJOR_RESPUESTA",$A65="SUBITEM_CASO",$A65="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D65))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E65" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A65,TIPOS_OPCION_E,0)),OR($A65="SELECCION_MEJOR_RESPUESTA",$A65="SELECCION_SIMPLE",$A65="SELECCION_UNICA",$A65="SELECCION_DE_LA_MEJOR_RESPUESTA",$A65="SUBITEM_CASO",$A65="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E65))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F65" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A65,TIPOS_OPCION_F,0)),OR($A65="SELECCION_MEJOR_RESPUESTA",$A65="SELECCION_SIMPLE",$A65="SELECCION_UNICA",$A65="SELECCION_DE_LA_MEJOR_RESPUESTA",$A65="SUBITEM_CASO",$A65="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F65))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G65" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A65,TIPOS_OPCION_G,0)),OR($A65="SELECCION_MEJOR_RESPUESTA",$A65="SELECCION_SIMPLE",$A65="SELECCION_UNICA",$A65="SELECCION_DE_LA_MEJOR_RESPUESTA",$A65="SUBITEM_CASO",$A65="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G65))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H65" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A65,TIPOS_OPCION_H,0)),OR($A65="SELECCION_MEJOR_RESPUESTA",$A65="SELECCION_SIMPLE",$A65="SELECCION_UNICA",$A65="SELECCION_DE_LA_MEJOR_RESPUESTA",$A65="SUBITEM_CASO",$A65="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H65))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I65" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A65="SELECCION_MEJOR_RESPUESTA",$A65="SELECCION_SIMPLE",$A65="SELECCION_UNICA",$A65="SELECCION_DE_LA_MEJOR_RESPUESTA",$A65="SUBITEM_CASO",$A65="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A65,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J65" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A65,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A66,TIPOS_REQUIEREN_GRUPO,0)),OR($A66="CASO_CLINICO_TRONCO",$A66="CASO_CLINICO",$A66="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A66="PROBLEMA",$A66="SUBPROBLEMA",$A66="SUBITEM_CASO",$A66="SUBITEM_DE_CASO_O_PROBLEMA",$A66="EMPAREJAMIENTO_TRONCO",$A66="EMPAREJAMIENTO_AMPLIADO",$A66="EMPAREJAMIENTO_DE_CONCEPTOS",$A66="OPCION_EMPAREJAMIENTO",$A66="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B66))&gt;0,LEN(TRIM($B66))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D66" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A66,TIPOS_OPCION_D,0)),OR($A66="SELECCION_MEJOR_RESPUESTA",$A66="SELECCION_SIMPLE",$A66="SELECCION_UNICA",$A66="SELECCION_DE_LA_MEJOR_RESPUESTA",$A66="SUBITEM_CASO",$A66="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D66))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E66" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A66,TIPOS_OPCION_E,0)),OR($A66="SELECCION_MEJOR_RESPUESTA",$A66="SELECCION_SIMPLE",$A66="SELECCION_UNICA",$A66="SELECCION_DE_LA_MEJOR_RESPUESTA",$A66="SUBITEM_CASO",$A66="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E66))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F66" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A66,TIPOS_OPCION_F,0)),OR($A66="SELECCION_MEJOR_RESPUESTA",$A66="SELECCION_SIMPLE",$A66="SELECCION_UNICA",$A66="SELECCION_DE_LA_MEJOR_RESPUESTA",$A66="SUBITEM_CASO",$A66="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F66))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G66" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A66,TIPOS_OPCION_G,0)),OR($A66="SELECCION_MEJOR_RESPUESTA",$A66="SELECCION_SIMPLE",$A66="SELECCION_UNICA",$A66="SELECCION_DE_LA_MEJOR_RESPUESTA",$A66="SUBITEM_CASO",$A66="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G66))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H66" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A66,TIPOS_OPCION_H,0)),OR($A66="SELECCION_MEJOR_RESPUESTA",$A66="SELECCION_SIMPLE",$A66="SELECCION_UNICA",$A66="SELECCION_DE_LA_MEJOR_RESPUESTA",$A66="SUBITEM_CASO",$A66="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H66))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I66" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A66="SELECCION_MEJOR_RESPUESTA",$A66="SELECCION_SIMPLE",$A66="SELECCION_UNICA",$A66="SELECCION_DE_LA_MEJOR_RESPUESTA",$A66="SUBITEM_CASO",$A66="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A66,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J66" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A66,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B67" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A67,TIPOS_REQUIEREN_GRUPO,0)),OR($A67="CASO_CLINICO_TRONCO",$A67="CASO_CLINICO",$A67="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A67="PROBLEMA",$A67="SUBPROBLEMA",$A67="SUBITEM_CASO",$A67="SUBITEM_DE_CASO_O_PROBLEMA",$A67="EMPAREJAMIENTO_TRONCO",$A67="EMPAREJAMIENTO_AMPLIADO",$A67="EMPAREJAMIENTO_DE_CONCEPTOS",$A67="OPCION_EMPAREJAMIENTO",$A67="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B67))&gt;0,LEN(TRIM($B67))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A67,TIPOS_OPCION_D,0)),OR($A67="SELECCION_MEJOR_RESPUESTA",$A67="SELECCION_SIMPLE",$A67="SELECCION_UNICA",$A67="SELECCION_DE_LA_MEJOR_RESPUESTA",$A67="SUBITEM_CASO",$A67="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D67))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A67,TIPOS_OPCION_E,0)),OR($A67="SELECCION_MEJOR_RESPUESTA",$A67="SELECCION_SIMPLE",$A67="SELECCION_UNICA",$A67="SELECCION_DE_LA_MEJOR_RESPUESTA",$A67="SUBITEM_CASO",$A67="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E67))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A67,TIPOS_OPCION_F,0)),OR($A67="SELECCION_MEJOR_RESPUESTA",$A67="SELECCION_SIMPLE",$A67="SELECCION_UNICA",$A67="SELECCION_DE_LA_MEJOR_RESPUESTA",$A67="SUBITEM_CASO",$A67="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F67))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A67,TIPOS_OPCION_G,0)),OR($A67="SELECCION_MEJOR_RESPUESTA",$A67="SELECCION_SIMPLE",$A67="SELECCION_UNICA",$A67="SELECCION_DE_LA_MEJOR_RESPUESTA",$A67="SUBITEM_CASO",$A67="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G67))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A67,TIPOS_OPCION_H,0)),OR($A67="SELECCION_MEJOR_RESPUESTA",$A67="SELECCION_SIMPLE",$A67="SELECCION_UNICA",$A67="SELECCION_DE_LA_MEJOR_RESPUESTA",$A67="SUBITEM_CASO",$A67="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H67))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A67="SELECCION_MEJOR_RESPUESTA",$A67="SELECCION_SIMPLE",$A67="SELECCION_UNICA",$A67="SELECCION_DE_LA_MEJOR_RESPUESTA",$A67="SUBITEM_CASO",$A67="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A67,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J67" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A67,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B68" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A68,TIPOS_REQUIEREN_GRUPO,0)),OR($A68="CASO_CLINICO_TRONCO",$A68="CASO_CLINICO",$A68="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A68="PROBLEMA",$A68="SUBPROBLEMA",$A68="SUBITEM_CASO",$A68="SUBITEM_DE_CASO_O_PROBLEMA",$A68="EMPAREJAMIENTO_TRONCO",$A68="EMPAREJAMIENTO_AMPLIADO",$A68="EMPAREJAMIENTO_DE_CONCEPTOS",$A68="OPCION_EMPAREJAMIENTO",$A68="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B68))&gt;0,LEN(TRIM($B68))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D68" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A68,TIPOS_OPCION_D,0)),OR($A68="SELECCION_MEJOR_RESPUESTA",$A68="SELECCION_SIMPLE",$A68="SELECCION_UNICA",$A68="SELECCION_DE_LA_MEJOR_RESPUESTA",$A68="SUBITEM_CASO",$A68="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D68))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E68" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A68,TIPOS_OPCION_E,0)),OR($A68="SELECCION_MEJOR_RESPUESTA",$A68="SELECCION_SIMPLE",$A68="SELECCION_UNICA",$A68="SELECCION_DE_LA_MEJOR_RESPUESTA",$A68="SUBITEM_CASO",$A68="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E68))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F68" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A68,TIPOS_OPCION_F,0)),OR($A68="SELECCION_MEJOR_RESPUESTA",$A68="SELECCION_SIMPLE",$A68="SELECCION_UNICA",$A68="SELECCION_DE_LA_MEJOR_RESPUESTA",$A68="SUBITEM_CASO",$A68="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F68))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G68" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A68,TIPOS_OPCION_G,0)),OR($A68="SELECCION_MEJOR_RESPUESTA",$A68="SELECCION_SIMPLE",$A68="SELECCION_UNICA",$A68="SELECCION_DE_LA_MEJOR_RESPUESTA",$A68="SUBITEM_CASO",$A68="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G68))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H68" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A68,TIPOS_OPCION_H,0)),OR($A68="SELECCION_MEJOR_RESPUESTA",$A68="SELECCION_SIMPLE",$A68="SELECCION_UNICA",$A68="SELECCION_DE_LA_MEJOR_RESPUESTA",$A68="SUBITEM_CASO",$A68="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H68))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I68" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A68="SELECCION_MEJOR_RESPUESTA",$A68="SELECCION_SIMPLE",$A68="SELECCION_UNICA",$A68="SELECCION_DE_LA_MEJOR_RESPUESTA",$A68="SUBITEM_CASO",$A68="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A68,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J68" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A68,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B69" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A69,TIPOS_REQUIEREN_GRUPO,0)),OR($A69="CASO_CLINICO_TRONCO",$A69="CASO_CLINICO",$A69="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A69="PROBLEMA",$A69="SUBPROBLEMA",$A69="SUBITEM_CASO",$A69="SUBITEM_DE_CASO_O_PROBLEMA",$A69="EMPAREJAMIENTO_TRONCO",$A69="EMPAREJAMIENTO_AMPLIADO",$A69="EMPAREJAMIENTO_DE_CONCEPTOS",$A69="OPCION_EMPAREJAMIENTO",$A69="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B69))&gt;0,LEN(TRIM($B69))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D69" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A69,TIPOS_OPCION_D,0)),OR($A69="SELECCION_MEJOR_RESPUESTA",$A69="SELECCION_SIMPLE",$A69="SELECCION_UNICA",$A69="SELECCION_DE_LA_MEJOR_RESPUESTA",$A69="SUBITEM_CASO",$A69="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D69))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E69" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A69,TIPOS_OPCION_E,0)),OR($A69="SELECCION_MEJOR_RESPUESTA",$A69="SELECCION_SIMPLE",$A69="SELECCION_UNICA",$A69="SELECCION_DE_LA_MEJOR_RESPUESTA",$A69="SUBITEM_CASO",$A69="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E69))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F69" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A69,TIPOS_OPCION_F,0)),OR($A69="SELECCION_MEJOR_RESPUESTA",$A69="SELECCION_SIMPLE",$A69="SELECCION_UNICA",$A69="SELECCION_DE_LA_MEJOR_RESPUESTA",$A69="SUBITEM_CASO",$A69="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F69))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G69" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A69,TIPOS_OPCION_G,0)),OR($A69="SELECCION_MEJOR_RESPUESTA",$A69="SELECCION_SIMPLE",$A69="SELECCION_UNICA",$A69="SELECCION_DE_LA_MEJOR_RESPUESTA",$A69="SUBITEM_CASO",$A69="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G69))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H69" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A69,TIPOS_OPCION_H,0)),OR($A69="SELECCION_MEJOR_RESPUESTA",$A69="SELECCION_SIMPLE",$A69="SELECCION_UNICA",$A69="SELECCION_DE_LA_MEJOR_RESPUESTA",$A69="SUBITEM_CASO",$A69="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H69))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I69" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A69="SELECCION_MEJOR_RESPUESTA",$A69="SELECCION_SIMPLE",$A69="SELECCION_UNICA",$A69="SELECCION_DE_LA_MEJOR_RESPUESTA",$A69="SUBITEM_CASO",$A69="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A69,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J69" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A69,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A70,TIPOS_REQUIEREN_GRUPO,0)),OR($A70="CASO_CLINICO_TRONCO",$A70="CASO_CLINICO",$A70="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A70="PROBLEMA",$A70="SUBPROBLEMA",$A70="SUBITEM_CASO",$A70="SUBITEM_DE_CASO_O_PROBLEMA",$A70="EMPAREJAMIENTO_TRONCO",$A70="EMPAREJAMIENTO_AMPLIADO",$A70="EMPAREJAMIENTO_DE_CONCEPTOS",$A70="OPCION_EMPAREJAMIENTO",$A70="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B70))&gt;0,LEN(TRIM($B70))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A70,TIPOS_OPCION_D,0)),OR($A70="SELECCION_MEJOR_RESPUESTA",$A70="SELECCION_SIMPLE",$A70="SELECCION_UNICA",$A70="SELECCION_DE_LA_MEJOR_RESPUESTA",$A70="SUBITEM_CASO",$A70="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D70))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A70,TIPOS_OPCION_E,0)),OR($A70="SELECCION_MEJOR_RESPUESTA",$A70="SELECCION_SIMPLE",$A70="SELECCION_UNICA",$A70="SELECCION_DE_LA_MEJOR_RESPUESTA",$A70="SUBITEM_CASO",$A70="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E70))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A70,TIPOS_OPCION_F,0)),OR($A70="SELECCION_MEJOR_RESPUESTA",$A70="SELECCION_SIMPLE",$A70="SELECCION_UNICA",$A70="SELECCION_DE_LA_MEJOR_RESPUESTA",$A70="SUBITEM_CASO",$A70="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F70))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A70,TIPOS_OPCION_G,0)),OR($A70="SELECCION_MEJOR_RESPUESTA",$A70="SELECCION_SIMPLE",$A70="SELECCION_UNICA",$A70="SELECCION_DE_LA_MEJOR_RESPUESTA",$A70="SUBITEM_CASO",$A70="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G70))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A70,TIPOS_OPCION_H,0)),OR($A70="SELECCION_MEJOR_RESPUESTA",$A70="SELECCION_SIMPLE",$A70="SELECCION_UNICA",$A70="SELECCION_DE_LA_MEJOR_RESPUESTA",$A70="SUBITEM_CASO",$A70="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H70))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A70="SELECCION_MEJOR_RESPUESTA",$A70="SELECCION_SIMPLE",$A70="SELECCION_UNICA",$A70="SELECCION_DE_LA_MEJOR_RESPUESTA",$A70="SUBITEM_CASO",$A70="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A70,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J70" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A70,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B71" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A71,TIPOS_REQUIEREN_GRUPO,0)),OR($A71="CASO_CLINICO_TRONCO",$A71="CASO_CLINICO",$A71="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A71="PROBLEMA",$A71="SUBPROBLEMA",$A71="SUBITEM_CASO",$A71="SUBITEM_DE_CASO_O_PROBLEMA",$A71="EMPAREJAMIENTO_TRONCO",$A71="EMPAREJAMIENTO_AMPLIADO",$A71="EMPAREJAMIENTO_DE_CONCEPTOS",$A71="OPCION_EMPAREJAMIENTO",$A71="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B71))&gt;0,LEN(TRIM($B71))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A71,TIPOS_OPCION_D,0)),OR($A71="SELECCION_MEJOR_RESPUESTA",$A71="SELECCION_SIMPLE",$A71="SELECCION_UNICA",$A71="SELECCION_DE_LA_MEJOR_RESPUESTA",$A71="SUBITEM_CASO",$A71="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D71))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A71,TIPOS_OPCION_E,0)),OR($A71="SELECCION_MEJOR_RESPUESTA",$A71="SELECCION_SIMPLE",$A71="SELECCION_UNICA",$A71="SELECCION_DE_LA_MEJOR_RESPUESTA",$A71="SUBITEM_CASO",$A71="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E71))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A71,TIPOS_OPCION_F,0)),OR($A71="SELECCION_MEJOR_RESPUESTA",$A71="SELECCION_SIMPLE",$A71="SELECCION_UNICA",$A71="SELECCION_DE_LA_MEJOR_RESPUESTA",$A71="SUBITEM_CASO",$A71="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F71))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A71,TIPOS_OPCION_G,0)),OR($A71="SELECCION_MEJOR_RESPUESTA",$A71="SELECCION_SIMPLE",$A71="SELECCION_UNICA",$A71="SELECCION_DE_LA_MEJOR_RESPUESTA",$A71="SUBITEM_CASO",$A71="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G71))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A71,TIPOS_OPCION_H,0)),OR($A71="SELECCION_MEJOR_RESPUESTA",$A71="SELECCION_SIMPLE",$A71="SELECCION_UNICA",$A71="SELECCION_DE_LA_MEJOR_RESPUESTA",$A71="SUBITEM_CASO",$A71="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H71))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A71="SELECCION_MEJOR_RESPUESTA",$A71="SELECCION_SIMPLE",$A71="SELECCION_UNICA",$A71="SELECCION_DE_LA_MEJOR_RESPUESTA",$A71="SUBITEM_CASO",$A71="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A71,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J71" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A71,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B72" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A72,TIPOS_REQUIEREN_GRUPO,0)),OR($A72="CASO_CLINICO_TRONCO",$A72="CASO_CLINICO",$A72="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A72="PROBLEMA",$A72="SUBPROBLEMA",$A72="SUBITEM_CASO",$A72="SUBITEM_DE_CASO_O_PROBLEMA",$A72="EMPAREJAMIENTO_TRONCO",$A72="EMPAREJAMIENTO_AMPLIADO",$A72="EMPAREJAMIENTO_DE_CONCEPTOS",$A72="OPCION_EMPAREJAMIENTO",$A72="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B72))&gt;0,LEN(TRIM($B72))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D72" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A72,TIPOS_OPCION_D,0)),OR($A72="SELECCION_MEJOR_RESPUESTA",$A72="SELECCION_SIMPLE",$A72="SELECCION_UNICA",$A72="SELECCION_DE_LA_MEJOR_RESPUESTA",$A72="SUBITEM_CASO",$A72="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D72))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E72" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A72,TIPOS_OPCION_E,0)),OR($A72="SELECCION_MEJOR_RESPUESTA",$A72="SELECCION_SIMPLE",$A72="SELECCION_UNICA",$A72="SELECCION_DE_LA_MEJOR_RESPUESTA",$A72="SUBITEM_CASO",$A72="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E72))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F72" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A72,TIPOS_OPCION_F,0)),OR($A72="SELECCION_MEJOR_RESPUESTA",$A72="SELECCION_SIMPLE",$A72="SELECCION_UNICA",$A72="SELECCION_DE_LA_MEJOR_RESPUESTA",$A72="SUBITEM_CASO",$A72="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F72))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G72" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A72,TIPOS_OPCION_G,0)),OR($A72="SELECCION_MEJOR_RESPUESTA",$A72="SELECCION_SIMPLE",$A72="SELECCION_UNICA",$A72="SELECCION_DE_LA_MEJOR_RESPUESTA",$A72="SUBITEM_CASO",$A72="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G72))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H72" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A72,TIPOS_OPCION_H,0)),OR($A72="SELECCION_MEJOR_RESPUESTA",$A72="SELECCION_SIMPLE",$A72="SELECCION_UNICA",$A72="SELECCION_DE_LA_MEJOR_RESPUESTA",$A72="SUBITEM_CASO",$A72="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H72))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I72" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A72="SELECCION_MEJOR_RESPUESTA",$A72="SELECCION_SIMPLE",$A72="SELECCION_UNICA",$A72="SELECCION_DE_LA_MEJOR_RESPUESTA",$A72="SUBITEM_CASO",$A72="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A72,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J72" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A72,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B73" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A73,TIPOS_REQUIEREN_GRUPO,0)),OR($A73="CASO_CLINICO_TRONCO",$A73="CASO_CLINICO",$A73="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A73="PROBLEMA",$A73="SUBPROBLEMA",$A73="SUBITEM_CASO",$A73="SUBITEM_DE_CASO_O_PROBLEMA",$A73="EMPAREJAMIENTO_TRONCO",$A73="EMPAREJAMIENTO_AMPLIADO",$A73="EMPAREJAMIENTO_DE_CONCEPTOS",$A73="OPCION_EMPAREJAMIENTO",$A73="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B73))&gt;0,LEN(TRIM($B73))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D73" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A73,TIPOS_OPCION_D,0)),OR($A73="SELECCION_MEJOR_RESPUESTA",$A73="SELECCION_SIMPLE",$A73="SELECCION_UNICA",$A73="SELECCION_DE_LA_MEJOR_RESPUESTA",$A73="SUBITEM_CASO",$A73="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D73))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E73" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A73,TIPOS_OPCION_E,0)),OR($A73="SELECCION_MEJOR_RESPUESTA",$A73="SELECCION_SIMPLE",$A73="SELECCION_UNICA",$A73="SELECCION_DE_LA_MEJOR_RESPUESTA",$A73="SUBITEM_CASO",$A73="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E73))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F73" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A73,TIPOS_OPCION_F,0)),OR($A73="SELECCION_MEJOR_RESPUESTA",$A73="SELECCION_SIMPLE",$A73="SELECCION_UNICA",$A73="SELECCION_DE_LA_MEJOR_RESPUESTA",$A73="SUBITEM_CASO",$A73="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F73))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G73" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A73,TIPOS_OPCION_G,0)),OR($A73="SELECCION_MEJOR_RESPUESTA",$A73="SELECCION_SIMPLE",$A73="SELECCION_UNICA",$A73="SELECCION_DE_LA_MEJOR_RESPUESTA",$A73="SUBITEM_CASO",$A73="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G73))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H73" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A73,TIPOS_OPCION_H,0)),OR($A73="SELECCION_MEJOR_RESPUESTA",$A73="SELECCION_SIMPLE",$A73="SELECCION_UNICA",$A73="SELECCION_DE_LA_MEJOR_RESPUESTA",$A73="SUBITEM_CASO",$A73="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H73))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I73" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A73="SELECCION_MEJOR_RESPUESTA",$A73="SELECCION_SIMPLE",$A73="SELECCION_UNICA",$A73="SELECCION_DE_LA_MEJOR_RESPUESTA",$A73="SUBITEM_CASO",$A73="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A73,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J73" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A73,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A74,TIPOS_REQUIEREN_GRUPO,0)),OR($A74="CASO_CLINICO_TRONCO",$A74="CASO_CLINICO",$A74="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A74="PROBLEMA",$A74="SUBPROBLEMA",$A74="SUBITEM_CASO",$A74="SUBITEM_DE_CASO_O_PROBLEMA",$A74="EMPAREJAMIENTO_TRONCO",$A74="EMPAREJAMIENTO_AMPLIADO",$A74="EMPAREJAMIENTO_DE_CONCEPTOS",$A74="OPCION_EMPAREJAMIENTO",$A74="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B74))&gt;0,LEN(TRIM($B74))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D74" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A74,TIPOS_OPCION_D,0)),OR($A74="SELECCION_MEJOR_RESPUESTA",$A74="SELECCION_SIMPLE",$A74="SELECCION_UNICA",$A74="SELECCION_DE_LA_MEJOR_RESPUESTA",$A74="SUBITEM_CASO",$A74="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D74))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E74" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A74,TIPOS_OPCION_E,0)),OR($A74="SELECCION_MEJOR_RESPUESTA",$A74="SELECCION_SIMPLE",$A74="SELECCION_UNICA",$A74="SELECCION_DE_LA_MEJOR_RESPUESTA",$A74="SUBITEM_CASO",$A74="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E74))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F74" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A74,TIPOS_OPCION_F,0)),OR($A74="SELECCION_MEJOR_RESPUESTA",$A74="SELECCION_SIMPLE",$A74="SELECCION_UNICA",$A74="SELECCION_DE_LA_MEJOR_RESPUESTA",$A74="SUBITEM_CASO",$A74="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F74))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G74" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A74,TIPOS_OPCION_G,0)),OR($A74="SELECCION_MEJOR_RESPUESTA",$A74="SELECCION_SIMPLE",$A74="SELECCION_UNICA",$A74="SELECCION_DE_LA_MEJOR_RESPUESTA",$A74="SUBITEM_CASO",$A74="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G74))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H74" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A74,TIPOS_OPCION_H,0)),OR($A74="SELECCION_MEJOR_RESPUESTA",$A74="SELECCION_SIMPLE",$A74="SELECCION_UNICA",$A74="SELECCION_DE_LA_MEJOR_RESPUESTA",$A74="SUBITEM_CASO",$A74="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H74))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I74" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A74="SELECCION_MEJOR_RESPUESTA",$A74="SELECCION_SIMPLE",$A74="SELECCION_UNICA",$A74="SELECCION_DE_LA_MEJOR_RESPUESTA",$A74="SUBITEM_CASO",$A74="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A74,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J74" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A74,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B75" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A75,TIPOS_REQUIEREN_GRUPO,0)),OR($A75="CASO_CLINICO_TRONCO",$A75="CASO_CLINICO",$A75="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A75="PROBLEMA",$A75="SUBPROBLEMA",$A75="SUBITEM_CASO",$A75="SUBITEM_DE_CASO_O_PROBLEMA",$A75="EMPAREJAMIENTO_TRONCO",$A75="EMPAREJAMIENTO_AMPLIADO",$A75="EMPAREJAMIENTO_DE_CONCEPTOS",$A75="OPCION_EMPAREJAMIENTO",$A75="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B75))&gt;0,LEN(TRIM($B75))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D75" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A75,TIPOS_OPCION_D,0)),OR($A75="SELECCION_MEJOR_RESPUESTA",$A75="SELECCION_SIMPLE",$A75="SELECCION_UNICA",$A75="SELECCION_DE_LA_MEJOR_RESPUESTA",$A75="SUBITEM_CASO",$A75="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D75))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E75" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A75,TIPOS_OPCION_E,0)),OR($A75="SELECCION_MEJOR_RESPUESTA",$A75="SELECCION_SIMPLE",$A75="SELECCION_UNICA",$A75="SELECCION_DE_LA_MEJOR_RESPUESTA",$A75="SUBITEM_CASO",$A75="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E75))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F75" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A75,TIPOS_OPCION_F,0)),OR($A75="SELECCION_MEJOR_RESPUESTA",$A75="SELECCION_SIMPLE",$A75="SELECCION_UNICA",$A75="SELECCION_DE_LA_MEJOR_RESPUESTA",$A75="SUBITEM_CASO",$A75="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F75))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G75" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A75,TIPOS_OPCION_G,0)),OR($A75="SELECCION_MEJOR_RESPUESTA",$A75="SELECCION_SIMPLE",$A75="SELECCION_UNICA",$A75="SELECCION_DE_LA_MEJOR_RESPUESTA",$A75="SUBITEM_CASO",$A75="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G75))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H75" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A75,TIPOS_OPCION_H,0)),OR($A75="SELECCION_MEJOR_RESPUESTA",$A75="SELECCION_SIMPLE",$A75="SELECCION_UNICA",$A75="SELECCION_DE_LA_MEJOR_RESPUESTA",$A75="SUBITEM_CASO",$A75="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H75))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I75" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A75="SELECCION_MEJOR_RESPUESTA",$A75="SELECCION_SIMPLE",$A75="SELECCION_UNICA",$A75="SELECCION_DE_LA_MEJOR_RESPUESTA",$A75="SUBITEM_CASO",$A75="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A75,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J75" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A75,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A76,TIPOS_REQUIEREN_GRUPO,0)),OR($A76="CASO_CLINICO_TRONCO",$A76="CASO_CLINICO",$A76="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A76="PROBLEMA",$A76="SUBPROBLEMA",$A76="SUBITEM_CASO",$A76="SUBITEM_DE_CASO_O_PROBLEMA",$A76="EMPAREJAMIENTO_TRONCO",$A76="EMPAREJAMIENTO_AMPLIADO",$A76="EMPAREJAMIENTO_DE_CONCEPTOS",$A76="OPCION_EMPAREJAMIENTO",$A76="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B76))&gt;0,LEN(TRIM($B76))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D76" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A76,TIPOS_OPCION_D,0)),OR($A76="SELECCION_MEJOR_RESPUESTA",$A76="SELECCION_SIMPLE",$A76="SELECCION_UNICA",$A76="SELECCION_DE_LA_MEJOR_RESPUESTA",$A76="SUBITEM_CASO",$A76="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D76))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E76" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A76,TIPOS_OPCION_E,0)),OR($A76="SELECCION_MEJOR_RESPUESTA",$A76="SELECCION_SIMPLE",$A76="SELECCION_UNICA",$A76="SELECCION_DE_LA_MEJOR_RESPUESTA",$A76="SUBITEM_CASO",$A76="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E76))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F76" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A76,TIPOS_OPCION_F,0)),OR($A76="SELECCION_MEJOR_RESPUESTA",$A76="SELECCION_SIMPLE",$A76="SELECCION_UNICA",$A76="SELECCION_DE_LA_MEJOR_RESPUESTA",$A76="SUBITEM_CASO",$A76="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F76))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G76" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A76,TIPOS_OPCION_G,0)),OR($A76="SELECCION_MEJOR_RESPUESTA",$A76="SELECCION_SIMPLE",$A76="SELECCION_UNICA",$A76="SELECCION_DE_LA_MEJOR_RESPUESTA",$A76="SUBITEM_CASO",$A76="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G76))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H76" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A76,TIPOS_OPCION_H,0)),OR($A76="SELECCION_MEJOR_RESPUESTA",$A76="SELECCION_SIMPLE",$A76="SELECCION_UNICA",$A76="SELECCION_DE_LA_MEJOR_RESPUESTA",$A76="SUBITEM_CASO",$A76="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H76))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I76" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A76="SELECCION_MEJOR_RESPUESTA",$A76="SELECCION_SIMPLE",$A76="SELECCION_UNICA",$A76="SELECCION_DE_LA_MEJOR_RESPUESTA",$A76="SUBITEM_CASO",$A76="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A76,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A76,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A77,TIPOS_REQUIEREN_GRUPO,0)),OR($A77="CASO_CLINICO_TRONCO",$A77="CASO_CLINICO",$A77="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A77="PROBLEMA",$A77="SUBPROBLEMA",$A77="SUBITEM_CASO",$A77="SUBITEM_DE_CASO_O_PROBLEMA",$A77="EMPAREJAMIENTO_TRONCO",$A77="EMPAREJAMIENTO_AMPLIADO",$A77="EMPAREJAMIENTO_DE_CONCEPTOS",$A77="OPCION_EMPAREJAMIENTO",$A77="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B77))&gt;0,LEN(TRIM($B77))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A77,TIPOS_OPCION_D,0)),OR($A77="SELECCION_MEJOR_RESPUESTA",$A77="SELECCION_SIMPLE",$A77="SELECCION_UNICA",$A77="SELECCION_DE_LA_MEJOR_RESPUESTA",$A77="SUBITEM_CASO",$A77="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D77))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A77,TIPOS_OPCION_E,0)),OR($A77="SELECCION_MEJOR_RESPUESTA",$A77="SELECCION_SIMPLE",$A77="SELECCION_UNICA",$A77="SELECCION_DE_LA_MEJOR_RESPUESTA",$A77="SUBITEM_CASO",$A77="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E77))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A77,TIPOS_OPCION_F,0)),OR($A77="SELECCION_MEJOR_RESPUESTA",$A77="SELECCION_SIMPLE",$A77="SELECCION_UNICA",$A77="SELECCION_DE_LA_MEJOR_RESPUESTA",$A77="SUBITEM_CASO",$A77="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F77))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A77,TIPOS_OPCION_G,0)),OR($A77="SELECCION_MEJOR_RESPUESTA",$A77="SELECCION_SIMPLE",$A77="SELECCION_UNICA",$A77="SELECCION_DE_LA_MEJOR_RESPUESTA",$A77="SUBITEM_CASO",$A77="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G77))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A77,TIPOS_OPCION_H,0)),OR($A77="SELECCION_MEJOR_RESPUESTA",$A77="SELECCION_SIMPLE",$A77="SELECCION_UNICA",$A77="SELECCION_DE_LA_MEJOR_RESPUESTA",$A77="SUBITEM_CASO",$A77="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H77))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A77="SELECCION_MEJOR_RESPUESTA",$A77="SELECCION_SIMPLE",$A77="SELECCION_UNICA",$A77="SELECCION_DE_LA_MEJOR_RESPUESTA",$A77="SUBITEM_CASO",$A77="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A77,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A77,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A78,TIPOS_REQUIEREN_GRUPO,0)),OR($A78="CASO_CLINICO_TRONCO",$A78="CASO_CLINICO",$A78="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A78="PROBLEMA",$A78="SUBPROBLEMA",$A78="SUBITEM_CASO",$A78="SUBITEM_DE_CASO_O_PROBLEMA",$A78="EMPAREJAMIENTO_TRONCO",$A78="EMPAREJAMIENTO_AMPLIADO",$A78="EMPAREJAMIENTO_DE_CONCEPTOS",$A78="OPCION_EMPAREJAMIENTO",$A78="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B78))&gt;0,LEN(TRIM($B78))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A78,TIPOS_OPCION_D,0)),OR($A78="SELECCION_MEJOR_RESPUESTA",$A78="SELECCION_SIMPLE",$A78="SELECCION_UNICA",$A78="SELECCION_DE_LA_MEJOR_RESPUESTA",$A78="SUBITEM_CASO",$A78="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D78))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A78,TIPOS_OPCION_E,0)),OR($A78="SELECCION_MEJOR_RESPUESTA",$A78="SELECCION_SIMPLE",$A78="SELECCION_UNICA",$A78="SELECCION_DE_LA_MEJOR_RESPUESTA",$A78="SUBITEM_CASO",$A78="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E78))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A78,TIPOS_OPCION_F,0)),OR($A78="SELECCION_MEJOR_RESPUESTA",$A78="SELECCION_SIMPLE",$A78="SELECCION_UNICA",$A78="SELECCION_DE_LA_MEJOR_RESPUESTA",$A78="SUBITEM_CASO",$A78="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F78))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A78,TIPOS_OPCION_G,0)),OR($A78="SELECCION_MEJOR_RESPUESTA",$A78="SELECCION_SIMPLE",$A78="SELECCION_UNICA",$A78="SELECCION_DE_LA_MEJOR_RESPUESTA",$A78="SUBITEM_CASO",$A78="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G78))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A78,TIPOS_OPCION_H,0)),OR($A78="SELECCION_MEJOR_RESPUESTA",$A78="SELECCION_SIMPLE",$A78="SELECCION_UNICA",$A78="SELECCION_DE_LA_MEJOR_RESPUESTA",$A78="SUBITEM_CASO",$A78="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H78))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I78" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A78="SELECCION_MEJOR_RESPUESTA",$A78="SELECCION_SIMPLE",$A78="SELECCION_UNICA",$A78="SELECCION_DE_LA_MEJOR_RESPUESTA",$A78="SUBITEM_CASO",$A78="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A78,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J78" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A78,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B79" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A79,TIPOS_REQUIEREN_GRUPO,0)),OR($A79="CASO_CLINICO_TRONCO",$A79="CASO_CLINICO",$A79="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A79="PROBLEMA",$A79="SUBPROBLEMA",$A79="SUBITEM_CASO",$A79="SUBITEM_DE_CASO_O_PROBLEMA",$A79="EMPAREJAMIENTO_TRONCO",$A79="EMPAREJAMIENTO_AMPLIADO",$A79="EMPAREJAMIENTO_DE_CONCEPTOS",$A79="OPCION_EMPAREJAMIENTO",$A79="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B79))&gt;0,LEN(TRIM($B79))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D79" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A79,TIPOS_OPCION_D,0)),OR($A79="SELECCION_MEJOR_RESPUESTA",$A79="SELECCION_SIMPLE",$A79="SELECCION_UNICA",$A79="SELECCION_DE_LA_MEJOR_RESPUESTA",$A79="SUBITEM_CASO",$A79="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D79))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E79" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A79,TIPOS_OPCION_E,0)),OR($A79="SELECCION_MEJOR_RESPUESTA",$A79="SELECCION_SIMPLE",$A79="SELECCION_UNICA",$A79="SELECCION_DE_LA_MEJOR_RESPUESTA",$A79="SUBITEM_CASO",$A79="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E79))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F79" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A79,TIPOS_OPCION_F,0)),OR($A79="SELECCION_MEJOR_RESPUESTA",$A79="SELECCION_SIMPLE",$A79="SELECCION_UNICA",$A79="SELECCION_DE_LA_MEJOR_RESPUESTA",$A79="SUBITEM_CASO",$A79="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F79))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G79" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A79,TIPOS_OPCION_G,0)),OR($A79="SELECCION_MEJOR_RESPUESTA",$A79="SELECCION_SIMPLE",$A79="SELECCION_UNICA",$A79="SELECCION_DE_LA_MEJOR_RESPUESTA",$A79="SUBITEM_CASO",$A79="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G79))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H79" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A79,TIPOS_OPCION_H,0)),OR($A79="SELECCION_MEJOR_RESPUESTA",$A79="SELECCION_SIMPLE",$A79="SELECCION_UNICA",$A79="SELECCION_DE_LA_MEJOR_RESPUESTA",$A79="SUBITEM_CASO",$A79="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H79))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I79" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A79="SELECCION_MEJOR_RESPUESTA",$A79="SELECCION_SIMPLE",$A79="SELECCION_UNICA",$A79="SELECCION_DE_LA_MEJOR_RESPUESTA",$A79="SUBITEM_CASO",$A79="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A79,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J79" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A79,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B80" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A80,TIPOS_REQUIEREN_GRUPO,0)),OR($A80="CASO_CLINICO_TRONCO",$A80="CASO_CLINICO",$A80="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A80="PROBLEMA",$A80="SUBPROBLEMA",$A80="SUBITEM_CASO",$A80="SUBITEM_DE_CASO_O_PROBLEMA",$A80="EMPAREJAMIENTO_TRONCO",$A80="EMPAREJAMIENTO_AMPLIADO",$A80="EMPAREJAMIENTO_DE_CONCEPTOS",$A80="OPCION_EMPAREJAMIENTO",$A80="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B80))&gt;0,LEN(TRIM($B80))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D80" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A80,TIPOS_OPCION_D,0)),OR($A80="SELECCION_MEJOR_RESPUESTA",$A80="SELECCION_SIMPLE",$A80="SELECCION_UNICA",$A80="SELECCION_DE_LA_MEJOR_RESPUESTA",$A80="SUBITEM_CASO",$A80="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D80))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E80" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A80,TIPOS_OPCION_E,0)),OR($A80="SELECCION_MEJOR_RESPUESTA",$A80="SELECCION_SIMPLE",$A80="SELECCION_UNICA",$A80="SELECCION_DE_LA_MEJOR_RESPUESTA",$A80="SUBITEM_CASO",$A80="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E80))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F80" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A80,TIPOS_OPCION_F,0)),OR($A80="SELECCION_MEJOR_RESPUESTA",$A80="SELECCION_SIMPLE",$A80="SELECCION_UNICA",$A80="SELECCION_DE_LA_MEJOR_RESPUESTA",$A80="SUBITEM_CASO",$A80="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F80))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G80" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A80,TIPOS_OPCION_G,0)),OR($A80="SELECCION_MEJOR_RESPUESTA",$A80="SELECCION_SIMPLE",$A80="SELECCION_UNICA",$A80="SELECCION_DE_LA_MEJOR_RESPUESTA",$A80="SUBITEM_CASO",$A80="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G80))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H80" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A80,TIPOS_OPCION_H,0)),OR($A80="SELECCION_MEJOR_RESPUESTA",$A80="SELECCION_SIMPLE",$A80="SELECCION_UNICA",$A80="SELECCION_DE_LA_MEJOR_RESPUESTA",$A80="SUBITEM_CASO",$A80="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H80))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I80" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A80="SELECCION_MEJOR_RESPUESTA",$A80="SELECCION_SIMPLE",$A80="SELECCION_UNICA",$A80="SELECCION_DE_LA_MEJOR_RESPUESTA",$A80="SUBITEM_CASO",$A80="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A80,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J80" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A80,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A81,TIPOS_REQUIEREN_GRUPO,0)),OR($A81="CASO_CLINICO_TRONCO",$A81="CASO_CLINICO",$A81="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A81="PROBLEMA",$A81="SUBPROBLEMA",$A81="SUBITEM_CASO",$A81="SUBITEM_DE_CASO_O_PROBLEMA",$A81="EMPAREJAMIENTO_TRONCO",$A81="EMPAREJAMIENTO_AMPLIADO",$A81="EMPAREJAMIENTO_DE_CONCEPTOS",$A81="OPCION_EMPAREJAMIENTO",$A81="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B81))&gt;0,LEN(TRIM($B81))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D81" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A81,TIPOS_OPCION_D,0)),OR($A81="SELECCION_MEJOR_RESPUESTA",$A81="SELECCION_SIMPLE",$A81="SELECCION_UNICA",$A81="SELECCION_DE_LA_MEJOR_RESPUESTA",$A81="SUBITEM_CASO",$A81="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D81))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E81" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A81,TIPOS_OPCION_E,0)),OR($A81="SELECCION_MEJOR_RESPUESTA",$A81="SELECCION_SIMPLE",$A81="SELECCION_UNICA",$A81="SELECCION_DE_LA_MEJOR_RESPUESTA",$A81="SUBITEM_CASO",$A81="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E81))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F81" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A81,TIPOS_OPCION_F,0)),OR($A81="SELECCION_MEJOR_RESPUESTA",$A81="SELECCION_SIMPLE",$A81="SELECCION_UNICA",$A81="SELECCION_DE_LA_MEJOR_RESPUESTA",$A81="SUBITEM_CASO",$A81="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F81))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G81" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A81,TIPOS_OPCION_G,0)),OR($A81="SELECCION_MEJOR_RESPUESTA",$A81="SELECCION_SIMPLE",$A81="SELECCION_UNICA",$A81="SELECCION_DE_LA_MEJOR_RESPUESTA",$A81="SUBITEM_CASO",$A81="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G81))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H81" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A81,TIPOS_OPCION_H,0)),OR($A81="SELECCION_MEJOR_RESPUESTA",$A81="SELECCION_SIMPLE",$A81="SELECCION_UNICA",$A81="SELECCION_DE_LA_MEJOR_RESPUESTA",$A81="SUBITEM_CASO",$A81="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H81))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I81" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A81="SELECCION_MEJOR_RESPUESTA",$A81="SELECCION_SIMPLE",$A81="SELECCION_UNICA",$A81="SELECCION_DE_LA_MEJOR_RESPUESTA",$A81="SUBITEM_CASO",$A81="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A81,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A81,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A82,TIPOS_REQUIEREN_GRUPO,0)),OR($A82="CASO_CLINICO_TRONCO",$A82="CASO_CLINICO",$A82="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A82="PROBLEMA",$A82="SUBPROBLEMA",$A82="SUBITEM_CASO",$A82="SUBITEM_DE_CASO_O_PROBLEMA",$A82="EMPAREJAMIENTO_TRONCO",$A82="EMPAREJAMIENTO_AMPLIADO",$A82="EMPAREJAMIENTO_DE_CONCEPTOS",$A82="OPCION_EMPAREJAMIENTO",$A82="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B82))&gt;0,LEN(TRIM($B82))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A82,TIPOS_OPCION_D,0)),OR($A82="SELECCION_MEJOR_RESPUESTA",$A82="SELECCION_SIMPLE",$A82="SELECCION_UNICA",$A82="SELECCION_DE_LA_MEJOR_RESPUESTA",$A82="SUBITEM_CASO",$A82="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D82))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A82,TIPOS_OPCION_E,0)),OR($A82="SELECCION_MEJOR_RESPUESTA",$A82="SELECCION_SIMPLE",$A82="SELECCION_UNICA",$A82="SELECCION_DE_LA_MEJOR_RESPUESTA",$A82="SUBITEM_CASO",$A82="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E82))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A82,TIPOS_OPCION_F,0)),OR($A82="SELECCION_MEJOR_RESPUESTA",$A82="SELECCION_SIMPLE",$A82="SELECCION_UNICA",$A82="SELECCION_DE_LA_MEJOR_RESPUESTA",$A82="SUBITEM_CASO",$A82="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F82))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A82,TIPOS_OPCION_G,0)),OR($A82="SELECCION_MEJOR_RESPUESTA",$A82="SELECCION_SIMPLE",$A82="SELECCION_UNICA",$A82="SELECCION_DE_LA_MEJOR_RESPUESTA",$A82="SUBITEM_CASO",$A82="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G82))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A82,TIPOS_OPCION_H,0)),OR($A82="SELECCION_MEJOR_RESPUESTA",$A82="SELECCION_SIMPLE",$A82="SELECCION_UNICA",$A82="SELECCION_DE_LA_MEJOR_RESPUESTA",$A82="SUBITEM_CASO",$A82="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H82))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I82" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A82="SELECCION_MEJOR_RESPUESTA",$A82="SELECCION_SIMPLE",$A82="SELECCION_UNICA",$A82="SELECCION_DE_LA_MEJOR_RESPUESTA",$A82="SUBITEM_CASO",$A82="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A82,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A82,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B83" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A83,TIPOS_REQUIEREN_GRUPO,0)),OR($A83="CASO_CLINICO_TRONCO",$A83="CASO_CLINICO",$A83="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A83="PROBLEMA",$A83="SUBPROBLEMA",$A83="SUBITEM_CASO",$A83="SUBITEM_DE_CASO_O_PROBLEMA",$A83="EMPAREJAMIENTO_TRONCO",$A83="EMPAREJAMIENTO_AMPLIADO",$A83="EMPAREJAMIENTO_DE_CONCEPTOS",$A83="OPCION_EMPAREJAMIENTO",$A83="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B83))&gt;0,LEN(TRIM($B83))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D83" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A83,TIPOS_OPCION_D,0)),OR($A83="SELECCION_MEJOR_RESPUESTA",$A83="SELECCION_SIMPLE",$A83="SELECCION_UNICA",$A83="SELECCION_DE_LA_MEJOR_RESPUESTA",$A83="SUBITEM_CASO",$A83="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D83))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E83" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A83,TIPOS_OPCION_E,0)),OR($A83="SELECCION_MEJOR_RESPUESTA",$A83="SELECCION_SIMPLE",$A83="SELECCION_UNICA",$A83="SELECCION_DE_LA_MEJOR_RESPUESTA",$A83="SUBITEM_CASO",$A83="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E83))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F83" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A83,TIPOS_OPCION_F,0)),OR($A83="SELECCION_MEJOR_RESPUESTA",$A83="SELECCION_SIMPLE",$A83="SELECCION_UNICA",$A83="SELECCION_DE_LA_MEJOR_RESPUESTA",$A83="SUBITEM_CASO",$A83="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F83))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G83" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A83,TIPOS_OPCION_G,0)),OR($A83="SELECCION_MEJOR_RESPUESTA",$A83="SELECCION_SIMPLE",$A83="SELECCION_UNICA",$A83="SELECCION_DE_LA_MEJOR_RESPUESTA",$A83="SUBITEM_CASO",$A83="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G83))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H83" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A83,TIPOS_OPCION_H,0)),OR($A83="SELECCION_MEJOR_RESPUESTA",$A83="SELECCION_SIMPLE",$A83="SELECCION_UNICA",$A83="SELECCION_DE_LA_MEJOR_RESPUESTA",$A83="SUBITEM_CASO",$A83="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H83))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I83" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A83="SELECCION_MEJOR_RESPUESTA",$A83="SELECCION_SIMPLE",$A83="SELECCION_UNICA",$A83="SELECCION_DE_LA_MEJOR_RESPUESTA",$A83="SUBITEM_CASO",$A83="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A83,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J83" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A83,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A84,TIPOS_REQUIEREN_GRUPO,0)),OR($A84="CASO_CLINICO_TRONCO",$A84="CASO_CLINICO",$A84="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A84="PROBLEMA",$A84="SUBPROBLEMA",$A84="SUBITEM_CASO",$A84="SUBITEM_DE_CASO_O_PROBLEMA",$A84="EMPAREJAMIENTO_TRONCO",$A84="EMPAREJAMIENTO_AMPLIADO",$A84="EMPAREJAMIENTO_DE_CONCEPTOS",$A84="OPCION_EMPAREJAMIENTO",$A84="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B84))&gt;0,LEN(TRIM($B84))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D84" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A84,TIPOS_OPCION_D,0)),OR($A84="SELECCION_MEJOR_RESPUESTA",$A84="SELECCION_SIMPLE",$A84="SELECCION_UNICA",$A84="SELECCION_DE_LA_MEJOR_RESPUESTA",$A84="SUBITEM_CASO",$A84="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D84))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E84" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A84,TIPOS_OPCION_E,0)),OR($A84="SELECCION_MEJOR_RESPUESTA",$A84="SELECCION_SIMPLE",$A84="SELECCION_UNICA",$A84="SELECCION_DE_LA_MEJOR_RESPUESTA",$A84="SUBITEM_CASO",$A84="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E84))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F84" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A84,TIPOS_OPCION_F,0)),OR($A84="SELECCION_MEJOR_RESPUESTA",$A84="SELECCION_SIMPLE",$A84="SELECCION_UNICA",$A84="SELECCION_DE_LA_MEJOR_RESPUESTA",$A84="SUBITEM_CASO",$A84="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F84))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G84" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A84,TIPOS_OPCION_G,0)),OR($A84="SELECCION_MEJOR_RESPUESTA",$A84="SELECCION_SIMPLE",$A84="SELECCION_UNICA",$A84="SELECCION_DE_LA_MEJOR_RESPUESTA",$A84="SUBITEM_CASO",$A84="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G84))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H84" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A84,TIPOS_OPCION_H,0)),OR($A84="SELECCION_MEJOR_RESPUESTA",$A84="SELECCION_SIMPLE",$A84="SELECCION_UNICA",$A84="SELECCION_DE_LA_MEJOR_RESPUESTA",$A84="SUBITEM_CASO",$A84="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H84))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I84" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A84="SELECCION_MEJOR_RESPUESTA",$A84="SELECCION_SIMPLE",$A84="SELECCION_UNICA",$A84="SELECCION_DE_LA_MEJOR_RESPUESTA",$A84="SUBITEM_CASO",$A84="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A84,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A84,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A85,TIPOS_REQUIEREN_GRUPO,0)),OR($A85="CASO_CLINICO_TRONCO",$A85="CASO_CLINICO",$A85="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A85="PROBLEMA",$A85="SUBPROBLEMA",$A85="SUBITEM_CASO",$A85="SUBITEM_DE_CASO_O_PROBLEMA",$A85="EMPAREJAMIENTO_TRONCO",$A85="EMPAREJAMIENTO_AMPLIADO",$A85="EMPAREJAMIENTO_DE_CONCEPTOS",$A85="OPCION_EMPAREJAMIENTO",$A85="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B85))&gt;0,LEN(TRIM($B85))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D85" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A85,TIPOS_OPCION_D,0)),OR($A85="SELECCION_MEJOR_RESPUESTA",$A85="SELECCION_SIMPLE",$A85="SELECCION_UNICA",$A85="SELECCION_DE_LA_MEJOR_RESPUESTA",$A85="SUBITEM_CASO",$A85="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D85))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E85" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A85,TIPOS_OPCION_E,0)),OR($A85="SELECCION_MEJOR_RESPUESTA",$A85="SELECCION_SIMPLE",$A85="SELECCION_UNICA",$A85="SELECCION_DE_LA_MEJOR_RESPUESTA",$A85="SUBITEM_CASO",$A85="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E85))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F85" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A85,TIPOS_OPCION_F,0)),OR($A85="SELECCION_MEJOR_RESPUESTA",$A85="SELECCION_SIMPLE",$A85="SELECCION_UNICA",$A85="SELECCION_DE_LA_MEJOR_RESPUESTA",$A85="SUBITEM_CASO",$A85="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F85))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G85" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A85,TIPOS_OPCION_G,0)),OR($A85="SELECCION_MEJOR_RESPUESTA",$A85="SELECCION_SIMPLE",$A85="SELECCION_UNICA",$A85="SELECCION_DE_LA_MEJOR_RESPUESTA",$A85="SUBITEM_CASO",$A85="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G85))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H85" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A85,TIPOS_OPCION_H,0)),OR($A85="SELECCION_MEJOR_RESPUESTA",$A85="SELECCION_SIMPLE",$A85="SELECCION_UNICA",$A85="SELECCION_DE_LA_MEJOR_RESPUESTA",$A85="SUBITEM_CASO",$A85="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H85))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I85" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A85="SELECCION_MEJOR_RESPUESTA",$A85="SELECCION_SIMPLE",$A85="SELECCION_UNICA",$A85="SELECCION_DE_LA_MEJOR_RESPUESTA",$A85="SUBITEM_CASO",$A85="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A85,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A85,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A86,TIPOS_REQUIEREN_GRUPO,0)),OR($A86="CASO_CLINICO_TRONCO",$A86="CASO_CLINICO",$A86="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A86="PROBLEMA",$A86="SUBPROBLEMA",$A86="SUBITEM_CASO",$A86="SUBITEM_DE_CASO_O_PROBLEMA",$A86="EMPAREJAMIENTO_TRONCO",$A86="EMPAREJAMIENTO_AMPLIADO",$A86="EMPAREJAMIENTO_DE_CONCEPTOS",$A86="OPCION_EMPAREJAMIENTO",$A86="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B86))&gt;0,LEN(TRIM($B86))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D86" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A86,TIPOS_OPCION_D,0)),OR($A86="SELECCION_MEJOR_RESPUESTA",$A86="SELECCION_SIMPLE",$A86="SELECCION_UNICA",$A86="SELECCION_DE_LA_MEJOR_RESPUESTA",$A86="SUBITEM_CASO",$A86="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D86))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E86" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A86,TIPOS_OPCION_E,0)),OR($A86="SELECCION_MEJOR_RESPUESTA",$A86="SELECCION_SIMPLE",$A86="SELECCION_UNICA",$A86="SELECCION_DE_LA_MEJOR_RESPUESTA",$A86="SUBITEM_CASO",$A86="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E86))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F86" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A86,TIPOS_OPCION_F,0)),OR($A86="SELECCION_MEJOR_RESPUESTA",$A86="SELECCION_SIMPLE",$A86="SELECCION_UNICA",$A86="SELECCION_DE_LA_MEJOR_RESPUESTA",$A86="SUBITEM_CASO",$A86="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F86))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G86" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A86,TIPOS_OPCION_G,0)),OR($A86="SELECCION_MEJOR_RESPUESTA",$A86="SELECCION_SIMPLE",$A86="SELECCION_UNICA",$A86="SELECCION_DE_LA_MEJOR_RESPUESTA",$A86="SUBITEM_CASO",$A86="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G86))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H86" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A86,TIPOS_OPCION_H,0)),OR($A86="SELECCION_MEJOR_RESPUESTA",$A86="SELECCION_SIMPLE",$A86="SELECCION_UNICA",$A86="SELECCION_DE_LA_MEJOR_RESPUESTA",$A86="SUBITEM_CASO",$A86="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H86))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I86" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A86="SELECCION_MEJOR_RESPUESTA",$A86="SELECCION_SIMPLE",$A86="SELECCION_UNICA",$A86="SELECCION_DE_LA_MEJOR_RESPUESTA",$A86="SUBITEM_CASO",$A86="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A86,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A86,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B87" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A87,TIPOS_REQUIEREN_GRUPO,0)),OR($A87="CASO_CLINICO_TRONCO",$A87="CASO_CLINICO",$A87="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A87="PROBLEMA",$A87="SUBPROBLEMA",$A87="SUBITEM_CASO",$A87="SUBITEM_DE_CASO_O_PROBLEMA",$A87="EMPAREJAMIENTO_TRONCO",$A87="EMPAREJAMIENTO_AMPLIADO",$A87="EMPAREJAMIENTO_DE_CONCEPTOS",$A87="OPCION_EMPAREJAMIENTO",$A87="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B87))&gt;0,LEN(TRIM($B87))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D87" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A87,TIPOS_OPCION_D,0)),OR($A87="SELECCION_MEJOR_RESPUESTA",$A87="SELECCION_SIMPLE",$A87="SELECCION_UNICA",$A87="SELECCION_DE_LA_MEJOR_RESPUESTA",$A87="SUBITEM_CASO",$A87="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D87))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E87" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A87,TIPOS_OPCION_E,0)),OR($A87="SELECCION_MEJOR_RESPUESTA",$A87="SELECCION_SIMPLE",$A87="SELECCION_UNICA",$A87="SELECCION_DE_LA_MEJOR_RESPUESTA",$A87="SUBITEM_CASO",$A87="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E87))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F87" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A87,TIPOS_OPCION_F,0)),OR($A87="SELECCION_MEJOR_RESPUESTA",$A87="SELECCION_SIMPLE",$A87="SELECCION_UNICA",$A87="SELECCION_DE_LA_MEJOR_RESPUESTA",$A87="SUBITEM_CASO",$A87="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F87))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G87" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A87,TIPOS_OPCION_G,0)),OR($A87="SELECCION_MEJOR_RESPUESTA",$A87="SELECCION_SIMPLE",$A87="SELECCION_UNICA",$A87="SELECCION_DE_LA_MEJOR_RESPUESTA",$A87="SUBITEM_CASO",$A87="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G87))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H87" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A87,TIPOS_OPCION_H,0)),OR($A87="SELECCION_MEJOR_RESPUESTA",$A87="SELECCION_SIMPLE",$A87="SELECCION_UNICA",$A87="SELECCION_DE_LA_MEJOR_RESPUESTA",$A87="SUBITEM_CASO",$A87="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H87))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I87" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A87="SELECCION_MEJOR_RESPUESTA",$A87="SELECCION_SIMPLE",$A87="SELECCION_UNICA",$A87="SELECCION_DE_LA_MEJOR_RESPUESTA",$A87="SUBITEM_CASO",$A87="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A87,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J87" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A87,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B88" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A88,TIPOS_REQUIEREN_GRUPO,0)),OR($A88="CASO_CLINICO_TRONCO",$A88="CASO_CLINICO",$A88="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A88="PROBLEMA",$A88="SUBPROBLEMA",$A88="SUBITEM_CASO",$A88="SUBITEM_DE_CASO_O_PROBLEMA",$A88="EMPAREJAMIENTO_TRONCO",$A88="EMPAREJAMIENTO_AMPLIADO",$A88="EMPAREJAMIENTO_DE_CONCEPTOS",$A88="OPCION_EMPAREJAMIENTO",$A88="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B88))&gt;0,LEN(TRIM($B88))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D88" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A88,TIPOS_OPCION_D,0)),OR($A88="SELECCION_MEJOR_RESPUESTA",$A88="SELECCION_SIMPLE",$A88="SELECCION_UNICA",$A88="SELECCION_DE_LA_MEJOR_RESPUESTA",$A88="SUBITEM_CASO",$A88="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D88))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E88" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A88,TIPOS_OPCION_E,0)),OR($A88="SELECCION_MEJOR_RESPUESTA",$A88="SELECCION_SIMPLE",$A88="SELECCION_UNICA",$A88="SELECCION_DE_LA_MEJOR_RESPUESTA",$A88="SUBITEM_CASO",$A88="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E88))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F88" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A88,TIPOS_OPCION_F,0)),OR($A88="SELECCION_MEJOR_RESPUESTA",$A88="SELECCION_SIMPLE",$A88="SELECCION_UNICA",$A88="SELECCION_DE_LA_MEJOR_RESPUESTA",$A88="SUBITEM_CASO",$A88="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F88))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G88" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A88,TIPOS_OPCION_G,0)),OR($A88="SELECCION_MEJOR_RESPUESTA",$A88="SELECCION_SIMPLE",$A88="SELECCION_UNICA",$A88="SELECCION_DE_LA_MEJOR_RESPUESTA",$A88="SUBITEM_CASO",$A88="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G88))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H88" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A88,TIPOS_OPCION_H,0)),OR($A88="SELECCION_MEJOR_RESPUESTA",$A88="SELECCION_SIMPLE",$A88="SELECCION_UNICA",$A88="SELECCION_DE_LA_MEJOR_RESPUESTA",$A88="SUBITEM_CASO",$A88="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H88))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I88" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A88="SELECCION_MEJOR_RESPUESTA",$A88="SELECCION_SIMPLE",$A88="SELECCION_UNICA",$A88="SELECCION_DE_LA_MEJOR_RESPUESTA",$A88="SUBITEM_CASO",$A88="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A88,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J88" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A88,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B89" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A89,TIPOS_REQUIEREN_GRUPO,0)),OR($A89="CASO_CLINICO_TRONCO",$A89="CASO_CLINICO",$A89="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A89="PROBLEMA",$A89="SUBPROBLEMA",$A89="SUBITEM_CASO",$A89="SUBITEM_DE_CASO_O_PROBLEMA",$A89="EMPAREJAMIENTO_TRONCO",$A89="EMPAREJAMIENTO_AMPLIADO",$A89="EMPAREJAMIENTO_DE_CONCEPTOS",$A89="OPCION_EMPAREJAMIENTO",$A89="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B89))&gt;0,LEN(TRIM($B89))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D89" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A89,TIPOS_OPCION_D,0)),OR($A89="SELECCION_MEJOR_RESPUESTA",$A89="SELECCION_SIMPLE",$A89="SELECCION_UNICA",$A89="SELECCION_DE_LA_MEJOR_RESPUESTA",$A89="SUBITEM_CASO",$A89="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D89))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E89" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A89,TIPOS_OPCION_E,0)),OR($A89="SELECCION_MEJOR_RESPUESTA",$A89="SELECCION_SIMPLE",$A89="SELECCION_UNICA",$A89="SELECCION_DE_LA_MEJOR_RESPUESTA",$A89="SUBITEM_CASO",$A89="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E89))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F89" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A89,TIPOS_OPCION_F,0)),OR($A89="SELECCION_MEJOR_RESPUESTA",$A89="SELECCION_SIMPLE",$A89="SELECCION_UNICA",$A89="SELECCION_DE_LA_MEJOR_RESPUESTA",$A89="SUBITEM_CASO",$A89="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F89))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G89" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A89,TIPOS_OPCION_G,0)),OR($A89="SELECCION_MEJOR_RESPUESTA",$A89="SELECCION_SIMPLE",$A89="SELECCION_UNICA",$A89="SELECCION_DE_LA_MEJOR_RESPUESTA",$A89="SUBITEM_CASO",$A89="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G89))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H89" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A89,TIPOS_OPCION_H,0)),OR($A89="SELECCION_MEJOR_RESPUESTA",$A89="SELECCION_SIMPLE",$A89="SELECCION_UNICA",$A89="SELECCION_DE_LA_MEJOR_RESPUESTA",$A89="SUBITEM_CASO",$A89="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H89))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I89" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A89="SELECCION_MEJOR_RESPUESTA",$A89="SELECCION_SIMPLE",$A89="SELECCION_UNICA",$A89="SELECCION_DE_LA_MEJOR_RESPUESTA",$A89="SUBITEM_CASO",$A89="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A89,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J89" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A89,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A90,TIPOS_REQUIEREN_GRUPO,0)),OR($A90="CASO_CLINICO_TRONCO",$A90="CASO_CLINICO",$A90="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A90="PROBLEMA",$A90="SUBPROBLEMA",$A90="SUBITEM_CASO",$A90="SUBITEM_DE_CASO_O_PROBLEMA",$A90="EMPAREJAMIENTO_TRONCO",$A90="EMPAREJAMIENTO_AMPLIADO",$A90="EMPAREJAMIENTO_DE_CONCEPTOS",$A90="OPCION_EMPAREJAMIENTO",$A90="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B90))&gt;0,LEN(TRIM($B90))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D90" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A90,TIPOS_OPCION_D,0)),OR($A90="SELECCION_MEJOR_RESPUESTA",$A90="SELECCION_SIMPLE",$A90="SELECCION_UNICA",$A90="SELECCION_DE_LA_MEJOR_RESPUESTA",$A90="SUBITEM_CASO",$A90="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D90))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E90" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A90,TIPOS_OPCION_E,0)),OR($A90="SELECCION_MEJOR_RESPUESTA",$A90="SELECCION_SIMPLE",$A90="SELECCION_UNICA",$A90="SELECCION_DE_LA_MEJOR_RESPUESTA",$A90="SUBITEM_CASO",$A90="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E90))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F90" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A90,TIPOS_OPCION_F,0)),OR($A90="SELECCION_MEJOR_RESPUESTA",$A90="SELECCION_SIMPLE",$A90="SELECCION_UNICA",$A90="SELECCION_DE_LA_MEJOR_RESPUESTA",$A90="SUBITEM_CASO",$A90="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F90))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G90" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A90,TIPOS_OPCION_G,0)),OR($A90="SELECCION_MEJOR_RESPUESTA",$A90="SELECCION_SIMPLE",$A90="SELECCION_UNICA",$A90="SELECCION_DE_LA_MEJOR_RESPUESTA",$A90="SUBITEM_CASO",$A90="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G90))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H90" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A90,TIPOS_OPCION_H,0)),OR($A90="SELECCION_MEJOR_RESPUESTA",$A90="SELECCION_SIMPLE",$A90="SELECCION_UNICA",$A90="SELECCION_DE_LA_MEJOR_RESPUESTA",$A90="SUBITEM_CASO",$A90="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H90))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I90" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A90="SELECCION_MEJOR_RESPUESTA",$A90="SELECCION_SIMPLE",$A90="SELECCION_UNICA",$A90="SELECCION_DE_LA_MEJOR_RESPUESTA",$A90="SUBITEM_CASO",$A90="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A90,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J90" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A90,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B91" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A91,TIPOS_REQUIEREN_GRUPO,0)),OR($A91="CASO_CLINICO_TRONCO",$A91="CASO_CLINICO",$A91="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A91="PROBLEMA",$A91="SUBPROBLEMA",$A91="SUBITEM_CASO",$A91="SUBITEM_DE_CASO_O_PROBLEMA",$A91="EMPAREJAMIENTO_TRONCO",$A91="EMPAREJAMIENTO_AMPLIADO",$A91="EMPAREJAMIENTO_DE_CONCEPTOS",$A91="OPCION_EMPAREJAMIENTO",$A91="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B91))&gt;0,LEN(TRIM($B91))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D91" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A91,TIPOS_OPCION_D,0)),OR($A91="SELECCION_MEJOR_RESPUESTA",$A91="SELECCION_SIMPLE",$A91="SELECCION_UNICA",$A91="SELECCION_DE_LA_MEJOR_RESPUESTA",$A91="SUBITEM_CASO",$A91="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D91))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E91" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A91,TIPOS_OPCION_E,0)),OR($A91="SELECCION_MEJOR_RESPUESTA",$A91="SELECCION_SIMPLE",$A91="SELECCION_UNICA",$A91="SELECCION_DE_LA_MEJOR_RESPUESTA",$A91="SUBITEM_CASO",$A91="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E91))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F91" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A91,TIPOS_OPCION_F,0)),OR($A91="SELECCION_MEJOR_RESPUESTA",$A91="SELECCION_SIMPLE",$A91="SELECCION_UNICA",$A91="SELECCION_DE_LA_MEJOR_RESPUESTA",$A91="SUBITEM_CASO",$A91="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F91))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G91" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A91,TIPOS_OPCION_G,0)),OR($A91="SELECCION_MEJOR_RESPUESTA",$A91="SELECCION_SIMPLE",$A91="SELECCION_UNICA",$A91="SELECCION_DE_LA_MEJOR_RESPUESTA",$A91="SUBITEM_CASO",$A91="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G91))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H91" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A91,TIPOS_OPCION_H,0)),OR($A91="SELECCION_MEJOR_RESPUESTA",$A91="SELECCION_SIMPLE",$A91="SELECCION_UNICA",$A91="SELECCION_DE_LA_MEJOR_RESPUESTA",$A91="SUBITEM_CASO",$A91="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H91))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I91" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A91="SELECCION_MEJOR_RESPUESTA",$A91="SELECCION_SIMPLE",$A91="SELECCION_UNICA",$A91="SELECCION_DE_LA_MEJOR_RESPUESTA",$A91="SUBITEM_CASO",$A91="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A91,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J91" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A91,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B92" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A92,TIPOS_REQUIEREN_GRUPO,0)),OR($A92="CASO_CLINICO_TRONCO",$A92="CASO_CLINICO",$A92="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A92="PROBLEMA",$A92="SUBPROBLEMA",$A92="SUBITEM_CASO",$A92="SUBITEM_DE_CASO_O_PROBLEMA",$A92="EMPAREJAMIENTO_TRONCO",$A92="EMPAREJAMIENTO_AMPLIADO",$A92="EMPAREJAMIENTO_DE_CONCEPTOS",$A92="OPCION_EMPAREJAMIENTO",$A92="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B92))&gt;0,LEN(TRIM($B92))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D92" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A92,TIPOS_OPCION_D,0)),OR($A92="SELECCION_MEJOR_RESPUESTA",$A92="SELECCION_SIMPLE",$A92="SELECCION_UNICA",$A92="SELECCION_DE_LA_MEJOR_RESPUESTA",$A92="SUBITEM_CASO",$A92="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D92))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E92" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A92,TIPOS_OPCION_E,0)),OR($A92="SELECCION_MEJOR_RESPUESTA",$A92="SELECCION_SIMPLE",$A92="SELECCION_UNICA",$A92="SELECCION_DE_LA_MEJOR_RESPUESTA",$A92="SUBITEM_CASO",$A92="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E92))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F92" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A92,TIPOS_OPCION_F,0)),OR($A92="SELECCION_MEJOR_RESPUESTA",$A92="SELECCION_SIMPLE",$A92="SELECCION_UNICA",$A92="SELECCION_DE_LA_MEJOR_RESPUESTA",$A92="SUBITEM_CASO",$A92="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F92))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G92" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A92,TIPOS_OPCION_G,0)),OR($A92="SELECCION_MEJOR_RESPUESTA",$A92="SELECCION_SIMPLE",$A92="SELECCION_UNICA",$A92="SELECCION_DE_LA_MEJOR_RESPUESTA",$A92="SUBITEM_CASO",$A92="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G92))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H92" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A92,TIPOS_OPCION_H,0)),OR($A92="SELECCION_MEJOR_RESPUESTA",$A92="SELECCION_SIMPLE",$A92="SELECCION_UNICA",$A92="SELECCION_DE_LA_MEJOR_RESPUESTA",$A92="SUBITEM_CASO",$A92="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H92))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I92" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A92="SELECCION_MEJOR_RESPUESTA",$A92="SELECCION_SIMPLE",$A92="SELECCION_UNICA",$A92="SELECCION_DE_LA_MEJOR_RESPUESTA",$A92="SUBITEM_CASO",$A92="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A92,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J92" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A92,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B93" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A93,TIPOS_REQUIEREN_GRUPO,0)),OR($A93="CASO_CLINICO_TRONCO",$A93="CASO_CLINICO",$A93="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A93="PROBLEMA",$A93="SUBPROBLEMA",$A93="SUBITEM_CASO",$A93="SUBITEM_DE_CASO_O_PROBLEMA",$A93="EMPAREJAMIENTO_TRONCO",$A93="EMPAREJAMIENTO_AMPLIADO",$A93="EMPAREJAMIENTO_DE_CONCEPTOS",$A93="OPCION_EMPAREJAMIENTO",$A93="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B93))&gt;0,LEN(TRIM($B93))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D93" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A93,TIPOS_OPCION_D,0)),OR($A93="SELECCION_MEJOR_RESPUESTA",$A93="SELECCION_SIMPLE",$A93="SELECCION_UNICA",$A93="SELECCION_DE_LA_MEJOR_RESPUESTA",$A93="SUBITEM_CASO",$A93="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D93))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E93" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A93,TIPOS_OPCION_E,0)),OR($A93="SELECCION_MEJOR_RESPUESTA",$A93="SELECCION_SIMPLE",$A93="SELECCION_UNICA",$A93="SELECCION_DE_LA_MEJOR_RESPUESTA",$A93="SUBITEM_CASO",$A93="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E93))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F93" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A93,TIPOS_OPCION_F,0)),OR($A93="SELECCION_MEJOR_RESPUESTA",$A93="SELECCION_SIMPLE",$A93="SELECCION_UNICA",$A93="SELECCION_DE_LA_MEJOR_RESPUESTA",$A93="SUBITEM_CASO",$A93="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F93))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G93" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A93,TIPOS_OPCION_G,0)),OR($A93="SELECCION_MEJOR_RESPUESTA",$A93="SELECCION_SIMPLE",$A93="SELECCION_UNICA",$A93="SELECCION_DE_LA_MEJOR_RESPUESTA",$A93="SUBITEM_CASO",$A93="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G93))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H93" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A93,TIPOS_OPCION_H,0)),OR($A93="SELECCION_MEJOR_RESPUESTA",$A93="SELECCION_SIMPLE",$A93="SELECCION_UNICA",$A93="SELECCION_DE_LA_MEJOR_RESPUESTA",$A93="SUBITEM_CASO",$A93="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H93))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I93" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A93="SELECCION_MEJOR_RESPUESTA",$A93="SELECCION_SIMPLE",$A93="SELECCION_UNICA",$A93="SELECCION_DE_LA_MEJOR_RESPUESTA",$A93="SUBITEM_CASO",$A93="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A93,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J93" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A93,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A94,TIPOS_REQUIEREN_GRUPO,0)),OR($A94="CASO_CLINICO_TRONCO",$A94="CASO_CLINICO",$A94="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A94="PROBLEMA",$A94="SUBPROBLEMA",$A94="SUBITEM_CASO",$A94="SUBITEM_DE_CASO_O_PROBLEMA",$A94="EMPAREJAMIENTO_TRONCO",$A94="EMPAREJAMIENTO_AMPLIADO",$A94="EMPAREJAMIENTO_DE_CONCEPTOS",$A94="OPCION_EMPAREJAMIENTO",$A94="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B94))&gt;0,LEN(TRIM($B94))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D94" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A94,TIPOS_OPCION_D,0)),OR($A94="SELECCION_MEJOR_RESPUESTA",$A94="SELECCION_SIMPLE",$A94="SELECCION_UNICA",$A94="SELECCION_DE_LA_MEJOR_RESPUESTA",$A94="SUBITEM_CASO",$A94="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D94))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E94" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A94,TIPOS_OPCION_E,0)),OR($A94="SELECCION_MEJOR_RESPUESTA",$A94="SELECCION_SIMPLE",$A94="SELECCION_UNICA",$A94="SELECCION_DE_LA_MEJOR_RESPUESTA",$A94="SUBITEM_CASO",$A94="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E94))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F94" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A94,TIPOS_OPCION_F,0)),OR($A94="SELECCION_MEJOR_RESPUESTA",$A94="SELECCION_SIMPLE",$A94="SELECCION_UNICA",$A94="SELECCION_DE_LA_MEJOR_RESPUESTA",$A94="SUBITEM_CASO",$A94="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F94))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G94" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A94,TIPOS_OPCION_G,0)),OR($A94="SELECCION_MEJOR_RESPUESTA",$A94="SELECCION_SIMPLE",$A94="SELECCION_UNICA",$A94="SELECCION_DE_LA_MEJOR_RESPUESTA",$A94="SUBITEM_CASO",$A94="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G94))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H94" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A94,TIPOS_OPCION_H,0)),OR($A94="SELECCION_MEJOR_RESPUESTA",$A94="SELECCION_SIMPLE",$A94="SELECCION_UNICA",$A94="SELECCION_DE_LA_MEJOR_RESPUESTA",$A94="SUBITEM_CASO",$A94="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H94))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I94" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A94="SELECCION_MEJOR_RESPUESTA",$A94="SELECCION_SIMPLE",$A94="SELECCION_UNICA",$A94="SELECCION_DE_LA_MEJOR_RESPUESTA",$A94="SUBITEM_CASO",$A94="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A94,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J94" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A94,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A95,TIPOS_REQUIEREN_GRUPO,0)),OR($A95="CASO_CLINICO_TRONCO",$A95="CASO_CLINICO",$A95="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A95="PROBLEMA",$A95="SUBPROBLEMA",$A95="SUBITEM_CASO",$A95="SUBITEM_DE_CASO_O_PROBLEMA",$A95="EMPAREJAMIENTO_TRONCO",$A95="EMPAREJAMIENTO_AMPLIADO",$A95="EMPAREJAMIENTO_DE_CONCEPTOS",$A95="OPCION_EMPAREJAMIENTO",$A95="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B95))&gt;0,LEN(TRIM($B95))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D95" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A95,TIPOS_OPCION_D,0)),OR($A95="SELECCION_MEJOR_RESPUESTA",$A95="SELECCION_SIMPLE",$A95="SELECCION_UNICA",$A95="SELECCION_DE_LA_MEJOR_RESPUESTA",$A95="SUBITEM_CASO",$A95="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D95))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E95" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A95,TIPOS_OPCION_E,0)),OR($A95="SELECCION_MEJOR_RESPUESTA",$A95="SELECCION_SIMPLE",$A95="SELECCION_UNICA",$A95="SELECCION_DE_LA_MEJOR_RESPUESTA",$A95="SUBITEM_CASO",$A95="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E95))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F95" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A95,TIPOS_OPCION_F,0)),OR($A95="SELECCION_MEJOR_RESPUESTA",$A95="SELECCION_SIMPLE",$A95="SELECCION_UNICA",$A95="SELECCION_DE_LA_MEJOR_RESPUESTA",$A95="SUBITEM_CASO",$A95="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F95))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G95" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A95,TIPOS_OPCION_G,0)),OR($A95="SELECCION_MEJOR_RESPUESTA",$A95="SELECCION_SIMPLE",$A95="SELECCION_UNICA",$A95="SELECCION_DE_LA_MEJOR_RESPUESTA",$A95="SUBITEM_CASO",$A95="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G95))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H95" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A95,TIPOS_OPCION_H,0)),OR($A95="SELECCION_MEJOR_RESPUESTA",$A95="SELECCION_SIMPLE",$A95="SELECCION_UNICA",$A95="SELECCION_DE_LA_MEJOR_RESPUESTA",$A95="SUBITEM_CASO",$A95="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H95))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I95" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A95="SELECCION_MEJOR_RESPUESTA",$A95="SELECCION_SIMPLE",$A95="SELECCION_UNICA",$A95="SELECCION_DE_LA_MEJOR_RESPUESTA",$A95="SUBITEM_CASO",$A95="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A95,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A95,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B96" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A96,TIPOS_REQUIEREN_GRUPO,0)),OR($A96="CASO_CLINICO_TRONCO",$A96="CASO_CLINICO",$A96="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A96="PROBLEMA",$A96="SUBPROBLEMA",$A96="SUBITEM_CASO",$A96="SUBITEM_DE_CASO_O_PROBLEMA",$A96="EMPAREJAMIENTO_TRONCO",$A96="EMPAREJAMIENTO_AMPLIADO",$A96="EMPAREJAMIENTO_DE_CONCEPTOS",$A96="OPCION_EMPAREJAMIENTO",$A96="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B96))&gt;0,LEN(TRIM($B96))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D96" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A96,TIPOS_OPCION_D,0)),OR($A96="SELECCION_MEJOR_RESPUESTA",$A96="SELECCION_SIMPLE",$A96="SELECCION_UNICA",$A96="SELECCION_DE_LA_MEJOR_RESPUESTA",$A96="SUBITEM_CASO",$A96="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D96))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E96" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A96,TIPOS_OPCION_E,0)),OR($A96="SELECCION_MEJOR_RESPUESTA",$A96="SELECCION_SIMPLE",$A96="SELECCION_UNICA",$A96="SELECCION_DE_LA_MEJOR_RESPUESTA",$A96="SUBITEM_CASO",$A96="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E96))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F96" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A96,TIPOS_OPCION_F,0)),OR($A96="SELECCION_MEJOR_RESPUESTA",$A96="SELECCION_SIMPLE",$A96="SELECCION_UNICA",$A96="SELECCION_DE_LA_MEJOR_RESPUESTA",$A96="SUBITEM_CASO",$A96="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F96))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G96" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A96,TIPOS_OPCION_G,0)),OR($A96="SELECCION_MEJOR_RESPUESTA",$A96="SELECCION_SIMPLE",$A96="SELECCION_UNICA",$A96="SELECCION_DE_LA_MEJOR_RESPUESTA",$A96="SUBITEM_CASO",$A96="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G96))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H96" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A96,TIPOS_OPCION_H,0)),OR($A96="SELECCION_MEJOR_RESPUESTA",$A96="SELECCION_SIMPLE",$A96="SELECCION_UNICA",$A96="SELECCION_DE_LA_MEJOR_RESPUESTA",$A96="SUBITEM_CASO",$A96="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H96))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I96" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A96="SELECCION_MEJOR_RESPUESTA",$A96="SELECCION_SIMPLE",$A96="SELECCION_UNICA",$A96="SELECCION_DE_LA_MEJOR_RESPUESTA",$A96="SUBITEM_CASO",$A96="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A96,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J96" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A96,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B97" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A97,TIPOS_REQUIEREN_GRUPO,0)),OR($A97="CASO_CLINICO_TRONCO",$A97="CASO_CLINICO",$A97="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A97="PROBLEMA",$A97="SUBPROBLEMA",$A97="SUBITEM_CASO",$A97="SUBITEM_DE_CASO_O_PROBLEMA",$A97="EMPAREJAMIENTO_TRONCO",$A97="EMPAREJAMIENTO_AMPLIADO",$A97="EMPAREJAMIENTO_DE_CONCEPTOS",$A97="OPCION_EMPAREJAMIENTO",$A97="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B97))&gt;0,LEN(TRIM($B97))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D97" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A97,TIPOS_OPCION_D,0)),OR($A97="SELECCION_MEJOR_RESPUESTA",$A97="SELECCION_SIMPLE",$A97="SELECCION_UNICA",$A97="SELECCION_DE_LA_MEJOR_RESPUESTA",$A97="SUBITEM_CASO",$A97="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D97))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E97" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A97,TIPOS_OPCION_E,0)),OR($A97="SELECCION_MEJOR_RESPUESTA",$A97="SELECCION_SIMPLE",$A97="SELECCION_UNICA",$A97="SELECCION_DE_LA_MEJOR_RESPUESTA",$A97="SUBITEM_CASO",$A97="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E97))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F97" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A97,TIPOS_OPCION_F,0)),OR($A97="SELECCION_MEJOR_RESPUESTA",$A97="SELECCION_SIMPLE",$A97="SELECCION_UNICA",$A97="SELECCION_DE_LA_MEJOR_RESPUESTA",$A97="SUBITEM_CASO",$A97="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F97))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G97" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A97,TIPOS_OPCION_G,0)),OR($A97="SELECCION_MEJOR_RESPUESTA",$A97="SELECCION_SIMPLE",$A97="SELECCION_UNICA",$A97="SELECCION_DE_LA_MEJOR_RESPUESTA",$A97="SUBITEM_CASO",$A97="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G97))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H97" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A97,TIPOS_OPCION_H,0)),OR($A97="SELECCION_MEJOR_RESPUESTA",$A97="SELECCION_SIMPLE",$A97="SELECCION_UNICA",$A97="SELECCION_DE_LA_MEJOR_RESPUESTA",$A97="SUBITEM_CASO",$A97="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H97))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I97" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A97="SELECCION_MEJOR_RESPUESTA",$A97="SELECCION_SIMPLE",$A97="SELECCION_UNICA",$A97="SELECCION_DE_LA_MEJOR_RESPUESTA",$A97="SUBITEM_CASO",$A97="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A97,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J97" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A97,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A98,TIPOS_REQUIEREN_GRUPO,0)),OR($A98="CASO_CLINICO_TRONCO",$A98="CASO_CLINICO",$A98="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A98="PROBLEMA",$A98="SUBPROBLEMA",$A98="SUBITEM_CASO",$A98="SUBITEM_DE_CASO_O_PROBLEMA",$A98="EMPAREJAMIENTO_TRONCO",$A98="EMPAREJAMIENTO_AMPLIADO",$A98="EMPAREJAMIENTO_DE_CONCEPTOS",$A98="OPCION_EMPAREJAMIENTO",$A98="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B98))&gt;0,LEN(TRIM($B98))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A98,TIPOS_OPCION_D,0)),OR($A98="SELECCION_MEJOR_RESPUESTA",$A98="SELECCION_SIMPLE",$A98="SELECCION_UNICA",$A98="SELECCION_DE_LA_MEJOR_RESPUESTA",$A98="SUBITEM_CASO",$A98="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D98))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A98,TIPOS_OPCION_E,0)),OR($A98="SELECCION_MEJOR_RESPUESTA",$A98="SELECCION_SIMPLE",$A98="SELECCION_UNICA",$A98="SELECCION_DE_LA_MEJOR_RESPUESTA",$A98="SUBITEM_CASO",$A98="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E98))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A98,TIPOS_OPCION_F,0)),OR($A98="SELECCION_MEJOR_RESPUESTA",$A98="SELECCION_SIMPLE",$A98="SELECCION_UNICA",$A98="SELECCION_DE_LA_MEJOR_RESPUESTA",$A98="SUBITEM_CASO",$A98="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F98))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A98,TIPOS_OPCION_G,0)),OR($A98="SELECCION_MEJOR_RESPUESTA",$A98="SELECCION_SIMPLE",$A98="SELECCION_UNICA",$A98="SELECCION_DE_LA_MEJOR_RESPUESTA",$A98="SUBITEM_CASO",$A98="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G98))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A98,TIPOS_OPCION_H,0)),OR($A98="SELECCION_MEJOR_RESPUESTA",$A98="SELECCION_SIMPLE",$A98="SELECCION_UNICA",$A98="SELECCION_DE_LA_MEJOR_RESPUESTA",$A98="SUBITEM_CASO",$A98="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H98))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I98" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A98="SELECCION_MEJOR_RESPUESTA",$A98="SELECCION_SIMPLE",$A98="SELECCION_UNICA",$A98="SELECCION_DE_LA_MEJOR_RESPUESTA",$A98="SUBITEM_CASO",$A98="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A98,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J98" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A98,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B99" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A99,TIPOS_REQUIEREN_GRUPO,0)),OR($A99="CASO_CLINICO_TRONCO",$A99="CASO_CLINICO",$A99="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A99="PROBLEMA",$A99="SUBPROBLEMA",$A99="SUBITEM_CASO",$A99="SUBITEM_DE_CASO_O_PROBLEMA",$A99="EMPAREJAMIENTO_TRONCO",$A99="EMPAREJAMIENTO_AMPLIADO",$A99="EMPAREJAMIENTO_DE_CONCEPTOS",$A99="OPCION_EMPAREJAMIENTO",$A99="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B99))&gt;0,LEN(TRIM($B99))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D99" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A99,TIPOS_OPCION_D,0)),OR($A99="SELECCION_MEJOR_RESPUESTA",$A99="SELECCION_SIMPLE",$A99="SELECCION_UNICA",$A99="SELECCION_DE_LA_MEJOR_RESPUESTA",$A99="SUBITEM_CASO",$A99="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D99))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E99" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A99,TIPOS_OPCION_E,0)),OR($A99="SELECCION_MEJOR_RESPUESTA",$A99="SELECCION_SIMPLE",$A99="SELECCION_UNICA",$A99="SELECCION_DE_LA_MEJOR_RESPUESTA",$A99="SUBITEM_CASO",$A99="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E99))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F99" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A99,TIPOS_OPCION_F,0)),OR($A99="SELECCION_MEJOR_RESPUESTA",$A99="SELECCION_SIMPLE",$A99="SELECCION_UNICA",$A99="SELECCION_DE_LA_MEJOR_RESPUESTA",$A99="SUBITEM_CASO",$A99="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F99))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G99" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A99,TIPOS_OPCION_G,0)),OR($A99="SELECCION_MEJOR_RESPUESTA",$A99="SELECCION_SIMPLE",$A99="SELECCION_UNICA",$A99="SELECCION_DE_LA_MEJOR_RESPUESTA",$A99="SUBITEM_CASO",$A99="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G99))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H99" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A99,TIPOS_OPCION_H,0)),OR($A99="SELECCION_MEJOR_RESPUESTA",$A99="SELECCION_SIMPLE",$A99="SELECCION_UNICA",$A99="SELECCION_DE_LA_MEJOR_RESPUESTA",$A99="SUBITEM_CASO",$A99="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H99))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I99" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A99="SELECCION_MEJOR_RESPUESTA",$A99="SELECCION_SIMPLE",$A99="SELECCION_UNICA",$A99="SELECCION_DE_LA_MEJOR_RESPUESTA",$A99="SUBITEM_CASO",$A99="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A99,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J99" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A99,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A100,TIPOS_REQUIEREN_GRUPO,0)),OR($A100="CASO_CLINICO_TRONCO",$A100="CASO_CLINICO",$A100="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A100="PROBLEMA",$A100="SUBPROBLEMA",$A100="SUBITEM_CASO",$A100="SUBITEM_DE_CASO_O_PROBLEMA",$A100="EMPAREJAMIENTO_TRONCO",$A100="EMPAREJAMIENTO_AMPLIADO",$A100="EMPAREJAMIENTO_DE_CONCEPTOS",$A100="OPCION_EMPAREJAMIENTO",$A100="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B100))&gt;0,LEN(TRIM($B100))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A100,TIPOS_OPCION_D,0)),OR($A100="SELECCION_MEJOR_RESPUESTA",$A100="SELECCION_SIMPLE",$A100="SELECCION_UNICA",$A100="SELECCION_DE_LA_MEJOR_RESPUESTA",$A100="SUBITEM_CASO",$A100="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D100))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A100,TIPOS_OPCION_E,0)),OR($A100="SELECCION_MEJOR_RESPUESTA",$A100="SELECCION_SIMPLE",$A100="SELECCION_UNICA",$A100="SELECCION_DE_LA_MEJOR_RESPUESTA",$A100="SUBITEM_CASO",$A100="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E100))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A100,TIPOS_OPCION_F,0)),OR($A100="SELECCION_MEJOR_RESPUESTA",$A100="SELECCION_SIMPLE",$A100="SELECCION_UNICA",$A100="SELECCION_DE_LA_MEJOR_RESPUESTA",$A100="SUBITEM_CASO",$A100="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F100))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A100,TIPOS_OPCION_G,0)),OR($A100="SELECCION_MEJOR_RESPUESTA",$A100="SELECCION_SIMPLE",$A100="SELECCION_UNICA",$A100="SELECCION_DE_LA_MEJOR_RESPUESTA",$A100="SUBITEM_CASO",$A100="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G100))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A100,TIPOS_OPCION_H,0)),OR($A100="SELECCION_MEJOR_RESPUESTA",$A100="SELECCION_SIMPLE",$A100="SELECCION_UNICA",$A100="SELECCION_DE_LA_MEJOR_RESPUESTA",$A100="SUBITEM_CASO",$A100="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H100))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A100="SELECCION_MEJOR_RESPUESTA",$A100="SELECCION_SIMPLE",$A100="SELECCION_UNICA",$A100="SELECCION_DE_LA_MEJOR_RESPUESTA",$A100="SUBITEM_CASO",$A100="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A100,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J100" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A100,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B101" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Grupo invalido" error="El grupo solo se llena en casos/problemas, subitems, emparejamiento ampliado y opciones de emparejamiento." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A101,TIPOS_REQUIEREN_GRUPO,0)),OR($A101="CASO_CLINICO_TRONCO",$A101="CASO_CLINICO",$A101="ITEMS_AGRUPADOS_POR_CASO_CLINICO_O_PROBLEMA",$A101="PROBLEMA",$A101="SUBPROBLEMA",$A101="SUBITEM_CASO",$A101="SUBITEM_DE_CASO_O_PROBLEMA",$A101="EMPAREJAMIENTO_TRONCO",$A101="EMPAREJAMIENTO_AMPLIADO",$A101="EMPAREJAMIENTO_DE_CONCEPTOS",$A101="OPCION_EMPAREJAMIENTO",$A101="OPCION_DE_EMPAREJAMIENTO_AMPLIADO")),LEN(TRIM($B101))&gt;0,LEN(TRIM($B101))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D101" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A101,TIPOS_OPCION_D,0)),OR($A101="SELECCION_MEJOR_RESPUESTA",$A101="SELECCION_SIMPLE",$A101="SELECCION_UNICA",$A101="SELECCION_DE_LA_MEJOR_RESPUESTA",$A101="SUBITEM_CASO",$A101="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($D101))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="E101" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A101,TIPOS_OPCION_E,0)),OR($A101="SELECCION_MEJOR_RESPUESTA",$A101="SELECCION_SIMPLE",$A101="SELECCION_UNICA",$A101="SELECCION_DE_LA_MEJOR_RESPUESTA",$A101="SUBITEM_CASO",$A101="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($E101))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F101" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A101,TIPOS_OPCION_F,0)),OR($A101="SELECCION_MEJOR_RESPUESTA",$A101="SELECCION_SIMPLE",$A101="SELECCION_UNICA",$A101="SELECCION_DE_LA_MEJOR_RESPUESTA",$A101="SUBITEM_CASO",$A101="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($F101))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="G101" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A101,TIPOS_OPCION_G,0)),OR($A101="SELECCION_MEJOR_RESPUESTA",$A101="SELECCION_SIMPLE",$A101="SELECCION_UNICA",$A101="SELECCION_DE_LA_MEJOR_RESPUESTA",$A101="SUBITEM_CASO",$A101="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($G101))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H101" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Inciso no permitido" error="Ese inciso no corresponde al tipo seleccionado. Revise la columna L para ver que falta o sobra." promptTitle="Ayuda para incisos" prompt="Verdadero o Falso Simple: A=Verdadero y B=Falso automáticamente; deje C-E vacíos. Respuesta A/B/Ambas/Ninguna: A-D automáticamente; E vacío. Verdadero o Falso Complejas: premisas 1-4 en A-D; E vacío. Mejor respuesta/Subítem: complete A-E." type="custom">
+      <formula1>IF(OR(ISNUMBER(MATCH($A101,TIPOS_OPCION_H,0)),OR($A101="SELECCION_MEJOR_RESPUESTA",$A101="SELECCION_SIMPLE",$A101="SELECCION_UNICA",$A101="SELECCION_DE_LA_MEJOR_RESPUESTA",$A101="SUBITEM_CASO",$A101="SUBITEM_DE_CASO_O_PROBLEMA")),TRUE,LEN(TRIM($H101))=0)</formula1>
+    </dataValidation>
+    <dataValidation sqref="I101" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta invalida" error="Seleccione una respuesta valida segun el tipo de pregunta." promptTitle="Ayuda para respuesta" prompt="Verdadero/Falso Simple inicia en A y puede cambiarse a B. Respuesta A/B/Ambas/Ninguna usa A-D. Verdadero/Falso Complejas usa combinaciones A-E." type="list">
+      <formula1>INDIRECT(IF(OR($A101="SELECCION_MEJOR_RESPUESTA",$A101="SELECCION_SIMPLE",$A101="SELECCION_UNICA",$A101="SELECCION_DE_LA_MEJOR_RESPUESTA",$A101="SUBITEM_CASO",$A101="SUBITEM_DE_CASO_O_PROBLEMA"),"RESP_ABCDE",IFERROR(VLOOKUP($A101,MAPA_RESPUESTA_TIPO,2,FALSE),"RESP_VACIA")))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J101" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Dificultad invalida" error="Use 1, 2 o 3. Casos/problemas y Emparejamiento Ampliado no llevan dificultad." type="list">
+      <formula1>INDIRECT(IF(ISNUMBER(MATCH($A101,TIPOS_SIN_DIFICULTAD,0)),"RESP_VACIA","DIFICULTADES_123"))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
